--- a/docs/public_policies.xlsx
+++ b/docs/public_policies.xlsx
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="976">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="974">
   <si>
     <t>resourceID</t>
   </si>
@@ -656,11 +656,7 @@
   </si>
   <si>
     <t>DO ANEXO I PPA DE 2000 - 2003:  Agenda Ambiental
-A incorporação da dimensão ambiental ao desenvolvimento
-econômico vai muito além da recuperação ou preservação dos recursos
-naturais. Degradação do meio ambiente implica não apenas escassez de
-recursos antes tidos como inesgotáveis, mas também aumento dos gastos
-públicos e dos custos das empresas e, notoriamente, piora a qualidade de vida
+A incorporação da dimensão ambiental ao desenvolvimento econômico vai muito além da recuperação ou preservação dos recursos naturais. Degradação do meio ambiente implica não apenas escassez de recursos antes tidos como inesgotáveis, mas também aumento dos gastos públicos e dos custos das empresas e, notoriamente, piora a qualidade de vida
 da população. Áreas.degradadas expulsam empresas e empregos. Nos
 próximos anos, o País deverá ser capaz de adotar estratégias de
 desenvolvimento sustentável.</t>
@@ -708,9 +704,8 @@
     <t xml:space="preserve"> Nº 4.703, DE 21 DE MAIO DE 2003</t>
   </si>
   <si>
-    <t xml:space="preserve">Art. 3°   O PRONABIO deverá ser implementado por meio de ações de âmbito nacional ou direcionadas a conjuntos de biomas, com estrutura que compreenda:
-I - componentes temáticos: a) conhecimento da biodiversidade//b) conservação da biodiversidade//c) utilização sustentável dos componentes da biodiversidade//d) monitoramento, avaliação, prevenção e mitigação de impactos sobre a biodiversidade//e) acesso aos recursos genéticos e aos conhecimentos tradicionais associados e repartição de benefícios//f) educação, sensibilização pública, informação e divulgação sobre biodiversidade//g) fortalecimento jurídico e institucional para a gestão da biodiversidade
-</t>
+    <t>Art. 3°   O PRONABIO deverá ser implementado por meio de ações de âmbito nacional ou direcionadas a conjuntos de biomas, com estrutura que compreenda:
+I - componentes temáticos: a) conhecimento da biodiversidade//b) conservação da biodiversidade//c) utilização sustentável dos componentes da biodiversidade//d) monitoramento, avaliação, prevenção e mitigação de impactos sobre a biodiversidade//e) acesso aos recursos genéticos e aos conhecimentos tradicionais associados e repartição de benefícios//f) educação, sensibilização pública, informação e divulgação sobre biodiversidade//g) fortalecimento jurídico e institucional para a gestão da biodiversidade</t>
   </si>
   <si>
     <t>Artigo 3° I   a)//b)//c)//d)//e)//f)//g)</t>
@@ -2979,9 +2974,6 @@
     <t xml:space="preserve"> Nº 121, DE 30 DE  DEZEMBRO DE  2022</t>
   </si>
   <si>
-    <t>Secretário de Estado de Infraestrutura e Meio Ambiente</t>
-  </si>
-  <si>
     <t>Artigo 1º - Para os efeitos desta Resolução, entende-se por:  
 I - Área de Uso Alternativo do Solo: área do imóvel rural sem a presença de vegetação nativa cadastrada no Cadastro Ambiental Rural – CAR//
 II - Área de Vegetação Natural: área do imóvel rural inscrita como vegetação nativa no Cadastro Ambiental Rural - CAR//
@@ -3014,9 +3006,6 @@
   </si>
   <si>
     <t>Nº 6, DE 03 DE MAIO DE 2022</t>
-  </si>
-  <si>
-    <t>Ministério do Meio Ambiente - Instituto Chico Mendes de Conservação da Biodiversidade - Gabinete da Presidência</t>
   </si>
   <si>
     <t xml:space="preserve"> A presente instrução normativa regula, no âmbito do Instituto Chico Mendes, a
@@ -3844,7 +3833,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <fonts count="29">
+  <fonts count="27">
     <font>
       <sz val="10.0"/>
       <color rgb="FF000000"/>
@@ -3870,18 +3859,6 @@
     <font>
       <sz val="12.0"/>
       <color theme="1"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12.0"/>
-      <color rgb="FF000000"/>
-      <name val="Times New Roman"/>
-    </font>
-    <font>
-      <u/>
-      <sz val="12.0"/>
-      <color rgb="FF000000"/>
       <name val="Times New Roman"/>
     </font>
     <font>
@@ -4036,7 +4013,7 @@
   <cellStyleXfs count="1">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" applyAlignment="1" applyFont="1"/>
   </cellStyleXfs>
-  <cellXfs count="70">
+  <cellXfs count="60">
     <xf borderId="0" fillId="0" fontId="0" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="0"/>
     </xf>
@@ -4053,194 +4030,164 @@
       <alignment vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFill="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="5" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyFont="1"/>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="6" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
+    </xf>
+    <xf borderId="0" fillId="3" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="7" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="8" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="9" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="10" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="11" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="3" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="12" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="4" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+    <xf borderId="0" fillId="0" fontId="13" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="14" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="3" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" shrinkToFit="0" vertical="bottom" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="15" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="16" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
+    </xf>
+    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="17" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0" shrinkToFit="0" wrapText="1"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="18" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="19" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
-    </xf>
-    <xf borderId="0" fillId="0" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
-      <alignment horizontal="center" readingOrder="0"/>
+      <alignment horizontal="center" readingOrder="0" vertical="center"/>
     </xf>
     <xf borderId="0" fillId="0" fontId="2" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="20" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="21" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="22" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="23" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="24" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="2" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="2" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" readingOrder="0" shrinkToFit="0" vertical="center" wrapText="1"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="center" vertical="bottom"/>
     </xf>
-    <xf borderId="0" fillId="0" fontId="28" numFmtId="0" xfId="0" applyFont="1"/>
-    <xf borderId="0" fillId="0" fontId="27" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
+    <xf borderId="0" fillId="0" fontId="26" numFmtId="0" xfId="0" applyFont="1"/>
+    <xf borderId="0" fillId="0" fontId="25" numFmtId="0" xfId="0" applyAlignment="1" applyFont="1">
       <alignment horizontal="right" readingOrder="0"/>
     </xf>
   </cellXfs>
@@ -4467,14 +4414,16 @@
   <cols>
     <col customWidth="1" min="1" max="1" width="11.88"/>
     <col customWidth="1" min="2" max="2" width="122.25"/>
-    <col customWidth="1" min="3" max="3" width="38.63"/>
+    <col customWidth="1" min="3" max="3" width="23.75"/>
     <col customWidth="1" min="4" max="4" width="51.38"/>
     <col customWidth="1" min="5" max="5" width="46.25"/>
-    <col customWidth="1" min="6" max="6" width="42.25"/>
-    <col customWidth="1" min="7" max="7" width="32.5"/>
-    <col customWidth="1" min="8" max="8" width="59.13"/>
-    <col customWidth="1" min="9" max="12" width="56.88"/>
-    <col customWidth="1" min="13" max="13" width="261.63"/>
+    <col customWidth="1" min="6" max="6" width="27.63"/>
+    <col customWidth="1" min="7" max="7" width="24.25"/>
+    <col customWidth="1" min="8" max="8" width="78.75"/>
+    <col customWidth="1" min="9" max="9" width="41.63"/>
+    <col customWidth="1" min="10" max="11" width="56.88"/>
+    <col customWidth="1" min="12" max="12" width="93.75"/>
+    <col customWidth="1" min="13" max="13" width="111.63"/>
     <col customWidth="1" min="14" max="14" width="35.63"/>
     <col customWidth="1" min="15" max="15" width="43.75"/>
     <col customWidth="1" min="16" max="16" width="46.13"/>
@@ -4547,7 +4496,7 @@
       <c r="AF1" s="4"/>
       <c r="AG1" s="4"/>
     </row>
-    <row r="2" ht="145.5" customHeight="1">
+    <row r="2" ht="97.5" customHeight="1">
       <c r="A2" s="5">
         <v>1.0</v>
       </c>
@@ -4651,10 +4600,10 @@
       <c r="L3" s="16" t="s">
         <v>36</v>
       </c>
-      <c r="M3" s="18" t="s">
+      <c r="M3" s="10" t="s">
         <v>37</v>
       </c>
-      <c r="N3" s="19" t="s">
+      <c r="N3" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O3" s="12" t="s">
@@ -4685,7 +4634,7 @@
       <c r="A4" s="5">
         <v>3.0</v>
       </c>
-      <c r="B4" s="20" t="s">
+      <c r="B4" s="6" t="s">
         <v>40</v>
       </c>
       <c r="C4" s="16" t="s">
@@ -4718,10 +4667,10 @@
       <c r="L4" s="16" t="s">
         <v>50</v>
       </c>
-      <c r="M4" s="18" t="s">
+      <c r="M4" s="10" t="s">
         <v>51</v>
       </c>
-      <c r="N4" s="19" t="s">
+      <c r="N4" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O4" s="12" t="s">
@@ -4758,7 +4707,7 @@
       <c r="C5" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D5" s="21" t="s">
+      <c r="D5" s="19" t="s">
         <v>55</v>
       </c>
       <c r="E5" s="12" t="s">
@@ -4785,10 +4734,10 @@
       <c r="L5" s="16" t="s">
         <v>61</v>
       </c>
-      <c r="M5" s="22" t="s">
+      <c r="M5" s="20" t="s">
         <v>62</v>
       </c>
-      <c r="N5" s="19" t="s">
+      <c r="N5" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O5" s="12" t="s">
@@ -4825,10 +4774,10 @@
       <c r="C6" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D6" s="23" t="s">
+      <c r="D6" s="17" t="s">
         <v>66</v>
       </c>
-      <c r="E6" s="23" t="s">
+      <c r="E6" s="17" t="s">
         <v>67</v>
       </c>
       <c r="F6" s="16" t="s">
@@ -4855,7 +4804,7 @@
       <c r="M6" s="10" t="s">
         <v>74</v>
       </c>
-      <c r="N6" s="19" t="s">
+      <c r="N6" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O6" s="12" t="s">
@@ -4892,10 +4841,10 @@
       <c r="C7" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D7" s="23" t="s">
+      <c r="D7" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="E7" s="23" t="s">
+      <c r="E7" s="17" t="s">
         <v>80</v>
       </c>
       <c r="F7" s="16" t="s">
@@ -4919,10 +4868,10 @@
       <c r="L7" s="16" t="s">
         <v>84</v>
       </c>
-      <c r="M7" s="24" t="s">
+      <c r="M7" s="20" t="s">
         <v>85</v>
       </c>
-      <c r="N7" s="19" t="s">
+      <c r="N7" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O7" s="12" t="s">
@@ -4949,7 +4898,7 @@
       <c r="AF7" s="13"/>
       <c r="AG7" s="13"/>
     </row>
-    <row r="8" ht="15.75" customHeight="1">
+    <row r="8" ht="73.5" customHeight="1">
       <c r="A8" s="5">
         <v>7.0</v>
       </c>
@@ -4959,10 +4908,10 @@
       <c r="C8" s="12" t="s">
         <v>88</v>
       </c>
-      <c r="D8" s="23" t="s">
+      <c r="D8" s="17" t="s">
         <v>89</v>
       </c>
-      <c r="E8" s="23" t="s">
+      <c r="E8" s="17" t="s">
         <v>90</v>
       </c>
       <c r="F8" s="16" t="s">
@@ -4971,7 +4920,7 @@
       <c r="G8" s="12" t="s">
         <v>91</v>
       </c>
-      <c r="H8" s="25" t="s">
+      <c r="H8" s="21" t="s">
         <v>92</v>
       </c>
       <c r="I8" s="12" t="s">
@@ -4986,10 +4935,10 @@
       <c r="L8" s="16" t="s">
         <v>94</v>
       </c>
-      <c r="M8" s="26" t="s">
+      <c r="M8" s="22" t="s">
         <v>95</v>
       </c>
-      <c r="N8" s="19" t="s">
+      <c r="N8" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O8" s="12" t="s">
@@ -5023,10 +4972,10 @@
       <c r="B9" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="C9" s="23" t="s">
+      <c r="C9" s="17" t="s">
         <v>65</v>
       </c>
-      <c r="D9" s="23" t="s">
+      <c r="D9" s="17" t="s">
         <v>98</v>
       </c>
       <c r="E9" s="12" t="s">
@@ -5056,7 +5005,7 @@
       <c r="M9" s="10" t="s">
         <v>102</v>
       </c>
-      <c r="N9" s="19" t="s">
+      <c r="N9" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O9" s="12" t="s">
@@ -5120,10 +5069,10 @@
       <c r="L10" s="16" t="s">
         <v>108</v>
       </c>
-      <c r="M10" s="22" t="s">
+      <c r="M10" s="20" t="s">
         <v>109</v>
       </c>
-      <c r="N10" s="19" t="s">
+      <c r="N10" s="18" t="s">
         <v>110</v>
       </c>
       <c r="O10" s="12" t="s">
@@ -5187,10 +5136,10 @@
       <c r="L11" s="16" t="s">
         <v>119</v>
       </c>
-      <c r="M11" s="22" t="s">
+      <c r="M11" s="20" t="s">
         <v>120</v>
       </c>
-      <c r="N11" s="19" t="s">
+      <c r="N11" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O11" s="12" t="s">
@@ -5221,16 +5170,16 @@
       <c r="A12" s="5">
         <v>11.0</v>
       </c>
-      <c r="B12" s="27" t="s">
+      <c r="B12" s="15" t="s">
         <v>122</v>
       </c>
       <c r="C12" s="16" t="s">
         <v>65</v>
       </c>
-      <c r="D12" s="23" t="s">
+      <c r="D12" s="17" t="s">
         <v>123</v>
       </c>
-      <c r="E12" s="28" t="s">
+      <c r="E12" s="19" t="s">
         <v>67</v>
       </c>
       <c r="F12" s="16" t="s">
@@ -5257,7 +5206,7 @@
       <c r="M12" s="10" t="s">
         <v>126</v>
       </c>
-      <c r="N12" s="19" t="s">
+      <c r="N12" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O12" s="12" t="s">
@@ -5288,7 +5237,7 @@
       <c r="A13" s="14">
         <v>12.0</v>
       </c>
-      <c r="B13" s="20" t="s">
+      <c r="B13" s="6" t="s">
         <v>128</v>
       </c>
       <c r="C13" s="16" t="s">
@@ -5315,16 +5264,16 @@
       <c r="J13" s="12" t="s">
         <v>133</v>
       </c>
-      <c r="K13" s="19" t="s">
+      <c r="K13" s="18" t="s">
         <v>134</v>
       </c>
       <c r="L13" s="16" t="s">
         <v>135</v>
       </c>
-      <c r="M13" s="22" t="s">
+      <c r="M13" s="20" t="s">
         <v>136</v>
       </c>
-      <c r="N13" s="19" t="s">
+      <c r="N13" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O13" s="12" t="s">
@@ -5382,16 +5331,16 @@
       <c r="J14" s="12" t="s">
         <v>143</v>
       </c>
-      <c r="K14" s="19" t="s">
+      <c r="K14" s="18" t="s">
         <v>124</v>
       </c>
       <c r="L14" s="16" t="s">
         <v>144</v>
       </c>
-      <c r="M14" s="22" t="s">
+      <c r="M14" s="20" t="s">
         <v>145</v>
       </c>
-      <c r="N14" s="19" t="s">
+      <c r="N14" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O14" s="12" t="s">
@@ -5428,7 +5377,7 @@
       <c r="C15" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D15" s="23" t="s">
+      <c r="D15" s="17" t="s">
         <v>149</v>
       </c>
       <c r="E15" s="12" t="s">
@@ -5455,10 +5404,10 @@
       <c r="L15" s="16" t="s">
         <v>154</v>
       </c>
-      <c r="M15" s="26" t="s">
+      <c r="M15" s="22" t="s">
         <v>155</v>
       </c>
-      <c r="N15" s="19" t="s">
+      <c r="N15" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O15" s="12" t="s">
@@ -5489,7 +5438,7 @@
       <c r="A16" s="5">
         <v>15.0</v>
       </c>
-      <c r="B16" s="20" t="s">
+      <c r="B16" s="6" t="s">
         <v>158</v>
       </c>
       <c r="C16" s="16" t="s">
@@ -5522,10 +5471,10 @@
       <c r="L16" s="16" t="s">
         <v>164</v>
       </c>
-      <c r="M16" s="22" t="s">
+      <c r="M16" s="20" t="s">
         <v>165</v>
       </c>
-      <c r="N16" s="19" t="s">
+      <c r="N16" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O16" s="12" t="s">
@@ -5562,7 +5511,7 @@
       <c r="C17" s="16" t="s">
         <v>28</v>
       </c>
-      <c r="D17" s="23" t="s">
+      <c r="D17" s="17" t="s">
         <v>170</v>
       </c>
       <c r="E17" s="12" t="s">
@@ -5589,10 +5538,10 @@
       <c r="L17" s="12" t="s">
         <v>173</v>
       </c>
-      <c r="M17" s="26" t="s">
+      <c r="M17" s="22" t="s">
         <v>174</v>
       </c>
-      <c r="N17" s="19" t="s">
+      <c r="N17" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O17" s="12" t="s">
@@ -5629,10 +5578,10 @@
       <c r="C18" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D18" s="29" t="s">
+      <c r="D18" s="12" t="s">
         <v>178</v>
       </c>
-      <c r="E18" s="23" t="s">
+      <c r="E18" s="17" t="s">
         <v>67</v>
       </c>
       <c r="F18" s="16" t="s">
@@ -5641,25 +5590,25 @@
       <c r="G18" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="H18" s="29" t="s">
+      <c r="H18" s="12" t="s">
         <v>179</v>
       </c>
-      <c r="I18" s="29" t="s">
+      <c r="I18" s="12" t="s">
         <v>180</v>
       </c>
-      <c r="J18" s="29" t="s">
+      <c r="J18" s="12" t="s">
         <v>181</v>
       </c>
-      <c r="K18" s="29" t="s">
+      <c r="K18" s="12" t="s">
         <v>182</v>
       </c>
-      <c r="L18" s="30" t="s">
+      <c r="L18" s="16" t="s">
         <v>183</v>
       </c>
-      <c r="M18" s="22" t="s">
+      <c r="M18" s="20" t="s">
         <v>184</v>
       </c>
-      <c r="N18" s="19" t="s">
+      <c r="N18" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O18" s="12" t="s">
@@ -5690,7 +5639,7 @@
       <c r="A19" s="14">
         <v>18.0</v>
       </c>
-      <c r="B19" s="31" t="s">
+      <c r="B19" s="23" t="s">
         <v>187</v>
       </c>
       <c r="C19" s="12" t="s">
@@ -5726,7 +5675,7 @@
       <c r="M19" s="10" t="s">
         <v>192</v>
       </c>
-      <c r="N19" s="19" t="s">
+      <c r="N19" s="18" t="s">
         <v>193</v>
       </c>
       <c r="O19" s="12" t="s">
@@ -5793,7 +5742,7 @@
       <c r="M20" s="10" t="s">
         <v>203</v>
       </c>
-      <c r="N20" s="19" t="s">
+      <c r="N20" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O20" s="12" t="s">
@@ -5824,13 +5773,13 @@
       <c r="A21" s="14">
         <v>20.0</v>
       </c>
-      <c r="B21" s="32" t="s">
+      <c r="B21" s="5" t="s">
         <v>205</v>
       </c>
-      <c r="C21" s="33" t="s">
+      <c r="C21" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D21" s="33" t="s">
+      <c r="D21" s="24" t="s">
         <v>206</v>
       </c>
       <c r="E21" s="12" t="s">
@@ -5845,22 +5794,22 @@
       <c r="H21" s="12" t="s">
         <v>209</v>
       </c>
-      <c r="I21" s="33" t="s">
+      <c r="I21" s="24" t="s">
         <v>210</v>
       </c>
-      <c r="J21" s="33" t="s">
+      <c r="J21" s="24" t="s">
         <v>211</v>
       </c>
-      <c r="K21" s="33" t="s">
+      <c r="K21" s="24" t="s">
         <v>212</v>
       </c>
-      <c r="L21" s="33" t="s">
+      <c r="L21" s="24" t="s">
         <v>213</v>
       </c>
       <c r="M21" s="10" t="s">
         <v>214</v>
       </c>
-      <c r="N21" s="19" t="s">
+      <c r="N21" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O21" s="12" t="s">
@@ -5891,19 +5840,19 @@
       <c r="A22" s="5">
         <v>21.0</v>
       </c>
-      <c r="B22" s="32" t="s">
+      <c r="B22" s="5" t="s">
         <v>216</v>
       </c>
-      <c r="C22" s="33" t="s">
+      <c r="C22" s="24" t="s">
         <v>28</v>
       </c>
-      <c r="D22" s="33" t="s">
+      <c r="D22" s="24" t="s">
         <v>217</v>
       </c>
       <c r="E22" s="12" t="s">
         <v>218</v>
       </c>
-      <c r="F22" s="33" t="s">
+      <c r="F22" s="24" t="s">
         <v>44</v>
       </c>
       <c r="G22" s="12" t="s">
@@ -5912,22 +5861,22 @@
       <c r="H22" s="12" t="s">
         <v>219</v>
       </c>
-      <c r="I22" s="33" t="s">
+      <c r="I22" s="24" t="s">
         <v>83</v>
       </c>
-      <c r="J22" s="33" t="s">
+      <c r="J22" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="K22" s="33" t="s">
+      <c r="K22" s="24" t="s">
         <v>21</v>
       </c>
-      <c r="L22" s="33" t="s">
+      <c r="L22" s="24" t="s">
         <v>220</v>
       </c>
       <c r="M22" s="10" t="s">
         <v>221</v>
       </c>
-      <c r="N22" s="19" t="s">
+      <c r="N22" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O22" s="12" t="s">
@@ -5979,7 +5928,7 @@
       <c r="H23" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="I23" s="33" t="s">
+      <c r="I23" s="24" t="s">
         <v>227</v>
       </c>
       <c r="J23" s="12" t="s">
@@ -5994,7 +5943,7 @@
       <c r="M23" s="10" t="s">
         <v>231</v>
       </c>
-      <c r="N23" s="19" t="s">
+      <c r="N23" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O23" s="12" t="s">
@@ -6025,7 +5974,7 @@
       <c r="A24" s="5">
         <v>23.0</v>
       </c>
-      <c r="B24" s="20" t="s">
+      <c r="B24" s="6" t="s">
         <v>233</v>
       </c>
       <c r="C24" s="12" t="s">
@@ -6061,7 +6010,7 @@
       <c r="M24" s="10" t="s">
         <v>241</v>
       </c>
-      <c r="N24" s="19" t="s">
+      <c r="N24" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O24" s="12" t="s">
@@ -6088,11 +6037,11 @@
       <c r="AF24" s="13"/>
       <c r="AG24" s="13"/>
     </row>
-    <row r="25" ht="294.0" customHeight="1">
+    <row r="25" ht="201.75" customHeight="1">
       <c r="A25" s="14">
         <v>24.0</v>
       </c>
-      <c r="B25" s="20" t="s">
+      <c r="B25" s="6" t="s">
         <v>243</v>
       </c>
       <c r="C25" s="12" t="s">
@@ -6128,7 +6077,7 @@
       <c r="M25" s="10" t="s">
         <v>252</v>
       </c>
-      <c r="N25" s="19" t="s">
+      <c r="N25" s="18" t="s">
         <v>110</v>
       </c>
       <c r="O25" s="12" t="s">
@@ -6165,10 +6114,10 @@
       <c r="C26" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D26" s="23" t="s">
+      <c r="D26" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="E26" s="23" t="s">
+      <c r="E26" s="17" t="s">
         <v>256</v>
       </c>
       <c r="F26" s="16" t="s">
@@ -6183,7 +6132,7 @@
       <c r="I26" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="J26" s="34" t="s">
+      <c r="J26" s="25" t="s">
         <v>259</v>
       </c>
       <c r="K26" s="12" t="s">
@@ -6195,7 +6144,7 @@
       <c r="M26" s="10" t="s">
         <v>262</v>
       </c>
-      <c r="N26" s="19" t="s">
+      <c r="N26" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O26" s="12" t="s">
@@ -6232,7 +6181,7 @@
       <c r="C27" s="16" t="s">
         <v>41</v>
       </c>
-      <c r="D27" s="23" t="s">
+      <c r="D27" s="17" t="s">
         <v>265</v>
       </c>
       <c r="E27" s="12" t="s">
@@ -6259,10 +6208,10 @@
       <c r="L27" s="16" t="s">
         <v>269</v>
       </c>
-      <c r="M27" s="35" t="s">
+      <c r="M27" s="26" t="s">
         <v>270</v>
       </c>
-      <c r="N27" s="19" t="s">
+      <c r="N27" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O27" s="12" t="s">
@@ -6299,10 +6248,10 @@
       <c r="C28" s="16" t="s">
         <v>17</v>
       </c>
-      <c r="D28" s="23" t="s">
+      <c r="D28" s="17" t="s">
         <v>274</v>
       </c>
-      <c r="E28" s="23" t="s">
+      <c r="E28" s="17" t="s">
         <v>19</v>
       </c>
       <c r="F28" s="16" t="s">
@@ -6329,7 +6278,7 @@
       <c r="M28" s="10" t="s">
         <v>278</v>
       </c>
-      <c r="N28" s="19" t="s">
+      <c r="N28" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O28" s="12" t="s">
@@ -6366,10 +6315,10 @@
       <c r="C29" s="16" t="s">
         <v>78</v>
       </c>
-      <c r="D29" s="23" t="s">
+      <c r="D29" s="17" t="s">
         <v>281</v>
       </c>
-      <c r="E29" s="23" t="s">
+      <c r="E29" s="17" t="s">
         <v>19</v>
       </c>
       <c r="F29" s="16" t="s">
@@ -6393,10 +6342,10 @@
       <c r="L29" s="16" t="s">
         <v>286</v>
       </c>
-      <c r="M29" s="24" t="s">
+      <c r="M29" s="20" t="s">
         <v>287</v>
       </c>
-      <c r="N29" s="19" t="s">
+      <c r="N29" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O29" s="12" t="s">
@@ -6427,7 +6376,7 @@
       <c r="A30" s="5">
         <v>29.0</v>
       </c>
-      <c r="B30" s="20" t="s">
+      <c r="B30" s="6" t="s">
         <v>289</v>
       </c>
       <c r="C30" s="16" t="s">
@@ -6436,7 +6385,7 @@
       <c r="D30" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="E30" s="21" t="s">
+      <c r="E30" s="19" t="s">
         <v>291</v>
       </c>
       <c r="F30" s="16" t="s">
@@ -6445,25 +6394,25 @@
       <c r="G30" s="12" t="s">
         <v>83</v>
       </c>
-      <c r="H30" s="29" t="s">
+      <c r="H30" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="I30" s="29" t="s">
+      <c r="I30" s="12" t="s">
         <v>293</v>
       </c>
-      <c r="J30" s="29" t="s">
+      <c r="J30" s="12" t="s">
         <v>294</v>
       </c>
-      <c r="K30" s="29" t="s">
+      <c r="K30" s="12" t="s">
         <v>295</v>
       </c>
-      <c r="L30" s="29" t="s">
+      <c r="L30" s="12" t="s">
         <v>296</v>
       </c>
       <c r="M30" s="10" t="s">
         <v>297</v>
       </c>
-      <c r="N30" s="19" t="s">
+      <c r="N30" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O30" s="12" t="s">
@@ -6494,7 +6443,7 @@
       <c r="A31" s="14">
         <v>30.0</v>
       </c>
-      <c r="B31" s="20" t="s">
+      <c r="B31" s="6" t="s">
         <v>299</v>
       </c>
       <c r="C31" s="16" t="s">
@@ -6527,10 +6476,10 @@
       <c r="L31" s="16" t="s">
         <v>303</v>
       </c>
-      <c r="M31" s="22" t="s">
+      <c r="M31" s="20" t="s">
         <v>304</v>
       </c>
-      <c r="N31" s="19" t="s">
+      <c r="N31" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O31" s="12" t="s">
@@ -6591,14 +6540,14 @@
       <c r="K32" s="17" t="s">
         <v>313</v>
       </c>
-      <c r="L32" s="36" t="s">
+      <c r="L32" s="27" t="s">
         <v>314</v>
       </c>
-      <c r="M32" s="24" t="s">
+      <c r="M32" s="20" t="s">
         <v>315</v>
       </c>
-      <c r="N32" s="19" t="s">
-        <v>21</v>
+      <c r="N32" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="O32" s="12" t="s">
         <v>194</v>
@@ -6658,14 +6607,14 @@
       <c r="K33" s="17" t="s">
         <v>190</v>
       </c>
-      <c r="L33" s="36" t="s">
+      <c r="L33" s="27" t="s">
         <v>323</v>
       </c>
-      <c r="M33" s="18" t="s">
+      <c r="M33" s="10" t="s">
         <v>324</v>
       </c>
-      <c r="N33" s="19" t="s">
-        <v>21</v>
+      <c r="N33" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="O33" s="12" t="s">
         <v>194</v>
@@ -6725,14 +6674,14 @@
       <c r="K34" s="17" t="s">
         <v>332</v>
       </c>
-      <c r="L34" s="36" t="s">
+      <c r="L34" s="27" t="s">
         <v>333</v>
       </c>
-      <c r="M34" s="22" t="s">
+      <c r="M34" s="20" t="s">
         <v>334</v>
       </c>
-      <c r="N34" s="19" t="s">
-        <v>21</v>
+      <c r="N34" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="O34" s="12" t="s">
         <v>194</v>
@@ -6792,14 +6741,14 @@
       <c r="K35" s="17" t="s">
         <v>342</v>
       </c>
-      <c r="L35" s="36" t="s">
+      <c r="L35" s="27" t="s">
         <v>343</v>
       </c>
-      <c r="M35" s="22" t="s">
+      <c r="M35" s="20" t="s">
         <v>344</v>
       </c>
-      <c r="N35" s="19" t="s">
-        <v>21</v>
+      <c r="N35" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="O35" s="12" t="s">
         <v>194</v>
@@ -6825,7 +6774,7 @@
       <c r="AF35" s="13"/>
       <c r="AG35" s="13"/>
     </row>
-    <row r="36" ht="409.5" customHeight="1">
+    <row r="36" ht="286.5" customHeight="1">
       <c r="A36" s="5">
         <v>35.0</v>
       </c>
@@ -6859,14 +6808,14 @@
       <c r="K36" s="17" t="s">
         <v>352</v>
       </c>
-      <c r="L36" s="36" t="s">
+      <c r="L36" s="27" t="s">
         <v>353</v>
       </c>
-      <c r="M36" s="22" t="s">
+      <c r="M36" s="20" t="s">
         <v>354</v>
       </c>
-      <c r="N36" s="19" t="s">
-        <v>21</v>
+      <c r="N36" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="O36" s="12" t="s">
         <v>194</v>
@@ -6926,14 +6875,14 @@
       <c r="K37" s="17" t="s">
         <v>361</v>
       </c>
-      <c r="L37" s="36" t="s">
+      <c r="L37" s="27" t="s">
         <v>362</v>
       </c>
-      <c r="M37" s="18" t="s">
+      <c r="M37" s="10" t="s">
         <v>363</v>
       </c>
-      <c r="N37" s="19" t="s">
-        <v>21</v>
+      <c r="N37" s="18" t="s">
+        <v>24</v>
       </c>
       <c r="O37" s="12" t="s">
         <v>194</v>
@@ -6972,7 +6921,7 @@
       <c r="D38" s="12" t="s">
         <v>366</v>
       </c>
-      <c r="E38" s="23" t="s">
+      <c r="E38" s="17" t="s">
         <v>256</v>
       </c>
       <c r="F38" s="16" t="s">
@@ -6996,10 +6945,10 @@
       <c r="L38" s="16" t="s">
         <v>368</v>
       </c>
-      <c r="M38" s="24" t="s">
+      <c r="M38" s="20" t="s">
         <v>369</v>
       </c>
-      <c r="N38" s="19" t="s">
+      <c r="N38" s="18" t="s">
         <v>110</v>
       </c>
       <c r="O38" s="12" t="s">
@@ -7030,10 +6979,10 @@
       <c r="A39" s="14">
         <v>38.0</v>
       </c>
-      <c r="B39" s="32" t="s">
+      <c r="B39" s="5" t="s">
         <v>372</v>
       </c>
-      <c r="C39" s="37" t="s">
+      <c r="C39" s="28" t="s">
         <v>41</v>
       </c>
       <c r="D39" s="12" t="s">
@@ -7066,7 +7015,7 @@
       <c r="M39" s="10" t="s">
         <v>376</v>
       </c>
-      <c r="N39" s="19" t="s">
+      <c r="N39" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O39" s="12" t="s">
@@ -7097,7 +7046,7 @@
       <c r="A40" s="5">
         <v>39.0</v>
       </c>
-      <c r="B40" s="20" t="s">
+      <c r="B40" s="6" t="s">
         <v>378</v>
       </c>
       <c r="C40" s="12" t="s">
@@ -7130,10 +7079,10 @@
       <c r="L40" s="12" t="s">
         <v>384</v>
       </c>
-      <c r="M40" s="24" t="s">
+      <c r="M40" s="20" t="s">
         <v>385</v>
       </c>
-      <c r="N40" s="19" t="s">
+      <c r="N40" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O40" s="12" t="s">
@@ -7164,7 +7113,7 @@
       <c r="A41" s="14">
         <v>40.0</v>
       </c>
-      <c r="B41" s="32" t="s">
+      <c r="B41" s="5" t="s">
         <v>387</v>
       </c>
       <c r="C41" s="12" t="s">
@@ -7200,7 +7149,7 @@
       <c r="M41" s="10" t="s">
         <v>394</v>
       </c>
-      <c r="N41" s="19" t="s">
+      <c r="N41" s="18" t="s">
         <v>110</v>
       </c>
       <c r="O41" s="12" t="s">
@@ -7231,7 +7180,7 @@
       <c r="A42" s="5">
         <v>41.0</v>
       </c>
-      <c r="B42" s="32" t="s">
+      <c r="B42" s="5" t="s">
         <v>396</v>
       </c>
       <c r="C42" s="12" t="s">
@@ -7267,7 +7216,7 @@
       <c r="M42" s="10" t="s">
         <v>402</v>
       </c>
-      <c r="N42" s="19" t="s">
+      <c r="N42" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O42" s="12" t="s">
@@ -7298,16 +7247,16 @@
       <c r="A43" s="14">
         <v>42.0</v>
       </c>
-      <c r="B43" s="20" t="s">
+      <c r="B43" s="6" t="s">
         <v>404</v>
       </c>
-      <c r="C43" s="29" t="s">
+      <c r="C43" s="12" t="s">
         <v>224</v>
       </c>
       <c r="D43" s="12" t="s">
         <v>405</v>
       </c>
-      <c r="E43" s="38" t="s">
+      <c r="E43" s="29" t="s">
         <v>406</v>
       </c>
       <c r="F43" s="12" t="s">
@@ -7334,7 +7283,7 @@
       <c r="M43" s="10" t="s">
         <v>413</v>
       </c>
-      <c r="N43" s="19" t="s">
+      <c r="N43" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O43" s="12" t="s">
@@ -7365,10 +7314,10 @@
       <c r="A44" s="5">
         <v>43.0</v>
       </c>
-      <c r="B44" s="20" t="s">
+      <c r="B44" s="6" t="s">
         <v>415</v>
       </c>
-      <c r="C44" s="29" t="s">
+      <c r="C44" s="12" t="s">
         <v>65</v>
       </c>
       <c r="D44" s="12" t="s">
@@ -7401,7 +7350,7 @@
       <c r="M44" s="10" t="s">
         <v>422</v>
       </c>
-      <c r="N44" s="19" t="s">
+      <c r="N44" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O44" s="12" t="s">
@@ -7432,7 +7381,7 @@
       <c r="A45" s="14">
         <v>44.0</v>
       </c>
-      <c r="B45" s="20" t="s">
+      <c r="B45" s="6" t="s">
         <v>425</v>
       </c>
       <c r="C45" s="12" t="s">
@@ -7465,10 +7414,10 @@
       <c r="L45" s="12" t="s">
         <v>428</v>
       </c>
-      <c r="M45" s="24" t="s">
+      <c r="M45" s="20" t="s">
         <v>429</v>
       </c>
-      <c r="N45" s="19" t="s">
+      <c r="N45" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O45" s="12" t="s">
@@ -7499,7 +7448,7 @@
       <c r="A46" s="5">
         <v>45.0</v>
       </c>
-      <c r="B46" s="20" t="s">
+      <c r="B46" s="6" t="s">
         <v>432</v>
       </c>
       <c r="C46" s="12" t="s">
@@ -7535,7 +7484,7 @@
       <c r="M46" s="10" t="s">
         <v>437</v>
       </c>
-      <c r="N46" s="19" t="s">
+      <c r="N46" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O46" s="12" t="s">
@@ -7566,7 +7515,7 @@
       <c r="A47" s="14">
         <v>46.0</v>
       </c>
-      <c r="B47" s="32" t="s">
+      <c r="B47" s="5" t="s">
         <v>439</v>
       </c>
       <c r="C47" s="12" t="s">
@@ -7602,7 +7551,7 @@
       <c r="M47" s="10" t="s">
         <v>270</v>
       </c>
-      <c r="N47" s="19" t="s">
+      <c r="N47" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O47" s="12" t="s">
@@ -7633,7 +7582,7 @@
       <c r="A48" s="5">
         <v>47.0</v>
       </c>
-      <c r="B48" s="20" t="s">
+      <c r="B48" s="6" t="s">
         <v>447</v>
       </c>
       <c r="C48" s="12" t="s">
@@ -7669,7 +7618,7 @@
       <c r="M48" s="10" t="s">
         <v>453</v>
       </c>
-      <c r="N48" s="19" t="s">
+      <c r="N48" s="18" t="s">
         <v>110</v>
       </c>
       <c r="O48" s="12" t="s">
@@ -7700,10 +7649,10 @@
       <c r="A49" s="14">
         <v>48.0</v>
       </c>
-      <c r="B49" s="20" t="s">
+      <c r="B49" s="6" t="s">
         <v>455</v>
       </c>
-      <c r="C49" s="29" t="s">
+      <c r="C49" s="12" t="s">
         <v>88</v>
       </c>
       <c r="D49" s="12" t="s">
@@ -7718,7 +7667,7 @@
       <c r="G49" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H49" s="39" t="s">
+      <c r="H49" s="9" t="s">
         <v>458</v>
       </c>
       <c r="I49" s="12" t="s">
@@ -7736,7 +7685,7 @@
       <c r="M49" s="10" t="s">
         <v>463</v>
       </c>
-      <c r="N49" s="19" t="s">
+      <c r="N49" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O49" s="12" t="s">
@@ -7767,10 +7716,10 @@
       <c r="A50" s="5">
         <v>49.0</v>
       </c>
-      <c r="B50" s="20" t="s">
+      <c r="B50" s="6" t="s">
         <v>465</v>
       </c>
-      <c r="C50" s="29" t="s">
+      <c r="C50" s="12" t="s">
         <v>88</v>
       </c>
       <c r="D50" s="12" t="s">
@@ -7797,13 +7746,13 @@
       <c r="K50" s="12" t="s">
         <v>471</v>
       </c>
-      <c r="L50" s="29" t="s">
+      <c r="L50" s="12" t="s">
         <v>472</v>
       </c>
       <c r="M50" s="10" t="s">
         <v>473</v>
       </c>
-      <c r="N50" s="19" t="s">
+      <c r="N50" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O50" s="12" t="s">
@@ -7834,7 +7783,7 @@
       <c r="A51" s="14">
         <v>50.0</v>
       </c>
-      <c r="B51" s="20" t="s">
+      <c r="B51" s="6" t="s">
         <v>475</v>
       </c>
       <c r="C51" s="12" t="s">
@@ -7852,7 +7801,7 @@
       <c r="G51" s="12" t="s">
         <v>477</v>
       </c>
-      <c r="H51" s="40" t="s">
+      <c r="H51" s="30" t="s">
         <v>478</v>
       </c>
       <c r="I51" s="12" t="s">
@@ -7867,10 +7816,10 @@
       <c r="L51" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="M51" s="24" t="s">
+      <c r="M51" s="20" t="s">
         <v>482</v>
       </c>
-      <c r="N51" s="19" t="s">
+      <c r="N51" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O51" s="12" t="s">
@@ -7901,10 +7850,10 @@
       <c r="A52" s="5">
         <v>51.0</v>
       </c>
-      <c r="B52" s="32" t="s">
+      <c r="B52" s="5" t="s">
         <v>485</v>
       </c>
-      <c r="C52" s="29" t="s">
+      <c r="C52" s="12" t="s">
         <v>65</v>
       </c>
       <c r="D52" s="12" t="s">
@@ -7937,7 +7886,7 @@
       <c r="M52" s="10" t="s">
         <v>491</v>
       </c>
-      <c r="N52" s="19" t="s">
+      <c r="N52" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O52" s="12" t="s">
@@ -7968,10 +7917,10 @@
       <c r="A53" s="14">
         <v>52.0</v>
       </c>
-      <c r="B53" s="32" t="s">
+      <c r="B53" s="5" t="s">
         <v>493</v>
       </c>
-      <c r="C53" s="29" t="s">
+      <c r="C53" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D53" s="12" t="s">
@@ -7986,13 +7935,13 @@
       <c r="G53" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H53" s="41" t="s">
+      <c r="H53" s="31" t="s">
         <v>495</v>
       </c>
       <c r="I53" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="J53" s="40" t="s">
+      <c r="J53" s="30" t="s">
         <v>496</v>
       </c>
       <c r="K53" s="12" t="s">
@@ -8004,7 +7953,7 @@
       <c r="M53" s="10" t="s">
         <v>499</v>
       </c>
-      <c r="N53" s="19" t="s">
+      <c r="N53" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O53" s="12" t="s">
@@ -8038,7 +7987,7 @@
       <c r="B54" s="15" t="s">
         <v>501</v>
       </c>
-      <c r="C54" s="29" t="s">
+      <c r="C54" s="12" t="s">
         <v>41</v>
       </c>
       <c r="D54" s="12" t="s">
@@ -8068,10 +8017,10 @@
       <c r="L54" s="12" t="s">
         <v>506</v>
       </c>
-      <c r="M54" s="41" t="s">
+      <c r="M54" s="31" t="s">
         <v>507</v>
       </c>
-      <c r="N54" s="19" t="s">
+      <c r="N54" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O54" s="12" t="s">
@@ -8102,43 +8051,43 @@
       <c r="A55" s="14">
         <v>54.0</v>
       </c>
-      <c r="B55" s="32" t="s">
+      <c r="B55" s="5" t="s">
         <v>509</v>
       </c>
-      <c r="C55" s="29" t="s">
+      <c r="C55" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D55" s="29" t="s">
+      <c r="D55" s="12" t="s">
         <v>510</v>
       </c>
-      <c r="E55" s="29" t="s">
+      <c r="E55" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F55" s="29" t="s">
+      <c r="F55" s="12" t="s">
         <v>511</v>
       </c>
-      <c r="G55" s="29" t="s">
+      <c r="G55" s="12" t="s">
         <v>512</v>
       </c>
-      <c r="H55" s="29" t="s">
+      <c r="H55" s="12" t="s">
         <v>513</v>
       </c>
-      <c r="I55" s="29" t="s">
+      <c r="I55" s="12" t="s">
         <v>514</v>
       </c>
-      <c r="J55" s="29" t="s">
+      <c r="J55" s="12" t="s">
         <v>515</v>
       </c>
-      <c r="K55" s="29" t="s">
+      <c r="K55" s="12" t="s">
         <v>516</v>
       </c>
-      <c r="L55" s="42" t="s">
+      <c r="L55" s="32" t="s">
         <v>517</v>
       </c>
-      <c r="M55" s="18" t="s">
+      <c r="M55" s="10" t="s">
         <v>518</v>
       </c>
-      <c r="N55" s="43" t="s">
+      <c r="N55" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O55" s="12" t="s">
@@ -8169,43 +8118,43 @@
       <c r="A56" s="5">
         <v>55.0</v>
       </c>
-      <c r="B56" s="32" t="s">
+      <c r="B56" s="5" t="s">
         <v>520</v>
       </c>
-      <c r="C56" s="29" t="s">
+      <c r="C56" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="D56" s="29" t="s">
+      <c r="D56" s="12" t="s">
         <v>521</v>
       </c>
-      <c r="E56" s="29" t="s">
+      <c r="E56" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F56" s="29" t="s">
+      <c r="F56" s="12" t="s">
         <v>522</v>
       </c>
-      <c r="G56" s="29" t="s">
+      <c r="G56" s="12" t="s">
         <v>523</v>
       </c>
-      <c r="H56" s="29" t="s">
+      <c r="H56" s="12" t="s">
         <v>524</v>
       </c>
-      <c r="I56" s="29" t="s">
+      <c r="I56" s="12" t="s">
         <v>525</v>
       </c>
-      <c r="J56" s="29" t="s">
+      <c r="J56" s="12" t="s">
         <v>526</v>
       </c>
-      <c r="K56" s="29" t="s">
+      <c r="K56" s="12" t="s">
         <v>527</v>
       </c>
-      <c r="L56" s="42" t="s">
+      <c r="L56" s="32" t="s">
         <v>528</v>
       </c>
-      <c r="M56" s="44" t="s">
+      <c r="M56" s="34" t="s">
         <v>529</v>
       </c>
-      <c r="N56" s="43" t="s">
+      <c r="N56" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O56" s="12" t="s">
@@ -8236,43 +8185,43 @@
       <c r="A57" s="14">
         <v>56.0</v>
       </c>
-      <c r="B57" s="45" t="s">
+      <c r="B57" s="35" t="s">
         <v>531</v>
       </c>
-      <c r="C57" s="29" t="s">
+      <c r="C57" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D57" s="29" t="s">
+      <c r="D57" s="12" t="s">
         <v>532</v>
       </c>
-      <c r="E57" s="29" t="s">
+      <c r="E57" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F57" s="46" t="s">
+      <c r="F57" s="36" t="s">
         <v>533</v>
       </c>
-      <c r="G57" s="29" t="s">
+      <c r="G57" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="H57" s="29" t="s">
+      <c r="H57" s="12" t="s">
         <v>535</v>
       </c>
-      <c r="I57" s="29" t="s">
+      <c r="I57" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="J57" s="29" t="s">
+      <c r="J57" s="12" t="s">
         <v>536</v>
       </c>
-      <c r="K57" s="29" t="s">
+      <c r="K57" s="12" t="s">
         <v>537</v>
       </c>
-      <c r="L57" s="42" t="s">
+      <c r="L57" s="32" t="s">
         <v>538</v>
       </c>
-      <c r="M57" s="44" t="s">
+      <c r="M57" s="34" t="s">
         <v>539</v>
       </c>
-      <c r="N57" s="43" t="s">
+      <c r="N57" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O57" s="12" t="s">
@@ -8303,43 +8252,43 @@
       <c r="A58" s="5">
         <v>57.0</v>
       </c>
-      <c r="B58" s="32" t="s">
+      <c r="B58" s="5" t="s">
         <v>541</v>
       </c>
-      <c r="C58" s="29" t="s">
+      <c r="C58" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D58" s="29" t="s">
+      <c r="D58" s="12" t="s">
         <v>542</v>
       </c>
-      <c r="E58" s="29" t="s">
+      <c r="E58" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="F58" s="29" t="s">
+      <c r="F58" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G58" s="29" t="s">
+      <c r="G58" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="H58" s="29" t="s">
+      <c r="H58" s="12" t="s">
         <v>544</v>
       </c>
-      <c r="I58" s="29" t="s">
+      <c r="I58" s="12" t="s">
         <v>545</v>
       </c>
-      <c r="J58" s="29" t="s">
+      <c r="J58" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K58" s="29" t="s">
+      <c r="K58" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L58" s="42" t="s">
+      <c r="L58" s="32" t="s">
         <v>546</v>
       </c>
-      <c r="M58" s="44" t="s">
+      <c r="M58" s="34" t="s">
         <v>547</v>
       </c>
-      <c r="N58" s="43" t="s">
+      <c r="N58" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O58" s="12" t="s">
@@ -8385,28 +8334,28 @@
       <c r="F59" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G59" s="29" t="s">
+      <c r="G59" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="H59" s="41" t="s">
+      <c r="H59" s="31" t="s">
         <v>551</v>
       </c>
-      <c r="I59" s="41" t="s">
+      <c r="I59" s="31" t="s">
         <v>534</v>
       </c>
-      <c r="J59" s="41" t="s">
+      <c r="J59" s="31" t="s">
         <v>552</v>
       </c>
-      <c r="K59" s="41" t="s">
+      <c r="K59" s="31" t="s">
         <v>553</v>
       </c>
-      <c r="L59" s="42" t="s">
+      <c r="L59" s="32" t="s">
         <v>554</v>
       </c>
-      <c r="M59" s="44" t="s">
+      <c r="M59" s="34" t="s">
         <v>555</v>
       </c>
-      <c r="N59" s="43" t="s">
+      <c r="N59" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O59" s="12" t="s">
@@ -8437,43 +8386,43 @@
       <c r="A60" s="5">
         <v>59.0</v>
       </c>
-      <c r="B60" s="45" t="s">
+      <c r="B60" s="35" t="s">
         <v>557</v>
       </c>
-      <c r="C60" s="29" t="s">
+      <c r="C60" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D60" s="29" t="s">
+      <c r="D60" s="12" t="s">
         <v>558</v>
       </c>
-      <c r="E60" s="29" t="s">
+      <c r="E60" s="12" t="s">
         <v>559</v>
       </c>
-      <c r="F60" s="29" t="s">
+      <c r="F60" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="G60" s="29" t="s">
+      <c r="G60" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="H60" s="29" t="s">
+      <c r="H60" s="12" t="s">
         <v>561</v>
       </c>
-      <c r="I60" s="29" t="s">
+      <c r="I60" s="12" t="s">
         <v>534</v>
       </c>
-      <c r="J60" s="29" t="s">
+      <c r="J60" s="12" t="s">
         <v>562</v>
       </c>
-      <c r="K60" s="29" t="s">
+      <c r="K60" s="12" t="s">
         <v>563</v>
       </c>
-      <c r="L60" s="42" t="s">
+      <c r="L60" s="32" t="s">
         <v>564</v>
       </c>
-      <c r="M60" s="44" t="s">
+      <c r="M60" s="34" t="s">
         <v>565</v>
       </c>
-      <c r="N60" s="43" t="s">
+      <c r="N60" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O60" s="12" t="s">
@@ -8504,43 +8453,43 @@
       <c r="A61" s="14">
         <v>60.0</v>
       </c>
-      <c r="B61" s="32" t="s">
+      <c r="B61" s="5" t="s">
         <v>567</v>
       </c>
-      <c r="C61" s="29" t="s">
+      <c r="C61" s="12" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="29" t="s">
+      <c r="D61" s="12" t="s">
         <v>568</v>
       </c>
-      <c r="E61" s="29" t="s">
+      <c r="E61" s="12" t="s">
         <v>569</v>
       </c>
-      <c r="F61" s="29" t="s">
+      <c r="F61" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G61" s="29" t="s">
+      <c r="G61" s="12" t="s">
         <v>570</v>
       </c>
-      <c r="H61" s="29" t="s">
+      <c r="H61" s="12" t="s">
         <v>571</v>
       </c>
-      <c r="I61" s="29" t="s">
+      <c r="I61" s="12" t="s">
         <v>572</v>
       </c>
-      <c r="J61" s="29" t="s">
+      <c r="J61" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="K61" s="29" t="s">
+      <c r="K61" s="12" t="s">
         <v>573</v>
       </c>
-      <c r="L61" s="42" t="s">
+      <c r="L61" s="32" t="s">
         <v>574</v>
       </c>
-      <c r="M61" s="44" t="s">
+      <c r="M61" s="34" t="s">
         <v>575</v>
       </c>
-      <c r="N61" s="43" t="s">
+      <c r="N61" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O61" s="12" t="s">
@@ -8571,43 +8520,43 @@
       <c r="A62" s="5">
         <v>61.0</v>
       </c>
-      <c r="B62" s="45" t="s">
+      <c r="B62" s="35" t="s">
         <v>577</v>
       </c>
-      <c r="C62" s="29" t="s">
+      <c r="C62" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="D62" s="29" t="s">
+      <c r="D62" s="12" t="s">
         <v>578</v>
       </c>
-      <c r="E62" s="29" t="s">
+      <c r="E62" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="F62" s="29" t="s">
+      <c r="F62" s="12" t="s">
         <v>579</v>
       </c>
-      <c r="G62" s="29" t="s">
+      <c r="G62" s="12" t="s">
         <v>580</v>
       </c>
-      <c r="H62" s="40" t="s">
+      <c r="H62" s="30" t="s">
         <v>581</v>
       </c>
-      <c r="I62" s="29" t="s">
+      <c r="I62" s="12" t="s">
         <v>582</v>
       </c>
-      <c r="J62" s="19" t="s">
+      <c r="J62" s="18" t="s">
         <v>536</v>
       </c>
-      <c r="K62" s="29" t="s">
+      <c r="K62" s="12" t="s">
         <v>583</v>
       </c>
-      <c r="L62" s="42" t="s">
+      <c r="L62" s="32" t="s">
         <v>584</v>
       </c>
-      <c r="M62" s="44" t="s">
+      <c r="M62" s="34" t="s">
         <v>585</v>
       </c>
-      <c r="N62" s="43" t="s">
+      <c r="N62" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O62" s="12" t="s">
@@ -8638,43 +8587,43 @@
       <c r="A63" s="14">
         <v>62.0</v>
       </c>
-      <c r="B63" s="45" t="s">
+      <c r="B63" s="35" t="s">
         <v>587</v>
       </c>
-      <c r="C63" s="29" t="s">
+      <c r="C63" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="D63" s="29" t="s">
+      <c r="D63" s="12" t="s">
         <v>588</v>
       </c>
-      <c r="E63" s="29" t="s">
+      <c r="E63" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="F63" s="29" t="s">
+      <c r="F63" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G63" s="29" t="s">
+      <c r="G63" s="12" t="s">
         <v>589</v>
       </c>
-      <c r="H63" s="29" t="s">
+      <c r="H63" s="12" t="s">
         <v>590</v>
       </c>
-      <c r="I63" s="29" t="s">
+      <c r="I63" s="12" t="s">
         <v>591</v>
       </c>
-      <c r="J63" s="29" t="s">
+      <c r="J63" s="12" t="s">
         <v>592</v>
       </c>
-      <c r="K63" s="29" t="s">
+      <c r="K63" s="12" t="s">
         <v>593</v>
       </c>
-      <c r="L63" s="42" t="s">
+      <c r="L63" s="32" t="s">
         <v>594</v>
       </c>
-      <c r="M63" s="44" t="s">
+      <c r="M63" s="34" t="s">
         <v>595</v>
       </c>
-      <c r="N63" s="43" t="s">
+      <c r="N63" s="33" t="s">
         <v>596</v>
       </c>
       <c r="O63" s="12" t="s">
@@ -8705,43 +8654,43 @@
       <c r="A64" s="5">
         <v>63.0</v>
       </c>
-      <c r="B64" s="45" t="s">
+      <c r="B64" s="35" t="s">
         <v>598</v>
       </c>
-      <c r="C64" s="29" t="s">
+      <c r="C64" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="D64" s="29" t="s">
+      <c r="D64" s="12" t="s">
         <v>600</v>
       </c>
-      <c r="E64" s="29" t="s">
+      <c r="E64" s="12" t="s">
         <v>601</v>
       </c>
-      <c r="F64" s="46" t="s">
+      <c r="F64" s="36" t="s">
         <v>602</v>
       </c>
-      <c r="G64" s="29" t="s">
+      <c r="G64" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H64" s="29" t="s">
+      <c r="H64" s="12" t="s">
         <v>603</v>
       </c>
-      <c r="I64" s="29" t="s">
+      <c r="I64" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="J64" s="29" t="s">
+      <c r="J64" s="12" t="s">
         <v>604</v>
       </c>
-      <c r="K64" s="29" t="s">
+      <c r="K64" s="12" t="s">
         <v>605</v>
       </c>
-      <c r="L64" s="42" t="s">
+      <c r="L64" s="32" t="s">
         <v>606</v>
       </c>
-      <c r="M64" s="44" t="s">
+      <c r="M64" s="34" t="s">
         <v>607</v>
       </c>
-      <c r="N64" s="43" t="s">
+      <c r="N64" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O64" s="12" t="s">
@@ -8772,43 +8721,43 @@
       <c r="A65" s="14">
         <v>64.0</v>
       </c>
-      <c r="B65" s="45" t="s">
+      <c r="B65" s="35" t="s">
         <v>609</v>
       </c>
-      <c r="C65" s="29" t="s">
+      <c r="C65" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="D65" s="29" t="s">
+      <c r="D65" s="12" t="s">
         <v>610</v>
       </c>
-      <c r="E65" s="29" t="s">
+      <c r="E65" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F65" s="29" t="s">
+      <c r="F65" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G65" s="29" t="s">
+      <c r="G65" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H65" s="29" t="s">
+      <c r="H65" s="12" t="s">
         <v>611</v>
       </c>
-      <c r="I65" s="29" t="s">
+      <c r="I65" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="J65" s="29" t="s">
+      <c r="J65" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K65" s="29" t="s">
+      <c r="K65" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L65" s="42" t="s">
+      <c r="L65" s="32" t="s">
         <v>612</v>
       </c>
-      <c r="M65" s="44" t="s">
+      <c r="M65" s="34" t="s">
         <v>613</v>
       </c>
-      <c r="N65" s="43" t="s">
+      <c r="N65" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O65" s="12" t="s">
@@ -8839,43 +8788,43 @@
       <c r="A66" s="5">
         <v>65.0</v>
       </c>
-      <c r="B66" s="32" t="s">
+      <c r="B66" s="5" t="s">
         <v>615</v>
       </c>
-      <c r="C66" s="29" t="s">
+      <c r="C66" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D66" s="29" t="s">
+      <c r="D66" s="12" t="s">
         <v>616</v>
       </c>
-      <c r="E66" s="29" t="s">
+      <c r="E66" s="12" t="s">
         <v>543</v>
       </c>
-      <c r="F66" s="29" t="s">
+      <c r="F66" s="12" t="s">
         <v>20</v>
       </c>
-      <c r="G66" s="29" t="s">
+      <c r="G66" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H66" s="29" t="s">
+      <c r="H66" s="12" t="s">
         <v>617</v>
       </c>
-      <c r="I66" s="29" t="s">
+      <c r="I66" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="J66" s="29" t="s">
+      <c r="J66" s="12" t="s">
         <v>618</v>
       </c>
-      <c r="K66" s="29" t="s">
+      <c r="K66" s="12" t="s">
         <v>619</v>
       </c>
-      <c r="L66" s="42" t="s">
+      <c r="L66" s="32" t="s">
         <v>620</v>
       </c>
-      <c r="M66" s="44" t="s">
+      <c r="M66" s="34" t="s">
         <v>621</v>
       </c>
-      <c r="N66" s="43" t="s">
+      <c r="N66" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O66" s="12" t="s">
@@ -8906,43 +8855,43 @@
       <c r="A67" s="14">
         <v>66.0</v>
       </c>
-      <c r="B67" s="32" t="s">
+      <c r="B67" s="5" t="s">
         <v>623</v>
       </c>
-      <c r="C67" s="29" t="s">
+      <c r="C67" s="12" t="s">
         <v>599</v>
       </c>
-      <c r="D67" s="29" t="s">
+      <c r="D67" s="12" t="s">
         <v>624</v>
       </c>
-      <c r="E67" s="29" t="s">
+      <c r="E67" s="12" t="s">
         <v>625</v>
       </c>
-      <c r="F67" s="29" t="s">
+      <c r="F67" s="12" t="s">
         <v>560</v>
       </c>
-      <c r="G67" s="29" t="s">
+      <c r="G67" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H67" s="29" t="s">
+      <c r="H67" s="12" t="s">
         <v>626</v>
       </c>
-      <c r="I67" s="29" t="s">
+      <c r="I67" s="12" t="s">
         <v>627</v>
       </c>
-      <c r="J67" s="29" t="s">
+      <c r="J67" s="12" t="s">
         <v>628</v>
       </c>
-      <c r="K67" s="29" t="s">
+      <c r="K67" s="12" t="s">
         <v>629</v>
       </c>
-      <c r="L67" s="42" t="s">
+      <c r="L67" s="32" t="s">
         <v>630</v>
       </c>
-      <c r="M67" s="44" t="s">
+      <c r="M67" s="34" t="s">
         <v>631</v>
       </c>
-      <c r="N67" s="43" t="s">
+      <c r="N67" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O67" s="12" t="s">
@@ -8973,43 +8922,43 @@
       <c r="A68" s="5">
         <v>67.0</v>
       </c>
-      <c r="B68" s="32" t="s">
+      <c r="B68" s="5" t="s">
         <v>633</v>
       </c>
-      <c r="C68" s="29" t="s">
+      <c r="C68" s="12" t="s">
         <v>65</v>
       </c>
-      <c r="D68" s="29" t="s">
+      <c r="D68" s="12" t="s">
         <v>634</v>
       </c>
-      <c r="E68" s="29" t="s">
+      <c r="E68" s="12" t="s">
         <v>635</v>
       </c>
-      <c r="F68" s="29" t="s">
+      <c r="F68" s="12" t="s">
         <v>636</v>
       </c>
-      <c r="G68" s="29" t="s">
+      <c r="G68" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H68" s="29" t="s">
+      <c r="H68" s="12" t="s">
         <v>637</v>
       </c>
-      <c r="I68" s="29" t="s">
+      <c r="I68" s="12" t="s">
         <v>583</v>
       </c>
-      <c r="J68" s="29" t="s">
+      <c r="J68" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K68" s="29" t="s">
+      <c r="K68" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L68" s="42" t="s">
+      <c r="L68" s="32" t="s">
         <v>638</v>
       </c>
-      <c r="M68" s="44" t="s">
+      <c r="M68" s="34" t="s">
         <v>639</v>
       </c>
-      <c r="N68" s="19" t="s">
+      <c r="N68" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O68" s="12" t="s">
@@ -9040,43 +8989,43 @@
       <c r="A69" s="14">
         <v>68.0</v>
       </c>
-      <c r="B69" s="45" t="s">
+      <c r="B69" s="35" t="s">
         <v>641</v>
       </c>
-      <c r="C69" s="29" t="s">
+      <c r="C69" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D69" s="29" t="s">
+      <c r="D69" s="12" t="s">
         <v>642</v>
       </c>
-      <c r="E69" s="29" t="s">
+      <c r="E69" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F69" s="29" t="s">
+      <c r="F69" s="12" t="s">
         <v>643</v>
       </c>
-      <c r="G69" s="29" t="s">
+      <c r="G69" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H69" s="29" t="s">
+      <c r="H69" s="12" t="s">
         <v>644</v>
       </c>
-      <c r="I69" s="29" t="s">
+      <c r="I69" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="J69" s="29" t="s">
+      <c r="J69" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K69" s="29" t="s">
+      <c r="K69" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L69" s="42" t="s">
+      <c r="L69" s="32" t="s">
         <v>645</v>
       </c>
-      <c r="M69" s="44" t="s">
+      <c r="M69" s="34" t="s">
         <v>646</v>
       </c>
-      <c r="N69" s="43" t="s">
+      <c r="N69" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O69" s="12" t="s">
@@ -9107,43 +9056,43 @@
       <c r="A70" s="5">
         <v>69.0</v>
       </c>
-      <c r="B70" s="32" t="s">
+      <c r="B70" s="5" t="s">
         <v>648</v>
       </c>
-      <c r="C70" s="29" t="s">
+      <c r="C70" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="D70" s="29" t="s">
+      <c r="D70" s="12" t="s">
         <v>649</v>
       </c>
-      <c r="E70" s="29" t="s">
+      <c r="E70" s="12" t="s">
         <v>650</v>
       </c>
-      <c r="F70" s="29" t="s">
+      <c r="F70" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="G70" s="29" t="s">
+      <c r="G70" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H70" s="29" t="s">
+      <c r="H70" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I70" s="29" t="s">
+      <c r="I70" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J70" s="29" t="s">
+      <c r="J70" s="12" t="s">
         <v>652</v>
       </c>
-      <c r="K70" s="29" t="s">
+      <c r="K70" s="12" t="s">
         <v>653</v>
       </c>
-      <c r="L70" s="42" t="s">
+      <c r="L70" s="32" t="s">
         <v>654</v>
       </c>
-      <c r="M70" s="18" t="s">
+      <c r="M70" s="10" t="s">
         <v>655</v>
       </c>
-      <c r="N70" s="19" t="s">
+      <c r="N70" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O70" s="12" t="s">
@@ -9174,43 +9123,43 @@
       <c r="A71" s="14">
         <v>70.0</v>
       </c>
-      <c r="B71" s="32" t="s">
+      <c r="B71" s="5" t="s">
         <v>657</v>
       </c>
-      <c r="C71" s="29" t="s">
+      <c r="C71" s="12" t="s">
         <v>28</v>
       </c>
-      <c r="D71" s="29" t="s">
+      <c r="D71" s="12" t="s">
         <v>658</v>
       </c>
-      <c r="E71" s="29" t="s">
+      <c r="E71" s="12" t="s">
         <v>659</v>
       </c>
-      <c r="F71" s="29" t="s">
+      <c r="F71" s="12" t="s">
         <v>660</v>
       </c>
-      <c r="G71" s="29" t="s">
+      <c r="G71" s="12" t="s">
         <v>68</v>
       </c>
-      <c r="H71" s="29" t="s">
+      <c r="H71" s="12" t="s">
         <v>661</v>
       </c>
-      <c r="I71" s="29" t="s">
+      <c r="I71" s="12" t="s">
         <v>459</v>
       </c>
-      <c r="J71" s="29" t="s">
+      <c r="J71" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="K71" s="29" t="s">
+      <c r="K71" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L71" s="42" t="s">
+      <c r="L71" s="32" t="s">
         <v>662</v>
       </c>
-      <c r="M71" s="44" t="s">
+      <c r="M71" s="34" t="s">
         <v>663</v>
       </c>
-      <c r="N71" s="19" t="s">
+      <c r="N71" s="18" t="s">
         <v>110</v>
       </c>
       <c r="O71" s="12" t="s">
@@ -9244,7 +9193,7 @@
       <c r="B72" s="5" t="s">
         <v>665</v>
       </c>
-      <c r="C72" s="29" t="s">
+      <c r="C72" s="12" t="s">
         <v>666</v>
       </c>
       <c r="D72" s="12" t="s">
@@ -9259,10 +9208,10 @@
       <c r="G72" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H72" s="29" t="s">
+      <c r="H72" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I72" s="29" t="s">
+      <c r="I72" s="12" t="s">
         <v>21</v>
       </c>
       <c r="J72" s="12" t="s">
@@ -9274,10 +9223,10 @@
       <c r="L72" s="12" t="s">
         <v>669</v>
       </c>
-      <c r="M72" s="24" t="s">
+      <c r="M72" s="20" t="s">
         <v>670</v>
       </c>
-      <c r="N72" s="19" t="s">
+      <c r="N72" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O72" s="12" t="s">
@@ -9311,7 +9260,7 @@
       <c r="B73" s="12" t="s">
         <v>673</v>
       </c>
-      <c r="C73" s="29" t="s">
+      <c r="C73" s="12" t="s">
         <v>666</v>
       </c>
       <c r="D73" s="12" t="s">
@@ -9341,10 +9290,10 @@
       <c r="L73" s="12" t="s">
         <v>679</v>
       </c>
-      <c r="M73" s="24" t="s">
+      <c r="M73" s="20" t="s">
         <v>680</v>
       </c>
-      <c r="N73" s="19" t="s">
+      <c r="N73" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O73" s="12" t="s">
@@ -9378,7 +9327,7 @@
       <c r="B74" s="12" t="s">
         <v>682</v>
       </c>
-      <c r="C74" s="29" t="s">
+      <c r="C74" s="12" t="s">
         <v>666</v>
       </c>
       <c r="D74" s="12" t="s">
@@ -9411,7 +9360,7 @@
       <c r="M74" s="10" t="s">
         <v>688</v>
       </c>
-      <c r="N74" s="19" t="s">
+      <c r="N74" s="18" t="s">
         <v>689</v>
       </c>
       <c r="O74" s="12" t="s">
@@ -9445,7 +9394,7 @@
       <c r="B75" s="12" t="s">
         <v>691</v>
       </c>
-      <c r="C75" s="29" t="s">
+      <c r="C75" s="12" t="s">
         <v>666</v>
       </c>
       <c r="D75" s="12" t="s">
@@ -9478,7 +9427,7 @@
       <c r="M75" s="10" t="s">
         <v>696</v>
       </c>
-      <c r="N75" s="19" t="s">
+      <c r="N75" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O75" s="12" t="s">
@@ -9542,10 +9491,10 @@
       <c r="L76" s="12" t="s">
         <v>704</v>
       </c>
-      <c r="M76" s="47" t="s">
+      <c r="M76" s="37" t="s">
         <v>705</v>
       </c>
-      <c r="N76" s="19" t="s">
+      <c r="N76" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O76" s="12" t="s">
@@ -9586,7 +9535,7 @@
         <v>708</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>709</v>
+        <v>19</v>
       </c>
       <c r="F77" s="12" t="s">
         <v>20</v>
@@ -9595,22 +9544,22 @@
         <v>124</v>
       </c>
       <c r="H77" s="12" t="s">
+        <v>709</v>
+      </c>
+      <c r="I77" s="12" t="s">
         <v>710</v>
       </c>
-      <c r="I77" s="12" t="s">
+      <c r="J77" s="9" t="s">
         <v>711</v>
       </c>
-      <c r="J77" s="9" t="s">
+      <c r="K77" s="9" t="s">
         <v>712</v>
       </c>
-      <c r="K77" s="9" t="s">
+      <c r="L77" s="9" t="s">
         <v>713</v>
       </c>
-      <c r="L77" s="9" t="s">
+      <c r="M77" s="37" t="s">
         <v>714</v>
-      </c>
-      <c r="M77" s="47" t="s">
-        <v>715</v>
       </c>
       <c r="N77" s="11" t="s">
         <v>24</v>
@@ -9619,7 +9568,7 @@
         <v>185</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>716</v>
+        <v>715</v>
       </c>
       <c r="Q77" s="13"/>
       <c r="R77" s="13"/>
@@ -9644,16 +9593,16 @@
         <v>77.0</v>
       </c>
       <c r="B78" s="12" t="s">
+        <v>716</v>
+      </c>
+      <c r="C78" s="12" t="s">
         <v>717</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="D78" s="12" t="s">
         <v>718</v>
       </c>
-      <c r="D78" s="12" t="s">
-        <v>719</v>
-      </c>
       <c r="E78" s="12" t="s">
-        <v>720</v>
+        <v>80</v>
       </c>
       <c r="F78" s="12" t="s">
         <v>668</v>
@@ -9662,22 +9611,22 @@
         <v>81</v>
       </c>
       <c r="H78" s="12" t="s">
-        <v>721</v>
+        <v>719</v>
       </c>
       <c r="I78" s="9" t="s">
         <v>81</v>
       </c>
       <c r="J78" s="9" t="s">
-        <v>712</v>
+        <v>711</v>
       </c>
       <c r="K78" s="9" t="s">
+        <v>720</v>
+      </c>
+      <c r="L78" s="9" t="s">
+        <v>721</v>
+      </c>
+      <c r="M78" s="37" t="s">
         <v>722</v>
-      </c>
-      <c r="L78" s="9" t="s">
-        <v>723</v>
-      </c>
-      <c r="M78" s="47" t="s">
-        <v>724</v>
       </c>
       <c r="N78" s="11" t="s">
         <v>24</v>
@@ -9686,7 +9635,7 @@
         <v>185</v>
       </c>
       <c r="P78" s="9" t="s">
-        <v>725</v>
+        <v>723</v>
       </c>
       <c r="Q78" s="13"/>
       <c r="R78" s="13"/>
@@ -9711,13 +9660,13 @@
         <v>78.0</v>
       </c>
       <c r="B79" s="12" t="s">
-        <v>726</v>
+        <v>724</v>
       </c>
       <c r="C79" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D79" s="12" t="s">
-        <v>727</v>
+        <v>725</v>
       </c>
       <c r="E79" s="12" t="s">
         <v>43</v>
@@ -9726,7 +9675,7 @@
         <v>668</v>
       </c>
       <c r="G79" s="12" t="s">
-        <v>728</v>
+        <v>726</v>
       </c>
       <c r="H79" s="12" t="s">
         <v>21</v>
@@ -9735,16 +9684,16 @@
         <v>21</v>
       </c>
       <c r="J79" s="9" t="s">
+        <v>727</v>
+      </c>
+      <c r="K79" s="9" t="s">
+        <v>728</v>
+      </c>
+      <c r="L79" s="9" t="s">
         <v>729</v>
       </c>
-      <c r="K79" s="9" t="s">
+      <c r="M79" s="38" t="s">
         <v>730</v>
-      </c>
-      <c r="L79" s="9" t="s">
-        <v>731</v>
-      </c>
-      <c r="M79" s="48" t="s">
-        <v>732</v>
       </c>
       <c r="N79" s="11" t="s">
         <v>166</v>
@@ -9753,7 +9702,7 @@
         <v>430</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>733</v>
+        <v>731</v>
       </c>
       <c r="Q79" s="13"/>
       <c r="R79" s="13"/>
@@ -9778,13 +9727,13 @@
         <v>79.0</v>
       </c>
       <c r="B80" s="12" t="s">
-        <v>734</v>
+        <v>732</v>
       </c>
       <c r="C80" s="12" t="s">
         <v>41</v>
       </c>
       <c r="D80" s="12" t="s">
-        <v>735</v>
+        <v>733</v>
       </c>
       <c r="E80" s="12" t="s">
         <v>43</v>
@@ -9796,31 +9745,31 @@
         <v>124</v>
       </c>
       <c r="H80" s="12" t="s">
+        <v>734</v>
+      </c>
+      <c r="I80" s="9" t="s">
+        <v>735</v>
+      </c>
+      <c r="J80" s="9" t="s">
         <v>736</v>
       </c>
-      <c r="I80" s="9" t="s">
+      <c r="K80" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="J80" s="9" t="s">
+      <c r="L80" s="9" t="s">
         <v>738</v>
       </c>
-      <c r="K80" s="9" t="s">
+      <c r="M80" s="39" t="s">
         <v>739</v>
-      </c>
-      <c r="L80" s="9" t="s">
-        <v>740</v>
-      </c>
-      <c r="M80" s="49" t="s">
-        <v>741</v>
       </c>
       <c r="N80" s="11" t="s">
         <v>166</v>
       </c>
       <c r="O80" s="12" t="s">
-        <v>742</v>
+        <v>740</v>
       </c>
       <c r="P80" s="9" t="s">
-        <v>743</v>
+        <v>741</v>
       </c>
       <c r="Q80" s="13"/>
       <c r="R80" s="13"/>
@@ -9844,41 +9793,41 @@
       <c r="A81" s="14">
         <v>80.0</v>
       </c>
-      <c r="B81" s="19" t="s">
+      <c r="B81" s="18" t="s">
         <v>254</v>
       </c>
-      <c r="C81" s="19" t="s">
+      <c r="C81" s="18" t="s">
         <v>17</v>
       </c>
-      <c r="D81" s="19" t="s">
-        <v>744</v>
-      </c>
-      <c r="E81" s="19" t="s">
+      <c r="D81" s="18" t="s">
+        <v>742</v>
+      </c>
+      <c r="E81" s="18" t="s">
         <v>559</v>
       </c>
-      <c r="F81" s="19" t="s">
+      <c r="F81" s="18" t="s">
         <v>20</v>
       </c>
       <c r="G81" s="12" t="s">
         <v>81</v>
       </c>
       <c r="H81" s="12" t="s">
+        <v>743</v>
+      </c>
+      <c r="I81" s="9" t="s">
+        <v>744</v>
+      </c>
+      <c r="J81" s="11" t="s">
         <v>745</v>
       </c>
-      <c r="I81" s="9" t="s">
+      <c r="K81" s="11" t="s">
         <v>746</v>
       </c>
-      <c r="J81" s="11" t="s">
+      <c r="L81" s="9" t="s">
         <v>747</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="M81" s="40" t="s">
         <v>748</v>
-      </c>
-      <c r="L81" s="9" t="s">
-        <v>749</v>
-      </c>
-      <c r="M81" s="50" t="s">
-        <v>750</v>
       </c>
       <c r="N81" s="11" t="s">
         <v>24</v>
@@ -9887,7 +9836,7 @@
         <v>185</v>
       </c>
       <c r="P81" s="9" t="s">
-        <v>751</v>
+        <v>749</v>
       </c>
       <c r="Q81" s="13"/>
       <c r="R81" s="13"/>
@@ -9912,49 +9861,49 @@
         <v>81.0</v>
       </c>
       <c r="B82" s="12" t="s">
+        <v>750</v>
+      </c>
+      <c r="C82" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D82" s="18" t="s">
+        <v>751</v>
+      </c>
+      <c r="E82" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F82" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G82" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H82" s="12" t="s">
         <v>752</v>
       </c>
-      <c r="C82" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D82" s="19" t="s">
+      <c r="I82" s="9" t="s">
         <v>753</v>
       </c>
-      <c r="E82" s="19" t="s">
-        <v>543</v>
-      </c>
-      <c r="F82" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G82" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="H82" s="12" t="s">
+      <c r="J82" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="K82" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="L82" s="9" t="s">
         <v>754</v>
       </c>
-      <c r="I82" s="9" t="s">
+      <c r="M82" s="42" t="s">
         <v>755</v>
-      </c>
-      <c r="J82" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="K82" s="51" t="s">
-        <v>21</v>
-      </c>
-      <c r="L82" s="9" t="s">
-        <v>756</v>
-      </c>
-      <c r="M82" s="52" t="s">
-        <v>757</v>
       </c>
       <c r="N82" s="11" t="s">
         <v>166</v>
       </c>
       <c r="O82" s="12" t="s">
-        <v>758</v>
+        <v>756</v>
       </c>
       <c r="P82" s="9" t="s">
-        <v>759</v>
+        <v>757</v>
       </c>
       <c r="Q82" s="13"/>
       <c r="R82" s="13"/>
@@ -9979,40 +9928,40 @@
         <v>82.0</v>
       </c>
       <c r="B83" s="9" t="s">
+        <v>758</v>
+      </c>
+      <c r="C83" s="18" t="s">
+        <v>28</v>
+      </c>
+      <c r="D83" s="11" t="s">
+        <v>759</v>
+      </c>
+      <c r="E83" s="18" t="s">
+        <v>543</v>
+      </c>
+      <c r="F83" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G83" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H83" s="9" t="s">
         <v>760</v>
       </c>
-      <c r="C83" s="19" t="s">
-        <v>28</v>
-      </c>
-      <c r="D83" s="11" t="s">
+      <c r="I83" s="9" t="s">
         <v>761</v>
-      </c>
-      <c r="E83" s="19" t="s">
-        <v>543</v>
-      </c>
-      <c r="F83" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G83" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="H83" s="9" t="s">
-        <v>762</v>
-      </c>
-      <c r="I83" s="9" t="s">
-        <v>763</v>
       </c>
       <c r="J83" s="11" t="s">
         <v>536</v>
       </c>
       <c r="K83" s="11" t="s">
+        <v>762</v>
+      </c>
+      <c r="L83" s="9" t="s">
+        <v>763</v>
+      </c>
+      <c r="M83" s="43" t="s">
         <v>764</v>
-      </c>
-      <c r="L83" s="9" t="s">
-        <v>765</v>
-      </c>
-      <c r="M83" s="53" t="s">
-        <v>766</v>
       </c>
       <c r="N83" s="11" t="s">
         <v>166</v>
@@ -10021,7 +9970,7 @@
         <v>185</v>
       </c>
       <c r="P83" s="9" t="s">
-        <v>767</v>
+        <v>765</v>
       </c>
       <c r="Q83" s="13"/>
       <c r="R83" s="13"/>
@@ -10046,40 +9995,40 @@
         <v>83.0</v>
       </c>
       <c r="B84" s="9" t="s">
-        <v>768</v>
+        <v>766</v>
       </c>
       <c r="C84" s="11" t="s">
         <v>17</v>
       </c>
       <c r="D84" s="11" t="s">
+        <v>767</v>
+      </c>
+      <c r="E84" s="11" t="s">
+        <v>768</v>
+      </c>
+      <c r="F84" s="18" t="s">
+        <v>20</v>
+      </c>
+      <c r="G84" s="18" t="s">
+        <v>81</v>
+      </c>
+      <c r="H84" s="9" t="s">
         <v>769</v>
       </c>
-      <c r="E84" s="11" t="s">
+      <c r="I84" s="11" t="s">
         <v>770</v>
-      </c>
-      <c r="F84" s="19" t="s">
-        <v>20</v>
-      </c>
-      <c r="G84" s="19" t="s">
-        <v>81</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>771</v>
-      </c>
-      <c r="I84" s="11" t="s">
-        <v>772</v>
       </c>
       <c r="J84" s="11" t="s">
         <v>331</v>
       </c>
       <c r="K84" s="11" t="s">
+        <v>771</v>
+      </c>
+      <c r="L84" s="9" t="s">
+        <v>772</v>
+      </c>
+      <c r="M84" s="44" t="s">
         <v>773</v>
-      </c>
-      <c r="L84" s="9" t="s">
-        <v>774</v>
-      </c>
-      <c r="M84" s="54" t="s">
-        <v>775</v>
       </c>
       <c r="N84" s="11" t="s">
         <v>24</v>
@@ -10088,7 +10037,7 @@
         <v>185</v>
       </c>
       <c r="P84" s="9" t="s">
-        <v>776</v>
+        <v>774</v>
       </c>
       <c r="Q84" s="13"/>
       <c r="R84" s="13"/>
@@ -10111,8 +10060,8 @@
     <row r="85" ht="18.75" customHeight="1">
       <c r="A85" s="13"/>
       <c r="B85" s="13"/>
-      <c r="C85" s="55"/>
-      <c r="D85" s="55"/>
+      <c r="C85" s="45"/>
+      <c r="D85" s="45"/>
       <c r="E85" s="13"/>
       <c r="F85" s="13"/>
       <c r="G85" s="13"/>
@@ -16739,407 +16688,407 @@
   </cols>
   <sheetData>
     <row r="1" ht="48.0" customHeight="1">
-      <c r="A1" s="56" t="s">
+      <c r="A1" s="46" t="s">
+        <v>775</v>
+      </c>
+      <c r="B1" s="46" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="47" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="48" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="48" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="48" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="48" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="47" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="47" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="47" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="47" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="49" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="47" t="s">
+        <v>776</v>
+      </c>
+      <c r="N1" s="50"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+    </row>
+    <row r="2" ht="42.75" customHeight="1">
+      <c r="A2" s="51" t="s">
         <v>777</v>
       </c>
-      <c r="B1" s="56" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="57" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="58" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="58" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="58" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="58" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="57" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="57" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="57" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="57" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="59" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="57" t="s">
+      <c r="B2" s="52"/>
+      <c r="C2" s="52"/>
+    </row>
+    <row r="3" ht="36.75" customHeight="1">
+      <c r="A3" s="51" t="s">
         <v>778</v>
       </c>
-      <c r="N1" s="60"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-    </row>
-    <row r="2" ht="42.75" customHeight="1">
-      <c r="A2" s="61" t="s">
+    </row>
+    <row r="4" ht="38.25" customHeight="1">
+      <c r="A4" s="51" t="s">
         <v>779</v>
       </c>
-      <c r="B2" s="62"/>
-      <c r="C2" s="62"/>
-    </row>
-    <row r="3" ht="36.75" customHeight="1">
-      <c r="A3" s="61" t="s">
+    </row>
+    <row r="5" ht="25.5" customHeight="1">
+      <c r="A5" s="51" t="s">
         <v>780</v>
       </c>
     </row>
-    <row r="4" ht="38.25" customHeight="1">
-      <c r="A4" s="61" t="s">
+    <row r="6" ht="37.5" customHeight="1">
+      <c r="A6" s="51" t="s">
         <v>781</v>
       </c>
     </row>
-    <row r="5" ht="25.5" customHeight="1">
-      <c r="A5" s="61" t="s">
+    <row r="7" ht="34.5" customHeight="1">
+      <c r="A7" s="51" t="s">
         <v>782</v>
       </c>
     </row>
-    <row r="6" ht="37.5" customHeight="1">
-      <c r="A6" s="61" t="s">
+    <row r="8" ht="30.0" customHeight="1">
+      <c r="A8" s="51" t="s">
         <v>783</v>
       </c>
     </row>
-    <row r="7" ht="34.5" customHeight="1">
-      <c r="A7" s="61" t="s">
+    <row r="9" ht="34.5" customHeight="1">
+      <c r="A9" s="51" t="s">
         <v>784</v>
       </c>
     </row>
-    <row r="8" ht="30.0" customHeight="1">
-      <c r="A8" s="61" t="s">
+    <row r="10" ht="27.75" customHeight="1">
+      <c r="A10" s="51" t="s">
         <v>785</v>
       </c>
     </row>
-    <row r="9" ht="34.5" customHeight="1">
-      <c r="A9" s="61" t="s">
+    <row r="11" ht="30.0" customHeight="1">
+      <c r="A11" s="51" t="s">
         <v>786</v>
       </c>
     </row>
-    <row r="10" ht="27.75" customHeight="1">
-      <c r="A10" s="61" t="s">
+    <row r="12" ht="38.25" customHeight="1">
+      <c r="A12" s="51" t="s">
         <v>787</v>
       </c>
     </row>
-    <row r="11" ht="30.0" customHeight="1">
-      <c r="A11" s="61" t="s">
+    <row r="13" ht="24.75" customHeight="1">
+      <c r="A13" s="51" t="s">
         <v>788</v>
       </c>
     </row>
-    <row r="12" ht="38.25" customHeight="1">
-      <c r="A12" s="61" t="s">
+    <row r="14" ht="25.5" customHeight="1">
+      <c r="A14" s="51" t="s">
         <v>789</v>
       </c>
     </row>
-    <row r="13" ht="24.75" customHeight="1">
-      <c r="A13" s="61" t="s">
+    <row r="15" ht="36.0" customHeight="1">
+      <c r="A15" s="51" t="s">
         <v>790</v>
       </c>
     </row>
-    <row r="14" ht="25.5" customHeight="1">
-      <c r="A14" s="61" t="s">
+    <row r="16" ht="39.0" customHeight="1">
+      <c r="A16" s="51" t="s">
         <v>791</v>
       </c>
     </row>
-    <row r="15" ht="36.0" customHeight="1">
-      <c r="A15" s="61" t="s">
+    <row r="17" ht="27.75" customHeight="1">
+      <c r="A17" s="51" t="s">
         <v>792</v>
       </c>
     </row>
-    <row r="16" ht="39.0" customHeight="1">
-      <c r="A16" s="61" t="s">
+    <row r="18" ht="36.0" customHeight="1">
+      <c r="A18" s="51" t="s">
         <v>793</v>
       </c>
     </row>
-    <row r="17" ht="27.75" customHeight="1">
-      <c r="A17" s="61" t="s">
+    <row r="19" ht="21.0" customHeight="1">
+      <c r="A19" s="51" t="s">
         <v>794</v>
       </c>
     </row>
-    <row r="18" ht="36.0" customHeight="1">
-      <c r="A18" s="61" t="s">
+    <row r="20" ht="35.25" customHeight="1">
+      <c r="A20" s="51" t="s">
         <v>795</v>
       </c>
     </row>
-    <row r="19" ht="21.0" customHeight="1">
-      <c r="A19" s="61" t="s">
+    <row r="21" ht="24.75" customHeight="1">
+      <c r="A21" s="51" t="s">
         <v>796</v>
       </c>
     </row>
-    <row r="20" ht="35.25" customHeight="1">
-      <c r="A20" s="61" t="s">
+    <row r="22" ht="28.5" customHeight="1">
+      <c r="A22" s="51" t="s">
         <v>797</v>
       </c>
     </row>
-    <row r="21" ht="24.75" customHeight="1">
-      <c r="A21" s="61" t="s">
+    <row r="23" ht="38.25" customHeight="1">
+      <c r="A23" s="51" t="s">
         <v>798</v>
       </c>
     </row>
-    <row r="22" ht="28.5" customHeight="1">
-      <c r="A22" s="61" t="s">
+    <row r="24" ht="38.25" customHeight="1">
+      <c r="A24" s="51" t="s">
         <v>799</v>
       </c>
     </row>
-    <row r="23" ht="38.25" customHeight="1">
-      <c r="A23" s="61" t="s">
+    <row r="25" ht="25.5" customHeight="1">
+      <c r="A25" s="51" t="s">
         <v>800</v>
       </c>
     </row>
-    <row r="24" ht="38.25" customHeight="1">
-      <c r="A24" s="61" t="s">
+    <row r="26" ht="42.0" customHeight="1">
+      <c r="A26" s="51" t="s">
         <v>801</v>
       </c>
     </row>
-    <row r="25" ht="25.5" customHeight="1">
-      <c r="A25" s="61" t="s">
+    <row r="27" ht="29.25" customHeight="1">
+      <c r="A27" s="51" t="s">
         <v>802</v>
       </c>
     </row>
-    <row r="26" ht="42.0" customHeight="1">
-      <c r="A26" s="61" t="s">
+    <row r="28" ht="34.5" customHeight="1">
+      <c r="A28" s="51" t="s">
         <v>803</v>
       </c>
     </row>
-    <row r="27" ht="29.25" customHeight="1">
-      <c r="A27" s="61" t="s">
+    <row r="29" ht="30.0" customHeight="1">
+      <c r="A29" s="51" t="s">
         <v>804</v>
       </c>
     </row>
-    <row r="28" ht="34.5" customHeight="1">
-      <c r="A28" s="61" t="s">
+    <row r="30" ht="36.0" customHeight="1">
+      <c r="A30" s="51" t="s">
         <v>805</v>
       </c>
     </row>
-    <row r="29" ht="30.0" customHeight="1">
-      <c r="A29" s="61" t="s">
+    <row r="31" ht="44.25" customHeight="1">
+      <c r="A31" s="51" t="s">
         <v>806</v>
       </c>
     </row>
-    <row r="30" ht="36.0" customHeight="1">
-      <c r="A30" s="61" t="s">
+    <row r="32" ht="38.25" customHeight="1">
+      <c r="A32" s="51" t="s">
         <v>807</v>
       </c>
     </row>
-    <row r="31" ht="44.25" customHeight="1">
-      <c r="A31" s="61" t="s">
+    <row r="33" ht="41.25" customHeight="1">
+      <c r="A33" s="51" t="s">
         <v>808</v>
       </c>
     </row>
-    <row r="32" ht="38.25" customHeight="1">
-      <c r="A32" s="61" t="s">
+    <row r="34" ht="30.0" customHeight="1">
+      <c r="A34" s="51" t="s">
         <v>809</v>
       </c>
     </row>
-    <row r="33" ht="41.25" customHeight="1">
-      <c r="A33" s="61" t="s">
+    <row r="35" ht="43.5" customHeight="1">
+      <c r="A35" s="51" t="s">
         <v>810</v>
       </c>
     </row>
-    <row r="34" ht="30.0" customHeight="1">
-      <c r="A34" s="61" t="s">
+    <row r="36" ht="27.0" customHeight="1">
+      <c r="A36" s="51" t="s">
         <v>811</v>
       </c>
     </row>
-    <row r="35" ht="43.5" customHeight="1">
-      <c r="A35" s="61" t="s">
+    <row r="37" ht="26.25" customHeight="1">
+      <c r="A37" s="51" t="s">
         <v>812</v>
       </c>
     </row>
-    <row r="36" ht="27.0" customHeight="1">
-      <c r="A36" s="61" t="s">
+    <row r="38" ht="34.5" customHeight="1">
+      <c r="A38" s="51" t="s">
         <v>813</v>
       </c>
     </row>
-    <row r="37" ht="26.25" customHeight="1">
-      <c r="A37" s="61" t="s">
+    <row r="39" ht="40.5" customHeight="1">
+      <c r="A39" s="51" t="s">
         <v>814</v>
       </c>
     </row>
-    <row r="38" ht="34.5" customHeight="1">
-      <c r="A38" s="61" t="s">
+    <row r="40" ht="29.25" customHeight="1">
+      <c r="A40" s="51" t="s">
         <v>815</v>
       </c>
     </row>
-    <row r="39" ht="40.5" customHeight="1">
-      <c r="A39" s="61" t="s">
+    <row r="41" ht="33.75" customHeight="1">
+      <c r="A41" s="51" t="s">
         <v>816</v>
       </c>
     </row>
-    <row r="40" ht="29.25" customHeight="1">
-      <c r="A40" s="61" t="s">
+    <row r="42" ht="24.75" customHeight="1">
+      <c r="A42" s="51" t="s">
         <v>817</v>
       </c>
     </row>
-    <row r="41" ht="33.75" customHeight="1">
-      <c r="A41" s="61" t="s">
+    <row r="43" ht="30.0" customHeight="1">
+      <c r="A43" s="51" t="s">
         <v>818</v>
       </c>
     </row>
-    <row r="42" ht="24.75" customHeight="1">
-      <c r="A42" s="61" t="s">
+    <row r="44" ht="26.25" customHeight="1">
+      <c r="A44" s="51" t="s">
         <v>819</v>
       </c>
     </row>
-    <row r="43" ht="30.0" customHeight="1">
-      <c r="A43" s="61" t="s">
+    <row r="45" ht="36.0" customHeight="1">
+      <c r="A45" s="51" t="s">
         <v>820</v>
       </c>
     </row>
-    <row r="44" ht="26.25" customHeight="1">
-      <c r="A44" s="61" t="s">
+    <row r="46" ht="27.0" customHeight="1">
+      <c r="A46" s="51" t="s">
         <v>821</v>
       </c>
     </row>
-    <row r="45" ht="36.0" customHeight="1">
-      <c r="A45" s="61" t="s">
+    <row r="47" ht="23.25" customHeight="1">
+      <c r="A47" s="51" t="s">
         <v>822</v>
       </c>
     </row>
-    <row r="46" ht="27.0" customHeight="1">
-      <c r="A46" s="61" t="s">
+    <row r="48" ht="25.5" customHeight="1">
+      <c r="A48" s="51" t="s">
         <v>823</v>
       </c>
     </row>
-    <row r="47" ht="23.25" customHeight="1">
-      <c r="A47" s="61" t="s">
+    <row r="49" ht="23.25" customHeight="1">
+      <c r="A49" s="51" t="s">
         <v>824</v>
       </c>
     </row>
-    <row r="48" ht="25.5" customHeight="1">
-      <c r="A48" s="61" t="s">
+    <row r="50" ht="25.5" customHeight="1">
+      <c r="A50" s="51" t="s">
         <v>825</v>
       </c>
     </row>
-    <row r="49" ht="23.25" customHeight="1">
-      <c r="A49" s="61" t="s">
+    <row r="51" ht="31.5" customHeight="1">
+      <c r="A51" s="51" t="s">
         <v>826</v>
       </c>
     </row>
-    <row r="50" ht="25.5" customHeight="1">
-      <c r="A50" s="61" t="s">
+    <row r="52" ht="34.5" customHeight="1">
+      <c r="A52" s="51" t="s">
         <v>827</v>
       </c>
     </row>
-    <row r="51" ht="31.5" customHeight="1">
-      <c r="A51" s="61" t="s">
+    <row r="53" ht="25.5" customHeight="1">
+      <c r="A53" s="51" t="s">
         <v>828</v>
       </c>
     </row>
-    <row r="52" ht="34.5" customHeight="1">
-      <c r="A52" s="61" t="s">
+    <row r="54" ht="27.75" customHeight="1">
+      <c r="A54" s="51" t="s">
         <v>829</v>
       </c>
     </row>
-    <row r="53" ht="25.5" customHeight="1">
-      <c r="A53" s="61" t="s">
+    <row r="55" ht="29.25" customHeight="1">
+      <c r="A55" s="51" t="s">
         <v>830</v>
       </c>
     </row>
-    <row r="54" ht="27.75" customHeight="1">
-      <c r="A54" s="61" t="s">
+    <row r="56" ht="19.5" customHeight="1">
+      <c r="A56" s="51" t="s">
         <v>831</v>
       </c>
     </row>
-    <row r="55" ht="29.25" customHeight="1">
-      <c r="A55" s="61" t="s">
+    <row r="57" ht="23.25" customHeight="1">
+      <c r="A57" s="51" t="s">
         <v>832</v>
       </c>
     </row>
-    <row r="56" ht="19.5" customHeight="1">
-      <c r="A56" s="61" t="s">
+    <row r="58" ht="26.25" customHeight="1">
+      <c r="A58" s="51" t="s">
         <v>833</v>
       </c>
     </row>
-    <row r="57" ht="23.25" customHeight="1">
-      <c r="A57" s="61" t="s">
+    <row r="59" ht="25.5" customHeight="1">
+      <c r="A59" s="51" t="s">
         <v>834</v>
       </c>
     </row>
-    <row r="58" ht="26.25" customHeight="1">
-      <c r="A58" s="61" t="s">
+    <row r="60" ht="33.0" customHeight="1">
+      <c r="A60" s="51" t="s">
         <v>835</v>
       </c>
     </row>
-    <row r="59" ht="25.5" customHeight="1">
-      <c r="A59" s="61" t="s">
+    <row r="61" ht="38.25" customHeight="1">
+      <c r="A61" s="51" t="s">
         <v>836</v>
       </c>
     </row>
-    <row r="60" ht="33.0" customHeight="1">
-      <c r="A60" s="61" t="s">
+    <row r="62" ht="39.75" customHeight="1">
+      <c r="A62" s="51" t="s">
         <v>837</v>
       </c>
     </row>
-    <row r="61" ht="38.25" customHeight="1">
-      <c r="A61" s="61" t="s">
+    <row r="63" ht="41.25" customHeight="1">
+      <c r="A63" s="51" t="s">
         <v>838</v>
       </c>
     </row>
-    <row r="62" ht="39.75" customHeight="1">
-      <c r="A62" s="61" t="s">
+    <row r="64" ht="29.25" customHeight="1">
+      <c r="A64" s="51" t="s">
         <v>839</v>
       </c>
     </row>
-    <row r="63" ht="41.25" customHeight="1">
-      <c r="A63" s="61" t="s">
+    <row r="65" ht="40.5" customHeight="1">
+      <c r="A65" s="51" t="s">
         <v>840</v>
       </c>
     </row>
-    <row r="64" ht="29.25" customHeight="1">
-      <c r="A64" s="61" t="s">
+    <row r="66" ht="42.0" customHeight="1">
+      <c r="A66" s="51" t="s">
         <v>841</v>
       </c>
     </row>
-    <row r="65" ht="40.5" customHeight="1">
-      <c r="A65" s="61" t="s">
+    <row r="67" ht="25.5" customHeight="1">
+      <c r="A67" s="51" t="s">
         <v>842</v>
       </c>
     </row>
-    <row r="66" ht="42.0" customHeight="1">
-      <c r="A66" s="61" t="s">
+    <row r="68" ht="36.0" customHeight="1">
+      <c r="A68" s="51" t="s">
         <v>843</v>
       </c>
     </row>
-    <row r="67" ht="25.5" customHeight="1">
-      <c r="A67" s="61" t="s">
+    <row r="69" ht="32.25" customHeight="1">
+      <c r="A69" s="51" t="s">
         <v>844</v>
       </c>
     </row>
-    <row r="68" ht="36.0" customHeight="1">
-      <c r="A68" s="61" t="s">
+    <row r="70" ht="31.5" customHeight="1">
+      <c r="A70" s="51" t="s">
         <v>845</v>
       </c>
     </row>
-    <row r="69" ht="32.25" customHeight="1">
-      <c r="A69" s="61" t="s">
+    <row r="71" ht="30.0" customHeight="1">
+      <c r="A71" s="51" t="s">
         <v>846</v>
       </c>
     </row>
-    <row r="70" ht="31.5" customHeight="1">
-      <c r="A70" s="61" t="s">
+    <row r="72" ht="30.75" customHeight="1">
+      <c r="A72" s="51" t="s">
         <v>847</v>
-      </c>
-    </row>
-    <row r="71" ht="30.0" customHeight="1">
-      <c r="A71" s="61" t="s">
-        <v>848</v>
-      </c>
-    </row>
-    <row r="72" ht="30.75" customHeight="1">
-      <c r="A72" s="61" t="s">
-        <v>849</v>
       </c>
     </row>
   </sheetData>
@@ -17172,2299 +17121,2299 @@
   </cols>
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
-      <c r="A1" s="63" t="s">
+      <c r="A1" s="53" t="s">
+        <v>848</v>
+      </c>
+      <c r="B1" s="53" t="s">
+        <v>849</v>
+      </c>
+      <c r="C1" s="54" t="s">
+        <v>2</v>
+      </c>
+      <c r="D1" s="54" t="s">
+        <v>3</v>
+      </c>
+      <c r="E1" s="54" t="s">
+        <v>4</v>
+      </c>
+      <c r="F1" s="55" t="s">
+        <v>5</v>
+      </c>
+      <c r="G1" s="54" t="s">
+        <v>6</v>
+      </c>
+      <c r="H1" s="54" t="s">
+        <v>7</v>
+      </c>
+      <c r="I1" s="54" t="s">
+        <v>8</v>
+      </c>
+      <c r="J1" s="54" t="s">
+        <v>9</v>
+      </c>
+      <c r="K1" s="54" t="s">
+        <v>10</v>
+      </c>
+      <c r="L1" s="54" t="s">
+        <v>11</v>
+      </c>
+      <c r="M1" s="54" t="s">
+        <v>776</v>
+      </c>
+      <c r="N1" s="56"/>
+      <c r="O1" s="50"/>
+      <c r="P1" s="50"/>
+      <c r="Q1" s="50"/>
+      <c r="R1" s="50"/>
+      <c r="S1" s="50"/>
+    </row>
+    <row r="2" ht="33.75" customHeight="1">
+      <c r="A2" s="57" t="s">
         <v>850</v>
       </c>
-      <c r="B1" s="63" t="s">
+      <c r="B2" s="58"/>
+      <c r="C2" s="58"/>
+      <c r="D2" s="58"/>
+      <c r="E2" s="58"/>
+      <c r="F2" s="58"/>
+      <c r="G2" s="58"/>
+      <c r="H2" s="58"/>
+      <c r="I2" s="58"/>
+      <c r="J2" s="58"/>
+      <c r="K2" s="58"/>
+      <c r="L2" s="58"/>
+      <c r="M2" s="58"/>
+      <c r="N2" s="58"/>
+    </row>
+    <row r="3" ht="31.5" customHeight="1">
+      <c r="A3" s="57" t="s">
         <v>851</v>
       </c>
-      <c r="C1" s="64" t="s">
-        <v>2</v>
-      </c>
-      <c r="D1" s="64" t="s">
-        <v>3</v>
-      </c>
-      <c r="E1" s="64" t="s">
-        <v>4</v>
-      </c>
-      <c r="F1" s="65" t="s">
-        <v>5</v>
-      </c>
-      <c r="G1" s="64" t="s">
-        <v>6</v>
-      </c>
-      <c r="H1" s="64" t="s">
-        <v>7</v>
-      </c>
-      <c r="I1" s="64" t="s">
-        <v>8</v>
-      </c>
-      <c r="J1" s="64" t="s">
-        <v>9</v>
-      </c>
-      <c r="K1" s="64" t="s">
-        <v>10</v>
-      </c>
-      <c r="L1" s="64" t="s">
-        <v>11</v>
-      </c>
-      <c r="M1" s="64" t="s">
-        <v>778</v>
-      </c>
-      <c r="N1" s="66"/>
-      <c r="O1" s="60"/>
-      <c r="P1" s="60"/>
-      <c r="Q1" s="60"/>
-      <c r="R1" s="60"/>
-      <c r="S1" s="60"/>
-    </row>
-    <row r="2" ht="33.75" customHeight="1">
-      <c r="A2" s="67" t="s">
+      <c r="B3" s="58"/>
+      <c r="C3" s="58"/>
+      <c r="D3" s="58"/>
+      <c r="E3" s="58"/>
+      <c r="F3" s="58"/>
+      <c r="G3" s="58"/>
+      <c r="H3" s="58"/>
+      <c r="I3" s="58"/>
+      <c r="J3" s="58"/>
+      <c r="K3" s="58"/>
+      <c r="L3" s="58"/>
+      <c r="M3" s="58"/>
+      <c r="N3" s="58"/>
+    </row>
+    <row r="4" ht="30.0" customHeight="1">
+      <c r="A4" s="57" t="s">
         <v>852</v>
       </c>
-      <c r="B2" s="68"/>
-      <c r="C2" s="68"/>
-      <c r="D2" s="68"/>
-      <c r="E2" s="68"/>
-      <c r="F2" s="68"/>
-      <c r="G2" s="68"/>
-      <c r="H2" s="68"/>
-      <c r="I2" s="68"/>
-      <c r="J2" s="68"/>
-      <c r="K2" s="68"/>
-      <c r="L2" s="68"/>
-      <c r="M2" s="68"/>
-      <c r="N2" s="68"/>
-    </row>
-    <row r="3" ht="31.5" customHeight="1">
-      <c r="A3" s="67" t="s">
+      <c r="B4" s="58"/>
+      <c r="C4" s="58"/>
+      <c r="D4" s="58"/>
+      <c r="E4" s="58"/>
+      <c r="F4" s="58"/>
+      <c r="G4" s="58"/>
+      <c r="H4" s="58"/>
+      <c r="I4" s="58"/>
+      <c r="J4" s="58"/>
+      <c r="K4" s="58"/>
+      <c r="L4" s="58"/>
+      <c r="M4" s="58"/>
+      <c r="N4" s="58"/>
+    </row>
+    <row r="5" ht="36.0" customHeight="1">
+      <c r="A5" s="57" t="s">
         <v>853</v>
       </c>
-      <c r="B3" s="68"/>
-      <c r="C3" s="68"/>
-      <c r="D3" s="68"/>
-      <c r="E3" s="68"/>
-      <c r="F3" s="68"/>
-      <c r="G3" s="68"/>
-      <c r="H3" s="68"/>
-      <c r="I3" s="68"/>
-      <c r="J3" s="68"/>
-      <c r="K3" s="68"/>
-      <c r="L3" s="68"/>
-      <c r="M3" s="68"/>
-      <c r="N3" s="68"/>
-    </row>
-    <row r="4" ht="30.0" customHeight="1">
-      <c r="A4" s="67" t="s">
+      <c r="B5" s="58"/>
+      <c r="C5" s="58"/>
+      <c r="D5" s="58"/>
+      <c r="E5" s="58"/>
+      <c r="F5" s="58"/>
+      <c r="G5" s="58"/>
+      <c r="H5" s="58"/>
+      <c r="I5" s="58"/>
+      <c r="J5" s="58"/>
+      <c r="K5" s="58"/>
+      <c r="L5" s="58"/>
+      <c r="M5" s="58"/>
+      <c r="N5" s="58"/>
+    </row>
+    <row r="6" ht="27.0" customHeight="1">
+      <c r="A6" s="57" t="s">
         <v>854</v>
       </c>
-      <c r="B4" s="68"/>
-      <c r="C4" s="68"/>
-      <c r="D4" s="68"/>
-      <c r="E4" s="68"/>
-      <c r="F4" s="68"/>
-      <c r="G4" s="68"/>
-      <c r="H4" s="68"/>
-      <c r="I4" s="68"/>
-      <c r="J4" s="68"/>
-      <c r="K4" s="68"/>
-      <c r="L4" s="68"/>
-      <c r="M4" s="68"/>
-      <c r="N4" s="68"/>
-    </row>
-    <row r="5" ht="36.0" customHeight="1">
-      <c r="A5" s="67" t="s">
+      <c r="B6" s="58"/>
+      <c r="C6" s="58"/>
+      <c r="D6" s="58"/>
+      <c r="E6" s="58"/>
+      <c r="F6" s="58"/>
+      <c r="G6" s="58"/>
+      <c r="H6" s="58"/>
+      <c r="I6" s="58"/>
+      <c r="J6" s="58"/>
+      <c r="K6" s="58"/>
+      <c r="L6" s="58"/>
+      <c r="M6" s="58"/>
+      <c r="N6" s="58"/>
+    </row>
+    <row r="7" ht="36.0" customHeight="1">
+      <c r="A7" s="57" t="s">
         <v>855</v>
       </c>
-      <c r="B5" s="68"/>
-      <c r="C5" s="68"/>
-      <c r="D5" s="68"/>
-      <c r="E5" s="68"/>
-      <c r="F5" s="68"/>
-      <c r="G5" s="68"/>
-      <c r="H5" s="68"/>
-      <c r="I5" s="68"/>
-      <c r="J5" s="68"/>
-      <c r="K5" s="68"/>
-      <c r="L5" s="68"/>
-      <c r="M5" s="68"/>
-      <c r="N5" s="68"/>
-    </row>
-    <row r="6" ht="27.0" customHeight="1">
-      <c r="A6" s="67" t="s">
+      <c r="B7" s="58"/>
+      <c r="C7" s="58"/>
+      <c r="D7" s="58"/>
+      <c r="E7" s="58"/>
+      <c r="F7" s="58"/>
+      <c r="G7" s="58"/>
+      <c r="H7" s="58"/>
+      <c r="I7" s="58"/>
+      <c r="J7" s="58"/>
+      <c r="K7" s="58"/>
+      <c r="L7" s="58"/>
+      <c r="M7" s="58"/>
+      <c r="N7" s="58"/>
+    </row>
+    <row r="8" ht="33.0" customHeight="1">
+      <c r="A8" s="57" t="s">
         <v>856</v>
       </c>
-      <c r="B6" s="68"/>
-      <c r="C6" s="68"/>
-      <c r="D6" s="68"/>
-      <c r="E6" s="68"/>
-      <c r="F6" s="68"/>
-      <c r="G6" s="68"/>
-      <c r="H6" s="68"/>
-      <c r="I6" s="68"/>
-      <c r="J6" s="68"/>
-      <c r="K6" s="68"/>
-      <c r="L6" s="68"/>
-      <c r="M6" s="68"/>
-      <c r="N6" s="68"/>
-    </row>
-    <row r="7" ht="36.0" customHeight="1">
-      <c r="A7" s="67" t="s">
+      <c r="B8" s="58"/>
+      <c r="C8" s="58"/>
+      <c r="D8" s="58"/>
+      <c r="E8" s="58"/>
+      <c r="F8" s="58"/>
+      <c r="G8" s="58"/>
+      <c r="H8" s="58"/>
+      <c r="I8" s="58"/>
+      <c r="J8" s="58"/>
+      <c r="K8" s="58"/>
+      <c r="L8" s="58"/>
+      <c r="M8" s="58"/>
+      <c r="N8" s="58"/>
+    </row>
+    <row r="9" ht="34.5" customHeight="1">
+      <c r="A9" s="57" t="s">
         <v>857</v>
       </c>
-      <c r="B7" s="68"/>
-      <c r="C7" s="68"/>
-      <c r="D7" s="68"/>
-      <c r="E7" s="68"/>
-      <c r="F7" s="68"/>
-      <c r="G7" s="68"/>
-      <c r="H7" s="68"/>
-      <c r="I7" s="68"/>
-      <c r="J7" s="68"/>
-      <c r="K7" s="68"/>
-      <c r="L7" s="68"/>
-      <c r="M7" s="68"/>
-      <c r="N7" s="68"/>
-    </row>
-    <row r="8" ht="33.0" customHeight="1">
-      <c r="A8" s="67" t="s">
+      <c r="B9" s="58"/>
+      <c r="C9" s="58"/>
+      <c r="D9" s="58"/>
+      <c r="E9" s="58"/>
+      <c r="F9" s="58"/>
+      <c r="G9" s="58"/>
+      <c r="H9" s="58"/>
+      <c r="I9" s="58"/>
+      <c r="J9" s="58"/>
+      <c r="K9" s="58"/>
+      <c r="L9" s="58"/>
+      <c r="M9" s="58"/>
+      <c r="N9" s="58"/>
+    </row>
+    <row r="10" ht="32.25" customHeight="1">
+      <c r="A10" s="57" t="s">
         <v>858</v>
       </c>
-      <c r="B8" s="68"/>
-      <c r="C8" s="68"/>
-      <c r="D8" s="68"/>
-      <c r="E8" s="68"/>
-      <c r="F8" s="68"/>
-      <c r="G8" s="68"/>
-      <c r="H8" s="68"/>
-      <c r="I8" s="68"/>
-      <c r="J8" s="68"/>
-      <c r="K8" s="68"/>
-      <c r="L8" s="68"/>
-      <c r="M8" s="68"/>
-      <c r="N8" s="68"/>
-    </row>
-    <row r="9" ht="34.5" customHeight="1">
-      <c r="A9" s="67" t="s">
+      <c r="B10" s="58"/>
+      <c r="C10" s="58"/>
+      <c r="D10" s="58"/>
+      <c r="E10" s="58"/>
+      <c r="F10" s="58"/>
+      <c r="G10" s="58"/>
+      <c r="H10" s="58"/>
+      <c r="I10" s="58"/>
+      <c r="J10" s="58"/>
+      <c r="K10" s="58"/>
+      <c r="L10" s="58"/>
+      <c r="M10" s="58"/>
+      <c r="N10" s="58"/>
+    </row>
+    <row r="11" ht="26.25" customHeight="1">
+      <c r="A11" s="57" t="s">
         <v>859</v>
       </c>
-      <c r="B9" s="68"/>
-      <c r="C9" s="68"/>
-      <c r="D9" s="68"/>
-      <c r="E9" s="68"/>
-      <c r="F9" s="68"/>
-      <c r="G9" s="68"/>
-      <c r="H9" s="68"/>
-      <c r="I9" s="68"/>
-      <c r="J9" s="68"/>
-      <c r="K9" s="68"/>
-      <c r="L9" s="68"/>
-      <c r="M9" s="68"/>
-      <c r="N9" s="68"/>
-    </row>
-    <row r="10" ht="32.25" customHeight="1">
-      <c r="A10" s="67" t="s">
+      <c r="B11" s="58"/>
+      <c r="C11" s="58"/>
+      <c r="D11" s="58"/>
+      <c r="E11" s="58"/>
+      <c r="F11" s="58"/>
+      <c r="G11" s="58"/>
+      <c r="H11" s="58"/>
+      <c r="I11" s="58"/>
+      <c r="J11" s="58"/>
+      <c r="K11" s="58"/>
+      <c r="L11" s="58"/>
+      <c r="M11" s="58"/>
+      <c r="N11" s="58"/>
+    </row>
+    <row r="12" ht="41.25" customHeight="1">
+      <c r="A12" s="57" t="s">
         <v>860</v>
       </c>
-      <c r="B10" s="68"/>
-      <c r="C10" s="68"/>
-      <c r="D10" s="68"/>
-      <c r="E10" s="68"/>
-      <c r="F10" s="68"/>
-      <c r="G10" s="68"/>
-      <c r="H10" s="68"/>
-      <c r="I10" s="68"/>
-      <c r="J10" s="68"/>
-      <c r="K10" s="68"/>
-      <c r="L10" s="68"/>
-      <c r="M10" s="68"/>
-      <c r="N10" s="68"/>
-    </row>
-    <row r="11" ht="26.25" customHeight="1">
-      <c r="A11" s="67" t="s">
+      <c r="B12" s="58"/>
+      <c r="C12" s="58"/>
+      <c r="D12" s="58"/>
+      <c r="E12" s="58"/>
+      <c r="F12" s="58"/>
+      <c r="G12" s="58"/>
+      <c r="H12" s="58"/>
+      <c r="I12" s="58"/>
+      <c r="J12" s="58"/>
+      <c r="K12" s="58"/>
+      <c r="L12" s="58"/>
+      <c r="M12" s="58"/>
+      <c r="N12" s="58"/>
+    </row>
+    <row r="13" ht="29.25" customHeight="1">
+      <c r="A13" s="57" t="s">
         <v>861</v>
       </c>
-      <c r="B11" s="68"/>
-      <c r="C11" s="68"/>
-      <c r="D11" s="68"/>
-      <c r="E11" s="68"/>
-      <c r="F11" s="68"/>
-      <c r="G11" s="68"/>
-      <c r="H11" s="68"/>
-      <c r="I11" s="68"/>
-      <c r="J11" s="68"/>
-      <c r="K11" s="68"/>
-      <c r="L11" s="68"/>
-      <c r="M11" s="68"/>
-      <c r="N11" s="68"/>
-    </row>
-    <row r="12" ht="41.25" customHeight="1">
-      <c r="A12" s="67" t="s">
+      <c r="B13" s="58"/>
+      <c r="C13" s="58"/>
+      <c r="D13" s="58"/>
+      <c r="E13" s="58"/>
+      <c r="F13" s="58"/>
+      <c r="G13" s="58"/>
+      <c r="H13" s="58"/>
+      <c r="I13" s="58"/>
+      <c r="J13" s="58"/>
+      <c r="K13" s="58"/>
+      <c r="L13" s="58"/>
+      <c r="M13" s="58"/>
+      <c r="N13" s="58"/>
+    </row>
+    <row r="14" ht="36.75" customHeight="1">
+      <c r="A14" s="57" t="s">
         <v>862</v>
       </c>
-      <c r="B12" s="68"/>
-      <c r="C12" s="68"/>
-      <c r="D12" s="68"/>
-      <c r="E12" s="68"/>
-      <c r="F12" s="68"/>
-      <c r="G12" s="68"/>
-      <c r="H12" s="68"/>
-      <c r="I12" s="68"/>
-      <c r="J12" s="68"/>
-      <c r="K12" s="68"/>
-      <c r="L12" s="68"/>
-      <c r="M12" s="68"/>
-      <c r="N12" s="68"/>
-    </row>
-    <row r="13" ht="29.25" customHeight="1">
-      <c r="A13" s="67" t="s">
+      <c r="B14" s="58"/>
+      <c r="C14" s="58"/>
+      <c r="D14" s="58"/>
+      <c r="E14" s="58"/>
+      <c r="F14" s="58"/>
+      <c r="G14" s="58"/>
+      <c r="H14" s="58"/>
+      <c r="I14" s="58"/>
+      <c r="J14" s="58"/>
+      <c r="K14" s="58"/>
+      <c r="L14" s="58"/>
+      <c r="M14" s="58"/>
+      <c r="N14" s="58"/>
+    </row>
+    <row r="15" ht="37.5" customHeight="1">
+      <c r="A15" s="57" t="s">
         <v>863</v>
       </c>
-      <c r="B13" s="68"/>
-      <c r="C13" s="68"/>
-      <c r="D13" s="68"/>
-      <c r="E13" s="68"/>
-      <c r="F13" s="68"/>
-      <c r="G13" s="68"/>
-      <c r="H13" s="68"/>
-      <c r="I13" s="68"/>
-      <c r="J13" s="68"/>
-      <c r="K13" s="68"/>
-      <c r="L13" s="68"/>
-      <c r="M13" s="68"/>
-      <c r="N13" s="68"/>
-    </row>
-    <row r="14" ht="36.75" customHeight="1">
-      <c r="A14" s="67" t="s">
+      <c r="B15" s="58"/>
+      <c r="C15" s="58"/>
+      <c r="D15" s="58"/>
+      <c r="E15" s="58"/>
+      <c r="F15" s="58"/>
+      <c r="G15" s="58"/>
+      <c r="H15" s="58"/>
+      <c r="I15" s="58"/>
+      <c r="J15" s="58"/>
+      <c r="K15" s="58"/>
+      <c r="L15" s="58"/>
+      <c r="M15" s="58"/>
+      <c r="N15" s="58"/>
+    </row>
+    <row r="16" ht="37.5" customHeight="1">
+      <c r="A16" s="57" t="s">
         <v>864</v>
       </c>
-      <c r="B14" s="68"/>
-      <c r="C14" s="68"/>
-      <c r="D14" s="68"/>
-      <c r="E14" s="68"/>
-      <c r="F14" s="68"/>
-      <c r="G14" s="68"/>
-      <c r="H14" s="68"/>
-      <c r="I14" s="68"/>
-      <c r="J14" s="68"/>
-      <c r="K14" s="68"/>
-      <c r="L14" s="68"/>
-      <c r="M14" s="68"/>
-      <c r="N14" s="68"/>
-    </row>
-    <row r="15" ht="37.5" customHeight="1">
-      <c r="A15" s="67" t="s">
+      <c r="B16" s="58"/>
+      <c r="C16" s="58"/>
+      <c r="D16" s="58"/>
+      <c r="E16" s="58"/>
+      <c r="F16" s="58"/>
+      <c r="G16" s="58"/>
+      <c r="H16" s="58"/>
+      <c r="I16" s="58"/>
+      <c r="J16" s="58"/>
+      <c r="K16" s="58"/>
+      <c r="L16" s="58"/>
+      <c r="M16" s="58"/>
+      <c r="N16" s="58"/>
+    </row>
+    <row r="17" ht="33.0" customHeight="1">
+      <c r="A17" s="57" t="s">
         <v>865</v>
       </c>
-      <c r="B15" s="68"/>
-      <c r="C15" s="68"/>
-      <c r="D15" s="68"/>
-      <c r="E15" s="68"/>
-      <c r="F15" s="68"/>
-      <c r="G15" s="68"/>
-      <c r="H15" s="68"/>
-      <c r="I15" s="68"/>
-      <c r="J15" s="68"/>
-      <c r="K15" s="68"/>
-      <c r="L15" s="68"/>
-      <c r="M15" s="68"/>
-      <c r="N15" s="68"/>
-    </row>
-    <row r="16" ht="37.5" customHeight="1">
-      <c r="A16" s="67" t="s">
+      <c r="B17" s="58"/>
+      <c r="C17" s="58"/>
+      <c r="D17" s="58"/>
+      <c r="E17" s="58"/>
+      <c r="F17" s="58"/>
+      <c r="G17" s="58"/>
+      <c r="H17" s="58"/>
+      <c r="I17" s="58"/>
+      <c r="J17" s="58"/>
+      <c r="K17" s="58"/>
+      <c r="L17" s="58"/>
+      <c r="M17" s="58"/>
+      <c r="N17" s="58"/>
+    </row>
+    <row r="18" ht="32.25" customHeight="1">
+      <c r="A18" s="57" t="s">
         <v>866</v>
       </c>
-      <c r="B16" s="68"/>
-      <c r="C16" s="68"/>
-      <c r="D16" s="68"/>
-      <c r="E16" s="68"/>
-      <c r="F16" s="68"/>
-      <c r="G16" s="68"/>
-      <c r="H16" s="68"/>
-      <c r="I16" s="68"/>
-      <c r="J16" s="68"/>
-      <c r="K16" s="68"/>
-      <c r="L16" s="68"/>
-      <c r="M16" s="68"/>
-      <c r="N16" s="68"/>
-    </row>
-    <row r="17" ht="33.0" customHeight="1">
-      <c r="A17" s="67" t="s">
+      <c r="B18" s="58"/>
+      <c r="C18" s="58"/>
+      <c r="D18" s="58"/>
+      <c r="E18" s="58"/>
+      <c r="F18" s="58"/>
+      <c r="G18" s="58"/>
+      <c r="H18" s="58"/>
+      <c r="I18" s="58"/>
+      <c r="J18" s="58"/>
+      <c r="K18" s="58"/>
+      <c r="L18" s="58"/>
+      <c r="M18" s="58"/>
+      <c r="N18" s="58"/>
+    </row>
+    <row r="19" ht="27.75" customHeight="1">
+      <c r="A19" s="57" t="s">
         <v>867</v>
       </c>
-      <c r="B17" s="68"/>
-      <c r="C17" s="68"/>
-      <c r="D17" s="68"/>
-      <c r="E17" s="68"/>
-      <c r="F17" s="68"/>
-      <c r="G17" s="68"/>
-      <c r="H17" s="68"/>
-      <c r="I17" s="68"/>
-      <c r="J17" s="68"/>
-      <c r="K17" s="68"/>
-      <c r="L17" s="68"/>
-      <c r="M17" s="68"/>
-      <c r="N17" s="68"/>
-    </row>
-    <row r="18" ht="32.25" customHeight="1">
-      <c r="A18" s="67" t="s">
+      <c r="B19" s="58"/>
+      <c r="C19" s="58"/>
+      <c r="D19" s="58"/>
+      <c r="E19" s="58"/>
+      <c r="F19" s="58"/>
+      <c r="G19" s="58"/>
+      <c r="H19" s="58"/>
+      <c r="I19" s="58"/>
+      <c r="J19" s="58"/>
+      <c r="K19" s="58"/>
+      <c r="L19" s="58"/>
+      <c r="M19" s="58"/>
+      <c r="N19" s="58"/>
+    </row>
+    <row r="20" ht="36.75" customHeight="1">
+      <c r="A20" s="57" t="s">
         <v>868</v>
       </c>
-      <c r="B18" s="68"/>
-      <c r="C18" s="68"/>
-      <c r="D18" s="68"/>
-      <c r="E18" s="68"/>
-      <c r="F18" s="68"/>
-      <c r="G18" s="68"/>
-      <c r="H18" s="68"/>
-      <c r="I18" s="68"/>
-      <c r="J18" s="68"/>
-      <c r="K18" s="68"/>
-      <c r="L18" s="68"/>
-      <c r="M18" s="68"/>
-      <c r="N18" s="68"/>
-    </row>
-    <row r="19" ht="27.75" customHeight="1">
-      <c r="A19" s="67" t="s">
+      <c r="B20" s="58"/>
+      <c r="C20" s="58"/>
+      <c r="D20" s="58"/>
+      <c r="E20" s="58"/>
+      <c r="F20" s="58"/>
+      <c r="G20" s="58"/>
+      <c r="H20" s="58"/>
+      <c r="I20" s="58"/>
+      <c r="J20" s="58"/>
+      <c r="K20" s="58"/>
+      <c r="L20" s="58"/>
+      <c r="M20" s="58"/>
+      <c r="N20" s="58"/>
+    </row>
+    <row r="21" ht="44.25" customHeight="1">
+      <c r="A21" s="57" t="s">
         <v>869</v>
       </c>
-      <c r="B19" s="68"/>
-      <c r="C19" s="68"/>
-      <c r="D19" s="68"/>
-      <c r="E19" s="68"/>
-      <c r="F19" s="68"/>
-      <c r="G19" s="68"/>
-      <c r="H19" s="68"/>
-      <c r="I19" s="68"/>
-      <c r="J19" s="68"/>
-      <c r="K19" s="68"/>
-      <c r="L19" s="68"/>
-      <c r="M19" s="68"/>
-      <c r="N19" s="68"/>
-    </row>
-    <row r="20" ht="36.75" customHeight="1">
-      <c r="A20" s="67" t="s">
+      <c r="B21" s="58"/>
+      <c r="C21" s="58"/>
+      <c r="D21" s="58"/>
+      <c r="E21" s="58"/>
+      <c r="F21" s="58"/>
+      <c r="G21" s="58"/>
+      <c r="H21" s="58"/>
+      <c r="I21" s="58"/>
+      <c r="J21" s="58"/>
+      <c r="K21" s="58"/>
+      <c r="L21" s="58"/>
+      <c r="M21" s="58"/>
+      <c r="N21" s="58"/>
+    </row>
+    <row r="22" ht="36.75" customHeight="1">
+      <c r="A22" s="57" t="s">
         <v>870</v>
       </c>
-      <c r="B20" s="68"/>
-      <c r="C20" s="68"/>
-      <c r="D20" s="68"/>
-      <c r="E20" s="68"/>
-      <c r="F20" s="68"/>
-      <c r="G20" s="68"/>
-      <c r="H20" s="68"/>
-      <c r="I20" s="68"/>
-      <c r="J20" s="68"/>
-      <c r="K20" s="68"/>
-      <c r="L20" s="68"/>
-      <c r="M20" s="68"/>
-      <c r="N20" s="68"/>
-    </row>
-    <row r="21" ht="44.25" customHeight="1">
-      <c r="A21" s="67" t="s">
+      <c r="B22" s="58"/>
+      <c r="C22" s="58"/>
+      <c r="D22" s="58"/>
+      <c r="E22" s="58"/>
+      <c r="F22" s="58"/>
+      <c r="G22" s="58"/>
+      <c r="H22" s="58"/>
+      <c r="I22" s="58"/>
+      <c r="J22" s="58"/>
+      <c r="K22" s="58"/>
+      <c r="L22" s="58"/>
+      <c r="M22" s="58"/>
+      <c r="N22" s="58"/>
+    </row>
+    <row r="23" ht="31.5" customHeight="1">
+      <c r="A23" s="57" t="s">
         <v>871</v>
       </c>
-      <c r="B21" s="68"/>
-      <c r="C21" s="68"/>
-      <c r="D21" s="68"/>
-      <c r="E21" s="68"/>
-      <c r="F21" s="68"/>
-      <c r="G21" s="68"/>
-      <c r="H21" s="68"/>
-      <c r="I21" s="68"/>
-      <c r="J21" s="68"/>
-      <c r="K21" s="68"/>
-      <c r="L21" s="68"/>
-      <c r="M21" s="68"/>
-      <c r="N21" s="68"/>
-    </row>
-    <row r="22" ht="36.75" customHeight="1">
-      <c r="A22" s="67" t="s">
+      <c r="B23" s="58"/>
+      <c r="C23" s="58"/>
+      <c r="D23" s="58"/>
+      <c r="E23" s="58"/>
+      <c r="F23" s="58"/>
+      <c r="G23" s="58"/>
+      <c r="H23" s="58"/>
+      <c r="I23" s="58"/>
+      <c r="J23" s="58"/>
+      <c r="K23" s="58"/>
+      <c r="L23" s="58"/>
+      <c r="M23" s="58"/>
+      <c r="N23" s="58"/>
+    </row>
+    <row r="24" ht="33.0" customHeight="1">
+      <c r="A24" s="57" t="s">
         <v>872</v>
       </c>
-      <c r="B22" s="68"/>
-      <c r="C22" s="68"/>
-      <c r="D22" s="68"/>
-      <c r="E22" s="68"/>
-      <c r="F22" s="68"/>
-      <c r="G22" s="68"/>
-      <c r="H22" s="68"/>
-      <c r="I22" s="68"/>
-      <c r="J22" s="68"/>
-      <c r="K22" s="68"/>
-      <c r="L22" s="68"/>
-      <c r="M22" s="68"/>
-      <c r="N22" s="68"/>
-    </row>
-    <row r="23" ht="31.5" customHeight="1">
-      <c r="A23" s="67" t="s">
+      <c r="B24" s="58"/>
+      <c r="C24" s="58"/>
+      <c r="D24" s="58"/>
+      <c r="E24" s="58"/>
+      <c r="F24" s="58"/>
+      <c r="G24" s="58"/>
+      <c r="H24" s="58"/>
+      <c r="I24" s="58"/>
+      <c r="J24" s="58"/>
+      <c r="K24" s="58"/>
+      <c r="L24" s="58"/>
+      <c r="M24" s="58"/>
+      <c r="N24" s="58"/>
+    </row>
+    <row r="25" ht="30.0" customHeight="1">
+      <c r="A25" s="57" t="s">
         <v>873</v>
       </c>
-      <c r="B23" s="68"/>
-      <c r="C23" s="68"/>
-      <c r="D23" s="68"/>
-      <c r="E23" s="68"/>
-      <c r="F23" s="68"/>
-      <c r="G23" s="68"/>
-      <c r="H23" s="68"/>
-      <c r="I23" s="68"/>
-      <c r="J23" s="68"/>
-      <c r="K23" s="68"/>
-      <c r="L23" s="68"/>
-      <c r="M23" s="68"/>
-      <c r="N23" s="68"/>
-    </row>
-    <row r="24" ht="33.0" customHeight="1">
-      <c r="A24" s="67" t="s">
+      <c r="B25" s="58"/>
+      <c r="C25" s="58"/>
+      <c r="D25" s="58"/>
+      <c r="E25" s="58"/>
+      <c r="F25" s="58"/>
+      <c r="G25" s="58"/>
+      <c r="H25" s="58"/>
+      <c r="I25" s="58"/>
+      <c r="J25" s="58"/>
+      <c r="K25" s="58"/>
+      <c r="L25" s="58"/>
+      <c r="M25" s="58"/>
+      <c r="N25" s="58"/>
+    </row>
+    <row r="26" ht="27.0" customHeight="1">
+      <c r="A26" s="57" t="s">
         <v>874</v>
       </c>
-      <c r="B24" s="68"/>
-      <c r="C24" s="68"/>
-      <c r="D24" s="68"/>
-      <c r="E24" s="68"/>
-      <c r="F24" s="68"/>
-      <c r="G24" s="68"/>
-      <c r="H24" s="68"/>
-      <c r="I24" s="68"/>
-      <c r="J24" s="68"/>
-      <c r="K24" s="68"/>
-      <c r="L24" s="68"/>
-      <c r="M24" s="68"/>
-      <c r="N24" s="68"/>
-    </row>
-    <row r="25" ht="30.0" customHeight="1">
-      <c r="A25" s="67" t="s">
+      <c r="B26" s="58"/>
+      <c r="C26" s="58"/>
+      <c r="D26" s="58"/>
+      <c r="E26" s="58"/>
+      <c r="F26" s="58"/>
+      <c r="G26" s="58"/>
+      <c r="H26" s="58"/>
+      <c r="I26" s="58"/>
+      <c r="J26" s="58"/>
+      <c r="K26" s="58"/>
+      <c r="L26" s="58"/>
+      <c r="M26" s="58"/>
+      <c r="N26" s="58"/>
+    </row>
+    <row r="27" ht="34.5" customHeight="1">
+      <c r="A27" s="57" t="s">
         <v>875</v>
       </c>
-      <c r="B25" s="68"/>
-      <c r="C25" s="68"/>
-      <c r="D25" s="68"/>
-      <c r="E25" s="68"/>
-      <c r="F25" s="68"/>
-      <c r="G25" s="68"/>
-      <c r="H25" s="68"/>
-      <c r="I25" s="68"/>
-      <c r="J25" s="68"/>
-      <c r="K25" s="68"/>
-      <c r="L25" s="68"/>
-      <c r="M25" s="68"/>
-      <c r="N25" s="68"/>
-    </row>
-    <row r="26" ht="27.0" customHeight="1">
-      <c r="A26" s="67" t="s">
+      <c r="B27" s="58"/>
+      <c r="C27" s="58"/>
+      <c r="D27" s="58"/>
+      <c r="E27" s="58"/>
+      <c r="F27" s="58"/>
+      <c r="G27" s="58"/>
+      <c r="H27" s="58"/>
+      <c r="I27" s="58"/>
+      <c r="J27" s="58"/>
+      <c r="K27" s="58"/>
+      <c r="L27" s="58"/>
+      <c r="M27" s="58"/>
+      <c r="N27" s="58"/>
+    </row>
+    <row r="28" ht="36.0" customHeight="1">
+      <c r="A28" s="57" t="s">
         <v>876</v>
       </c>
-      <c r="B26" s="68"/>
-      <c r="C26" s="68"/>
-      <c r="D26" s="68"/>
-      <c r="E26" s="68"/>
-      <c r="F26" s="68"/>
-      <c r="G26" s="68"/>
-      <c r="H26" s="68"/>
-      <c r="I26" s="68"/>
-      <c r="J26" s="68"/>
-      <c r="K26" s="68"/>
-      <c r="L26" s="68"/>
-      <c r="M26" s="68"/>
-      <c r="N26" s="68"/>
-    </row>
-    <row r="27" ht="34.5" customHeight="1">
-      <c r="A27" s="67" t="s">
+      <c r="B28" s="58"/>
+      <c r="C28" s="58"/>
+      <c r="D28" s="58"/>
+      <c r="E28" s="58"/>
+      <c r="F28" s="58"/>
+      <c r="G28" s="58"/>
+      <c r="H28" s="58"/>
+      <c r="I28" s="58"/>
+      <c r="J28" s="58"/>
+      <c r="K28" s="58"/>
+      <c r="L28" s="58"/>
+      <c r="M28" s="58"/>
+      <c r="N28" s="58"/>
+    </row>
+    <row r="29" ht="33.0" customHeight="1">
+      <c r="A29" s="57" t="s">
         <v>877</v>
       </c>
-      <c r="B27" s="68"/>
-      <c r="C27" s="68"/>
-      <c r="D27" s="68"/>
-      <c r="E27" s="68"/>
-      <c r="F27" s="68"/>
-      <c r="G27" s="68"/>
-      <c r="H27" s="68"/>
-      <c r="I27" s="68"/>
-      <c r="J27" s="68"/>
-      <c r="K27" s="68"/>
-      <c r="L27" s="68"/>
-      <c r="M27" s="68"/>
-      <c r="N27" s="68"/>
-    </row>
-    <row r="28" ht="36.0" customHeight="1">
-      <c r="A28" s="67" t="s">
+      <c r="B29" s="58"/>
+      <c r="C29" s="58"/>
+      <c r="D29" s="58"/>
+      <c r="E29" s="58"/>
+      <c r="F29" s="58"/>
+      <c r="G29" s="58"/>
+      <c r="H29" s="58"/>
+      <c r="I29" s="58"/>
+      <c r="J29" s="58"/>
+      <c r="K29" s="58"/>
+      <c r="L29" s="58"/>
+      <c r="M29" s="58"/>
+      <c r="N29" s="58"/>
+    </row>
+    <row r="30" ht="30.75" customHeight="1">
+      <c r="A30" s="57" t="s">
         <v>878</v>
       </c>
-      <c r="B28" s="68"/>
-      <c r="C28" s="68"/>
-      <c r="D28" s="68"/>
-      <c r="E28" s="68"/>
-      <c r="F28" s="68"/>
-      <c r="G28" s="68"/>
-      <c r="H28" s="68"/>
-      <c r="I28" s="68"/>
-      <c r="J28" s="68"/>
-      <c r="K28" s="68"/>
-      <c r="L28" s="68"/>
-      <c r="M28" s="68"/>
-      <c r="N28" s="68"/>
-    </row>
-    <row r="29" ht="33.0" customHeight="1">
-      <c r="A29" s="67" t="s">
+      <c r="B30" s="58"/>
+      <c r="C30" s="58"/>
+      <c r="D30" s="58"/>
+      <c r="E30" s="58"/>
+      <c r="F30" s="58"/>
+      <c r="G30" s="58"/>
+      <c r="H30" s="58"/>
+      <c r="I30" s="58"/>
+      <c r="J30" s="58"/>
+      <c r="K30" s="58"/>
+      <c r="L30" s="58"/>
+      <c r="M30" s="58"/>
+      <c r="N30" s="58"/>
+    </row>
+    <row r="31" ht="32.25" customHeight="1">
+      <c r="A31" s="57" t="s">
         <v>879</v>
       </c>
-      <c r="B29" s="68"/>
-      <c r="C29" s="68"/>
-      <c r="D29" s="68"/>
-      <c r="E29" s="68"/>
-      <c r="F29" s="68"/>
-      <c r="G29" s="68"/>
-      <c r="H29" s="68"/>
-      <c r="I29" s="68"/>
-      <c r="J29" s="68"/>
-      <c r="K29" s="68"/>
-      <c r="L29" s="68"/>
-      <c r="M29" s="68"/>
-      <c r="N29" s="68"/>
-    </row>
-    <row r="30" ht="30.75" customHeight="1">
-      <c r="A30" s="67" t="s">
+      <c r="B31" s="58"/>
+      <c r="C31" s="58"/>
+      <c r="D31" s="58"/>
+      <c r="E31" s="58"/>
+      <c r="F31" s="58"/>
+      <c r="G31" s="58"/>
+      <c r="H31" s="58"/>
+      <c r="I31" s="58"/>
+      <c r="J31" s="58"/>
+      <c r="K31" s="58"/>
+      <c r="L31" s="58"/>
+      <c r="M31" s="58"/>
+      <c r="N31" s="58"/>
+    </row>
+    <row r="32" ht="38.25" customHeight="1">
+      <c r="A32" s="57" t="s">
         <v>880</v>
       </c>
-      <c r="B30" s="68"/>
-      <c r="C30" s="68"/>
-      <c r="D30" s="68"/>
-      <c r="E30" s="68"/>
-      <c r="F30" s="68"/>
-      <c r="G30" s="68"/>
-      <c r="H30" s="68"/>
-      <c r="I30" s="68"/>
-      <c r="J30" s="68"/>
-      <c r="K30" s="68"/>
-      <c r="L30" s="68"/>
-      <c r="M30" s="68"/>
-      <c r="N30" s="68"/>
-    </row>
-    <row r="31" ht="32.25" customHeight="1">
-      <c r="A31" s="67" t="s">
+      <c r="B32" s="58"/>
+      <c r="C32" s="58"/>
+      <c r="D32" s="58"/>
+      <c r="E32" s="58"/>
+      <c r="F32" s="58"/>
+      <c r="G32" s="58"/>
+      <c r="H32" s="58"/>
+      <c r="I32" s="58"/>
+      <c r="J32" s="58"/>
+      <c r="K32" s="58"/>
+      <c r="L32" s="58"/>
+      <c r="M32" s="58"/>
+      <c r="N32" s="58"/>
+    </row>
+    <row r="33" ht="33.75" customHeight="1">
+      <c r="A33" s="57" t="s">
         <v>881</v>
       </c>
-      <c r="B31" s="68"/>
-      <c r="C31" s="68"/>
-      <c r="D31" s="68"/>
-      <c r="E31" s="68"/>
-      <c r="F31" s="68"/>
-      <c r="G31" s="68"/>
-      <c r="H31" s="68"/>
-      <c r="I31" s="68"/>
-      <c r="J31" s="68"/>
-      <c r="K31" s="68"/>
-      <c r="L31" s="68"/>
-      <c r="M31" s="68"/>
-      <c r="N31" s="68"/>
-    </row>
-    <row r="32" ht="38.25" customHeight="1">
-      <c r="A32" s="67" t="s">
+      <c r="B33" s="58"/>
+      <c r="C33" s="58"/>
+      <c r="D33" s="58"/>
+      <c r="E33" s="58"/>
+      <c r="F33" s="58"/>
+      <c r="G33" s="58"/>
+      <c r="H33" s="58"/>
+      <c r="I33" s="58"/>
+      <c r="J33" s="58"/>
+      <c r="K33" s="58"/>
+      <c r="L33" s="58"/>
+      <c r="M33" s="58"/>
+      <c r="N33" s="58"/>
+    </row>
+    <row r="34" ht="34.5" customHeight="1">
+      <c r="A34" s="57" t="s">
         <v>882</v>
       </c>
-      <c r="B32" s="68"/>
-      <c r="C32" s="68"/>
-      <c r="D32" s="68"/>
-      <c r="E32" s="68"/>
-      <c r="F32" s="68"/>
-      <c r="G32" s="68"/>
-      <c r="H32" s="68"/>
-      <c r="I32" s="68"/>
-      <c r="J32" s="68"/>
-      <c r="K32" s="68"/>
-      <c r="L32" s="68"/>
-      <c r="M32" s="68"/>
-      <c r="N32" s="68"/>
-    </row>
-    <row r="33" ht="33.75" customHeight="1">
-      <c r="A33" s="67" t="s">
+      <c r="B34" s="58"/>
+      <c r="C34" s="58"/>
+      <c r="D34" s="58"/>
+      <c r="E34" s="58"/>
+      <c r="F34" s="58"/>
+      <c r="G34" s="58"/>
+      <c r="H34" s="58"/>
+      <c r="I34" s="58"/>
+      <c r="J34" s="58"/>
+      <c r="K34" s="58"/>
+      <c r="L34" s="58"/>
+      <c r="M34" s="58"/>
+      <c r="N34" s="58"/>
+    </row>
+    <row r="35" ht="36.75" customHeight="1">
+      <c r="A35" s="57" t="s">
         <v>883</v>
       </c>
-      <c r="B33" s="68"/>
-      <c r="C33" s="68"/>
-      <c r="D33" s="68"/>
-      <c r="E33" s="68"/>
-      <c r="F33" s="68"/>
-      <c r="G33" s="68"/>
-      <c r="H33" s="68"/>
-      <c r="I33" s="68"/>
-      <c r="J33" s="68"/>
-      <c r="K33" s="68"/>
-      <c r="L33" s="68"/>
-      <c r="M33" s="68"/>
-      <c r="N33" s="68"/>
-    </row>
-    <row r="34" ht="34.5" customHeight="1">
-      <c r="A34" s="67" t="s">
+      <c r="B35" s="58"/>
+      <c r="C35" s="58"/>
+      <c r="D35" s="58"/>
+      <c r="E35" s="58"/>
+      <c r="F35" s="58"/>
+      <c r="G35" s="58"/>
+      <c r="H35" s="58"/>
+      <c r="I35" s="58"/>
+      <c r="J35" s="58"/>
+      <c r="K35" s="58"/>
+      <c r="L35" s="58"/>
+      <c r="M35" s="58"/>
+      <c r="N35" s="58"/>
+    </row>
+    <row r="36" ht="31.5" customHeight="1">
+      <c r="A36" s="57" t="s">
         <v>884</v>
       </c>
-      <c r="B34" s="68"/>
-      <c r="C34" s="68"/>
-      <c r="D34" s="68"/>
-      <c r="E34" s="68"/>
-      <c r="F34" s="68"/>
-      <c r="G34" s="68"/>
-      <c r="H34" s="68"/>
-      <c r="I34" s="68"/>
-      <c r="J34" s="68"/>
-      <c r="K34" s="68"/>
-      <c r="L34" s="68"/>
-      <c r="M34" s="68"/>
-      <c r="N34" s="68"/>
-    </row>
-    <row r="35" ht="36.75" customHeight="1">
-      <c r="A35" s="67" t="s">
+      <c r="B36" s="58"/>
+      <c r="C36" s="58"/>
+      <c r="D36" s="58"/>
+      <c r="E36" s="58"/>
+      <c r="F36" s="58"/>
+      <c r="G36" s="58"/>
+      <c r="H36" s="58"/>
+      <c r="I36" s="58"/>
+      <c r="J36" s="58"/>
+      <c r="K36" s="58"/>
+      <c r="L36" s="58"/>
+      <c r="M36" s="58"/>
+      <c r="N36" s="58"/>
+    </row>
+    <row r="37" ht="30.0" customHeight="1">
+      <c r="A37" s="57" t="s">
         <v>885</v>
       </c>
-      <c r="B35" s="68"/>
-      <c r="C35" s="68"/>
-      <c r="D35" s="68"/>
-      <c r="E35" s="68"/>
-      <c r="F35" s="68"/>
-      <c r="G35" s="68"/>
-      <c r="H35" s="68"/>
-      <c r="I35" s="68"/>
-      <c r="J35" s="68"/>
-      <c r="K35" s="68"/>
-      <c r="L35" s="68"/>
-      <c r="M35" s="68"/>
-      <c r="N35" s="68"/>
-    </row>
-    <row r="36" ht="31.5" customHeight="1">
-      <c r="A36" s="67" t="s">
+      <c r="B37" s="58"/>
+      <c r="C37" s="58"/>
+      <c r="D37" s="58"/>
+      <c r="E37" s="58"/>
+      <c r="F37" s="58"/>
+      <c r="G37" s="58"/>
+      <c r="H37" s="58"/>
+      <c r="I37" s="58"/>
+      <c r="J37" s="58"/>
+      <c r="K37" s="58"/>
+      <c r="L37" s="58"/>
+      <c r="M37" s="58"/>
+      <c r="N37" s="58"/>
+    </row>
+    <row r="38" ht="24.75" customHeight="1">
+      <c r="A38" s="57" t="s">
         <v>886</v>
       </c>
-      <c r="B36" s="68"/>
-      <c r="C36" s="68"/>
-      <c r="D36" s="68"/>
-      <c r="E36" s="68"/>
-      <c r="F36" s="68"/>
-      <c r="G36" s="68"/>
-      <c r="H36" s="68"/>
-      <c r="I36" s="68"/>
-      <c r="J36" s="68"/>
-      <c r="K36" s="68"/>
-      <c r="L36" s="68"/>
-      <c r="M36" s="68"/>
-      <c r="N36" s="68"/>
-    </row>
-    <row r="37" ht="30.0" customHeight="1">
-      <c r="A37" s="67" t="s">
+      <c r="B38" s="58"/>
+      <c r="C38" s="58"/>
+      <c r="D38" s="58"/>
+      <c r="E38" s="58"/>
+      <c r="F38" s="58"/>
+      <c r="G38" s="58"/>
+      <c r="H38" s="58"/>
+      <c r="I38" s="58"/>
+      <c r="J38" s="58"/>
+      <c r="K38" s="58"/>
+      <c r="L38" s="58"/>
+      <c r="M38" s="58"/>
+      <c r="N38" s="58"/>
+    </row>
+    <row r="39" ht="25.5" customHeight="1">
+      <c r="A39" s="57" t="s">
         <v>887</v>
       </c>
-      <c r="B37" s="68"/>
-      <c r="C37" s="68"/>
-      <c r="D37" s="68"/>
-      <c r="E37" s="68"/>
-      <c r="F37" s="68"/>
-      <c r="G37" s="68"/>
-      <c r="H37" s="68"/>
-      <c r="I37" s="68"/>
-      <c r="J37" s="68"/>
-      <c r="K37" s="68"/>
-      <c r="L37" s="68"/>
-      <c r="M37" s="68"/>
-      <c r="N37" s="68"/>
-    </row>
-    <row r="38" ht="24.75" customHeight="1">
-      <c r="A38" s="67" t="s">
+      <c r="B39" s="58"/>
+      <c r="C39" s="58"/>
+      <c r="D39" s="58"/>
+      <c r="E39" s="58"/>
+      <c r="F39" s="58"/>
+      <c r="G39" s="58"/>
+      <c r="H39" s="58"/>
+      <c r="I39" s="58"/>
+      <c r="J39" s="58"/>
+      <c r="K39" s="58"/>
+      <c r="L39" s="58"/>
+      <c r="M39" s="58"/>
+      <c r="N39" s="58"/>
+    </row>
+    <row r="40" ht="35.25" customHeight="1">
+      <c r="A40" s="57" t="s">
         <v>888</v>
       </c>
-      <c r="B38" s="68"/>
-      <c r="C38" s="68"/>
-      <c r="D38" s="68"/>
-      <c r="E38" s="68"/>
-      <c r="F38" s="68"/>
-      <c r="G38" s="68"/>
-      <c r="H38" s="68"/>
-      <c r="I38" s="68"/>
-      <c r="J38" s="68"/>
-      <c r="K38" s="68"/>
-      <c r="L38" s="68"/>
-      <c r="M38" s="68"/>
-      <c r="N38" s="68"/>
-    </row>
-    <row r="39" ht="25.5" customHeight="1">
-      <c r="A39" s="67" t="s">
+      <c r="B40" s="58"/>
+      <c r="C40" s="58"/>
+      <c r="D40" s="58"/>
+      <c r="E40" s="58"/>
+      <c r="F40" s="58"/>
+      <c r="G40" s="58"/>
+      <c r="H40" s="58"/>
+      <c r="I40" s="58"/>
+      <c r="J40" s="58"/>
+      <c r="K40" s="58"/>
+      <c r="L40" s="58"/>
+      <c r="M40" s="58"/>
+      <c r="N40" s="58"/>
+    </row>
+    <row r="41" ht="27.75" customHeight="1">
+      <c r="A41" s="57" t="s">
         <v>889</v>
       </c>
-      <c r="B39" s="68"/>
-      <c r="C39" s="68"/>
-      <c r="D39" s="68"/>
-      <c r="E39" s="68"/>
-      <c r="F39" s="68"/>
-      <c r="G39" s="68"/>
-      <c r="H39" s="68"/>
-      <c r="I39" s="68"/>
-      <c r="J39" s="68"/>
-      <c r="K39" s="68"/>
-      <c r="L39" s="68"/>
-      <c r="M39" s="68"/>
-      <c r="N39" s="68"/>
-    </row>
-    <row r="40" ht="35.25" customHeight="1">
-      <c r="A40" s="67" t="s">
+      <c r="B41" s="58"/>
+      <c r="C41" s="58"/>
+      <c r="D41" s="58"/>
+      <c r="E41" s="58"/>
+      <c r="F41" s="58"/>
+      <c r="G41" s="58"/>
+      <c r="H41" s="58"/>
+      <c r="I41" s="58"/>
+      <c r="J41" s="58"/>
+      <c r="K41" s="58"/>
+      <c r="L41" s="58"/>
+      <c r="M41" s="58"/>
+      <c r="N41" s="58"/>
+    </row>
+    <row r="42" ht="30.75" customHeight="1">
+      <c r="A42" s="57" t="s">
         <v>890</v>
       </c>
-      <c r="B40" s="68"/>
-      <c r="C40" s="68"/>
-      <c r="D40" s="68"/>
-      <c r="E40" s="68"/>
-      <c r="F40" s="68"/>
-      <c r="G40" s="68"/>
-      <c r="H40" s="68"/>
-      <c r="I40" s="68"/>
-      <c r="J40" s="68"/>
-      <c r="K40" s="68"/>
-      <c r="L40" s="68"/>
-      <c r="M40" s="68"/>
-      <c r="N40" s="68"/>
-    </row>
-    <row r="41" ht="27.75" customHeight="1">
-      <c r="A41" s="67" t="s">
+      <c r="B42" s="58"/>
+      <c r="C42" s="58"/>
+      <c r="D42" s="58"/>
+      <c r="E42" s="58"/>
+      <c r="F42" s="58"/>
+      <c r="G42" s="58"/>
+      <c r="H42" s="58"/>
+      <c r="I42" s="58"/>
+      <c r="J42" s="58"/>
+      <c r="K42" s="58"/>
+      <c r="L42" s="58"/>
+      <c r="M42" s="58"/>
+      <c r="N42" s="58"/>
+    </row>
+    <row r="43" ht="27.75" customHeight="1">
+      <c r="A43" s="57" t="s">
         <v>891</v>
       </c>
-      <c r="B41" s="68"/>
-      <c r="C41" s="68"/>
-      <c r="D41" s="68"/>
-      <c r="E41" s="68"/>
-      <c r="F41" s="68"/>
-      <c r="G41" s="68"/>
-      <c r="H41" s="68"/>
-      <c r="I41" s="68"/>
-      <c r="J41" s="68"/>
-      <c r="K41" s="68"/>
-      <c r="L41" s="68"/>
-      <c r="M41" s="68"/>
-      <c r="N41" s="68"/>
-    </row>
-    <row r="42" ht="30.75" customHeight="1">
-      <c r="A42" s="67" t="s">
+      <c r="B43" s="58"/>
+      <c r="C43" s="58"/>
+      <c r="D43" s="58"/>
+      <c r="E43" s="58"/>
+      <c r="F43" s="58"/>
+      <c r="G43" s="58"/>
+      <c r="H43" s="58"/>
+      <c r="I43" s="58"/>
+      <c r="J43" s="58"/>
+      <c r="K43" s="58"/>
+      <c r="L43" s="58"/>
+      <c r="M43" s="58"/>
+      <c r="N43" s="58"/>
+    </row>
+    <row r="44" ht="27.0" customHeight="1">
+      <c r="A44" s="57" t="s">
         <v>892</v>
       </c>
-      <c r="B42" s="68"/>
-      <c r="C42" s="68"/>
-      <c r="D42" s="68"/>
-      <c r="E42" s="68"/>
-      <c r="F42" s="68"/>
-      <c r="G42" s="68"/>
-      <c r="H42" s="68"/>
-      <c r="I42" s="68"/>
-      <c r="J42" s="68"/>
-      <c r="K42" s="68"/>
-      <c r="L42" s="68"/>
-      <c r="M42" s="68"/>
-      <c r="N42" s="68"/>
-    </row>
-    <row r="43" ht="27.75" customHeight="1">
-      <c r="A43" s="67" t="s">
+      <c r="B44" s="58"/>
+      <c r="C44" s="58"/>
+      <c r="D44" s="58"/>
+      <c r="E44" s="58"/>
+      <c r="F44" s="58"/>
+      <c r="G44" s="58"/>
+      <c r="H44" s="58"/>
+      <c r="I44" s="58"/>
+      <c r="J44" s="58"/>
+      <c r="K44" s="58"/>
+      <c r="L44" s="58"/>
+      <c r="M44" s="58"/>
+      <c r="N44" s="58"/>
+    </row>
+    <row r="45" ht="25.5" customHeight="1">
+      <c r="A45" s="57" t="s">
         <v>893</v>
       </c>
-      <c r="B43" s="68"/>
-      <c r="C43" s="68"/>
-      <c r="D43" s="68"/>
-      <c r="E43" s="68"/>
-      <c r="F43" s="68"/>
-      <c r="G43" s="68"/>
-      <c r="H43" s="68"/>
-      <c r="I43" s="68"/>
-      <c r="J43" s="68"/>
-      <c r="K43" s="68"/>
-      <c r="L43" s="68"/>
-      <c r="M43" s="68"/>
-      <c r="N43" s="68"/>
-    </row>
-    <row r="44" ht="27.0" customHeight="1">
-      <c r="A44" s="67" t="s">
+      <c r="B45" s="58"/>
+      <c r="C45" s="58"/>
+      <c r="D45" s="58"/>
+      <c r="E45" s="58"/>
+      <c r="F45" s="58"/>
+      <c r="G45" s="58"/>
+      <c r="H45" s="58"/>
+      <c r="I45" s="58"/>
+      <c r="J45" s="58"/>
+      <c r="K45" s="58"/>
+      <c r="L45" s="58"/>
+      <c r="M45" s="58"/>
+      <c r="N45" s="58"/>
+    </row>
+    <row r="46" ht="27.75" customHeight="1">
+      <c r="A46" s="57" t="s">
         <v>894</v>
       </c>
-      <c r="B44" s="68"/>
-      <c r="C44" s="68"/>
-      <c r="D44" s="68"/>
-      <c r="E44" s="68"/>
-      <c r="F44" s="68"/>
-      <c r="G44" s="68"/>
-      <c r="H44" s="68"/>
-      <c r="I44" s="68"/>
-      <c r="J44" s="68"/>
-      <c r="K44" s="68"/>
-      <c r="L44" s="68"/>
-      <c r="M44" s="68"/>
-      <c r="N44" s="68"/>
-    </row>
-    <row r="45" ht="25.5" customHeight="1">
-      <c r="A45" s="67" t="s">
+      <c r="B46" s="58"/>
+      <c r="C46" s="58"/>
+      <c r="D46" s="58"/>
+      <c r="E46" s="58"/>
+      <c r="F46" s="58"/>
+      <c r="G46" s="58"/>
+      <c r="H46" s="58"/>
+      <c r="I46" s="58"/>
+      <c r="J46" s="58"/>
+      <c r="K46" s="58"/>
+      <c r="L46" s="58"/>
+      <c r="M46" s="58"/>
+      <c r="N46" s="58"/>
+    </row>
+    <row r="47" ht="33.0" customHeight="1">
+      <c r="A47" s="57" t="s">
         <v>895</v>
       </c>
-      <c r="B45" s="68"/>
-      <c r="C45" s="68"/>
-      <c r="D45" s="68"/>
-      <c r="E45" s="68"/>
-      <c r="F45" s="68"/>
-      <c r="G45" s="68"/>
-      <c r="H45" s="68"/>
-      <c r="I45" s="68"/>
-      <c r="J45" s="68"/>
-      <c r="K45" s="68"/>
-      <c r="L45" s="68"/>
-      <c r="M45" s="68"/>
-      <c r="N45" s="68"/>
-    </row>
-    <row r="46" ht="27.75" customHeight="1">
-      <c r="A46" s="67" t="s">
+      <c r="B47" s="58"/>
+      <c r="C47" s="58"/>
+      <c r="D47" s="58"/>
+      <c r="E47" s="58"/>
+      <c r="F47" s="58"/>
+      <c r="G47" s="58"/>
+      <c r="H47" s="58"/>
+      <c r="I47" s="58"/>
+      <c r="J47" s="58"/>
+      <c r="K47" s="58"/>
+      <c r="L47" s="58"/>
+      <c r="M47" s="58"/>
+      <c r="N47" s="58"/>
+    </row>
+    <row r="48" ht="36.0" customHeight="1">
+      <c r="A48" s="57" t="s">
         <v>896</v>
       </c>
-      <c r="B46" s="68"/>
-      <c r="C46" s="68"/>
-      <c r="D46" s="68"/>
-      <c r="E46" s="68"/>
-      <c r="F46" s="68"/>
-      <c r="G46" s="68"/>
-      <c r="H46" s="68"/>
-      <c r="I46" s="68"/>
-      <c r="J46" s="68"/>
-      <c r="K46" s="68"/>
-      <c r="L46" s="68"/>
-      <c r="M46" s="68"/>
-      <c r="N46" s="68"/>
-    </row>
-    <row r="47" ht="33.0" customHeight="1">
-      <c r="A47" s="67" t="s">
+      <c r="B48" s="58"/>
+      <c r="C48" s="58"/>
+      <c r="D48" s="58"/>
+      <c r="E48" s="58"/>
+      <c r="F48" s="58"/>
+      <c r="G48" s="58"/>
+      <c r="H48" s="58"/>
+      <c r="I48" s="58"/>
+      <c r="J48" s="58"/>
+      <c r="K48" s="58"/>
+      <c r="L48" s="58"/>
+      <c r="M48" s="58"/>
+      <c r="N48" s="58"/>
+    </row>
+    <row r="49" ht="24.75" customHeight="1">
+      <c r="A49" s="57" t="s">
         <v>897</v>
       </c>
-      <c r="B47" s="68"/>
-      <c r="C47" s="68"/>
-      <c r="D47" s="68"/>
-      <c r="E47" s="68"/>
-      <c r="F47" s="68"/>
-      <c r="G47" s="68"/>
-      <c r="H47" s="68"/>
-      <c r="I47" s="68"/>
-      <c r="J47" s="68"/>
-      <c r="K47" s="68"/>
-      <c r="L47" s="68"/>
-      <c r="M47" s="68"/>
-      <c r="N47" s="68"/>
-    </row>
-    <row r="48" ht="36.0" customHeight="1">
-      <c r="A48" s="67" t="s">
+      <c r="B49" s="58"/>
+      <c r="C49" s="58"/>
+      <c r="D49" s="58"/>
+      <c r="E49" s="58"/>
+      <c r="F49" s="58"/>
+      <c r="G49" s="58"/>
+      <c r="H49" s="58"/>
+      <c r="I49" s="58"/>
+      <c r="J49" s="58"/>
+      <c r="K49" s="58"/>
+      <c r="L49" s="58"/>
+      <c r="M49" s="58"/>
+      <c r="N49" s="58"/>
+    </row>
+    <row r="50" ht="27.0" customHeight="1">
+      <c r="A50" s="57" t="s">
         <v>898</v>
       </c>
-      <c r="B48" s="68"/>
-      <c r="C48" s="68"/>
-      <c r="D48" s="68"/>
-      <c r="E48" s="68"/>
-      <c r="F48" s="68"/>
-      <c r="G48" s="68"/>
-      <c r="H48" s="68"/>
-      <c r="I48" s="68"/>
-      <c r="J48" s="68"/>
-      <c r="K48" s="68"/>
-      <c r="L48" s="68"/>
-      <c r="M48" s="68"/>
-      <c r="N48" s="68"/>
-    </row>
-    <row r="49" ht="24.75" customHeight="1">
-      <c r="A49" s="67" t="s">
+      <c r="B50" s="58"/>
+      <c r="C50" s="58"/>
+      <c r="D50" s="58"/>
+      <c r="E50" s="58"/>
+      <c r="F50" s="58"/>
+      <c r="G50" s="58"/>
+      <c r="H50" s="58"/>
+      <c r="I50" s="58"/>
+      <c r="J50" s="58"/>
+      <c r="K50" s="58"/>
+      <c r="L50" s="58"/>
+      <c r="M50" s="58"/>
+      <c r="N50" s="58"/>
+    </row>
+    <row r="51" ht="30.75" customHeight="1">
+      <c r="A51" s="57" t="s">
         <v>899</v>
       </c>
-      <c r="B49" s="68"/>
-      <c r="C49" s="68"/>
-      <c r="D49" s="68"/>
-      <c r="E49" s="68"/>
-      <c r="F49" s="68"/>
-      <c r="G49" s="68"/>
-      <c r="H49" s="68"/>
-      <c r="I49" s="68"/>
-      <c r="J49" s="68"/>
-      <c r="K49" s="68"/>
-      <c r="L49" s="68"/>
-      <c r="M49" s="68"/>
-      <c r="N49" s="68"/>
-    </row>
-    <row r="50" ht="27.0" customHeight="1">
-      <c r="A50" s="67" t="s">
+      <c r="B51" s="58"/>
+      <c r="C51" s="58"/>
+      <c r="D51" s="58"/>
+      <c r="E51" s="58"/>
+      <c r="F51" s="58"/>
+      <c r="G51" s="58"/>
+      <c r="H51" s="58"/>
+      <c r="I51" s="58"/>
+      <c r="J51" s="58"/>
+      <c r="K51" s="58"/>
+      <c r="L51" s="58"/>
+      <c r="M51" s="58"/>
+      <c r="N51" s="58"/>
+    </row>
+    <row r="52" ht="26.25" customHeight="1">
+      <c r="A52" s="57" t="s">
         <v>900</v>
       </c>
-      <c r="B50" s="68"/>
-      <c r="C50" s="68"/>
-      <c r="D50" s="68"/>
-      <c r="E50" s="68"/>
-      <c r="F50" s="68"/>
-      <c r="G50" s="68"/>
-      <c r="H50" s="68"/>
-      <c r="I50" s="68"/>
-      <c r="J50" s="68"/>
-      <c r="K50" s="68"/>
-      <c r="L50" s="68"/>
-      <c r="M50" s="68"/>
-      <c r="N50" s="68"/>
-    </row>
-    <row r="51" ht="30.75" customHeight="1">
-      <c r="A51" s="67" t="s">
+      <c r="B52" s="58"/>
+      <c r="C52" s="58"/>
+      <c r="D52" s="58"/>
+      <c r="E52" s="58"/>
+      <c r="F52" s="58"/>
+      <c r="G52" s="58"/>
+      <c r="H52" s="58"/>
+      <c r="I52" s="58"/>
+      <c r="J52" s="58"/>
+      <c r="K52" s="58"/>
+      <c r="L52" s="58"/>
+      <c r="M52" s="58"/>
+      <c r="N52" s="58"/>
+    </row>
+    <row r="53" ht="25.5" customHeight="1">
+      <c r="A53" s="57" t="s">
         <v>901</v>
       </c>
-      <c r="B51" s="68"/>
-      <c r="C51" s="68"/>
-      <c r="D51" s="68"/>
-      <c r="E51" s="68"/>
-      <c r="F51" s="68"/>
-      <c r="G51" s="68"/>
-      <c r="H51" s="68"/>
-      <c r="I51" s="68"/>
-      <c r="J51" s="68"/>
-      <c r="K51" s="68"/>
-      <c r="L51" s="68"/>
-      <c r="M51" s="68"/>
-      <c r="N51" s="68"/>
-    </row>
-    <row r="52" ht="26.25" customHeight="1">
-      <c r="A52" s="67" t="s">
+      <c r="B53" s="58"/>
+      <c r="C53" s="58"/>
+      <c r="D53" s="58"/>
+      <c r="E53" s="58"/>
+      <c r="F53" s="58"/>
+      <c r="G53" s="58"/>
+      <c r="H53" s="58"/>
+      <c r="I53" s="58"/>
+      <c r="J53" s="58"/>
+      <c r="K53" s="58"/>
+      <c r="L53" s="58"/>
+      <c r="M53" s="58"/>
+      <c r="N53" s="58"/>
+    </row>
+    <row r="54" ht="25.5" customHeight="1">
+      <c r="A54" s="57" t="s">
         <v>902</v>
       </c>
-      <c r="B52" s="68"/>
-      <c r="C52" s="68"/>
-      <c r="D52" s="68"/>
-      <c r="E52" s="68"/>
-      <c r="F52" s="68"/>
-      <c r="G52" s="68"/>
-      <c r="H52" s="68"/>
-      <c r="I52" s="68"/>
-      <c r="J52" s="68"/>
-      <c r="K52" s="68"/>
-      <c r="L52" s="68"/>
-      <c r="M52" s="68"/>
-      <c r="N52" s="68"/>
-    </row>
-    <row r="53" ht="25.5" customHeight="1">
-      <c r="A53" s="67" t="s">
+      <c r="B54" s="58"/>
+      <c r="C54" s="58"/>
+      <c r="D54" s="58"/>
+      <c r="E54" s="58"/>
+      <c r="F54" s="58"/>
+      <c r="G54" s="58"/>
+      <c r="H54" s="58"/>
+      <c r="I54" s="58"/>
+      <c r="J54" s="58"/>
+      <c r="K54" s="58"/>
+      <c r="L54" s="58"/>
+      <c r="M54" s="58"/>
+      <c r="N54" s="58"/>
+    </row>
+    <row r="55" ht="23.25" customHeight="1">
+      <c r="A55" s="57" t="s">
         <v>903</v>
       </c>
-      <c r="B53" s="68"/>
-      <c r="C53" s="68"/>
-      <c r="D53" s="68"/>
-      <c r="E53" s="68"/>
-      <c r="F53" s="68"/>
-      <c r="G53" s="68"/>
-      <c r="H53" s="68"/>
-      <c r="I53" s="68"/>
-      <c r="J53" s="68"/>
-      <c r="K53" s="68"/>
-      <c r="L53" s="68"/>
-      <c r="M53" s="68"/>
-      <c r="N53" s="68"/>
-    </row>
-    <row r="54" ht="25.5" customHeight="1">
-      <c r="A54" s="67" t="s">
+      <c r="B55" s="58"/>
+      <c r="C55" s="58"/>
+      <c r="D55" s="58"/>
+      <c r="E55" s="58"/>
+      <c r="F55" s="58"/>
+      <c r="G55" s="58"/>
+      <c r="H55" s="58"/>
+      <c r="I55" s="58"/>
+      <c r="J55" s="58"/>
+      <c r="K55" s="58"/>
+      <c r="L55" s="58"/>
+      <c r="M55" s="58"/>
+      <c r="N55" s="58"/>
+    </row>
+    <row r="56" ht="33.75" customHeight="1">
+      <c r="A56" s="57" t="s">
         <v>904</v>
       </c>
-      <c r="B54" s="68"/>
-      <c r="C54" s="68"/>
-      <c r="D54" s="68"/>
-      <c r="E54" s="68"/>
-      <c r="F54" s="68"/>
-      <c r="G54" s="68"/>
-      <c r="H54" s="68"/>
-      <c r="I54" s="68"/>
-      <c r="J54" s="68"/>
-      <c r="K54" s="68"/>
-      <c r="L54" s="68"/>
-      <c r="M54" s="68"/>
-      <c r="N54" s="68"/>
-    </row>
-    <row r="55" ht="23.25" customHeight="1">
-      <c r="A55" s="67" t="s">
+      <c r="B56" s="58"/>
+      <c r="C56" s="58"/>
+      <c r="D56" s="58"/>
+      <c r="E56" s="58"/>
+      <c r="F56" s="58"/>
+      <c r="G56" s="58"/>
+      <c r="H56" s="58"/>
+      <c r="I56" s="58"/>
+      <c r="J56" s="58"/>
+      <c r="K56" s="58"/>
+      <c r="L56" s="58"/>
+      <c r="M56" s="58"/>
+      <c r="N56" s="58"/>
+    </row>
+    <row r="57" ht="27.75" customHeight="1">
+      <c r="A57" s="57" t="s">
         <v>905</v>
       </c>
-      <c r="B55" s="68"/>
-      <c r="C55" s="68"/>
-      <c r="D55" s="68"/>
-      <c r="E55" s="68"/>
-      <c r="F55" s="68"/>
-      <c r="G55" s="68"/>
-      <c r="H55" s="68"/>
-      <c r="I55" s="68"/>
-      <c r="J55" s="68"/>
-      <c r="K55" s="68"/>
-      <c r="L55" s="68"/>
-      <c r="M55" s="68"/>
-      <c r="N55" s="68"/>
-    </row>
-    <row r="56" ht="33.75" customHeight="1">
-      <c r="A56" s="67" t="s">
+      <c r="B57" s="58"/>
+      <c r="C57" s="58"/>
+      <c r="D57" s="58"/>
+      <c r="E57" s="58"/>
+      <c r="F57" s="58"/>
+      <c r="G57" s="58"/>
+      <c r="H57" s="58"/>
+      <c r="I57" s="58"/>
+      <c r="J57" s="58"/>
+      <c r="K57" s="58"/>
+      <c r="L57" s="58"/>
+      <c r="M57" s="58"/>
+      <c r="N57" s="58"/>
+    </row>
+    <row r="58" ht="31.5" customHeight="1">
+      <c r="A58" s="57" t="s">
         <v>906</v>
       </c>
-      <c r="B56" s="68"/>
-      <c r="C56" s="68"/>
-      <c r="D56" s="68"/>
-      <c r="E56" s="68"/>
-      <c r="F56" s="68"/>
-      <c r="G56" s="68"/>
-      <c r="H56" s="68"/>
-      <c r="I56" s="68"/>
-      <c r="J56" s="68"/>
-      <c r="K56" s="68"/>
-      <c r="L56" s="68"/>
-      <c r="M56" s="68"/>
-      <c r="N56" s="68"/>
-    </row>
-    <row r="57" ht="27.75" customHeight="1">
-      <c r="A57" s="67" t="s">
+      <c r="B58" s="58"/>
+      <c r="C58" s="58"/>
+      <c r="D58" s="58"/>
+      <c r="E58" s="58"/>
+      <c r="F58" s="58"/>
+      <c r="G58" s="58"/>
+      <c r="H58" s="58"/>
+      <c r="I58" s="58"/>
+      <c r="J58" s="58"/>
+      <c r="K58" s="58"/>
+      <c r="L58" s="58"/>
+      <c r="M58" s="58"/>
+      <c r="N58" s="58"/>
+    </row>
+    <row r="59" ht="29.25" customHeight="1">
+      <c r="A59" s="57" t="s">
         <v>907</v>
       </c>
-      <c r="B57" s="68"/>
-      <c r="C57" s="68"/>
-      <c r="D57" s="68"/>
-      <c r="E57" s="68"/>
-      <c r="F57" s="68"/>
-      <c r="G57" s="68"/>
-      <c r="H57" s="68"/>
-      <c r="I57" s="68"/>
-      <c r="J57" s="68"/>
-      <c r="K57" s="68"/>
-      <c r="L57" s="68"/>
-      <c r="M57" s="68"/>
-      <c r="N57" s="68"/>
-    </row>
-    <row r="58" ht="31.5" customHeight="1">
-      <c r="A58" s="67" t="s">
+      <c r="B59" s="58"/>
+      <c r="C59" s="58"/>
+      <c r="D59" s="58"/>
+      <c r="E59" s="58"/>
+      <c r="F59" s="58"/>
+      <c r="G59" s="58"/>
+      <c r="H59" s="58"/>
+      <c r="I59" s="58"/>
+      <c r="J59" s="58"/>
+      <c r="K59" s="58"/>
+      <c r="L59" s="58"/>
+      <c r="M59" s="58"/>
+      <c r="N59" s="58"/>
+    </row>
+    <row r="60" ht="30.75" customHeight="1">
+      <c r="A60" s="57" t="s">
         <v>908</v>
       </c>
-      <c r="B58" s="68"/>
-      <c r="C58" s="68"/>
-      <c r="D58" s="68"/>
-      <c r="E58" s="68"/>
-      <c r="F58" s="68"/>
-      <c r="G58" s="68"/>
-      <c r="H58" s="68"/>
-      <c r="I58" s="68"/>
-      <c r="J58" s="68"/>
-      <c r="K58" s="68"/>
-      <c r="L58" s="68"/>
-      <c r="M58" s="68"/>
-      <c r="N58" s="68"/>
-    </row>
-    <row r="59" ht="29.25" customHeight="1">
-      <c r="A59" s="67" t="s">
+      <c r="B60" s="58"/>
+      <c r="C60" s="58"/>
+      <c r="D60" s="58"/>
+      <c r="E60" s="58"/>
+      <c r="F60" s="58"/>
+      <c r="G60" s="58"/>
+      <c r="H60" s="58"/>
+      <c r="I60" s="58"/>
+      <c r="J60" s="58"/>
+      <c r="K60" s="58"/>
+      <c r="L60" s="58"/>
+      <c r="M60" s="58"/>
+      <c r="N60" s="58"/>
+    </row>
+    <row r="61" ht="31.5" customHeight="1">
+      <c r="A61" s="57" t="s">
         <v>909</v>
       </c>
-      <c r="B59" s="68"/>
-      <c r="C59" s="68"/>
-      <c r="D59" s="68"/>
-      <c r="E59" s="68"/>
-      <c r="F59" s="68"/>
-      <c r="G59" s="68"/>
-      <c r="H59" s="68"/>
-      <c r="I59" s="68"/>
-      <c r="J59" s="68"/>
-      <c r="K59" s="68"/>
-      <c r="L59" s="68"/>
-      <c r="M59" s="68"/>
-      <c r="N59" s="68"/>
-    </row>
-    <row r="60" ht="30.75" customHeight="1">
-      <c r="A60" s="67" t="s">
+      <c r="B61" s="58"/>
+      <c r="C61" s="58"/>
+      <c r="D61" s="58"/>
+      <c r="E61" s="58"/>
+      <c r="F61" s="58"/>
+      <c r="G61" s="58"/>
+      <c r="H61" s="58"/>
+      <c r="I61" s="58"/>
+      <c r="J61" s="58"/>
+      <c r="K61" s="58"/>
+      <c r="L61" s="58"/>
+      <c r="M61" s="58"/>
+      <c r="N61" s="58"/>
+    </row>
+    <row r="62" ht="41.25" customHeight="1">
+      <c r="A62" s="57" t="s">
         <v>910</v>
       </c>
-      <c r="B60" s="68"/>
-      <c r="C60" s="68"/>
-      <c r="D60" s="68"/>
-      <c r="E60" s="68"/>
-      <c r="F60" s="68"/>
-      <c r="G60" s="68"/>
-      <c r="H60" s="68"/>
-      <c r="I60" s="68"/>
-      <c r="J60" s="68"/>
-      <c r="K60" s="68"/>
-      <c r="L60" s="68"/>
-      <c r="M60" s="68"/>
-      <c r="N60" s="68"/>
-    </row>
-    <row r="61" ht="31.5" customHeight="1">
-      <c r="A61" s="67" t="s">
+      <c r="B62" s="58"/>
+      <c r="C62" s="58"/>
+      <c r="D62" s="58"/>
+      <c r="E62" s="58"/>
+      <c r="F62" s="58"/>
+      <c r="G62" s="58"/>
+      <c r="H62" s="58"/>
+      <c r="I62" s="58"/>
+      <c r="J62" s="58"/>
+      <c r="K62" s="58"/>
+      <c r="L62" s="58"/>
+      <c r="M62" s="58"/>
+      <c r="N62" s="58"/>
+    </row>
+    <row r="63" ht="41.25" customHeight="1">
+      <c r="A63" s="57" t="s">
         <v>911</v>
       </c>
-      <c r="B61" s="68"/>
-      <c r="C61" s="68"/>
-      <c r="D61" s="68"/>
-      <c r="E61" s="68"/>
-      <c r="F61" s="68"/>
-      <c r="G61" s="68"/>
-      <c r="H61" s="68"/>
-      <c r="I61" s="68"/>
-      <c r="J61" s="68"/>
-      <c r="K61" s="68"/>
-      <c r="L61" s="68"/>
-      <c r="M61" s="68"/>
-      <c r="N61" s="68"/>
-    </row>
-    <row r="62" ht="41.25" customHeight="1">
-      <c r="A62" s="67" t="s">
+      <c r="B63" s="58"/>
+      <c r="C63" s="58"/>
+      <c r="D63" s="58"/>
+      <c r="E63" s="58"/>
+      <c r="F63" s="58"/>
+      <c r="G63" s="58"/>
+      <c r="H63" s="58"/>
+      <c r="I63" s="58"/>
+      <c r="J63" s="58"/>
+      <c r="K63" s="58"/>
+      <c r="L63" s="58"/>
+      <c r="M63" s="58"/>
+      <c r="N63" s="58"/>
+    </row>
+    <row r="64" ht="32.25" customHeight="1">
+      <c r="A64" s="57" t="s">
         <v>912</v>
       </c>
-      <c r="B62" s="68"/>
-      <c r="C62" s="68"/>
-      <c r="D62" s="68"/>
-      <c r="E62" s="68"/>
-      <c r="F62" s="68"/>
-      <c r="G62" s="68"/>
-      <c r="H62" s="68"/>
-      <c r="I62" s="68"/>
-      <c r="J62" s="68"/>
-      <c r="K62" s="68"/>
-      <c r="L62" s="68"/>
-      <c r="M62" s="68"/>
-      <c r="N62" s="68"/>
-    </row>
-    <row r="63" ht="41.25" customHeight="1">
-      <c r="A63" s="67" t="s">
+      <c r="B64" s="58"/>
+      <c r="C64" s="58"/>
+      <c r="D64" s="58"/>
+      <c r="E64" s="58"/>
+      <c r="F64" s="58"/>
+      <c r="G64" s="58"/>
+      <c r="H64" s="58"/>
+      <c r="I64" s="58"/>
+      <c r="J64" s="58"/>
+      <c r="K64" s="58"/>
+      <c r="L64" s="58"/>
+      <c r="M64" s="58"/>
+      <c r="N64" s="58"/>
+    </row>
+    <row r="65" ht="33.0" customHeight="1">
+      <c r="A65" s="57" t="s">
         <v>913</v>
       </c>
-      <c r="B63" s="68"/>
-      <c r="C63" s="68"/>
-      <c r="D63" s="68"/>
-      <c r="E63" s="68"/>
-      <c r="F63" s="68"/>
-      <c r="G63" s="68"/>
-      <c r="H63" s="68"/>
-      <c r="I63" s="68"/>
-      <c r="J63" s="68"/>
-      <c r="K63" s="68"/>
-      <c r="L63" s="68"/>
-      <c r="M63" s="68"/>
-      <c r="N63" s="68"/>
-    </row>
-    <row r="64" ht="32.25" customHeight="1">
-      <c r="A64" s="67" t="s">
+      <c r="B65" s="58"/>
+      <c r="C65" s="58"/>
+      <c r="D65" s="58"/>
+      <c r="E65" s="58"/>
+      <c r="F65" s="58"/>
+      <c r="G65" s="58"/>
+      <c r="H65" s="58"/>
+      <c r="I65" s="58"/>
+      <c r="J65" s="58"/>
+      <c r="K65" s="58"/>
+      <c r="L65" s="58"/>
+      <c r="M65" s="58"/>
+      <c r="N65" s="58"/>
+    </row>
+    <row r="66" ht="33.75" customHeight="1">
+      <c r="A66" s="57" t="s">
         <v>914</v>
       </c>
-      <c r="B64" s="68"/>
-      <c r="C64" s="68"/>
-      <c r="D64" s="68"/>
-      <c r="E64" s="68"/>
-      <c r="F64" s="68"/>
-      <c r="G64" s="68"/>
-      <c r="H64" s="68"/>
-      <c r="I64" s="68"/>
-      <c r="J64" s="68"/>
-      <c r="K64" s="68"/>
-      <c r="L64" s="68"/>
-      <c r="M64" s="68"/>
-      <c r="N64" s="68"/>
-    </row>
-    <row r="65" ht="33.0" customHeight="1">
-      <c r="A65" s="67" t="s">
+      <c r="B66" s="58"/>
+      <c r="C66" s="58"/>
+      <c r="D66" s="58"/>
+      <c r="E66" s="58"/>
+      <c r="F66" s="58"/>
+      <c r="G66" s="58"/>
+      <c r="H66" s="58"/>
+      <c r="I66" s="58"/>
+      <c r="J66" s="58"/>
+      <c r="K66" s="58"/>
+      <c r="L66" s="58"/>
+      <c r="M66" s="58"/>
+      <c r="N66" s="58"/>
+    </row>
+    <row r="67" ht="27.0" customHeight="1">
+      <c r="A67" s="57" t="s">
         <v>915</v>
       </c>
-      <c r="B65" s="68"/>
-      <c r="C65" s="68"/>
-      <c r="D65" s="68"/>
-      <c r="E65" s="68"/>
-      <c r="F65" s="68"/>
-      <c r="G65" s="68"/>
-      <c r="H65" s="68"/>
-      <c r="I65" s="68"/>
-      <c r="J65" s="68"/>
-      <c r="K65" s="68"/>
-      <c r="L65" s="68"/>
-      <c r="M65" s="68"/>
-      <c r="N65" s="68"/>
-    </row>
-    <row r="66" ht="33.75" customHeight="1">
-      <c r="A66" s="67" t="s">
+      <c r="B67" s="58"/>
+      <c r="C67" s="58"/>
+      <c r="D67" s="58"/>
+      <c r="E67" s="58"/>
+      <c r="F67" s="58"/>
+      <c r="G67" s="58"/>
+      <c r="H67" s="58"/>
+      <c r="I67" s="58"/>
+      <c r="J67" s="58"/>
+      <c r="K67" s="58"/>
+      <c r="L67" s="58"/>
+      <c r="M67" s="58"/>
+      <c r="N67" s="58"/>
+    </row>
+    <row r="68" ht="18.75" customHeight="1">
+      <c r="A68" s="57" t="s">
         <v>916</v>
       </c>
-      <c r="B66" s="68"/>
-      <c r="C66" s="68"/>
-      <c r="D66" s="68"/>
-      <c r="E66" s="68"/>
-      <c r="F66" s="68"/>
-      <c r="G66" s="68"/>
-      <c r="H66" s="68"/>
-      <c r="I66" s="68"/>
-      <c r="J66" s="68"/>
-      <c r="K66" s="68"/>
-      <c r="L66" s="68"/>
-      <c r="M66" s="68"/>
-      <c r="N66" s="68"/>
-    </row>
-    <row r="67" ht="27.0" customHeight="1">
-      <c r="A67" s="67" t="s">
+      <c r="B68" s="58"/>
+      <c r="C68" s="58"/>
+      <c r="D68" s="58"/>
+      <c r="E68" s="58"/>
+      <c r="F68" s="58"/>
+      <c r="G68" s="58"/>
+      <c r="H68" s="58"/>
+      <c r="I68" s="58"/>
+      <c r="J68" s="58"/>
+      <c r="K68" s="58"/>
+      <c r="L68" s="58"/>
+      <c r="M68" s="58"/>
+      <c r="N68" s="58"/>
+    </row>
+    <row r="69" ht="21.75" customHeight="1">
+      <c r="A69" s="57" t="s">
         <v>917</v>
       </c>
-      <c r="B67" s="68"/>
-      <c r="C67" s="68"/>
-      <c r="D67" s="68"/>
-      <c r="E67" s="68"/>
-      <c r="F67" s="68"/>
-      <c r="G67" s="68"/>
-      <c r="H67" s="68"/>
-      <c r="I67" s="68"/>
-      <c r="J67" s="68"/>
-      <c r="K67" s="68"/>
-      <c r="L67" s="68"/>
-      <c r="M67" s="68"/>
-      <c r="N67" s="68"/>
-    </row>
-    <row r="68" ht="18.75" customHeight="1">
-      <c r="A68" s="67" t="s">
+      <c r="B69" s="58"/>
+      <c r="C69" s="58"/>
+      <c r="D69" s="58"/>
+      <c r="E69" s="58"/>
+      <c r="F69" s="58"/>
+      <c r="G69" s="58"/>
+      <c r="H69" s="58"/>
+      <c r="I69" s="58"/>
+      <c r="J69" s="58"/>
+      <c r="K69" s="58"/>
+      <c r="L69" s="58"/>
+      <c r="M69" s="58"/>
+      <c r="N69" s="58"/>
+    </row>
+    <row r="70" ht="22.5" customHeight="1">
+      <c r="A70" s="57" t="s">
         <v>918</v>
       </c>
-      <c r="B68" s="68"/>
-      <c r="C68" s="68"/>
-      <c r="D68" s="68"/>
-      <c r="E68" s="68"/>
-      <c r="F68" s="68"/>
-      <c r="G68" s="68"/>
-      <c r="H68" s="68"/>
-      <c r="I68" s="68"/>
-      <c r="J68" s="68"/>
-      <c r="K68" s="68"/>
-      <c r="L68" s="68"/>
-      <c r="M68" s="68"/>
-      <c r="N68" s="68"/>
-    </row>
-    <row r="69" ht="21.75" customHeight="1">
-      <c r="A69" s="67" t="s">
+      <c r="B70" s="58"/>
+      <c r="C70" s="58"/>
+      <c r="D70" s="58"/>
+      <c r="E70" s="58"/>
+      <c r="F70" s="58"/>
+      <c r="G70" s="58"/>
+      <c r="H70" s="58"/>
+      <c r="I70" s="58"/>
+      <c r="J70" s="58"/>
+      <c r="K70" s="58"/>
+      <c r="L70" s="58"/>
+      <c r="M70" s="58"/>
+      <c r="N70" s="58"/>
+    </row>
+    <row r="71" ht="18.75" customHeight="1">
+      <c r="A71" s="57" t="s">
         <v>919</v>
       </c>
-      <c r="B69" s="68"/>
-      <c r="C69" s="68"/>
-      <c r="D69" s="68"/>
-      <c r="E69" s="68"/>
-      <c r="F69" s="68"/>
-      <c r="G69" s="68"/>
-      <c r="H69" s="68"/>
-      <c r="I69" s="68"/>
-      <c r="J69" s="68"/>
-      <c r="K69" s="68"/>
-      <c r="L69" s="68"/>
-      <c r="M69" s="68"/>
-      <c r="N69" s="68"/>
-    </row>
-    <row r="70" ht="22.5" customHeight="1">
-      <c r="A70" s="67" t="s">
+      <c r="B71" s="58"/>
+      <c r="C71" s="58"/>
+      <c r="D71" s="58"/>
+      <c r="E71" s="58"/>
+      <c r="F71" s="58"/>
+      <c r="G71" s="58"/>
+      <c r="H71" s="58"/>
+      <c r="I71" s="58"/>
+      <c r="J71" s="58"/>
+      <c r="K71" s="58"/>
+      <c r="L71" s="58"/>
+      <c r="M71" s="58"/>
+      <c r="N71" s="58"/>
+    </row>
+    <row r="72" ht="27.0" customHeight="1">
+      <c r="A72" s="57" t="s">
         <v>920</v>
       </c>
-      <c r="B70" s="68"/>
-      <c r="C70" s="68"/>
-      <c r="D70" s="68"/>
-      <c r="E70" s="68"/>
-      <c r="F70" s="68"/>
-      <c r="G70" s="68"/>
-      <c r="H70" s="68"/>
-      <c r="I70" s="68"/>
-      <c r="J70" s="68"/>
-      <c r="K70" s="68"/>
-      <c r="L70" s="68"/>
-      <c r="M70" s="68"/>
-      <c r="N70" s="68"/>
-    </row>
-    <row r="71" ht="18.75" customHeight="1">
-      <c r="A71" s="67" t="s">
+      <c r="B72" s="58"/>
+      <c r="C72" s="58"/>
+      <c r="D72" s="58"/>
+      <c r="E72" s="58"/>
+      <c r="F72" s="58"/>
+      <c r="G72" s="58"/>
+      <c r="H72" s="58"/>
+      <c r="I72" s="58"/>
+      <c r="J72" s="58"/>
+      <c r="K72" s="58"/>
+      <c r="L72" s="58"/>
+      <c r="M72" s="58"/>
+      <c r="N72" s="58"/>
+    </row>
+    <row r="73" ht="27.75" customHeight="1">
+      <c r="A73" s="57" t="s">
         <v>921</v>
       </c>
-      <c r="B71" s="68"/>
-      <c r="C71" s="68"/>
-      <c r="D71" s="68"/>
-      <c r="E71" s="68"/>
-      <c r="F71" s="68"/>
-      <c r="G71" s="68"/>
-      <c r="H71" s="68"/>
-      <c r="I71" s="68"/>
-      <c r="J71" s="68"/>
-      <c r="K71" s="68"/>
-      <c r="L71" s="68"/>
-      <c r="M71" s="68"/>
-      <c r="N71" s="68"/>
-    </row>
-    <row r="72" ht="27.0" customHeight="1">
-      <c r="A72" s="67" t="s">
+      <c r="B73" s="58"/>
+      <c r="C73" s="58"/>
+      <c r="D73" s="58"/>
+      <c r="E73" s="58"/>
+      <c r="F73" s="58"/>
+      <c r="G73" s="58"/>
+      <c r="H73" s="58"/>
+      <c r="I73" s="58"/>
+      <c r="J73" s="58"/>
+      <c r="K73" s="58"/>
+      <c r="L73" s="58"/>
+      <c r="M73" s="58"/>
+      <c r="N73" s="58"/>
+    </row>
+    <row r="74" ht="36.75" customHeight="1">
+      <c r="A74" s="57" t="s">
         <v>922</v>
       </c>
-      <c r="B72" s="68"/>
-      <c r="C72" s="68"/>
-      <c r="D72" s="68"/>
-      <c r="E72" s="68"/>
-      <c r="F72" s="68"/>
-      <c r="G72" s="68"/>
-      <c r="H72" s="68"/>
-      <c r="I72" s="68"/>
-      <c r="J72" s="68"/>
-      <c r="K72" s="68"/>
-      <c r="L72" s="68"/>
-      <c r="M72" s="68"/>
-      <c r="N72" s="68"/>
-    </row>
-    <row r="73" ht="27.75" customHeight="1">
-      <c r="A73" s="67" t="s">
+      <c r="B74" s="58"/>
+      <c r="C74" s="58"/>
+      <c r="D74" s="58"/>
+      <c r="E74" s="58"/>
+      <c r="F74" s="58"/>
+      <c r="G74" s="58"/>
+      <c r="H74" s="58"/>
+      <c r="I74" s="58"/>
+      <c r="J74" s="58"/>
+      <c r="K74" s="58"/>
+      <c r="L74" s="58"/>
+      <c r="M74" s="58"/>
+      <c r="N74" s="58"/>
+    </row>
+    <row r="75" ht="36.75" customHeight="1">
+      <c r="A75" s="57" t="s">
         <v>923</v>
       </c>
-      <c r="B73" s="68"/>
-      <c r="C73" s="68"/>
-      <c r="D73" s="68"/>
-      <c r="E73" s="68"/>
-      <c r="F73" s="68"/>
-      <c r="G73" s="68"/>
-      <c r="H73" s="68"/>
-      <c r="I73" s="68"/>
-      <c r="J73" s="68"/>
-      <c r="K73" s="68"/>
-      <c r="L73" s="68"/>
-      <c r="M73" s="68"/>
-      <c r="N73" s="68"/>
-    </row>
-    <row r="74" ht="36.75" customHeight="1">
-      <c r="A74" s="67" t="s">
+      <c r="B75" s="58"/>
+      <c r="C75" s="58"/>
+      <c r="D75" s="58"/>
+      <c r="E75" s="58"/>
+      <c r="F75" s="58"/>
+      <c r="G75" s="58"/>
+      <c r="H75" s="58"/>
+      <c r="I75" s="58"/>
+      <c r="J75" s="58"/>
+      <c r="K75" s="58"/>
+      <c r="L75" s="58"/>
+      <c r="M75" s="58"/>
+      <c r="N75" s="58"/>
+    </row>
+    <row r="76" ht="25.5" customHeight="1">
+      <c r="A76" s="57" t="s">
         <v>924</v>
       </c>
-      <c r="B74" s="68"/>
-      <c r="C74" s="68"/>
-      <c r="D74" s="68"/>
-      <c r="E74" s="68"/>
-      <c r="F74" s="68"/>
-      <c r="G74" s="68"/>
-      <c r="H74" s="68"/>
-      <c r="I74" s="68"/>
-      <c r="J74" s="68"/>
-      <c r="K74" s="68"/>
-      <c r="L74" s="68"/>
-      <c r="M74" s="68"/>
-      <c r="N74" s="68"/>
-    </row>
-    <row r="75" ht="36.75" customHeight="1">
-      <c r="A75" s="67" t="s">
+      <c r="B76" s="58"/>
+      <c r="C76" s="58"/>
+      <c r="D76" s="58"/>
+      <c r="E76" s="58"/>
+      <c r="F76" s="58"/>
+      <c r="G76" s="58"/>
+      <c r="H76" s="58"/>
+      <c r="I76" s="58"/>
+      <c r="J76" s="58"/>
+      <c r="K76" s="58"/>
+      <c r="L76" s="58"/>
+      <c r="M76" s="58"/>
+      <c r="N76" s="58"/>
+    </row>
+    <row r="77" ht="27.0" customHeight="1">
+      <c r="A77" s="57" t="s">
         <v>925</v>
       </c>
-      <c r="B75" s="68"/>
-      <c r="C75" s="68"/>
-      <c r="D75" s="68"/>
-      <c r="E75" s="68"/>
-      <c r="F75" s="68"/>
-      <c r="G75" s="68"/>
-      <c r="H75" s="68"/>
-      <c r="I75" s="68"/>
-      <c r="J75" s="68"/>
-      <c r="K75" s="68"/>
-      <c r="L75" s="68"/>
-      <c r="M75" s="68"/>
-      <c r="N75" s="68"/>
-    </row>
-    <row r="76" ht="25.5" customHeight="1">
-      <c r="A76" s="67" t="s">
+      <c r="B77" s="58"/>
+      <c r="C77" s="58"/>
+      <c r="D77" s="58"/>
+      <c r="E77" s="58"/>
+      <c r="F77" s="58"/>
+      <c r="G77" s="58"/>
+      <c r="H77" s="58"/>
+      <c r="I77" s="58"/>
+      <c r="J77" s="58"/>
+      <c r="K77" s="58"/>
+      <c r="L77" s="58"/>
+      <c r="M77" s="58"/>
+      <c r="N77" s="58"/>
+    </row>
+    <row r="78" ht="24.75" customHeight="1">
+      <c r="A78" s="57" t="s">
         <v>926</v>
       </c>
-      <c r="B76" s="68"/>
-      <c r="C76" s="68"/>
-      <c r="D76" s="68"/>
-      <c r="E76" s="68"/>
-      <c r="F76" s="68"/>
-      <c r="G76" s="68"/>
-      <c r="H76" s="68"/>
-      <c r="I76" s="68"/>
-      <c r="J76" s="68"/>
-      <c r="K76" s="68"/>
-      <c r="L76" s="68"/>
-      <c r="M76" s="68"/>
-      <c r="N76" s="68"/>
-    </row>
-    <row r="77" ht="27.0" customHeight="1">
-      <c r="A77" s="67" t="s">
+      <c r="B78" s="58"/>
+      <c r="C78" s="58"/>
+      <c r="D78" s="58"/>
+      <c r="E78" s="58"/>
+      <c r="F78" s="58"/>
+      <c r="G78" s="58"/>
+      <c r="H78" s="58"/>
+      <c r="I78" s="58"/>
+      <c r="J78" s="58"/>
+      <c r="K78" s="58"/>
+      <c r="L78" s="58"/>
+      <c r="M78" s="58"/>
+      <c r="N78" s="58"/>
+    </row>
+    <row r="79" ht="30.0" customHeight="1">
+      <c r="A79" s="57" t="s">
         <v>927</v>
       </c>
-      <c r="B77" s="68"/>
-      <c r="C77" s="68"/>
-      <c r="D77" s="68"/>
-      <c r="E77" s="68"/>
-      <c r="F77" s="68"/>
-      <c r="G77" s="68"/>
-      <c r="H77" s="68"/>
-      <c r="I77" s="68"/>
-      <c r="J77" s="68"/>
-      <c r="K77" s="68"/>
-      <c r="L77" s="68"/>
-      <c r="M77" s="68"/>
-      <c r="N77" s="68"/>
-    </row>
-    <row r="78" ht="24.75" customHeight="1">
-      <c r="A78" s="67" t="s">
+      <c r="B79" s="58"/>
+      <c r="C79" s="58"/>
+      <c r="D79" s="58"/>
+      <c r="E79" s="58"/>
+      <c r="F79" s="58"/>
+      <c r="G79" s="58"/>
+      <c r="H79" s="58"/>
+      <c r="I79" s="58"/>
+      <c r="J79" s="58"/>
+      <c r="K79" s="58"/>
+      <c r="L79" s="58"/>
+      <c r="M79" s="58"/>
+      <c r="N79" s="58"/>
+    </row>
+    <row r="80" ht="30.0" customHeight="1">
+      <c r="A80" s="57" t="s">
         <v>928</v>
       </c>
-      <c r="B78" s="68"/>
-      <c r="C78" s="68"/>
-      <c r="D78" s="68"/>
-      <c r="E78" s="68"/>
-      <c r="F78" s="68"/>
-      <c r="G78" s="68"/>
-      <c r="H78" s="68"/>
-      <c r="I78" s="68"/>
-      <c r="J78" s="68"/>
-      <c r="K78" s="68"/>
-      <c r="L78" s="68"/>
-      <c r="M78" s="68"/>
-      <c r="N78" s="68"/>
-    </row>
-    <row r="79" ht="30.0" customHeight="1">
-      <c r="A79" s="67" t="s">
+      <c r="B80" s="58"/>
+      <c r="C80" s="58"/>
+      <c r="D80" s="58"/>
+      <c r="E80" s="58"/>
+      <c r="F80" s="58"/>
+      <c r="G80" s="58"/>
+      <c r="H80" s="58"/>
+      <c r="I80" s="58"/>
+      <c r="J80" s="58"/>
+      <c r="K80" s="58"/>
+      <c r="L80" s="58"/>
+      <c r="M80" s="58"/>
+      <c r="N80" s="58"/>
+    </row>
+    <row r="81" ht="27.75" customHeight="1">
+      <c r="A81" s="57" t="s">
         <v>929</v>
       </c>
-      <c r="B79" s="68"/>
-      <c r="C79" s="68"/>
-      <c r="D79" s="68"/>
-      <c r="E79" s="68"/>
-      <c r="F79" s="68"/>
-      <c r="G79" s="68"/>
-      <c r="H79" s="68"/>
-      <c r="I79" s="68"/>
-      <c r="J79" s="68"/>
-      <c r="K79" s="68"/>
-      <c r="L79" s="68"/>
-      <c r="M79" s="68"/>
-      <c r="N79" s="68"/>
-    </row>
-    <row r="80" ht="30.0" customHeight="1">
-      <c r="A80" s="67" t="s">
+      <c r="B81" s="58"/>
+      <c r="C81" s="58"/>
+      <c r="D81" s="58"/>
+      <c r="E81" s="58"/>
+      <c r="F81" s="58"/>
+      <c r="G81" s="58"/>
+      <c r="H81" s="58"/>
+      <c r="I81" s="58"/>
+      <c r="J81" s="58"/>
+      <c r="K81" s="58"/>
+      <c r="L81" s="58"/>
+      <c r="M81" s="58"/>
+      <c r="N81" s="58"/>
+    </row>
+    <row r="82" ht="24.0" customHeight="1">
+      <c r="A82" s="57" t="s">
         <v>930</v>
       </c>
-      <c r="B80" s="68"/>
-      <c r="C80" s="68"/>
-      <c r="D80" s="68"/>
-      <c r="E80" s="68"/>
-      <c r="F80" s="68"/>
-      <c r="G80" s="68"/>
-      <c r="H80" s="68"/>
-      <c r="I80" s="68"/>
-      <c r="J80" s="68"/>
-      <c r="K80" s="68"/>
-      <c r="L80" s="68"/>
-      <c r="M80" s="68"/>
-      <c r="N80" s="68"/>
-    </row>
-    <row r="81" ht="27.75" customHeight="1">
-      <c r="A81" s="67" t="s">
+      <c r="B82" s="58"/>
+      <c r="C82" s="58"/>
+      <c r="D82" s="58"/>
+      <c r="E82" s="58"/>
+      <c r="F82" s="58"/>
+      <c r="G82" s="58"/>
+      <c r="H82" s="58"/>
+      <c r="I82" s="58"/>
+      <c r="J82" s="58"/>
+      <c r="K82" s="58"/>
+      <c r="L82" s="58"/>
+      <c r="M82" s="58"/>
+      <c r="N82" s="58"/>
+    </row>
+    <row r="83" ht="34.5" customHeight="1">
+      <c r="A83" s="57" t="s">
         <v>931</v>
       </c>
-      <c r="B81" s="68"/>
-      <c r="C81" s="68"/>
-      <c r="D81" s="68"/>
-      <c r="E81" s="68"/>
-      <c r="F81" s="68"/>
-      <c r="G81" s="68"/>
-      <c r="H81" s="68"/>
-      <c r="I81" s="68"/>
-      <c r="J81" s="68"/>
-      <c r="K81" s="68"/>
-      <c r="L81" s="68"/>
-      <c r="M81" s="68"/>
-      <c r="N81" s="68"/>
-    </row>
-    <row r="82" ht="24.0" customHeight="1">
-      <c r="A82" s="67" t="s">
+      <c r="B83" s="58"/>
+      <c r="C83" s="58"/>
+      <c r="D83" s="58"/>
+      <c r="E83" s="58"/>
+      <c r="F83" s="58"/>
+      <c r="G83" s="58"/>
+      <c r="H83" s="58"/>
+      <c r="I83" s="58"/>
+      <c r="J83" s="58"/>
+      <c r="K83" s="58"/>
+      <c r="L83" s="58"/>
+      <c r="M83" s="58"/>
+      <c r="N83" s="58"/>
+    </row>
+    <row r="84" ht="33.0" customHeight="1">
+      <c r="A84" s="57" t="s">
         <v>932</v>
       </c>
-      <c r="B82" s="68"/>
-      <c r="C82" s="68"/>
-      <c r="D82" s="68"/>
-      <c r="E82" s="68"/>
-      <c r="F82" s="68"/>
-      <c r="G82" s="68"/>
-      <c r="H82" s="68"/>
-      <c r="I82" s="68"/>
-      <c r="J82" s="68"/>
-      <c r="K82" s="68"/>
-      <c r="L82" s="68"/>
-      <c r="M82" s="68"/>
-      <c r="N82" s="68"/>
-    </row>
-    <row r="83" ht="34.5" customHeight="1">
-      <c r="A83" s="67" t="s">
+      <c r="B84" s="58"/>
+      <c r="C84" s="58"/>
+      <c r="D84" s="58"/>
+      <c r="E84" s="58"/>
+      <c r="F84" s="58"/>
+      <c r="G84" s="58"/>
+      <c r="H84" s="58"/>
+      <c r="I84" s="58"/>
+      <c r="J84" s="58"/>
+      <c r="K84" s="58"/>
+      <c r="L84" s="58"/>
+      <c r="M84" s="58"/>
+      <c r="N84" s="58"/>
+    </row>
+    <row r="85" ht="25.5" customHeight="1">
+      <c r="A85" s="57" t="s">
         <v>933</v>
       </c>
-      <c r="B83" s="68"/>
-      <c r="C83" s="68"/>
-      <c r="D83" s="68"/>
-      <c r="E83" s="68"/>
-      <c r="F83" s="68"/>
-      <c r="G83" s="68"/>
-      <c r="H83" s="68"/>
-      <c r="I83" s="68"/>
-      <c r="J83" s="68"/>
-      <c r="K83" s="68"/>
-      <c r="L83" s="68"/>
-      <c r="M83" s="68"/>
-      <c r="N83" s="68"/>
-    </row>
-    <row r="84" ht="33.0" customHeight="1">
-      <c r="A84" s="67" t="s">
+      <c r="B85" s="58"/>
+      <c r="C85" s="58"/>
+      <c r="D85" s="58"/>
+      <c r="E85" s="58"/>
+      <c r="F85" s="58"/>
+      <c r="G85" s="58"/>
+      <c r="H85" s="58"/>
+      <c r="I85" s="58"/>
+      <c r="J85" s="58"/>
+      <c r="K85" s="58"/>
+      <c r="L85" s="58"/>
+      <c r="M85" s="58"/>
+      <c r="N85" s="58"/>
+    </row>
+    <row r="86" ht="33.75" customHeight="1">
+      <c r="A86" s="57" t="s">
         <v>934</v>
       </c>
-      <c r="B84" s="68"/>
-      <c r="C84" s="68"/>
-      <c r="D84" s="68"/>
-      <c r="E84" s="68"/>
-      <c r="F84" s="68"/>
-      <c r="G84" s="68"/>
-      <c r="H84" s="68"/>
-      <c r="I84" s="68"/>
-      <c r="J84" s="68"/>
-      <c r="K84" s="68"/>
-      <c r="L84" s="68"/>
-      <c r="M84" s="68"/>
-      <c r="N84" s="68"/>
-    </row>
-    <row r="85" ht="25.5" customHeight="1">
-      <c r="A85" s="67" t="s">
+      <c r="B86" s="58"/>
+      <c r="C86" s="58"/>
+      <c r="D86" s="58"/>
+      <c r="E86" s="58"/>
+      <c r="F86" s="58"/>
+      <c r="G86" s="58"/>
+      <c r="H86" s="58"/>
+      <c r="I86" s="58"/>
+      <c r="J86" s="58"/>
+      <c r="K86" s="58"/>
+      <c r="L86" s="58"/>
+      <c r="M86" s="58"/>
+      <c r="N86" s="58"/>
+    </row>
+    <row r="87" ht="31.5" customHeight="1">
+      <c r="A87" s="57" t="s">
         <v>935</v>
       </c>
-      <c r="B85" s="68"/>
-      <c r="C85" s="68"/>
-      <c r="D85" s="68"/>
-      <c r="E85" s="68"/>
-      <c r="F85" s="68"/>
-      <c r="G85" s="68"/>
-      <c r="H85" s="68"/>
-      <c r="I85" s="68"/>
-      <c r="J85" s="68"/>
-      <c r="K85" s="68"/>
-      <c r="L85" s="68"/>
-      <c r="M85" s="68"/>
-      <c r="N85" s="68"/>
-    </row>
-    <row r="86" ht="33.75" customHeight="1">
-      <c r="A86" s="67" t="s">
+      <c r="B87" s="58"/>
+      <c r="C87" s="58"/>
+      <c r="D87" s="58"/>
+      <c r="E87" s="58"/>
+      <c r="F87" s="58"/>
+      <c r="G87" s="58"/>
+      <c r="H87" s="58"/>
+      <c r="I87" s="58"/>
+      <c r="J87" s="58"/>
+      <c r="K87" s="58"/>
+      <c r="L87" s="58"/>
+      <c r="M87" s="58"/>
+      <c r="N87" s="58"/>
+    </row>
+    <row r="88" ht="27.75" customHeight="1">
+      <c r="A88" s="57" t="s">
         <v>936</v>
       </c>
-      <c r="B86" s="68"/>
-      <c r="C86" s="68"/>
-      <c r="D86" s="68"/>
-      <c r="E86" s="68"/>
-      <c r="F86" s="68"/>
-      <c r="G86" s="68"/>
-      <c r="H86" s="68"/>
-      <c r="I86" s="68"/>
-      <c r="J86" s="68"/>
-      <c r="K86" s="68"/>
-      <c r="L86" s="68"/>
-      <c r="M86" s="68"/>
-      <c r="N86" s="68"/>
-    </row>
-    <row r="87" ht="31.5" customHeight="1">
-      <c r="A87" s="67" t="s">
+      <c r="B88" s="58"/>
+      <c r="C88" s="58"/>
+      <c r="D88" s="58"/>
+      <c r="E88" s="58"/>
+      <c r="F88" s="58"/>
+      <c r="G88" s="58"/>
+      <c r="H88" s="58"/>
+      <c r="I88" s="58"/>
+      <c r="J88" s="58"/>
+      <c r="K88" s="58"/>
+      <c r="L88" s="58"/>
+      <c r="M88" s="58"/>
+      <c r="N88" s="58"/>
+    </row>
+    <row r="89" ht="25.5" customHeight="1">
+      <c r="A89" s="57" t="s">
         <v>937</v>
       </c>
-      <c r="B87" s="68"/>
-      <c r="C87" s="68"/>
-      <c r="D87" s="68"/>
-      <c r="E87" s="68"/>
-      <c r="F87" s="68"/>
-      <c r="G87" s="68"/>
-      <c r="H87" s="68"/>
-      <c r="I87" s="68"/>
-      <c r="J87" s="68"/>
-      <c r="K87" s="68"/>
-      <c r="L87" s="68"/>
-      <c r="M87" s="68"/>
-      <c r="N87" s="68"/>
-    </row>
-    <row r="88" ht="27.75" customHeight="1">
-      <c r="A88" s="67" t="s">
+      <c r="B89" s="58"/>
+      <c r="C89" s="58"/>
+      <c r="D89" s="58"/>
+      <c r="E89" s="58"/>
+      <c r="F89" s="58"/>
+      <c r="G89" s="58"/>
+      <c r="H89" s="58"/>
+      <c r="I89" s="58"/>
+      <c r="J89" s="58"/>
+      <c r="K89" s="58"/>
+      <c r="L89" s="58"/>
+      <c r="M89" s="58"/>
+      <c r="N89" s="58"/>
+    </row>
+    <row r="90" ht="28.5" customHeight="1">
+      <c r="A90" s="57" t="s">
         <v>938</v>
       </c>
-      <c r="B88" s="68"/>
-      <c r="C88" s="68"/>
-      <c r="D88" s="68"/>
-      <c r="E88" s="68"/>
-      <c r="F88" s="68"/>
-      <c r="G88" s="68"/>
-      <c r="H88" s="68"/>
-      <c r="I88" s="68"/>
-      <c r="J88" s="68"/>
-      <c r="K88" s="68"/>
-      <c r="L88" s="68"/>
-      <c r="M88" s="68"/>
-      <c r="N88" s="68"/>
-    </row>
-    <row r="89" ht="25.5" customHeight="1">
-      <c r="A89" s="67" t="s">
+      <c r="B90" s="58"/>
+      <c r="C90" s="58"/>
+      <c r="D90" s="58"/>
+      <c r="E90" s="58"/>
+      <c r="F90" s="58"/>
+      <c r="G90" s="58"/>
+      <c r="H90" s="58"/>
+      <c r="I90" s="58"/>
+      <c r="J90" s="58"/>
+      <c r="K90" s="58"/>
+      <c r="L90" s="58"/>
+      <c r="M90" s="58"/>
+      <c r="N90" s="58"/>
+    </row>
+    <row r="91" ht="32.25" customHeight="1">
+      <c r="A91" s="57" t="s">
         <v>939</v>
       </c>
-      <c r="B89" s="68"/>
-      <c r="C89" s="68"/>
-      <c r="D89" s="68"/>
-      <c r="E89" s="68"/>
-      <c r="F89" s="68"/>
-      <c r="G89" s="68"/>
-      <c r="H89" s="68"/>
-      <c r="I89" s="68"/>
-      <c r="J89" s="68"/>
-      <c r="K89" s="68"/>
-      <c r="L89" s="68"/>
-      <c r="M89" s="68"/>
-      <c r="N89" s="68"/>
-    </row>
-    <row r="90" ht="28.5" customHeight="1">
-      <c r="A90" s="67" t="s">
+      <c r="B91" s="58"/>
+      <c r="C91" s="58"/>
+      <c r="D91" s="58"/>
+      <c r="E91" s="58"/>
+      <c r="F91" s="58"/>
+      <c r="G91" s="58"/>
+      <c r="H91" s="58"/>
+      <c r="I91" s="58"/>
+      <c r="J91" s="58"/>
+      <c r="K91" s="58"/>
+      <c r="L91" s="58"/>
+      <c r="M91" s="58"/>
+      <c r="N91" s="58"/>
+    </row>
+    <row r="92" ht="32.25" customHeight="1">
+      <c r="A92" s="57" t="s">
         <v>940</v>
       </c>
-      <c r="B90" s="68"/>
-      <c r="C90" s="68"/>
-      <c r="D90" s="68"/>
-      <c r="E90" s="68"/>
-      <c r="F90" s="68"/>
-      <c r="G90" s="68"/>
-      <c r="H90" s="68"/>
-      <c r="I90" s="68"/>
-      <c r="J90" s="68"/>
-      <c r="K90" s="68"/>
-      <c r="L90" s="68"/>
-      <c r="M90" s="68"/>
-      <c r="N90" s="68"/>
-    </row>
-    <row r="91" ht="32.25" customHeight="1">
-      <c r="A91" s="67" t="s">
+      <c r="B92" s="58"/>
+      <c r="C92" s="58"/>
+      <c r="D92" s="58"/>
+      <c r="E92" s="58"/>
+      <c r="F92" s="58"/>
+      <c r="G92" s="58"/>
+      <c r="H92" s="58"/>
+      <c r="I92" s="58"/>
+      <c r="J92" s="58"/>
+      <c r="K92" s="58"/>
+      <c r="L92" s="58"/>
+      <c r="M92" s="58"/>
+      <c r="N92" s="58"/>
+    </row>
+    <row r="93" ht="25.5" customHeight="1">
+      <c r="A93" s="57" t="s">
         <v>941</v>
       </c>
-      <c r="B91" s="68"/>
-      <c r="C91" s="68"/>
-      <c r="D91" s="68"/>
-      <c r="E91" s="68"/>
-      <c r="F91" s="68"/>
-      <c r="G91" s="68"/>
-      <c r="H91" s="68"/>
-      <c r="I91" s="68"/>
-      <c r="J91" s="68"/>
-      <c r="K91" s="68"/>
-      <c r="L91" s="68"/>
-      <c r="M91" s="68"/>
-      <c r="N91" s="68"/>
-    </row>
-    <row r="92" ht="32.25" customHeight="1">
-      <c r="A92" s="67" t="s">
+      <c r="B93" s="58"/>
+      <c r="C93" s="58"/>
+      <c r="D93" s="58"/>
+      <c r="E93" s="58"/>
+      <c r="F93" s="58"/>
+      <c r="G93" s="58"/>
+      <c r="H93" s="58"/>
+      <c r="I93" s="58"/>
+      <c r="J93" s="58"/>
+      <c r="K93" s="58"/>
+      <c r="L93" s="58"/>
+      <c r="M93" s="58"/>
+      <c r="N93" s="58"/>
+    </row>
+    <row r="94" ht="36.75" customHeight="1">
+      <c r="A94" s="57" t="s">
         <v>942</v>
       </c>
-      <c r="B92" s="68"/>
-      <c r="C92" s="68"/>
-      <c r="D92" s="68"/>
-      <c r="E92" s="68"/>
-      <c r="F92" s="68"/>
-      <c r="G92" s="68"/>
-      <c r="H92" s="68"/>
-      <c r="I92" s="68"/>
-      <c r="J92" s="68"/>
-      <c r="K92" s="68"/>
-      <c r="L92" s="68"/>
-      <c r="M92" s="68"/>
-      <c r="N92" s="68"/>
-    </row>
-    <row r="93" ht="25.5" customHeight="1">
-      <c r="A93" s="67" t="s">
+      <c r="B94" s="58"/>
+      <c r="C94" s="58"/>
+      <c r="D94" s="58"/>
+      <c r="E94" s="58"/>
+      <c r="F94" s="58"/>
+      <c r="G94" s="58"/>
+      <c r="H94" s="58"/>
+      <c r="I94" s="58"/>
+      <c r="J94" s="58"/>
+      <c r="K94" s="58"/>
+      <c r="L94" s="58"/>
+      <c r="M94" s="58"/>
+      <c r="N94" s="58"/>
+    </row>
+    <row r="95" ht="30.75" customHeight="1">
+      <c r="A95" s="57" t="s">
         <v>943</v>
       </c>
-      <c r="B93" s="68"/>
-      <c r="C93" s="68"/>
-      <c r="D93" s="68"/>
-      <c r="E93" s="68"/>
-      <c r="F93" s="68"/>
-      <c r="G93" s="68"/>
-      <c r="H93" s="68"/>
-      <c r="I93" s="68"/>
-      <c r="J93" s="68"/>
-      <c r="K93" s="68"/>
-      <c r="L93" s="68"/>
-      <c r="M93" s="68"/>
-      <c r="N93" s="68"/>
-    </row>
-    <row r="94" ht="36.75" customHeight="1">
-      <c r="A94" s="67" t="s">
+      <c r="B95" s="58"/>
+      <c r="C95" s="58"/>
+      <c r="D95" s="58"/>
+      <c r="E95" s="58"/>
+      <c r="F95" s="58"/>
+      <c r="G95" s="58"/>
+      <c r="H95" s="58"/>
+      <c r="I95" s="58"/>
+      <c r="J95" s="58"/>
+      <c r="K95" s="58"/>
+      <c r="L95" s="58"/>
+      <c r="M95" s="58"/>
+      <c r="N95" s="58"/>
+    </row>
+    <row r="96" ht="34.5" customHeight="1">
+      <c r="A96" s="57" t="s">
         <v>944</v>
       </c>
-      <c r="B94" s="68"/>
-      <c r="C94" s="68"/>
-      <c r="D94" s="68"/>
-      <c r="E94" s="68"/>
-      <c r="F94" s="68"/>
-      <c r="G94" s="68"/>
-      <c r="H94" s="68"/>
-      <c r="I94" s="68"/>
-      <c r="J94" s="68"/>
-      <c r="K94" s="68"/>
-      <c r="L94" s="68"/>
-      <c r="M94" s="68"/>
-      <c r="N94" s="68"/>
-    </row>
-    <row r="95" ht="30.75" customHeight="1">
-      <c r="A95" s="67" t="s">
+      <c r="B96" s="58"/>
+      <c r="C96" s="58"/>
+      <c r="D96" s="58"/>
+      <c r="E96" s="58"/>
+      <c r="F96" s="58"/>
+      <c r="G96" s="58"/>
+      <c r="H96" s="58"/>
+      <c r="I96" s="58"/>
+      <c r="J96" s="58"/>
+      <c r="K96" s="58"/>
+      <c r="L96" s="58"/>
+      <c r="M96" s="58"/>
+      <c r="N96" s="58"/>
+    </row>
+    <row r="97" ht="32.25" customHeight="1">
+      <c r="A97" s="57" t="s">
         <v>945</v>
       </c>
-      <c r="B95" s="68"/>
-      <c r="C95" s="68"/>
-      <c r="D95" s="68"/>
-      <c r="E95" s="68"/>
-      <c r="F95" s="68"/>
-      <c r="G95" s="68"/>
-      <c r="H95" s="68"/>
-      <c r="I95" s="68"/>
-      <c r="J95" s="68"/>
-      <c r="K95" s="68"/>
-      <c r="L95" s="68"/>
-      <c r="M95" s="68"/>
-      <c r="N95" s="68"/>
-    </row>
-    <row r="96" ht="34.5" customHeight="1">
-      <c r="A96" s="67" t="s">
+      <c r="B97" s="58"/>
+      <c r="C97" s="58"/>
+      <c r="D97" s="58"/>
+      <c r="E97" s="58"/>
+      <c r="F97" s="58"/>
+      <c r="G97" s="58"/>
+      <c r="H97" s="58"/>
+      <c r="I97" s="58"/>
+      <c r="J97" s="58"/>
+      <c r="K97" s="58"/>
+      <c r="L97" s="58"/>
+      <c r="M97" s="58"/>
+      <c r="N97" s="58"/>
+    </row>
+    <row r="98" ht="36.0" customHeight="1">
+      <c r="A98" s="57" t="s">
         <v>946</v>
       </c>
-      <c r="B96" s="68"/>
-      <c r="C96" s="68"/>
-      <c r="D96" s="68"/>
-      <c r="E96" s="68"/>
-      <c r="F96" s="68"/>
-      <c r="G96" s="68"/>
-      <c r="H96" s="68"/>
-      <c r="I96" s="68"/>
-      <c r="J96" s="68"/>
-      <c r="K96" s="68"/>
-      <c r="L96" s="68"/>
-      <c r="M96" s="68"/>
-      <c r="N96" s="68"/>
-    </row>
-    <row r="97" ht="32.25" customHeight="1">
-      <c r="A97" s="67" t="s">
+      <c r="B98" s="58"/>
+      <c r="C98" s="58"/>
+      <c r="D98" s="58"/>
+      <c r="E98" s="58"/>
+      <c r="F98" s="58"/>
+      <c r="G98" s="58"/>
+      <c r="H98" s="58"/>
+      <c r="I98" s="58"/>
+      <c r="J98" s="58"/>
+      <c r="K98" s="58"/>
+      <c r="L98" s="58"/>
+      <c r="M98" s="58"/>
+      <c r="N98" s="58"/>
+    </row>
+    <row r="99" ht="23.25" customHeight="1">
+      <c r="A99" s="57" t="s">
         <v>947</v>
       </c>
-      <c r="B97" s="68"/>
-      <c r="C97" s="68"/>
-      <c r="D97" s="68"/>
-      <c r="E97" s="68"/>
-      <c r="F97" s="68"/>
-      <c r="G97" s="68"/>
-      <c r="H97" s="68"/>
-      <c r="I97" s="68"/>
-      <c r="J97" s="68"/>
-      <c r="K97" s="68"/>
-      <c r="L97" s="68"/>
-      <c r="M97" s="68"/>
-      <c r="N97" s="68"/>
-    </row>
-    <row r="98" ht="36.0" customHeight="1">
-      <c r="A98" s="67" t="s">
+      <c r="B99" s="58"/>
+      <c r="C99" s="58"/>
+      <c r="D99" s="58"/>
+      <c r="E99" s="58"/>
+      <c r="F99" s="58"/>
+      <c r="G99" s="58"/>
+      <c r="H99" s="58"/>
+      <c r="I99" s="58"/>
+      <c r="J99" s="58"/>
+      <c r="K99" s="58"/>
+      <c r="L99" s="58"/>
+      <c r="M99" s="58"/>
+      <c r="N99" s="58"/>
+    </row>
+    <row r="100" ht="25.5" customHeight="1">
+      <c r="A100" s="57" t="s">
         <v>948</v>
       </c>
-      <c r="B98" s="68"/>
-      <c r="C98" s="68"/>
-      <c r="D98" s="68"/>
-      <c r="E98" s="68"/>
-      <c r="F98" s="68"/>
-      <c r="G98" s="68"/>
-      <c r="H98" s="68"/>
-      <c r="I98" s="68"/>
-      <c r="J98" s="68"/>
-      <c r="K98" s="68"/>
-      <c r="L98" s="68"/>
-      <c r="M98" s="68"/>
-      <c r="N98" s="68"/>
-    </row>
-    <row r="99" ht="23.25" customHeight="1">
-      <c r="A99" s="67" t="s">
+      <c r="B100" s="58"/>
+      <c r="C100" s="58"/>
+      <c r="D100" s="58"/>
+      <c r="E100" s="58"/>
+      <c r="F100" s="58"/>
+      <c r="G100" s="58"/>
+      <c r="H100" s="58"/>
+      <c r="I100" s="58"/>
+      <c r="J100" s="58"/>
+      <c r="K100" s="58"/>
+      <c r="L100" s="58"/>
+      <c r="M100" s="58"/>
+      <c r="N100" s="58"/>
+    </row>
+    <row r="101" ht="30.75" customHeight="1">
+      <c r="A101" s="57" t="s">
         <v>949</v>
       </c>
-      <c r="B99" s="68"/>
-      <c r="C99" s="68"/>
-      <c r="D99" s="68"/>
-      <c r="E99" s="68"/>
-      <c r="F99" s="68"/>
-      <c r="G99" s="68"/>
-      <c r="H99" s="68"/>
-      <c r="I99" s="68"/>
-      <c r="J99" s="68"/>
-      <c r="K99" s="68"/>
-      <c r="L99" s="68"/>
-      <c r="M99" s="68"/>
-      <c r="N99" s="68"/>
-    </row>
-    <row r="100" ht="25.5" customHeight="1">
-      <c r="A100" s="67" t="s">
+      <c r="B101" s="58"/>
+      <c r="C101" s="58"/>
+      <c r="D101" s="58"/>
+      <c r="E101" s="58"/>
+      <c r="F101" s="58"/>
+      <c r="G101" s="58"/>
+      <c r="H101" s="58"/>
+      <c r="I101" s="58"/>
+      <c r="J101" s="58"/>
+      <c r="K101" s="58"/>
+      <c r="L101" s="58"/>
+      <c r="M101" s="58"/>
+      <c r="N101" s="58"/>
+    </row>
+    <row r="102" ht="27.75" customHeight="1">
+      <c r="A102" s="57" t="s">
         <v>950</v>
       </c>
-      <c r="B100" s="68"/>
-      <c r="C100" s="68"/>
-      <c r="D100" s="68"/>
-      <c r="E100" s="68"/>
-      <c r="F100" s="68"/>
-      <c r="G100" s="68"/>
-      <c r="H100" s="68"/>
-      <c r="I100" s="68"/>
-      <c r="J100" s="68"/>
-      <c r="K100" s="68"/>
-      <c r="L100" s="68"/>
-      <c r="M100" s="68"/>
-      <c r="N100" s="68"/>
-    </row>
-    <row r="101" ht="30.75" customHeight="1">
-      <c r="A101" s="67" t="s">
+      <c r="B102" s="58"/>
+      <c r="C102" s="58"/>
+      <c r="D102" s="58"/>
+      <c r="E102" s="58"/>
+      <c r="F102" s="58"/>
+      <c r="G102" s="58"/>
+      <c r="H102" s="58"/>
+      <c r="I102" s="58"/>
+      <c r="J102" s="58"/>
+      <c r="K102" s="58"/>
+      <c r="L102" s="58"/>
+      <c r="M102" s="58"/>
+      <c r="N102" s="58"/>
+    </row>
+    <row r="103" ht="25.5" customHeight="1">
+      <c r="A103" s="57" t="s">
         <v>951</v>
       </c>
-      <c r="B101" s="68"/>
-      <c r="C101" s="68"/>
-      <c r="D101" s="68"/>
-      <c r="E101" s="68"/>
-      <c r="F101" s="68"/>
-      <c r="G101" s="68"/>
-      <c r="H101" s="68"/>
-      <c r="I101" s="68"/>
-      <c r="J101" s="68"/>
-      <c r="K101" s="68"/>
-      <c r="L101" s="68"/>
-      <c r="M101" s="68"/>
-      <c r="N101" s="68"/>
-    </row>
-    <row r="102" ht="27.75" customHeight="1">
-      <c r="A102" s="67" t="s">
+      <c r="B103" s="58"/>
+      <c r="C103" s="58"/>
+      <c r="D103" s="58"/>
+      <c r="E103" s="58"/>
+      <c r="F103" s="58"/>
+      <c r="G103" s="58"/>
+      <c r="H103" s="58"/>
+      <c r="I103" s="58"/>
+      <c r="J103" s="58"/>
+      <c r="K103" s="58"/>
+      <c r="L103" s="58"/>
+      <c r="M103" s="58"/>
+      <c r="N103" s="58"/>
+    </row>
+    <row r="104" ht="30.0" customHeight="1">
+      <c r="A104" s="57" t="s">
         <v>952</v>
       </c>
-      <c r="B102" s="68"/>
-      <c r="C102" s="68"/>
-      <c r="D102" s="68"/>
-      <c r="E102" s="68"/>
-      <c r="F102" s="68"/>
-      <c r="G102" s="68"/>
-      <c r="H102" s="68"/>
-      <c r="I102" s="68"/>
-      <c r="J102" s="68"/>
-      <c r="K102" s="68"/>
-      <c r="L102" s="68"/>
-      <c r="M102" s="68"/>
-      <c r="N102" s="68"/>
-    </row>
-    <row r="103" ht="25.5" customHeight="1">
-      <c r="A103" s="67" t="s">
+      <c r="B104" s="58"/>
+      <c r="C104" s="58"/>
+      <c r="D104" s="58"/>
+      <c r="E104" s="58"/>
+      <c r="F104" s="58"/>
+      <c r="G104" s="58"/>
+      <c r="H104" s="58"/>
+      <c r="I104" s="58"/>
+      <c r="J104" s="58"/>
+      <c r="K104" s="58"/>
+      <c r="L104" s="58"/>
+      <c r="M104" s="58"/>
+      <c r="N104" s="58"/>
+    </row>
+    <row r="105" ht="21.0" customHeight="1">
+      <c r="A105" s="57" t="s">
         <v>953</v>
       </c>
-      <c r="B103" s="68"/>
-      <c r="C103" s="68"/>
-      <c r="D103" s="68"/>
-      <c r="E103" s="68"/>
-      <c r="F103" s="68"/>
-      <c r="G103" s="68"/>
-      <c r="H103" s="68"/>
-      <c r="I103" s="68"/>
-      <c r="J103" s="68"/>
-      <c r="K103" s="68"/>
-      <c r="L103" s="68"/>
-      <c r="M103" s="68"/>
-      <c r="N103" s="68"/>
-    </row>
-    <row r="104" ht="30.0" customHeight="1">
-      <c r="A104" s="67" t="s">
+      <c r="B105" s="58"/>
+      <c r="C105" s="58"/>
+      <c r="D105" s="58"/>
+      <c r="E105" s="58"/>
+      <c r="F105" s="58"/>
+      <c r="G105" s="58"/>
+      <c r="H105" s="58"/>
+      <c r="I105" s="58"/>
+      <c r="J105" s="58"/>
+      <c r="K105" s="58"/>
+      <c r="L105" s="58"/>
+      <c r="M105" s="58"/>
+      <c r="N105" s="58"/>
+    </row>
+    <row r="106" ht="27.0" customHeight="1">
+      <c r="A106" s="57" t="s">
         <v>954</v>
       </c>
-      <c r="B104" s="68"/>
-      <c r="C104" s="68"/>
-      <c r="D104" s="68"/>
-      <c r="E104" s="68"/>
-      <c r="F104" s="68"/>
-      <c r="G104" s="68"/>
-      <c r="H104" s="68"/>
-      <c r="I104" s="68"/>
-      <c r="J104" s="68"/>
-      <c r="K104" s="68"/>
-      <c r="L104" s="68"/>
-      <c r="M104" s="68"/>
-      <c r="N104" s="68"/>
-    </row>
-    <row r="105" ht="21.0" customHeight="1">
-      <c r="A105" s="67" t="s">
+      <c r="B106" s="58"/>
+      <c r="C106" s="58"/>
+      <c r="D106" s="58"/>
+      <c r="E106" s="58"/>
+      <c r="F106" s="58"/>
+      <c r="G106" s="58"/>
+      <c r="H106" s="58"/>
+      <c r="I106" s="58"/>
+      <c r="J106" s="58"/>
+      <c r="K106" s="58"/>
+      <c r="L106" s="58"/>
+      <c r="M106" s="58"/>
+      <c r="N106" s="58"/>
+    </row>
+    <row r="107" ht="39.0" customHeight="1">
+      <c r="A107" s="57" t="s">
         <v>955</v>
       </c>
-      <c r="B105" s="68"/>
-      <c r="C105" s="68"/>
-      <c r="D105" s="68"/>
-      <c r="E105" s="68"/>
-      <c r="F105" s="68"/>
-      <c r="G105" s="68"/>
-      <c r="H105" s="68"/>
-      <c r="I105" s="68"/>
-      <c r="J105" s="68"/>
-      <c r="K105" s="68"/>
-      <c r="L105" s="68"/>
-      <c r="M105" s="68"/>
-      <c r="N105" s="68"/>
-    </row>
-    <row r="106" ht="27.0" customHeight="1">
-      <c r="A106" s="67" t="s">
+      <c r="B107" s="58"/>
+      <c r="C107" s="58"/>
+      <c r="D107" s="58"/>
+      <c r="E107" s="58"/>
+      <c r="F107" s="58"/>
+      <c r="G107" s="58"/>
+      <c r="H107" s="58"/>
+      <c r="I107" s="58"/>
+      <c r="J107" s="58"/>
+      <c r="K107" s="58"/>
+      <c r="L107" s="58"/>
+      <c r="M107" s="58"/>
+      <c r="N107" s="58"/>
+    </row>
+    <row r="108" ht="37.5" customHeight="1">
+      <c r="A108" s="57" t="s">
         <v>956</v>
       </c>
-      <c r="B106" s="68"/>
-      <c r="C106" s="68"/>
-      <c r="D106" s="68"/>
-      <c r="E106" s="68"/>
-      <c r="F106" s="68"/>
-      <c r="G106" s="68"/>
-      <c r="H106" s="68"/>
-      <c r="I106" s="68"/>
-      <c r="J106" s="68"/>
-      <c r="K106" s="68"/>
-      <c r="L106" s="68"/>
-      <c r="M106" s="68"/>
-      <c r="N106" s="68"/>
-    </row>
-    <row r="107" ht="39.0" customHeight="1">
-      <c r="A107" s="67" t="s">
+      <c r="B108" s="58"/>
+      <c r="C108" s="58"/>
+      <c r="D108" s="58"/>
+      <c r="E108" s="58"/>
+      <c r="F108" s="58"/>
+      <c r="G108" s="58"/>
+      <c r="H108" s="58"/>
+      <c r="I108" s="58"/>
+      <c r="J108" s="58"/>
+      <c r="K108" s="58"/>
+      <c r="L108" s="58"/>
+      <c r="M108" s="58"/>
+      <c r="N108" s="58"/>
+    </row>
+    <row r="109" ht="32.25" customHeight="1">
+      <c r="A109" s="57" t="s">
         <v>957</v>
       </c>
-      <c r="B107" s="68"/>
-      <c r="C107" s="68"/>
-      <c r="D107" s="68"/>
-      <c r="E107" s="68"/>
-      <c r="F107" s="68"/>
-      <c r="G107" s="68"/>
-      <c r="H107" s="68"/>
-      <c r="I107" s="68"/>
-      <c r="J107" s="68"/>
-      <c r="K107" s="68"/>
-      <c r="L107" s="68"/>
-      <c r="M107" s="68"/>
-      <c r="N107" s="68"/>
-    </row>
-    <row r="108" ht="37.5" customHeight="1">
-      <c r="A108" s="67" t="s">
+      <c r="B109" s="58"/>
+      <c r="C109" s="58"/>
+      <c r="D109" s="58"/>
+      <c r="E109" s="58"/>
+      <c r="F109" s="58"/>
+      <c r="G109" s="58"/>
+      <c r="H109" s="58"/>
+      <c r="I109" s="58"/>
+      <c r="J109" s="58"/>
+      <c r="K109" s="58"/>
+      <c r="L109" s="58"/>
+      <c r="M109" s="58"/>
+      <c r="N109" s="58"/>
+    </row>
+    <row r="110" ht="27.75" customHeight="1">
+      <c r="A110" s="57" t="s">
         <v>958</v>
       </c>
-      <c r="B108" s="68"/>
-      <c r="C108" s="68"/>
-      <c r="D108" s="68"/>
-      <c r="E108" s="68"/>
-      <c r="F108" s="68"/>
-      <c r="G108" s="68"/>
-      <c r="H108" s="68"/>
-      <c r="I108" s="68"/>
-      <c r="J108" s="68"/>
-      <c r="K108" s="68"/>
-      <c r="L108" s="68"/>
-      <c r="M108" s="68"/>
-      <c r="N108" s="68"/>
-    </row>
-    <row r="109" ht="32.25" customHeight="1">
-      <c r="A109" s="67" t="s">
+      <c r="B110" s="58"/>
+      <c r="C110" s="58"/>
+      <c r="D110" s="58"/>
+      <c r="E110" s="58"/>
+      <c r="F110" s="58"/>
+      <c r="G110" s="58"/>
+      <c r="H110" s="58"/>
+      <c r="I110" s="58"/>
+      <c r="J110" s="58"/>
+      <c r="K110" s="58"/>
+      <c r="L110" s="58"/>
+      <c r="M110" s="58"/>
+      <c r="N110" s="58"/>
+    </row>
+    <row r="111" ht="27.0" customHeight="1">
+      <c r="A111" s="57" t="s">
         <v>959</v>
       </c>
-      <c r="B109" s="68"/>
-      <c r="C109" s="68"/>
-      <c r="D109" s="68"/>
-      <c r="E109" s="68"/>
-      <c r="F109" s="68"/>
-      <c r="G109" s="68"/>
-      <c r="H109" s="68"/>
-      <c r="I109" s="68"/>
-      <c r="J109" s="68"/>
-      <c r="K109" s="68"/>
-      <c r="L109" s="68"/>
-      <c r="M109" s="68"/>
-      <c r="N109" s="68"/>
-    </row>
-    <row r="110" ht="27.75" customHeight="1">
-      <c r="A110" s="67" t="s">
+      <c r="B111" s="58"/>
+      <c r="C111" s="58"/>
+      <c r="D111" s="58"/>
+      <c r="E111" s="58"/>
+      <c r="F111" s="58"/>
+      <c r="G111" s="58"/>
+      <c r="H111" s="58"/>
+      <c r="I111" s="58"/>
+      <c r="J111" s="58"/>
+      <c r="K111" s="58"/>
+      <c r="L111" s="58"/>
+      <c r="M111" s="58"/>
+      <c r="N111" s="58"/>
+    </row>
+    <row r="112" ht="36.0" customHeight="1">
+      <c r="A112" s="57" t="s">
         <v>960</v>
       </c>
-      <c r="B110" s="68"/>
-      <c r="C110" s="68"/>
-      <c r="D110" s="68"/>
-      <c r="E110" s="68"/>
-      <c r="F110" s="68"/>
-      <c r="G110" s="68"/>
-      <c r="H110" s="68"/>
-      <c r="I110" s="68"/>
-      <c r="J110" s="68"/>
-      <c r="K110" s="68"/>
-      <c r="L110" s="68"/>
-      <c r="M110" s="68"/>
-      <c r="N110" s="68"/>
-    </row>
-    <row r="111" ht="27.0" customHeight="1">
-      <c r="A111" s="67" t="s">
+      <c r="B112" s="58"/>
+      <c r="C112" s="58"/>
+      <c r="D112" s="58"/>
+      <c r="E112" s="58"/>
+      <c r="F112" s="58"/>
+      <c r="G112" s="58"/>
+      <c r="H112" s="58"/>
+      <c r="I112" s="58"/>
+      <c r="J112" s="58"/>
+      <c r="K112" s="58"/>
+      <c r="L112" s="58"/>
+      <c r="M112" s="58"/>
+      <c r="N112" s="58"/>
+    </row>
+    <row r="113" ht="48.0" customHeight="1">
+      <c r="A113" s="57" t="s">
         <v>961</v>
       </c>
-      <c r="B111" s="68"/>
-      <c r="C111" s="68"/>
-      <c r="D111" s="68"/>
-      <c r="E111" s="68"/>
-      <c r="F111" s="68"/>
-      <c r="G111" s="68"/>
-      <c r="H111" s="68"/>
-      <c r="I111" s="68"/>
-      <c r="J111" s="68"/>
-      <c r="K111" s="68"/>
-      <c r="L111" s="68"/>
-      <c r="M111" s="68"/>
-      <c r="N111" s="68"/>
-    </row>
-    <row r="112" ht="36.0" customHeight="1">
-      <c r="A112" s="67" t="s">
+      <c r="B113" s="58"/>
+      <c r="C113" s="58"/>
+      <c r="D113" s="58"/>
+      <c r="E113" s="58"/>
+      <c r="F113" s="58"/>
+      <c r="G113" s="58"/>
+      <c r="H113" s="58"/>
+      <c r="I113" s="58"/>
+      <c r="J113" s="58"/>
+      <c r="K113" s="58"/>
+      <c r="L113" s="58"/>
+      <c r="M113" s="58"/>
+      <c r="N113" s="58"/>
+    </row>
+    <row r="114" ht="34.5" customHeight="1">
+      <c r="A114" s="57" t="s">
         <v>962</v>
       </c>
-      <c r="B112" s="68"/>
-      <c r="C112" s="68"/>
-      <c r="D112" s="68"/>
-      <c r="E112" s="68"/>
-      <c r="F112" s="68"/>
-      <c r="G112" s="68"/>
-      <c r="H112" s="68"/>
-      <c r="I112" s="68"/>
-      <c r="J112" s="68"/>
-      <c r="K112" s="68"/>
-      <c r="L112" s="68"/>
-      <c r="M112" s="68"/>
-      <c r="N112" s="68"/>
-    </row>
-    <row r="113" ht="48.0" customHeight="1">
-      <c r="A113" s="67" t="s">
+      <c r="B114" s="58"/>
+      <c r="C114" s="58"/>
+      <c r="D114" s="58"/>
+      <c r="E114" s="58"/>
+      <c r="F114" s="58"/>
+      <c r="G114" s="58"/>
+      <c r="H114" s="58"/>
+      <c r="I114" s="58"/>
+      <c r="J114" s="58"/>
+      <c r="K114" s="58"/>
+      <c r="L114" s="58"/>
+      <c r="M114" s="58"/>
+      <c r="N114" s="58"/>
+    </row>
+    <row r="115" ht="35.25" customHeight="1">
+      <c r="A115" s="57" t="s">
         <v>963</v>
       </c>
-      <c r="B113" s="68"/>
-      <c r="C113" s="68"/>
-      <c r="D113" s="68"/>
-      <c r="E113" s="68"/>
-      <c r="F113" s="68"/>
-      <c r="G113" s="68"/>
-      <c r="H113" s="68"/>
-      <c r="I113" s="68"/>
-      <c r="J113" s="68"/>
-      <c r="K113" s="68"/>
-      <c r="L113" s="68"/>
-      <c r="M113" s="68"/>
-      <c r="N113" s="68"/>
-    </row>
-    <row r="114" ht="34.5" customHeight="1">
-      <c r="A114" s="67" t="s">
+      <c r="B115" s="58"/>
+      <c r="C115" s="58"/>
+      <c r="D115" s="58"/>
+      <c r="E115" s="58"/>
+      <c r="F115" s="58"/>
+      <c r="G115" s="58"/>
+      <c r="H115" s="58"/>
+      <c r="I115" s="58"/>
+      <c r="J115" s="58"/>
+      <c r="K115" s="58"/>
+      <c r="L115" s="58"/>
+      <c r="M115" s="58"/>
+      <c r="N115" s="58"/>
+    </row>
+    <row r="116" ht="39.75" customHeight="1">
+      <c r="A116" s="57" t="s">
         <v>964</v>
       </c>
-      <c r="B114" s="68"/>
-      <c r="C114" s="68"/>
-      <c r="D114" s="68"/>
-      <c r="E114" s="68"/>
-      <c r="F114" s="68"/>
-      <c r="G114" s="68"/>
-      <c r="H114" s="68"/>
-      <c r="I114" s="68"/>
-      <c r="J114" s="68"/>
-      <c r="K114" s="68"/>
-      <c r="L114" s="68"/>
-      <c r="M114" s="68"/>
-      <c r="N114" s="68"/>
-    </row>
-    <row r="115" ht="35.25" customHeight="1">
-      <c r="A115" s="67" t="s">
+      <c r="B116" s="58"/>
+      <c r="C116" s="58"/>
+      <c r="D116" s="58"/>
+      <c r="E116" s="58"/>
+      <c r="F116" s="58"/>
+      <c r="G116" s="58"/>
+      <c r="H116" s="58"/>
+      <c r="I116" s="58"/>
+      <c r="J116" s="58"/>
+      <c r="K116" s="58"/>
+      <c r="L116" s="58"/>
+      <c r="M116" s="58"/>
+      <c r="N116" s="58"/>
+    </row>
+    <row r="117" ht="30.0" customHeight="1">
+      <c r="A117" s="57" t="s">
         <v>965</v>
       </c>
-      <c r="B115" s="68"/>
-      <c r="C115" s="68"/>
-      <c r="D115" s="68"/>
-      <c r="E115" s="68"/>
-      <c r="F115" s="68"/>
-      <c r="G115" s="68"/>
-      <c r="H115" s="68"/>
-      <c r="I115" s="68"/>
-      <c r="J115" s="68"/>
-      <c r="K115" s="68"/>
-      <c r="L115" s="68"/>
-      <c r="M115" s="68"/>
-      <c r="N115" s="68"/>
-    </row>
-    <row r="116" ht="39.75" customHeight="1">
-      <c r="A116" s="67" t="s">
+      <c r="B117" s="58"/>
+      <c r="C117" s="58"/>
+      <c r="D117" s="58"/>
+      <c r="E117" s="58"/>
+      <c r="F117" s="58"/>
+      <c r="G117" s="58"/>
+      <c r="H117" s="58"/>
+      <c r="I117" s="58"/>
+      <c r="J117" s="58"/>
+      <c r="K117" s="58"/>
+      <c r="L117" s="58"/>
+      <c r="M117" s="58"/>
+      <c r="N117" s="58"/>
+    </row>
+    <row r="118" ht="31.5" customHeight="1">
+      <c r="A118" s="57" t="s">
         <v>966</v>
       </c>
-      <c r="B116" s="68"/>
-      <c r="C116" s="68"/>
-      <c r="D116" s="68"/>
-      <c r="E116" s="68"/>
-      <c r="F116" s="68"/>
-      <c r="G116" s="68"/>
-      <c r="H116" s="68"/>
-      <c r="I116" s="68"/>
-      <c r="J116" s="68"/>
-      <c r="K116" s="68"/>
-      <c r="L116" s="68"/>
-      <c r="M116" s="68"/>
-      <c r="N116" s="68"/>
-    </row>
-    <row r="117" ht="30.0" customHeight="1">
-      <c r="A117" s="67" t="s">
+      <c r="B118" s="58"/>
+      <c r="C118" s="58"/>
+      <c r="D118" s="58"/>
+      <c r="E118" s="58"/>
+      <c r="F118" s="58"/>
+      <c r="G118" s="58"/>
+      <c r="H118" s="58"/>
+      <c r="I118" s="58"/>
+      <c r="J118" s="58"/>
+      <c r="K118" s="58"/>
+      <c r="L118" s="58"/>
+      <c r="M118" s="58"/>
+      <c r="N118" s="58"/>
+    </row>
+    <row r="119" ht="34.5" customHeight="1">
+      <c r="A119" s="57" t="s">
         <v>967</v>
       </c>
-      <c r="B117" s="68"/>
-      <c r="C117" s="68"/>
-      <c r="D117" s="68"/>
-      <c r="E117" s="68"/>
-      <c r="F117" s="68"/>
-      <c r="G117" s="68"/>
-      <c r="H117" s="68"/>
-      <c r="I117" s="68"/>
-      <c r="J117" s="68"/>
-      <c r="K117" s="68"/>
-      <c r="L117" s="68"/>
-      <c r="M117" s="68"/>
-      <c r="N117" s="68"/>
-    </row>
-    <row r="118" ht="31.5" customHeight="1">
-      <c r="A118" s="67" t="s">
+      <c r="B119" s="58"/>
+      <c r="C119" s="58"/>
+      <c r="D119" s="58"/>
+      <c r="E119" s="58"/>
+      <c r="F119" s="58"/>
+      <c r="G119" s="58"/>
+      <c r="H119" s="58"/>
+      <c r="I119" s="58"/>
+      <c r="J119" s="58"/>
+      <c r="K119" s="58"/>
+      <c r="L119" s="58"/>
+      <c r="M119" s="58"/>
+      <c r="N119" s="58"/>
+    </row>
+    <row r="120" ht="29.25" customHeight="1">
+      <c r="A120" s="57" t="s">
         <v>968</v>
       </c>
-      <c r="B118" s="68"/>
-      <c r="C118" s="68"/>
-      <c r="D118" s="68"/>
-      <c r="E118" s="68"/>
-      <c r="F118" s="68"/>
-      <c r="G118" s="68"/>
-      <c r="H118" s="68"/>
-      <c r="I118" s="68"/>
-      <c r="J118" s="68"/>
-      <c r="K118" s="68"/>
-      <c r="L118" s="68"/>
-      <c r="M118" s="68"/>
-      <c r="N118" s="68"/>
-    </row>
-    <row r="119" ht="34.5" customHeight="1">
-      <c r="A119" s="67" t="s">
+      <c r="B120" s="58"/>
+      <c r="C120" s="58"/>
+      <c r="D120" s="58"/>
+      <c r="E120" s="58"/>
+      <c r="F120" s="58"/>
+      <c r="G120" s="58"/>
+      <c r="H120" s="58"/>
+      <c r="I120" s="58"/>
+      <c r="J120" s="58"/>
+      <c r="K120" s="58"/>
+      <c r="L120" s="58"/>
+      <c r="M120" s="58"/>
+      <c r="N120" s="58"/>
+    </row>
+    <row r="121">
+      <c r="A121" s="57" t="s">
         <v>969</v>
       </c>
-      <c r="B119" s="68"/>
-      <c r="C119" s="68"/>
-      <c r="D119" s="68"/>
-      <c r="E119" s="68"/>
-      <c r="F119" s="68"/>
-      <c r="G119" s="68"/>
-      <c r="H119" s="68"/>
-      <c r="I119" s="68"/>
-      <c r="J119" s="68"/>
-      <c r="K119" s="68"/>
-      <c r="L119" s="68"/>
-      <c r="M119" s="68"/>
-      <c r="N119" s="68"/>
-    </row>
-    <row r="120" ht="29.25" customHeight="1">
-      <c r="A120" s="67" t="s">
+      <c r="B121" s="58"/>
+      <c r="C121" s="58"/>
+      <c r="D121" s="58"/>
+      <c r="E121" s="58"/>
+      <c r="F121" s="58"/>
+      <c r="G121" s="58"/>
+      <c r="H121" s="58"/>
+      <c r="I121" s="58"/>
+      <c r="J121" s="58"/>
+      <c r="K121" s="58"/>
+      <c r="L121" s="58"/>
+      <c r="M121" s="58"/>
+      <c r="N121" s="58"/>
+    </row>
+    <row r="122">
+      <c r="A122" s="57" t="s">
         <v>970</v>
       </c>
-      <c r="B120" s="68"/>
-      <c r="C120" s="68"/>
-      <c r="D120" s="68"/>
-      <c r="E120" s="68"/>
-      <c r="F120" s="68"/>
-      <c r="G120" s="68"/>
-      <c r="H120" s="68"/>
-      <c r="I120" s="68"/>
-      <c r="J120" s="68"/>
-      <c r="K120" s="68"/>
-      <c r="L120" s="68"/>
-      <c r="M120" s="68"/>
-      <c r="N120" s="68"/>
-    </row>
-    <row r="121">
-      <c r="A121" s="67" t="s">
+      <c r="B122" s="58"/>
+      <c r="C122" s="58"/>
+      <c r="D122" s="58"/>
+      <c r="E122" s="58"/>
+      <c r="F122" s="58"/>
+      <c r="G122" s="58"/>
+      <c r="H122" s="58"/>
+      <c r="I122" s="58"/>
+      <c r="J122" s="58"/>
+      <c r="K122" s="58"/>
+      <c r="L122" s="58"/>
+      <c r="M122" s="58"/>
+      <c r="N122" s="58"/>
+    </row>
+    <row r="123" ht="34.5" customHeight="1">
+      <c r="A123" s="57" t="s">
         <v>971</v>
       </c>
-      <c r="B121" s="68"/>
-      <c r="C121" s="68"/>
-      <c r="D121" s="68"/>
-      <c r="E121" s="68"/>
-      <c r="F121" s="68"/>
-      <c r="G121" s="68"/>
-      <c r="H121" s="68"/>
-      <c r="I121" s="68"/>
-      <c r="J121" s="68"/>
-      <c r="K121" s="68"/>
-      <c r="L121" s="68"/>
-      <c r="M121" s="68"/>
-      <c r="N121" s="68"/>
-    </row>
-    <row r="122">
-      <c r="A122" s="67" t="s">
+      <c r="B123" s="58"/>
+      <c r="C123" s="58"/>
+      <c r="D123" s="58"/>
+      <c r="E123" s="58"/>
+      <c r="F123" s="58"/>
+      <c r="G123" s="58"/>
+      <c r="H123" s="58"/>
+      <c r="I123" s="58"/>
+      <c r="J123" s="58"/>
+      <c r="K123" s="58"/>
+      <c r="L123" s="58"/>
+      <c r="M123" s="58"/>
+      <c r="N123" s="58"/>
+    </row>
+    <row r="124" ht="30.0" customHeight="1">
+      <c r="A124" s="57" t="s">
         <v>972</v>
       </c>
-      <c r="B122" s="68"/>
-      <c r="C122" s="68"/>
-      <c r="D122" s="68"/>
-      <c r="E122" s="68"/>
-      <c r="F122" s="68"/>
-      <c r="G122" s="68"/>
-      <c r="H122" s="68"/>
-      <c r="I122" s="68"/>
-      <c r="J122" s="68"/>
-      <c r="K122" s="68"/>
-      <c r="L122" s="68"/>
-      <c r="M122" s="68"/>
-      <c r="N122" s="68"/>
-    </row>
-    <row r="123" ht="34.5" customHeight="1">
-      <c r="A123" s="67" t="s">
+      <c r="B124" s="58"/>
+      <c r="C124" s="58"/>
+      <c r="D124" s="58"/>
+      <c r="E124" s="58"/>
+      <c r="F124" s="58"/>
+      <c r="G124" s="58"/>
+      <c r="H124" s="58"/>
+      <c r="I124" s="58"/>
+      <c r="J124" s="58"/>
+      <c r="K124" s="58"/>
+      <c r="L124" s="58"/>
+      <c r="M124" s="58"/>
+      <c r="N124" s="58"/>
+    </row>
+    <row r="125">
+      <c r="A125" s="59" t="s">
         <v>973</v>
       </c>
-      <c r="B123" s="68"/>
-      <c r="C123" s="68"/>
-      <c r="D123" s="68"/>
-      <c r="E123" s="68"/>
-      <c r="F123" s="68"/>
-      <c r="G123" s="68"/>
-      <c r="H123" s="68"/>
-      <c r="I123" s="68"/>
-      <c r="J123" s="68"/>
-      <c r="K123" s="68"/>
-      <c r="L123" s="68"/>
-      <c r="M123" s="68"/>
-      <c r="N123" s="68"/>
-    </row>
-    <row r="124" ht="30.0" customHeight="1">
-      <c r="A124" s="67" t="s">
-        <v>974</v>
-      </c>
-      <c r="B124" s="68"/>
-      <c r="C124" s="68"/>
-      <c r="D124" s="68"/>
-      <c r="E124" s="68"/>
-      <c r="F124" s="68"/>
-      <c r="G124" s="68"/>
-      <c r="H124" s="68"/>
-      <c r="I124" s="68"/>
-      <c r="J124" s="68"/>
-      <c r="K124" s="68"/>
-      <c r="L124" s="68"/>
-      <c r="M124" s="68"/>
-      <c r="N124" s="68"/>
-    </row>
-    <row r="125">
-      <c r="A125" s="69" t="s">
-        <v>975</v>
-      </c>
-      <c r="B125" s="68"/>
-      <c r="C125" s="68"/>
-      <c r="D125" s="68"/>
-      <c r="E125" s="68"/>
-      <c r="F125" s="68"/>
-      <c r="G125" s="68"/>
-      <c r="H125" s="68"/>
-      <c r="I125" s="68"/>
-      <c r="J125" s="68"/>
-      <c r="K125" s="68"/>
-      <c r="L125" s="68"/>
-      <c r="M125" s="68"/>
-      <c r="N125" s="68"/>
+      <c r="B125" s="58"/>
+      <c r="C125" s="58"/>
+      <c r="D125" s="58"/>
+      <c r="E125" s="58"/>
+      <c r="F125" s="58"/>
+      <c r="G125" s="58"/>
+      <c r="H125" s="58"/>
+      <c r="I125" s="58"/>
+      <c r="J125" s="58"/>
+      <c r="K125" s="58"/>
+      <c r="L125" s="58"/>
+      <c r="M125" s="58"/>
+      <c r="N125" s="58"/>
     </row>
     <row r="126">
-      <c r="A126" s="68"/>
-      <c r="B126" s="68"/>
-      <c r="C126" s="68"/>
-      <c r="D126" s="68"/>
-      <c r="E126" s="68"/>
-      <c r="F126" s="68"/>
-      <c r="G126" s="68"/>
-      <c r="H126" s="68"/>
-      <c r="I126" s="68"/>
-      <c r="J126" s="68"/>
-      <c r="K126" s="68"/>
-      <c r="L126" s="68"/>
-      <c r="M126" s="68"/>
-      <c r="N126" s="68"/>
+      <c r="A126" s="58"/>
+      <c r="B126" s="58"/>
+      <c r="C126" s="58"/>
+      <c r="D126" s="58"/>
+      <c r="E126" s="58"/>
+      <c r="F126" s="58"/>
+      <c r="G126" s="58"/>
+      <c r="H126" s="58"/>
+      <c r="I126" s="58"/>
+      <c r="J126" s="58"/>
+      <c r="K126" s="58"/>
+      <c r="L126" s="58"/>
+      <c r="M126" s="58"/>
+      <c r="N126" s="58"/>
     </row>
   </sheetData>
   <drawing r:id="rId1"/>

--- a/docs/public_policies.xlsx
+++ b/docs/public_policies.xlsx
@@ -8,19 +8,19 @@
     <sheet state="visible" name="Página7" sheetId="3" r:id="rId6"/>
   </sheets>
   <definedNames>
-    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'POLITICAS PUBLICAS (BIOLOGICAS '!$B$1:$AG$38</definedName>
+    <definedName hidden="1" localSheetId="0" name="_xlnm._FilterDatabase">'POLITICAS PUBLICAS (BIOLOGICAS '!$B$1:$AG$37</definedName>
   </definedNames>
   <calcPr/>
   <extLst>
     <ext uri="GoogleSheetsCustomDataVersion2">
-      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="ujEjBk6bUp/+bsZgACShNTFuYsIgBFnyR88Ye4xecn8="/>
+      <go:sheetsCustomData xmlns:go="http://customooxmlschemas.google.com/" r:id="rId7" roundtripDataChecksum="2A+tcrpxsHxMfNoc78YAN7z6RpbENnhate94dJhXdSE="/>
     </ext>
   </extLst>
 </workbook>
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1481" uniqueCount="974">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1466" uniqueCount="965">
   <si>
     <t>resourceID</t>
   </si>
@@ -839,72 +839,6 @@
   </si>
   <si>
     <t>Aprova execução da Convenção no âmbito nacional.</t>
-  </si>
-  <si>
-    <t>Sistema Nacional de Unidades de Conservação da Natureza — SNUC.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Lei </t>
-  </si>
-  <si>
-    <t>Nº 9.985, DE 18 DE JULHO DE 2000.</t>
-  </si>
-  <si>
-    <t>Para os fins previstos nesta Lei, entende-se por:
-I - unidade de conservação//II - conservação da natureza//III - diversidade biológica//IV - recurso ambiental// V - preservação//VI - proteção integral//VII - conservação in situ//VIII - manejo//IX - uso indireto//X - uso direto//XI - uso sustentável//XII - extrativismo//XIII - recuperação//XIV - restauração//XVI - zoneamento//XVII - plano de manejo//XVIII - zona de amortecimento//XIX - corredores ecológicos</t>
-  </si>
-  <si>
-    <t>Artigo 2º I//II//III//IV//V// VI//VII//VIII//IX// X//XI//XII// XIII//XIV//XVI// XVII//XVIII//XIX</t>
-  </si>
-  <si>
-    <t>Artigo 57º  Indigenas//XIII - Comunidades Tradicionais</t>
-  </si>
-  <si>
-    <t>Artigo 57º//Artigo 4º  XIII</t>
-  </si>
-  <si>
-    <t xml:space="preserve">
-BRASIL. Presidência da República. Decreto nº 2.519, de 16 de março de 1998. Promulga a Convenção sobre Diversidade Biológica, assinada no Rio de Janeiro, em 05 de junho de 1992. Diário Oficial da União, Brasília, DF, 17 mar 1998. Seção 1, p. 1.
-____. Ministério do Meio Ambiente. Quarto Relatório Nacional para a Convenção sobre Diversidade Biológica. Brasília: MMA, 2010.</t>
-  </si>
-  <si>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color rgb="FF000000"/>
-        <sz val="12.0"/>
-        <u/>
-      </rPr>
-      <t>https://www.gov.br/mma/pt-br/assuntos/biodiversidade-e-biomas/areas-protegidas/sistema-nacional-de-unidades-de-conservacao-da-natureza-snuc</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color rgb="FF000000"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t xml:space="preserve"> ; </t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color rgb="FF000000"/>
-        <sz val="12.0"/>
-        <u/>
-      </rPr>
-      <t>https://www.planalto.gov.br/ccivil_03/leis/l9985.htm</t>
-    </r>
-    <r>
-      <rPr>
-        <rFont val="Times New Roman"/>
-        <color rgb="FF000000"/>
-        <sz val="12.0"/>
-      </rPr>
-      <t xml:space="preserve"> </t>
-    </r>
-  </si>
-  <si>
-    <t xml:space="preserve">Detalha categorias de UC e instrumentos legais. </t>
   </si>
   <si>
     <t>Id. Ministério do Meio Ambiente. Diretrizes e prioridades do plano de ação para implementação da Política Nacional da Biodiversidade. Brasília: MMA, 2006. (Série Biodiversidade, 22).</t>
@@ -1872,6 +1806,9 @@
   </si>
   <si>
     <t>Lei da Biodiversidade</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Lei </t>
   </si>
   <si>
     <t>Nº 13.123, DE 20 DE MAIO DE 2015</t>
@@ -5903,21 +5840,21 @@
       <c r="AF22" s="13"/>
       <c r="AG22" s="13"/>
     </row>
-    <row r="23" ht="132.75" customHeight="1">
+    <row r="23" ht="76.5" customHeight="1">
       <c r="A23" s="14">
         <v>22.0</v>
       </c>
-      <c r="B23" s="14" t="s">
+      <c r="B23" s="6" t="s">
         <v>223</v>
       </c>
       <c r="C23" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D23" s="12" t="s">
         <v>224</v>
       </c>
-      <c r="D23" s="12" t="s">
+      <c r="E23" s="12" t="s">
         <v>225</v>
-      </c>
-      <c r="E23" s="12" t="s">
-        <v>43</v>
       </c>
       <c r="F23" s="12" t="s">
         <v>44</v>
@@ -5928,7 +5865,7 @@
       <c r="H23" s="12" t="s">
         <v>226</v>
       </c>
-      <c r="I23" s="24" t="s">
+      <c r="I23" s="12" t="s">
         <v>227</v>
       </c>
       <c r="J23" s="12" t="s">
@@ -5947,7 +5884,7 @@
         <v>166</v>
       </c>
       <c r="O23" s="12" t="s">
-        <v>185</v>
+        <v>194</v>
       </c>
       <c r="P23" s="12" t="s">
         <v>232</v>
@@ -5970,7 +5907,7 @@
       <c r="AF23" s="13"/>
       <c r="AG23" s="13"/>
     </row>
-    <row r="24" ht="76.5" customHeight="1">
+    <row r="24" ht="201.75" customHeight="1">
       <c r="A24" s="5">
         <v>23.0</v>
       </c>
@@ -5978,7 +5915,7 @@
         <v>233</v>
       </c>
       <c r="C24" s="12" t="s">
-        <v>28</v>
+        <v>78</v>
       </c>
       <c r="D24" s="12" t="s">
         <v>234</v>
@@ -5990,34 +5927,34 @@
         <v>44</v>
       </c>
       <c r="G24" s="12" t="s">
-        <v>83</v>
+        <v>236</v>
       </c>
       <c r="H24" s="12" t="s">
-        <v>236</v>
+        <v>237</v>
       </c>
       <c r="I24" s="12" t="s">
-        <v>237</v>
+        <v>238</v>
       </c>
       <c r="J24" s="12" t="s">
-        <v>238</v>
+        <v>239</v>
       </c>
       <c r="K24" s="12" t="s">
-        <v>239</v>
+        <v>240</v>
       </c>
       <c r="L24" s="12" t="s">
-        <v>240</v>
+        <v>241</v>
       </c>
       <c r="M24" s="10" t="s">
-        <v>241</v>
+        <v>242</v>
       </c>
       <c r="N24" s="18" t="s">
-        <v>166</v>
+        <v>110</v>
       </c>
       <c r="O24" s="12" t="s">
         <v>194</v>
       </c>
       <c r="P24" s="12" t="s">
-        <v>242</v>
+        <v>243</v>
       </c>
       <c r="Q24" s="13"/>
       <c r="R24" s="13"/>
@@ -6037,27 +5974,27 @@
       <c r="AF24" s="13"/>
       <c r="AG24" s="13"/>
     </row>
-    <row r="25" ht="201.75" customHeight="1">
+    <row r="25" ht="83.25" customHeight="1">
       <c r="A25" s="14">
         <v>24.0</v>
       </c>
       <c r="B25" s="6" t="s">
-        <v>243</v>
-      </c>
-      <c r="C25" s="12" t="s">
-        <v>78</v>
-      </c>
-      <c r="D25" s="12" t="s">
         <v>244</v>
       </c>
-      <c r="E25" s="12" t="s">
+      <c r="C25" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D25" s="17" t="s">
         <v>245</v>
       </c>
-      <c r="F25" s="12" t="s">
-        <v>44</v>
+      <c r="E25" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="F25" s="16" t="s">
+        <v>20</v>
       </c>
       <c r="G25" s="12" t="s">
-        <v>246</v>
+        <v>83</v>
       </c>
       <c r="H25" s="12" t="s">
         <v>247</v>
@@ -6065,23 +6002,23 @@
       <c r="I25" s="12" t="s">
         <v>248</v>
       </c>
-      <c r="J25" s="12" t="s">
+      <c r="J25" s="25" t="s">
         <v>249</v>
       </c>
       <c r="K25" s="12" t="s">
         <v>250</v>
       </c>
-      <c r="L25" s="12" t="s">
+      <c r="L25" s="16" t="s">
         <v>251</v>
       </c>
       <c r="M25" s="10" t="s">
         <v>252</v>
       </c>
       <c r="N25" s="18" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="O25" s="12" t="s">
-        <v>194</v>
+        <v>185</v>
       </c>
       <c r="P25" s="12" t="s">
         <v>253</v>
@@ -6104,7 +6041,7 @@
       <c r="AF25" s="13"/>
       <c r="AG25" s="13"/>
     </row>
-    <row r="26" ht="83.25" customHeight="1">
+    <row r="26" ht="15.75" customHeight="1">
       <c r="A26" s="5">
         <v>25.0</v>
       </c>
@@ -6112,46 +6049,46 @@
         <v>254</v>
       </c>
       <c r="C26" s="16" t="s">
-        <v>17</v>
+        <v>41</v>
       </c>
       <c r="D26" s="17" t="s">
         <v>255</v>
       </c>
-      <c r="E26" s="17" t="s">
+      <c r="E26" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F26" s="16" t="s">
+        <v>44</v>
+      </c>
+      <c r="G26" s="12" t="s">
         <v>256</v>
       </c>
-      <c r="F26" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G26" s="12" t="s">
-        <v>83</v>
-      </c>
       <c r="H26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I26" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J26" s="12" t="s">
         <v>257</v>
       </c>
-      <c r="I26" s="12" t="s">
+      <c r="K26" s="12" t="s">
         <v>258</v>
       </c>
-      <c r="J26" s="25" t="s">
+      <c r="L26" s="16" t="s">
         <v>259</v>
       </c>
-      <c r="K26" s="12" t="s">
+      <c r="M26" s="26" t="s">
         <v>260</v>
       </c>
-      <c r="L26" s="16" t="s">
+      <c r="N26" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="O26" s="12" t="s">
         <v>261</v>
       </c>
-      <c r="M26" s="10" t="s">
+      <c r="P26" s="12" t="s">
         <v>262</v>
-      </c>
-      <c r="N26" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="O26" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P26" s="12" t="s">
-        <v>263</v>
       </c>
       <c r="Q26" s="13"/>
       <c r="R26" s="13"/>
@@ -6176,49 +6113,49 @@
         <v>26.0</v>
       </c>
       <c r="B27" s="6" t="s">
+        <v>263</v>
+      </c>
+      <c r="C27" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D27" s="17" t="s">
         <v>264</v>
       </c>
-      <c r="C27" s="16" t="s">
-        <v>41</v>
-      </c>
-      <c r="D27" s="17" t="s">
+      <c r="E27" s="17" t="s">
+        <v>19</v>
+      </c>
+      <c r="F27" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G27" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H27" s="12" t="s">
         <v>265</v>
       </c>
-      <c r="E27" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F27" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G27" s="12" t="s">
+      <c r="I27" s="12" t="s">
         <v>266</v>
       </c>
-      <c r="H27" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I27" s="12" t="s">
-        <v>21</v>
-      </c>
       <c r="J27" s="12" t="s">
+        <v>181</v>
+      </c>
+      <c r="K27" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="L27" s="16" t="s">
         <v>267</v>
       </c>
-      <c r="K27" s="12" t="s">
+      <c r="M27" s="10" t="s">
         <v>268</v>
       </c>
-      <c r="L27" s="16" t="s">
+      <c r="N27" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="O27" s="12" t="s">
+        <v>261</v>
+      </c>
+      <c r="P27" s="12" t="s">
         <v>269</v>
-      </c>
-      <c r="M27" s="26" t="s">
-        <v>270</v>
-      </c>
-      <c r="N27" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="O27" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="P27" s="12" t="s">
-        <v>272</v>
       </c>
       <c r="Q27" s="13"/>
       <c r="R27" s="13"/>
@@ -6238,18 +6175,18 @@
       <c r="AF27" s="13"/>
       <c r="AG27" s="13"/>
     </row>
-    <row r="28" ht="15.75" customHeight="1">
+    <row r="28" ht="78.75" customHeight="1">
       <c r="A28" s="5">
         <v>27.0</v>
       </c>
       <c r="B28" s="6" t="s">
-        <v>273</v>
+        <v>270</v>
       </c>
       <c r="C28" s="16" t="s">
-        <v>17</v>
+        <v>78</v>
       </c>
       <c r="D28" s="17" t="s">
-        <v>274</v>
+        <v>271</v>
       </c>
       <c r="E28" s="17" t="s">
         <v>19</v>
@@ -6261,31 +6198,31 @@
         <v>83</v>
       </c>
       <c r="H28" s="12" t="s">
+        <v>272</v>
+      </c>
+      <c r="I28" s="12" t="s">
+        <v>273</v>
+      </c>
+      <c r="J28" s="12" t="s">
+        <v>274</v>
+      </c>
+      <c r="K28" s="12" t="s">
         <v>275</v>
       </c>
-      <c r="I28" s="12" t="s">
+      <c r="L28" s="16" t="s">
         <v>276</v>
       </c>
-      <c r="J28" s="12" t="s">
-        <v>181</v>
-      </c>
-      <c r="K28" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="L28" s="16" t="s">
+      <c r="M28" s="20" t="s">
         <v>277</v>
-      </c>
-      <c r="M28" s="10" t="s">
-        <v>278</v>
       </c>
       <c r="N28" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O28" s="12" t="s">
-        <v>271</v>
+        <v>167</v>
       </c>
       <c r="P28" s="12" t="s">
-        <v>279</v>
+        <v>278</v>
       </c>
       <c r="Q28" s="13"/>
       <c r="R28" s="13"/>
@@ -6305,21 +6242,21 @@
       <c r="AF28" s="13"/>
       <c r="AG28" s="13"/>
     </row>
-    <row r="29" ht="78.75" customHeight="1">
+    <row r="29" ht="15.75" customHeight="1">
       <c r="A29" s="14">
         <v>28.0</v>
       </c>
       <c r="B29" s="6" t="s">
+        <v>279</v>
+      </c>
+      <c r="C29" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D29" s="17" t="s">
         <v>280</v>
       </c>
-      <c r="C29" s="16" t="s">
-        <v>78</v>
-      </c>
-      <c r="D29" s="17" t="s">
+      <c r="E29" s="19" t="s">
         <v>281</v>
-      </c>
-      <c r="E29" s="17" t="s">
-        <v>19</v>
       </c>
       <c r="F29" s="16" t="s">
         <v>20</v>
@@ -6339,17 +6276,17 @@
       <c r="K29" s="12" t="s">
         <v>285</v>
       </c>
-      <c r="L29" s="16" t="s">
+      <c r="L29" s="12" t="s">
         <v>286</v>
       </c>
-      <c r="M29" s="20" t="s">
+      <c r="M29" s="10" t="s">
         <v>287</v>
       </c>
       <c r="N29" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O29" s="12" t="s">
-        <v>167</v>
+        <v>261</v>
       </c>
       <c r="P29" s="12" t="s">
         <v>288</v>
@@ -6372,7 +6309,7 @@
       <c r="AF29" s="13"/>
       <c r="AG29" s="13"/>
     </row>
-    <row r="30" ht="15.75" customHeight="1">
+    <row r="30" ht="100.5" customHeight="1">
       <c r="A30" s="5">
         <v>29.0</v>
       </c>
@@ -6380,46 +6317,46 @@
         <v>289</v>
       </c>
       <c r="C30" s="16" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D30" s="17" t="s">
         <v>290</v>
       </c>
-      <c r="E30" s="19" t="s">
-        <v>291</v>
+      <c r="E30" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="F30" s="16" t="s">
-        <v>20</v>
+        <v>44</v>
       </c>
       <c r="G30" s="12" t="s">
         <v>83</v>
       </c>
       <c r="H30" s="12" t="s">
+        <v>291</v>
+      </c>
+      <c r="I30" s="12" t="s">
         <v>292</v>
       </c>
-      <c r="I30" s="12" t="s">
+      <c r="J30" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K30" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L30" s="16" t="s">
         <v>293</v>
       </c>
-      <c r="J30" s="12" t="s">
+      <c r="M30" s="20" t="s">
         <v>294</v>
       </c>
-      <c r="K30" s="12" t="s">
+      <c r="N30" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="O30" s="12" t="s">
+        <v>194</v>
+      </c>
+      <c r="P30" s="12" t="s">
         <v>295</v>
-      </c>
-      <c r="L30" s="12" t="s">
-        <v>296</v>
-      </c>
-      <c r="M30" s="10" t="s">
-        <v>297</v>
-      </c>
-      <c r="N30" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="O30" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="P30" s="12" t="s">
-        <v>298</v>
       </c>
       <c r="Q30" s="13"/>
       <c r="R30" s="13"/>
@@ -6439,54 +6376,54 @@
       <c r="AF30" s="13"/>
       <c r="AG30" s="13"/>
     </row>
-    <row r="31" ht="100.5" customHeight="1">
+    <row r="31" ht="252.75" customHeight="1">
       <c r="A31" s="14">
         <v>30.0</v>
       </c>
-      <c r="B31" s="6" t="s">
-        <v>299</v>
+      <c r="B31" s="15" t="s">
+        <v>296</v>
       </c>
       <c r="C31" s="16" t="s">
-        <v>28</v>
-      </c>
-      <c r="D31" s="17" t="s">
-        <v>300</v>
+        <v>297</v>
+      </c>
+      <c r="D31" s="12" t="s">
+        <v>298</v>
       </c>
       <c r="E31" s="12" t="s">
-        <v>43</v>
+        <v>80</v>
       </c>
       <c r="F31" s="16" t="s">
         <v>44</v>
       </c>
       <c r="G31" s="12" t="s">
-        <v>83</v>
-      </c>
-      <c r="H31" s="12" t="s">
+        <v>299</v>
+      </c>
+      <c r="H31" s="17" t="s">
+        <v>300</v>
+      </c>
+      <c r="I31" s="17" t="s">
         <v>301</v>
       </c>
-      <c r="I31" s="12" t="s">
+      <c r="J31" s="17" t="s">
         <v>302</v>
       </c>
-      <c r="J31" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K31" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L31" s="16" t="s">
+      <c r="K31" s="17" t="s">
         <v>303</v>
       </c>
+      <c r="L31" s="27" t="s">
+        <v>304</v>
+      </c>
       <c r="M31" s="20" t="s">
-        <v>304</v>
+        <v>305</v>
       </c>
       <c r="N31" s="18" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="O31" s="12" t="s">
         <v>194</v>
       </c>
       <c r="P31" s="12" t="s">
-        <v>305</v>
+        <v>306</v>
       </c>
       <c r="Q31" s="13"/>
       <c r="R31" s="13"/>
@@ -6506,15 +6443,15 @@
       <c r="AF31" s="13"/>
       <c r="AG31" s="13"/>
     </row>
-    <row r="32" ht="252.75" customHeight="1">
+    <row r="32" ht="169.5" customHeight="1">
       <c r="A32" s="5">
         <v>31.0</v>
       </c>
       <c r="B32" s="15" t="s">
-        <v>306</v>
+        <v>307</v>
       </c>
       <c r="C32" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D32" s="12" t="s">
         <v>308</v>
@@ -6538,13 +6475,13 @@
         <v>312</v>
       </c>
       <c r="K32" s="17" t="s">
+        <v>190</v>
+      </c>
+      <c r="L32" s="27" t="s">
         <v>313</v>
       </c>
-      <c r="L32" s="27" t="s">
+      <c r="M32" s="10" t="s">
         <v>314</v>
-      </c>
-      <c r="M32" s="20" t="s">
-        <v>315</v>
       </c>
       <c r="N32" s="18" t="s">
         <v>24</v>
@@ -6553,7 +6490,7 @@
         <v>194</v>
       </c>
       <c r="P32" s="12" t="s">
-        <v>316</v>
+        <v>315</v>
       </c>
       <c r="Q32" s="13"/>
       <c r="R32" s="13"/>
@@ -6573,18 +6510,18 @@
       <c r="AF32" s="13"/>
       <c r="AG32" s="13"/>
     </row>
-    <row r="33" ht="169.5" customHeight="1">
+    <row r="33" ht="152.25" customHeight="1">
       <c r="A33" s="14">
         <v>32.0</v>
       </c>
       <c r="B33" s="15" t="s">
+        <v>316</v>
+      </c>
+      <c r="C33" s="16" t="s">
+        <v>297</v>
+      </c>
+      <c r="D33" s="12" t="s">
         <v>317</v>
-      </c>
-      <c r="C33" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="D33" s="12" t="s">
-        <v>318</v>
       </c>
       <c r="E33" s="12" t="s">
         <v>80</v>
@@ -6593,24 +6530,24 @@
         <v>44</v>
       </c>
       <c r="G33" s="12" t="s">
+        <v>318</v>
+      </c>
+      <c r="H33" s="17" t="s">
         <v>319</v>
       </c>
-      <c r="H33" s="17" t="s">
+      <c r="I33" s="17" t="s">
         <v>320</v>
       </c>
-      <c r="I33" s="17" t="s">
+      <c r="J33" s="17" t="s">
         <v>321</v>
       </c>
-      <c r="J33" s="17" t="s">
+      <c r="K33" s="17" t="s">
         <v>322</v>
-      </c>
-      <c r="K33" s="17" t="s">
-        <v>190</v>
       </c>
       <c r="L33" s="27" t="s">
         <v>323</v>
       </c>
-      <c r="M33" s="10" t="s">
+      <c r="M33" s="20" t="s">
         <v>324</v>
       </c>
       <c r="N33" s="18" t="s">
@@ -6640,7 +6577,7 @@
       <c r="AF33" s="13"/>
       <c r="AG33" s="13"/>
     </row>
-    <row r="34" ht="152.25" customHeight="1">
+    <row r="34" ht="210.0" customHeight="1">
       <c r="A34" s="5">
         <v>33.0</v>
       </c>
@@ -6648,7 +6585,7 @@
         <v>326</v>
       </c>
       <c r="C34" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D34" s="12" t="s">
         <v>327</v>
@@ -6707,7 +6644,7 @@
       <c r="AF34" s="13"/>
       <c r="AG34" s="13"/>
     </row>
-    <row r="35" ht="210.0" customHeight="1">
+    <row r="35" ht="286.5" customHeight="1">
       <c r="A35" s="14">
         <v>34.0</v>
       </c>
@@ -6715,7 +6652,7 @@
         <v>336</v>
       </c>
       <c r="C35" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D35" s="12" t="s">
         <v>337</v>
@@ -6774,7 +6711,7 @@
       <c r="AF35" s="13"/>
       <c r="AG35" s="13"/>
     </row>
-    <row r="36" ht="286.5" customHeight="1">
+    <row r="36" ht="227.25" customHeight="1">
       <c r="A36" s="5">
         <v>35.0</v>
       </c>
@@ -6782,7 +6719,7 @@
         <v>346</v>
       </c>
       <c r="C36" s="16" t="s">
-        <v>307</v>
+        <v>297</v>
       </c>
       <c r="D36" s="12" t="s">
         <v>347</v>
@@ -6803,16 +6740,16 @@
         <v>350</v>
       </c>
       <c r="J36" s="17" t="s">
+        <v>321</v>
+      </c>
+      <c r="K36" s="17" t="s">
         <v>351</v>
       </c>
-      <c r="K36" s="17" t="s">
+      <c r="L36" s="27" t="s">
         <v>352</v>
       </c>
-      <c r="L36" s="27" t="s">
+      <c r="M36" s="10" t="s">
         <v>353</v>
-      </c>
-      <c r="M36" s="20" t="s">
-        <v>354</v>
       </c>
       <c r="N36" s="18" t="s">
         <v>24</v>
@@ -6821,7 +6758,7 @@
         <v>194</v>
       </c>
       <c r="P36" s="12" t="s">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="Q36" s="13"/>
       <c r="R36" s="13"/>
@@ -6841,54 +6778,54 @@
       <c r="AF36" s="13"/>
       <c r="AG36" s="13"/>
     </row>
-    <row r="37" ht="227.25" customHeight="1">
+    <row r="37" ht="108.0" customHeight="1">
       <c r="A37" s="14">
         <v>36.0</v>
       </c>
-      <c r="B37" s="15" t="s">
+      <c r="B37" s="6" t="s">
+        <v>355</v>
+      </c>
+      <c r="C37" s="16" t="s">
+        <v>17</v>
+      </c>
+      <c r="D37" s="12" t="s">
         <v>356</v>
       </c>
-      <c r="C37" s="16" t="s">
-        <v>307</v>
-      </c>
-      <c r="D37" s="12" t="s">
+      <c r="E37" s="17" t="s">
+        <v>246</v>
+      </c>
+      <c r="F37" s="16" t="s">
+        <v>20</v>
+      </c>
+      <c r="G37" s="12" t="s">
+        <v>256</v>
+      </c>
+      <c r="H37" s="12" t="s">
         <v>357</v>
       </c>
-      <c r="E37" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F37" s="16" t="s">
-        <v>44</v>
-      </c>
-      <c r="G37" s="12" t="s">
+      <c r="I37" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="J37" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K37" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L37" s="16" t="s">
         <v>358</v>
       </c>
-      <c r="H37" s="17" t="s">
+      <c r="M37" s="20" t="s">
         <v>359</v>
       </c>
-      <c r="I37" s="17" t="s">
+      <c r="N37" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="O37" s="12" t="s">
         <v>360</v>
       </c>
-      <c r="J37" s="17" t="s">
-        <v>331</v>
-      </c>
-      <c r="K37" s="17" t="s">
+      <c r="P37" s="12" t="s">
         <v>361</v>
-      </c>
-      <c r="L37" s="27" t="s">
-        <v>362</v>
-      </c>
-      <c r="M37" s="10" t="s">
-        <v>363</v>
-      </c>
-      <c r="N37" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="O37" s="12" t="s">
-        <v>194</v>
-      </c>
-      <c r="P37" s="12" t="s">
-        <v>364</v>
       </c>
       <c r="Q37" s="13"/>
       <c r="R37" s="13"/>
@@ -6908,33 +6845,33 @@
       <c r="AF37" s="13"/>
       <c r="AG37" s="13"/>
     </row>
-    <row r="38" ht="108.0" customHeight="1">
+    <row r="38" ht="105.0" customHeight="1">
       <c r="A38" s="5">
         <v>37.0</v>
       </c>
-      <c r="B38" s="6" t="s">
-        <v>365</v>
-      </c>
-      <c r="C38" s="16" t="s">
-        <v>17</v>
+      <c r="B38" s="5" t="s">
+        <v>362</v>
+      </c>
+      <c r="C38" s="28" t="s">
+        <v>41</v>
       </c>
       <c r="D38" s="12" t="s">
-        <v>366</v>
-      </c>
-      <c r="E38" s="17" t="s">
+        <v>363</v>
+      </c>
+      <c r="E38" s="12" t="s">
+        <v>235</v>
+      </c>
+      <c r="F38" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G38" s="12" t="s">
+        <v>83</v>
+      </c>
+      <c r="H38" s="12" t="s">
+        <v>364</v>
+      </c>
+      <c r="I38" s="12" t="s">
         <v>256</v>
-      </c>
-      <c r="F38" s="16" t="s">
-        <v>20</v>
-      </c>
-      <c r="G38" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="H38" s="12" t="s">
-        <v>367</v>
-      </c>
-      <c r="I38" s="12" t="s">
-        <v>83</v>
       </c>
       <c r="J38" s="12" t="s">
         <v>21</v>
@@ -6942,20 +6879,20 @@
       <c r="K38" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="L38" s="16" t="s">
-        <v>368</v>
-      </c>
-      <c r="M38" s="20" t="s">
-        <v>369</v>
+      <c r="L38" s="12" t="s">
+        <v>365</v>
+      </c>
+      <c r="M38" s="10" t="s">
+        <v>366</v>
       </c>
       <c r="N38" s="18" t="s">
-        <v>110</v>
+        <v>166</v>
       </c>
       <c r="O38" s="12" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="P38" s="12" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="Q38" s="13"/>
       <c r="R38" s="13"/>
@@ -6975,21 +6912,21 @@
       <c r="AF38" s="13"/>
       <c r="AG38" s="13"/>
     </row>
-    <row r="39" ht="105.0" customHeight="1">
+    <row r="39" ht="147.75" customHeight="1">
       <c r="A39" s="14">
         <v>38.0</v>
       </c>
-      <c r="B39" s="5" t="s">
-        <v>372</v>
-      </c>
-      <c r="C39" s="28" t="s">
-        <v>41</v>
-      </c>
-      <c r="D39" s="12" t="s">
-        <v>373</v>
+      <c r="B39" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="C39" s="12" t="s">
+        <v>369</v>
+      </c>
+      <c r="D39" s="12">
+        <v>1988.0</v>
       </c>
       <c r="E39" s="12" t="s">
-        <v>245</v>
+        <v>43</v>
       </c>
       <c r="F39" s="12" t="s">
         <v>44</v>
@@ -6998,31 +6935,31 @@
         <v>83</v>
       </c>
       <c r="H39" s="12" t="s">
+        <v>370</v>
+      </c>
+      <c r="I39" s="12" t="s">
+        <v>371</v>
+      </c>
+      <c r="J39" s="12" t="s">
+        <v>372</v>
+      </c>
+      <c r="K39" s="12" t="s">
+        <v>373</v>
+      </c>
+      <c r="L39" s="12" t="s">
         <v>374</v>
       </c>
-      <c r="I39" s="12" t="s">
-        <v>266</v>
-      </c>
-      <c r="J39" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K39" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L39" s="12" t="s">
+      <c r="M39" s="20" t="s">
         <v>375</v>
-      </c>
-      <c r="M39" s="10" t="s">
-        <v>376</v>
       </c>
       <c r="N39" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O39" s="12" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="P39" s="12" t="s">
-        <v>377</v>
+        <v>376</v>
       </c>
       <c r="Q39" s="13"/>
       <c r="R39" s="13"/>
@@ -7042,27 +6979,27 @@
       <c r="AF39" s="13"/>
       <c r="AG39" s="13"/>
     </row>
-    <row r="40" ht="147.75" customHeight="1">
+    <row r="40" ht="84.75" customHeight="1">
       <c r="A40" s="5">
         <v>39.0</v>
       </c>
-      <c r="B40" s="6" t="s">
+      <c r="B40" s="5" t="s">
+        <v>377</v>
+      </c>
+      <c r="C40" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D40" s="12" t="s">
         <v>378</v>
       </c>
-      <c r="C40" s="12" t="s">
-        <v>379</v>
-      </c>
-      <c r="D40" s="12">
-        <v>1988.0</v>
-      </c>
       <c r="E40" s="12" t="s">
-        <v>43</v>
+        <v>207</v>
       </c>
       <c r="F40" s="12" t="s">
         <v>44</v>
       </c>
       <c r="G40" s="12" t="s">
-        <v>83</v>
+        <v>379</v>
       </c>
       <c r="H40" s="12" t="s">
         <v>380</v>
@@ -7071,25 +7008,25 @@
         <v>381</v>
       </c>
       <c r="J40" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="K40" s="12" t="s">
         <v>382</v>
       </c>
-      <c r="K40" s="12" t="s">
+      <c r="L40" s="12" t="s">
         <v>383</v>
       </c>
-      <c r="L40" s="12" t="s">
+      <c r="M40" s="10" t="s">
         <v>384</v>
       </c>
-      <c r="M40" s="20" t="s">
+      <c r="N40" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="O40" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="P40" s="12" t="s">
         <v>385</v>
-      </c>
-      <c r="N40" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="O40" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="P40" s="12" t="s">
-        <v>386</v>
       </c>
       <c r="Q40" s="13"/>
       <c r="R40" s="13"/>
@@ -7109,54 +7046,54 @@
       <c r="AF40" s="13"/>
       <c r="AG40" s="13"/>
     </row>
-    <row r="41" ht="84.75" customHeight="1">
+    <row r="41" ht="130.5" customHeight="1">
       <c r="A41" s="14">
         <v>40.0</v>
       </c>
       <c r="B41" s="5" t="s">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C41" s="12" t="s">
         <v>65</v>
       </c>
       <c r="D41" s="12" t="s">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="E41" s="12" t="s">
-        <v>207</v>
+        <v>43</v>
       </c>
       <c r="F41" s="12" t="s">
         <v>44</v>
       </c>
       <c r="G41" s="12" t="s">
+        <v>388</v>
+      </c>
+      <c r="H41" s="12" t="s">
         <v>389</v>
       </c>
-      <c r="H41" s="12" t="s">
+      <c r="I41" s="12" t="s">
         <v>390</v>
       </c>
-      <c r="I41" s="12" t="s">
+      <c r="J41" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K41" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L41" s="12" t="s">
         <v>391</v>
       </c>
-      <c r="J41" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="K41" s="12" t="s">
+      <c r="M41" s="10" t="s">
         <v>392</v>
       </c>
-      <c r="L41" s="12" t="s">
+      <c r="N41" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="O41" s="12" t="s">
+        <v>360</v>
+      </c>
+      <c r="P41" s="12" t="s">
         <v>393</v>
-      </c>
-      <c r="M41" s="10" t="s">
-        <v>394</v>
-      </c>
-      <c r="N41" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="O41" s="12" t="s">
-        <v>370</v>
-      </c>
-      <c r="P41" s="12" t="s">
-        <v>395</v>
       </c>
       <c r="Q41" s="13"/>
       <c r="R41" s="13"/>
@@ -7176,21 +7113,21 @@
       <c r="AF41" s="13"/>
       <c r="AG41" s="13"/>
     </row>
-    <row r="42" ht="130.5" customHeight="1">
+    <row r="42" ht="88.5" customHeight="1">
       <c r="A42" s="5">
         <v>41.0</v>
       </c>
-      <c r="B42" s="5" t="s">
+      <c r="B42" s="6" t="s">
+        <v>394</v>
+      </c>
+      <c r="C42" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D42" s="12" t="s">
         <v>396</v>
       </c>
-      <c r="C42" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D42" s="12" t="s">
+      <c r="E42" s="29" t="s">
         <v>397</v>
-      </c>
-      <c r="E42" s="12" t="s">
-        <v>43</v>
       </c>
       <c r="F42" s="12" t="s">
         <v>44</v>
@@ -7205,25 +7142,25 @@
         <v>400</v>
       </c>
       <c r="J42" s="12" t="s">
-        <v>21</v>
+        <v>401</v>
       </c>
       <c r="K42" s="12" t="s">
-        <v>21</v>
+        <v>402</v>
       </c>
       <c r="L42" s="12" t="s">
-        <v>401</v>
+        <v>403</v>
       </c>
       <c r="M42" s="10" t="s">
-        <v>402</v>
+        <v>404</v>
       </c>
       <c r="N42" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O42" s="12" t="s">
-        <v>370</v>
+        <v>360</v>
       </c>
       <c r="P42" s="12" t="s">
-        <v>403</v>
+        <v>405</v>
       </c>
       <c r="Q42" s="13"/>
       <c r="R42" s="13"/>
@@ -7243,27 +7180,27 @@
       <c r="AF42" s="13"/>
       <c r="AG42" s="13"/>
     </row>
-    <row r="43" ht="88.5" customHeight="1">
+    <row r="43" ht="107.25" customHeight="1">
       <c r="A43" s="14">
         <v>42.0</v>
       </c>
       <c r="B43" s="6" t="s">
-        <v>404</v>
+        <v>406</v>
       </c>
       <c r="C43" s="12" t="s">
-        <v>224</v>
+        <v>65</v>
       </c>
       <c r="D43" s="12" t="s">
-        <v>405</v>
-      </c>
-      <c r="E43" s="29" t="s">
-        <v>406</v>
+        <v>407</v>
+      </c>
+      <c r="E43" s="12" t="s">
+        <v>43</v>
       </c>
       <c r="F43" s="12" t="s">
         <v>44</v>
       </c>
       <c r="G43" s="12" t="s">
-        <v>407</v>
+        <v>81</v>
       </c>
       <c r="H43" s="12" t="s">
         <v>408</v>
@@ -7287,10 +7224,10 @@
         <v>166</v>
       </c>
       <c r="O43" s="12" t="s">
-        <v>370</v>
+        <v>414</v>
       </c>
       <c r="P43" s="12" t="s">
-        <v>414</v>
+        <v>415</v>
       </c>
       <c r="Q43" s="13"/>
       <c r="R43" s="13"/>
@@ -7310,18 +7247,18 @@
       <c r="AF43" s="13"/>
       <c r="AG43" s="13"/>
     </row>
-    <row r="44" ht="107.25" customHeight="1">
+    <row r="44" ht="88.5" customHeight="1">
       <c r="A44" s="5">
         <v>43.0</v>
       </c>
       <c r="B44" s="6" t="s">
-        <v>415</v>
+        <v>416</v>
       </c>
       <c r="C44" s="12" t="s">
         <v>65</v>
       </c>
       <c r="D44" s="12" t="s">
-        <v>416</v>
+        <v>417</v>
       </c>
       <c r="E44" s="12" t="s">
         <v>43</v>
@@ -7333,31 +7270,31 @@
         <v>81</v>
       </c>
       <c r="H44" s="12" t="s">
-        <v>417</v>
+        <v>21</v>
       </c>
       <c r="I44" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J44" s="12" t="s">
         <v>418</v>
       </c>
-      <c r="J44" s="12" t="s">
+      <c r="K44" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="L44" s="12" t="s">
         <v>419</v>
       </c>
-      <c r="K44" s="12" t="s">
+      <c r="M44" s="20" t="s">
         <v>420</v>
-      </c>
-      <c r="L44" s="12" t="s">
-        <v>421</v>
-      </c>
-      <c r="M44" s="10" t="s">
-        <v>422</v>
       </c>
       <c r="N44" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O44" s="12" t="s">
-        <v>423</v>
+        <v>421</v>
       </c>
       <c r="P44" s="12" t="s">
-        <v>424</v>
+        <v>422</v>
       </c>
       <c r="Q44" s="13"/>
       <c r="R44" s="13"/>
@@ -7377,18 +7314,18 @@
       <c r="AF44" s="13"/>
       <c r="AG44" s="13"/>
     </row>
-    <row r="45" ht="88.5" customHeight="1">
+    <row r="45" ht="75.0" customHeight="1">
       <c r="A45" s="14">
         <v>44.0</v>
       </c>
       <c r="B45" s="6" t="s">
-        <v>425</v>
+        <v>423</v>
       </c>
       <c r="C45" s="12" t="s">
-        <v>65</v>
+        <v>395</v>
       </c>
       <c r="D45" s="12" t="s">
-        <v>426</v>
+        <v>424</v>
       </c>
       <c r="E45" s="12" t="s">
         <v>43</v>
@@ -7397,7 +7334,7 @@
         <v>44</v>
       </c>
       <c r="G45" s="12" t="s">
-        <v>81</v>
+        <v>425</v>
       </c>
       <c r="H45" s="12" t="s">
         <v>21</v>
@@ -7406,25 +7343,25 @@
         <v>21</v>
       </c>
       <c r="J45" s="12" t="s">
+        <v>257</v>
+      </c>
+      <c r="K45" s="12" t="s">
+        <v>426</v>
+      </c>
+      <c r="L45" s="12" t="s">
         <v>427</v>
       </c>
-      <c r="K45" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="L45" s="12" t="s">
+      <c r="M45" s="10" t="s">
         <v>428</v>
-      </c>
-      <c r="M45" s="20" t="s">
-        <v>429</v>
       </c>
       <c r="N45" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O45" s="12" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="P45" s="12" t="s">
-        <v>431</v>
+        <v>429</v>
       </c>
       <c r="Q45" s="13"/>
       <c r="R45" s="13"/>
@@ -7444,18 +7381,18 @@
       <c r="AF45" s="13"/>
       <c r="AG45" s="13"/>
     </row>
-    <row r="46" ht="75.0" customHeight="1">
+    <row r="46" ht="73.5" customHeight="1">
       <c r="A46" s="5">
         <v>45.0</v>
       </c>
-      <c r="B46" s="6" t="s">
-        <v>432</v>
+      <c r="B46" s="5" t="s">
+        <v>430</v>
       </c>
       <c r="C46" s="12" t="s">
-        <v>224</v>
+        <v>395</v>
       </c>
       <c r="D46" s="12" t="s">
-        <v>433</v>
+        <v>431</v>
       </c>
       <c r="E46" s="12" t="s">
         <v>43</v>
@@ -7464,16 +7401,16 @@
         <v>44</v>
       </c>
       <c r="G46" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H46" s="12" t="s">
+        <v>432</v>
+      </c>
+      <c r="I46" s="12" t="s">
+        <v>433</v>
+      </c>
+      <c r="J46" s="12" t="s">
         <v>434</v>
-      </c>
-      <c r="H46" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I46" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J46" s="12" t="s">
-        <v>267</v>
       </c>
       <c r="K46" s="12" t="s">
         <v>435</v>
@@ -7482,16 +7419,16 @@
         <v>436</v>
       </c>
       <c r="M46" s="10" t="s">
-        <v>437</v>
+        <v>260</v>
       </c>
       <c r="N46" s="18" t="s">
         <v>166</v>
       </c>
       <c r="O46" s="12" t="s">
-        <v>430</v>
+        <v>261</v>
       </c>
       <c r="P46" s="12" t="s">
-        <v>438</v>
+        <v>437</v>
       </c>
       <c r="Q46" s="13"/>
       <c r="R46" s="13"/>
@@ -7515,23 +7452,23 @@
       <c r="A47" s="14">
         <v>46.0</v>
       </c>
-      <c r="B47" s="5" t="s">
+      <c r="B47" s="6" t="s">
+        <v>438</v>
+      </c>
+      <c r="C47" s="12" t="s">
+        <v>65</v>
+      </c>
+      <c r="D47" s="12" t="s">
         <v>439</v>
       </c>
-      <c r="C47" s="12" t="s">
-        <v>224</v>
-      </c>
-      <c r="D47" s="12" t="s">
+      <c r="E47" s="12" t="s">
         <v>440</v>
-      </c>
-      <c r="E47" s="12" t="s">
-        <v>43</v>
       </c>
       <c r="F47" s="12" t="s">
         <v>44</v>
       </c>
       <c r="G47" s="12" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="H47" s="12" t="s">
         <v>441</v>
@@ -7540,25 +7477,25 @@
         <v>442</v>
       </c>
       <c r="J47" s="12" t="s">
+        <v>106</v>
+      </c>
+      <c r="K47" s="12" t="s">
         <v>443</v>
       </c>
-      <c r="K47" s="12" t="s">
+      <c r="L47" s="12" t="s">
+        <v>436</v>
+      </c>
+      <c r="M47" s="10" t="s">
         <v>444</v>
       </c>
-      <c r="L47" s="12" t="s">
+      <c r="N47" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="O47" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="P47" s="12" t="s">
         <v>445</v>
-      </c>
-      <c r="M47" s="10" t="s">
-        <v>270</v>
-      </c>
-      <c r="N47" s="18" t="s">
-        <v>166</v>
-      </c>
-      <c r="O47" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="P47" s="12" t="s">
-        <v>446</v>
       </c>
       <c r="Q47" s="13"/>
       <c r="R47" s="13"/>
@@ -7583,16 +7520,16 @@
         <v>47.0</v>
       </c>
       <c r="B48" s="6" t="s">
+        <v>446</v>
+      </c>
+      <c r="C48" s="12" t="s">
+        <v>88</v>
+      </c>
+      <c r="D48" s="12" t="s">
         <v>447</v>
       </c>
-      <c r="C48" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D48" s="12" t="s">
+      <c r="E48" s="12" t="s">
         <v>448</v>
-      </c>
-      <c r="E48" s="12" t="s">
-        <v>449</v>
       </c>
       <c r="F48" s="12" t="s">
         <v>44</v>
@@ -7600,32 +7537,32 @@
       <c r="G48" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H48" s="12" t="s">
+      <c r="H48" s="9" t="s">
+        <v>449</v>
+      </c>
+      <c r="I48" s="12" t="s">
         <v>450</v>
       </c>
-      <c r="I48" s="12" t="s">
+      <c r="J48" s="12" t="s">
         <v>451</v>
       </c>
-      <c r="J48" s="12" t="s">
-        <v>106</v>
-      </c>
-      <c r="K48" s="12" t="s">
+      <c r="K48" s="11" t="s">
         <v>452</v>
       </c>
       <c r="L48" s="12" t="s">
-        <v>445</v>
+        <v>453</v>
       </c>
       <c r="M48" s="10" t="s">
-        <v>453</v>
+        <v>454</v>
       </c>
       <c r="N48" s="18" t="s">
-        <v>110</v>
+        <v>24</v>
       </c>
       <c r="O48" s="12" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="P48" s="12" t="s">
-        <v>454</v>
+        <v>455</v>
       </c>
       <c r="Q48" s="13"/>
       <c r="R48" s="13"/>
@@ -7645,54 +7582,54 @@
       <c r="AF48" s="13"/>
       <c r="AG48" s="13"/>
     </row>
-    <row r="49" ht="73.5" customHeight="1">
+    <row r="49" ht="72.75" customHeight="1">
       <c r="A49" s="14">
         <v>48.0</v>
       </c>
       <c r="B49" s="6" t="s">
-        <v>455</v>
+        <v>456</v>
       </c>
       <c r="C49" s="12" t="s">
         <v>88</v>
       </c>
       <c r="D49" s="12" t="s">
-        <v>456</v>
+        <v>457</v>
       </c>
       <c r="E49" s="12" t="s">
-        <v>457</v>
+        <v>458</v>
       </c>
       <c r="F49" s="12" t="s">
         <v>44</v>
       </c>
       <c r="G49" s="12" t="s">
-        <v>81</v>
+        <v>459</v>
       </c>
       <c r="H49" s="9" t="s">
-        <v>458</v>
+        <v>460</v>
       </c>
       <c r="I49" s="12" t="s">
         <v>459</v>
       </c>
       <c r="J49" s="12" t="s">
-        <v>460</v>
-      </c>
-      <c r="K49" s="11" t="s">
         <v>461</v>
       </c>
+      <c r="K49" s="12" t="s">
+        <v>462</v>
+      </c>
       <c r="L49" s="12" t="s">
-        <v>462</v>
+        <v>463</v>
       </c>
       <c r="M49" s="10" t="s">
-        <v>463</v>
+        <v>464</v>
       </c>
       <c r="N49" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O49" s="12" t="s">
-        <v>430</v>
+        <v>421</v>
       </c>
       <c r="P49" s="12" t="s">
-        <v>464</v>
+        <v>465</v>
       </c>
       <c r="Q49" s="13"/>
       <c r="R49" s="13"/>
@@ -7712,21 +7649,21 @@
       <c r="AF49" s="13"/>
       <c r="AG49" s="13"/>
     </row>
-    <row r="50" ht="72.75" customHeight="1">
+    <row r="50" ht="74.25" customHeight="1">
       <c r="A50" s="5">
         <v>49.0</v>
       </c>
       <c r="B50" s="6" t="s">
-        <v>465</v>
+        <v>466</v>
       </c>
       <c r="C50" s="12" t="s">
-        <v>88</v>
+        <v>395</v>
       </c>
       <c r="D50" s="12" t="s">
-        <v>466</v>
+        <v>467</v>
       </c>
       <c r="E50" s="12" t="s">
-        <v>467</v>
+        <v>43</v>
       </c>
       <c r="F50" s="12" t="s">
         <v>44</v>
@@ -7734,14 +7671,14 @@
       <c r="G50" s="12" t="s">
         <v>468</v>
       </c>
-      <c r="H50" s="9" t="s">
+      <c r="H50" s="30" t="s">
         <v>469</v>
       </c>
       <c r="I50" s="12" t="s">
-        <v>468</v>
+        <v>470</v>
       </c>
       <c r="J50" s="12" t="s">
-        <v>470</v>
+        <v>162</v>
       </c>
       <c r="K50" s="12" t="s">
         <v>471</v>
@@ -7749,17 +7686,17 @@
       <c r="L50" s="12" t="s">
         <v>472</v>
       </c>
-      <c r="M50" s="10" t="s">
+      <c r="M50" s="20" t="s">
         <v>473</v>
       </c>
       <c r="N50" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O50" s="12" t="s">
-        <v>430</v>
+        <v>474</v>
       </c>
       <c r="P50" s="12" t="s">
-        <v>474</v>
+        <v>475</v>
       </c>
       <c r="Q50" s="13"/>
       <c r="R50" s="13"/>
@@ -7779,36 +7716,36 @@
       <c r="AF50" s="13"/>
       <c r="AG50" s="13"/>
     </row>
-    <row r="51" ht="74.25" customHeight="1">
+    <row r="51" ht="111.75" customHeight="1">
       <c r="A51" s="14">
         <v>50.0</v>
       </c>
-      <c r="B51" s="6" t="s">
-        <v>475</v>
+      <c r="B51" s="5" t="s">
+        <v>476</v>
       </c>
       <c r="C51" s="12" t="s">
-        <v>224</v>
+        <v>65</v>
       </c>
       <c r="D51" s="12" t="s">
-        <v>476</v>
+        <v>477</v>
       </c>
       <c r="E51" s="12" t="s">
-        <v>43</v>
+        <v>30</v>
       </c>
       <c r="F51" s="12" t="s">
-        <v>44</v>
+        <v>20</v>
       </c>
       <c r="G51" s="12" t="s">
-        <v>477</v>
-      </c>
-      <c r="H51" s="30" t="s">
+        <v>81</v>
+      </c>
+      <c r="H51" s="12" t="s">
         <v>478</v>
       </c>
       <c r="I51" s="12" t="s">
+        <v>379</v>
+      </c>
+      <c r="J51" s="12" t="s">
         <v>479</v>
-      </c>
-      <c r="J51" s="12" t="s">
-        <v>162</v>
       </c>
       <c r="K51" s="12" t="s">
         <v>480</v>
@@ -7816,17 +7753,17 @@
       <c r="L51" s="12" t="s">
         <v>481</v>
       </c>
-      <c r="M51" s="20" t="s">
+      <c r="M51" s="10" t="s">
         <v>482</v>
       </c>
       <c r="N51" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O51" s="12" t="s">
+        <v>474</v>
+      </c>
+      <c r="P51" s="12" t="s">
         <v>483</v>
-      </c>
-      <c r="P51" s="12" t="s">
-        <v>484</v>
       </c>
       <c r="Q51" s="13"/>
       <c r="R51" s="13"/>
@@ -7846,18 +7783,18 @@
       <c r="AF51" s="13"/>
       <c r="AG51" s="13"/>
     </row>
-    <row r="52" ht="111.75" customHeight="1">
+    <row r="52" ht="133.5" customHeight="1">
       <c r="A52" s="5">
         <v>51.0</v>
       </c>
       <c r="B52" s="5" t="s">
+        <v>484</v>
+      </c>
+      <c r="C52" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D52" s="12" t="s">
         <v>485</v>
-      </c>
-      <c r="C52" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D52" s="12" t="s">
-        <v>486</v>
       </c>
       <c r="E52" s="12" t="s">
         <v>30</v>
@@ -7868,32 +7805,32 @@
       <c r="G52" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H52" s="12" t="s">
+      <c r="H52" s="31" t="s">
+        <v>486</v>
+      </c>
+      <c r="I52" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="J52" s="30" t="s">
         <v>487</v>
       </c>
-      <c r="I52" s="12" t="s">
-        <v>389</v>
-      </c>
-      <c r="J52" s="12" t="s">
+      <c r="K52" s="12" t="s">
         <v>488</v>
       </c>
-      <c r="K52" s="12" t="s">
+      <c r="L52" s="12" t="s">
         <v>489</v>
       </c>
-      <c r="L52" s="12" t="s">
+      <c r="M52" s="10" t="s">
         <v>490</v>
-      </c>
-      <c r="M52" s="10" t="s">
-        <v>491</v>
       </c>
       <c r="N52" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O52" s="12" t="s">
-        <v>483</v>
+        <v>261</v>
       </c>
       <c r="P52" s="12" t="s">
-        <v>492</v>
+        <v>491</v>
       </c>
       <c r="Q52" s="13"/>
       <c r="R52" s="13"/>
@@ -7913,54 +7850,54 @@
       <c r="AF52" s="13"/>
       <c r="AG52" s="13"/>
     </row>
-    <row r="53" ht="133.5" customHeight="1">
+    <row r="53" ht="90.0" customHeight="1">
       <c r="A53" s="14">
         <v>52.0</v>
       </c>
-      <c r="B53" s="5" t="s">
+      <c r="B53" s="15" t="s">
+        <v>492</v>
+      </c>
+      <c r="C53" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D53" s="12" t="s">
         <v>493</v>
       </c>
-      <c r="C53" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D53" s="12" t="s">
+      <c r="E53" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F53" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G53" s="12" t="s">
         <v>494</v>
       </c>
-      <c r="E53" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F53" s="12" t="s">
-        <v>20</v>
-      </c>
-      <c r="G53" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H53" s="31" t="s">
+      <c r="H53" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I53" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J53" s="12" t="s">
         <v>495</v>
       </c>
-      <c r="I53" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="J53" s="30" t="s">
+      <c r="K53" s="12" t="s">
         <v>496</v>
       </c>
-      <c r="K53" s="12" t="s">
+      <c r="L53" s="12" t="s">
         <v>497</v>
       </c>
-      <c r="L53" s="12" t="s">
+      <c r="M53" s="31" t="s">
         <v>498</v>
       </c>
-      <c r="M53" s="10" t="s">
+      <c r="N53" s="18" t="s">
+        <v>166</v>
+      </c>
+      <c r="O53" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="P53" s="12" t="s">
         <v>499</v>
-      </c>
-      <c r="N53" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="O53" s="12" t="s">
-        <v>271</v>
-      </c>
-      <c r="P53" s="12" t="s">
-        <v>500</v>
       </c>
       <c r="Q53" s="13"/>
       <c r="R53" s="13"/>
@@ -7980,54 +7917,54 @@
       <c r="AF53" s="13"/>
       <c r="AG53" s="13"/>
     </row>
-    <row r="54" ht="90.0" customHeight="1">
+    <row r="54" ht="60.0" customHeight="1">
       <c r="A54" s="5">
         <v>53.0</v>
       </c>
-      <c r="B54" s="15" t="s">
+      <c r="B54" s="5" t="s">
+        <v>500</v>
+      </c>
+      <c r="C54" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D54" s="12" t="s">
         <v>501</v>
       </c>
-      <c r="C54" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D54" s="12" t="s">
+      <c r="E54" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F54" s="12" t="s">
         <v>502</v>
-      </c>
-      <c r="E54" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F54" s="12" t="s">
-        <v>44</v>
       </c>
       <c r="G54" s="12" t="s">
         <v>503</v>
       </c>
       <c r="H54" s="12" t="s">
-        <v>21</v>
+        <v>504</v>
       </c>
       <c r="I54" s="12" t="s">
-        <v>21</v>
+        <v>505</v>
       </c>
       <c r="J54" s="12" t="s">
-        <v>504</v>
+        <v>506</v>
       </c>
       <c r="K54" s="12" t="s">
-        <v>505</v>
-      </c>
-      <c r="L54" s="12" t="s">
-        <v>506</v>
-      </c>
-      <c r="M54" s="31" t="s">
         <v>507</v>
       </c>
-      <c r="N54" s="18" t="s">
-        <v>166</v>
+      <c r="L54" s="32" t="s">
+        <v>508</v>
+      </c>
+      <c r="M54" s="10" t="s">
+        <v>509</v>
+      </c>
+      <c r="N54" s="33" t="s">
+        <v>24</v>
       </c>
       <c r="O54" s="12" t="s">
-        <v>430</v>
+        <v>185</v>
       </c>
       <c r="P54" s="12" t="s">
-        <v>508</v>
+        <v>510</v>
       </c>
       <c r="Q54" s="13"/>
       <c r="R54" s="13"/>
@@ -8047,45 +7984,45 @@
       <c r="AF54" s="13"/>
       <c r="AG54" s="13"/>
     </row>
-    <row r="55" ht="60.0" customHeight="1">
+    <row r="55" ht="159.75" customHeight="1">
       <c r="A55" s="14">
         <v>54.0</v>
       </c>
       <c r="B55" s="5" t="s">
-        <v>509</v>
+        <v>511</v>
       </c>
       <c r="C55" s="12" t="s">
-        <v>28</v>
+        <v>395</v>
       </c>
       <c r="D55" s="12" t="s">
-        <v>510</v>
+        <v>512</v>
       </c>
       <c r="E55" s="12" t="s">
         <v>30</v>
       </c>
       <c r="F55" s="12" t="s">
-        <v>511</v>
+        <v>513</v>
       </c>
       <c r="G55" s="12" t="s">
-        <v>512</v>
+        <v>514</v>
       </c>
       <c r="H55" s="12" t="s">
-        <v>513</v>
+        <v>515</v>
       </c>
       <c r="I55" s="12" t="s">
-        <v>514</v>
+        <v>516</v>
       </c>
       <c r="J55" s="12" t="s">
-        <v>515</v>
+        <v>517</v>
       </c>
       <c r="K55" s="12" t="s">
-        <v>516</v>
+        <v>518</v>
       </c>
       <c r="L55" s="32" t="s">
-        <v>517</v>
-      </c>
-      <c r="M55" s="10" t="s">
-        <v>518</v>
+        <v>519</v>
+      </c>
+      <c r="M55" s="34" t="s">
+        <v>520</v>
       </c>
       <c r="N55" s="33" t="s">
         <v>24</v>
@@ -8094,7 +8031,7 @@
         <v>185</v>
       </c>
       <c r="P55" s="12" t="s">
-        <v>519</v>
+        <v>521</v>
       </c>
       <c r="Q55" s="13"/>
       <c r="R55" s="13"/>
@@ -8114,45 +8051,45 @@
       <c r="AF55" s="13"/>
       <c r="AG55" s="13"/>
     </row>
-    <row r="56" ht="159.75" customHeight="1">
+    <row r="56" ht="96.75" customHeight="1">
       <c r="A56" s="5">
         <v>55.0</v>
       </c>
-      <c r="B56" s="5" t="s">
-        <v>520</v>
+      <c r="B56" s="35" t="s">
+        <v>522</v>
       </c>
       <c r="C56" s="12" t="s">
-        <v>224</v>
+        <v>65</v>
       </c>
       <c r="D56" s="12" t="s">
-        <v>521</v>
+        <v>523</v>
       </c>
       <c r="E56" s="12" t="s">
         <v>30</v>
       </c>
-      <c r="F56" s="12" t="s">
-        <v>522</v>
+      <c r="F56" s="36" t="s">
+        <v>524</v>
       </c>
       <c r="G56" s="12" t="s">
-        <v>523</v>
+        <v>525</v>
       </c>
       <c r="H56" s="12" t="s">
-        <v>524</v>
+        <v>526</v>
       </c>
       <c r="I56" s="12" t="s">
-        <v>525</v>
+        <v>81</v>
       </c>
       <c r="J56" s="12" t="s">
-        <v>526</v>
+        <v>527</v>
       </c>
       <c r="K56" s="12" t="s">
-        <v>527</v>
+        <v>528</v>
       </c>
       <c r="L56" s="32" t="s">
-        <v>528</v>
+        <v>529</v>
       </c>
       <c r="M56" s="34" t="s">
-        <v>529</v>
+        <v>530</v>
       </c>
       <c r="N56" s="33" t="s">
         <v>24</v>
@@ -8161,7 +8098,7 @@
         <v>185</v>
       </c>
       <c r="P56" s="12" t="s">
-        <v>530</v>
+        <v>531</v>
       </c>
       <c r="Q56" s="13"/>
       <c r="R56" s="13"/>
@@ -8181,45 +8118,45 @@
       <c r="AF56" s="13"/>
       <c r="AG56" s="13"/>
     </row>
-    <row r="57" ht="96.75" customHeight="1">
+    <row r="57" ht="72.0" customHeight="1">
       <c r="A57" s="14">
         <v>56.0</v>
       </c>
-      <c r="B57" s="35" t="s">
-        <v>531</v>
+      <c r="B57" s="5" t="s">
+        <v>532</v>
       </c>
       <c r="C57" s="12" t="s">
-        <v>65</v>
+        <v>28</v>
       </c>
       <c r="D57" s="12" t="s">
-        <v>532</v>
+        <v>533</v>
       </c>
       <c r="E57" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F57" s="36" t="s">
-        <v>533</v>
+        <v>534</v>
+      </c>
+      <c r="F57" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="G57" s="12" t="s">
-        <v>534</v>
+        <v>525</v>
       </c>
       <c r="H57" s="12" t="s">
         <v>535</v>
       </c>
       <c r="I57" s="12" t="s">
-        <v>81</v>
+        <v>536</v>
       </c>
       <c r="J57" s="12" t="s">
-        <v>536</v>
+        <v>21</v>
       </c>
       <c r="K57" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L57" s="32" t="s">
         <v>537</v>
       </c>
-      <c r="L57" s="32" t="s">
+      <c r="M57" s="34" t="s">
         <v>538</v>
-      </c>
-      <c r="M57" s="34" t="s">
-        <v>539</v>
       </c>
       <c r="N57" s="33" t="s">
         <v>24</v>
@@ -8228,7 +8165,7 @@
         <v>185</v>
       </c>
       <c r="P57" s="12" t="s">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="Q57" s="13"/>
       <c r="R57" s="13"/>
@@ -8248,54 +8185,54 @@
       <c r="AF57" s="13"/>
       <c r="AG57" s="13"/>
     </row>
-    <row r="58" ht="72.0" customHeight="1">
+    <row r="58" ht="108.0" customHeight="1">
       <c r="A58" s="5">
         <v>57.0</v>
       </c>
       <c r="B58" s="5" t="s">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C58" s="12" t="s">
         <v>28</v>
       </c>
       <c r="D58" s="12" t="s">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="E58" s="12" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="F58" s="12" t="s">
         <v>20</v>
       </c>
       <c r="G58" s="12" t="s">
-        <v>534</v>
-      </c>
-      <c r="H58" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="H58" s="31" t="s">
+        <v>542</v>
+      </c>
+      <c r="I58" s="31" t="s">
+        <v>525</v>
+      </c>
+      <c r="J58" s="31" t="s">
+        <v>543</v>
+      </c>
+      <c r="K58" s="31" t="s">
         <v>544</v>
       </c>
-      <c r="I58" s="12" t="s">
+      <c r="L58" s="32" t="s">
         <v>545</v>
       </c>
-      <c r="J58" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K58" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L58" s="32" t="s">
+      <c r="M58" s="34" t="s">
         <v>546</v>
-      </c>
-      <c r="M58" s="34" t="s">
-        <v>547</v>
       </c>
       <c r="N58" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O58" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P58" s="12" t="s">
-        <v>548</v>
+        <v>421</v>
+      </c>
+      <c r="P58" s="9" t="s">
+        <v>547</v>
       </c>
       <c r="Q58" s="13"/>
       <c r="R58" s="13"/>
@@ -8315,54 +8252,54 @@
       <c r="AF58" s="13"/>
       <c r="AG58" s="13"/>
     </row>
-    <row r="59" ht="108.0" customHeight="1">
+    <row r="59" ht="162.0" customHeight="1">
       <c r="A59" s="14">
         <v>58.0</v>
       </c>
-      <c r="B59" s="5" t="s">
+      <c r="B59" s="35" t="s">
+        <v>548</v>
+      </c>
+      <c r="C59" s="12" t="s">
+        <v>17</v>
+      </c>
+      <c r="D59" s="12" t="s">
         <v>549</v>
       </c>
-      <c r="C59" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D59" s="12" t="s">
+      <c r="E59" s="12" t="s">
         <v>550</v>
       </c>
-      <c r="E59" s="12" t="s">
-        <v>543</v>
-      </c>
       <c r="F59" s="12" t="s">
-        <v>20</v>
+        <v>551</v>
       </c>
       <c r="G59" s="12" t="s">
-        <v>534</v>
-      </c>
-      <c r="H59" s="31" t="s">
-        <v>551</v>
-      </c>
-      <c r="I59" s="31" t="s">
-        <v>534</v>
-      </c>
-      <c r="J59" s="31" t="s">
+        <v>525</v>
+      </c>
+      <c r="H59" s="12" t="s">
         <v>552</v>
       </c>
-      <c r="K59" s="31" t="s">
+      <c r="I59" s="12" t="s">
+        <v>525</v>
+      </c>
+      <c r="J59" s="12" t="s">
         <v>553</v>
       </c>
+      <c r="K59" s="12" t="s">
+        <v>554</v>
+      </c>
       <c r="L59" s="32" t="s">
-        <v>554</v>
+        <v>555</v>
       </c>
       <c r="M59" s="34" t="s">
-        <v>555</v>
+        <v>556</v>
       </c>
       <c r="N59" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O59" s="12" t="s">
-        <v>430</v>
+        <v>185</v>
       </c>
       <c r="P59" s="9" t="s">
-        <v>556</v>
+        <v>557</v>
       </c>
       <c r="Q59" s="13"/>
       <c r="R59" s="13"/>
@@ -8382,45 +8319,45 @@
       <c r="AF59" s="13"/>
       <c r="AG59" s="13"/>
     </row>
-    <row r="60" ht="162.0" customHeight="1">
+    <row r="60" ht="126.0" customHeight="1">
       <c r="A60" s="5">
         <v>59.0</v>
       </c>
-      <c r="B60" s="35" t="s">
-        <v>557</v>
+      <c r="B60" s="5" t="s">
+        <v>558</v>
       </c>
       <c r="C60" s="12" t="s">
         <v>17</v>
       </c>
       <c r="D60" s="12" t="s">
-        <v>558</v>
+        <v>559</v>
       </c>
       <c r="E60" s="12" t="s">
-        <v>559</v>
+        <v>560</v>
       </c>
       <c r="F60" s="12" t="s">
-        <v>560</v>
+        <v>20</v>
       </c>
       <c r="G60" s="12" t="s">
-        <v>534</v>
+        <v>561</v>
       </c>
       <c r="H60" s="12" t="s">
-        <v>561</v>
+        <v>562</v>
       </c>
       <c r="I60" s="12" t="s">
-        <v>534</v>
+        <v>563</v>
       </c>
       <c r="J60" s="12" t="s">
-        <v>562</v>
+        <v>372</v>
       </c>
       <c r="K60" s="12" t="s">
-        <v>563</v>
+        <v>564</v>
       </c>
       <c r="L60" s="32" t="s">
-        <v>564</v>
+        <v>565</v>
       </c>
       <c r="M60" s="34" t="s">
-        <v>565</v>
+        <v>566</v>
       </c>
       <c r="N60" s="33" t="s">
         <v>24</v>
@@ -8429,7 +8366,7 @@
         <v>185</v>
       </c>
       <c r="P60" s="9" t="s">
-        <v>566</v>
+        <v>567</v>
       </c>
       <c r="Q60" s="13"/>
       <c r="R60" s="13"/>
@@ -8449,45 +8386,45 @@
       <c r="AF60" s="13"/>
       <c r="AG60" s="13"/>
     </row>
-    <row r="61" ht="126.0" customHeight="1">
+    <row r="61" ht="155.25" customHeight="1">
       <c r="A61" s="14">
         <v>60.0</v>
       </c>
-      <c r="B61" s="5" t="s">
-        <v>567</v>
+      <c r="B61" s="35" t="s">
+        <v>568</v>
       </c>
       <c r="C61" s="12" t="s">
-        <v>17</v>
+        <v>395</v>
       </c>
       <c r="D61" s="12" t="s">
-        <v>568</v>
+        <v>569</v>
       </c>
       <c r="E61" s="12" t="s">
-        <v>569</v>
+        <v>534</v>
       </c>
       <c r="F61" s="12" t="s">
-        <v>20</v>
+        <v>570</v>
       </c>
       <c r="G61" s="12" t="s">
-        <v>570</v>
-      </c>
-      <c r="H61" s="12" t="s">
         <v>571</v>
       </c>
+      <c r="H61" s="30" t="s">
+        <v>572</v>
+      </c>
       <c r="I61" s="12" t="s">
-        <v>572</v>
-      </c>
-      <c r="J61" s="12" t="s">
-        <v>382</v>
+        <v>573</v>
+      </c>
+      <c r="J61" s="18" t="s">
+        <v>527</v>
       </c>
       <c r="K61" s="12" t="s">
-        <v>573</v>
+        <v>574</v>
       </c>
       <c r="L61" s="32" t="s">
-        <v>574</v>
+        <v>575</v>
       </c>
       <c r="M61" s="34" t="s">
-        <v>575</v>
+        <v>576</v>
       </c>
       <c r="N61" s="33" t="s">
         <v>24</v>
@@ -8496,7 +8433,7 @@
         <v>185</v>
       </c>
       <c r="P61" s="9" t="s">
-        <v>576</v>
+        <v>577</v>
       </c>
       <c r="Q61" s="13"/>
       <c r="R61" s="13"/>
@@ -8516,54 +8453,54 @@
       <c r="AF61" s="13"/>
       <c r="AG61" s="13"/>
     </row>
-    <row r="62" ht="155.25" customHeight="1">
+    <row r="62" ht="207.0" customHeight="1">
       <c r="A62" s="5">
         <v>61.0</v>
       </c>
       <c r="B62" s="35" t="s">
-        <v>577</v>
+        <v>578</v>
       </c>
       <c r="C62" s="12" t="s">
-        <v>224</v>
+        <v>395</v>
       </c>
       <c r="D62" s="12" t="s">
-        <v>578</v>
+        <v>579</v>
       </c>
       <c r="E62" s="12" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="F62" s="12" t="s">
-        <v>579</v>
+        <v>20</v>
       </c>
       <c r="G62" s="12" t="s">
         <v>580</v>
       </c>
-      <c r="H62" s="30" t="s">
+      <c r="H62" s="12" t="s">
         <v>581</v>
       </c>
       <c r="I62" s="12" t="s">
         <v>582</v>
       </c>
-      <c r="J62" s="18" t="s">
-        <v>536</v>
+      <c r="J62" s="12" t="s">
+        <v>583</v>
       </c>
       <c r="K62" s="12" t="s">
-        <v>583</v>
+        <v>584</v>
       </c>
       <c r="L62" s="32" t="s">
-        <v>584</v>
+        <v>585</v>
       </c>
       <c r="M62" s="34" t="s">
-        <v>585</v>
+        <v>586</v>
       </c>
       <c r="N62" s="33" t="s">
-        <v>24</v>
+        <v>587</v>
       </c>
       <c r="O62" s="12" t="s">
         <v>185</v>
       </c>
       <c r="P62" s="9" t="s">
-        <v>586</v>
+        <v>588</v>
       </c>
       <c r="Q62" s="13"/>
       <c r="R62" s="13"/>
@@ -8583,54 +8520,54 @@
       <c r="AF62" s="13"/>
       <c r="AG62" s="13"/>
     </row>
-    <row r="63" ht="207.0" customHeight="1">
+    <row r="63" ht="104.25" customHeight="1">
       <c r="A63" s="14">
         <v>62.0</v>
       </c>
       <c r="B63" s="35" t="s">
-        <v>587</v>
+        <v>589</v>
       </c>
       <c r="C63" s="12" t="s">
-        <v>224</v>
+        <v>590</v>
       </c>
       <c r="D63" s="12" t="s">
-        <v>588</v>
+        <v>591</v>
       </c>
       <c r="E63" s="12" t="s">
-        <v>543</v>
-      </c>
-      <c r="F63" s="12" t="s">
-        <v>20</v>
+        <v>592</v>
+      </c>
+      <c r="F63" s="36" t="s">
+        <v>593</v>
       </c>
       <c r="G63" s="12" t="s">
-        <v>589</v>
+        <v>81</v>
       </c>
       <c r="H63" s="12" t="s">
-        <v>590</v>
+        <v>594</v>
       </c>
       <c r="I63" s="12" t="s">
-        <v>591</v>
+        <v>81</v>
       </c>
       <c r="J63" s="12" t="s">
-        <v>592</v>
+        <v>595</v>
       </c>
       <c r="K63" s="12" t="s">
-        <v>593</v>
+        <v>596</v>
       </c>
       <c r="L63" s="32" t="s">
-        <v>594</v>
+        <v>597</v>
       </c>
       <c r="M63" s="34" t="s">
-        <v>595</v>
+        <v>598</v>
       </c>
       <c r="N63" s="33" t="s">
-        <v>596</v>
+        <v>24</v>
       </c>
       <c r="O63" s="12" t="s">
         <v>185</v>
       </c>
       <c r="P63" s="9" t="s">
-        <v>597</v>
+        <v>599</v>
       </c>
       <c r="Q63" s="13"/>
       <c r="R63" s="13"/>
@@ -8650,45 +8587,45 @@
       <c r="AF63" s="13"/>
       <c r="AG63" s="13"/>
     </row>
-    <row r="64" ht="104.25" customHeight="1">
+    <row r="64" ht="108.75" customHeight="1">
       <c r="A64" s="5">
         <v>63.0</v>
       </c>
       <c r="B64" s="35" t="s">
-        <v>598</v>
+        <v>600</v>
       </c>
       <c r="C64" s="12" t="s">
-        <v>599</v>
+        <v>395</v>
       </c>
       <c r="D64" s="12" t="s">
-        <v>600</v>
+        <v>601</v>
       </c>
       <c r="E64" s="12" t="s">
-        <v>601</v>
-      </c>
-      <c r="F64" s="36" t="s">
-        <v>602</v>
+        <v>30</v>
+      </c>
+      <c r="F64" s="12" t="s">
+        <v>20</v>
       </c>
       <c r="G64" s="12" t="s">
         <v>81</v>
       </c>
       <c r="H64" s="12" t="s">
-        <v>603</v>
+        <v>602</v>
       </c>
       <c r="I64" s="12" t="s">
         <v>81</v>
       </c>
       <c r="J64" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="K64" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L64" s="32" t="s">
+        <v>603</v>
+      </c>
+      <c r="M64" s="34" t="s">
         <v>604</v>
-      </c>
-      <c r="K64" s="12" t="s">
-        <v>605</v>
-      </c>
-      <c r="L64" s="32" t="s">
-        <v>606</v>
-      </c>
-      <c r="M64" s="34" t="s">
-        <v>607</v>
       </c>
       <c r="N64" s="33" t="s">
         <v>24</v>
@@ -8697,7 +8634,7 @@
         <v>185</v>
       </c>
       <c r="P64" s="9" t="s">
-        <v>608</v>
+        <v>605</v>
       </c>
       <c r="Q64" s="13"/>
       <c r="R64" s="13"/>
@@ -8717,21 +8654,21 @@
       <c r="AF64" s="13"/>
       <c r="AG64" s="13"/>
     </row>
-    <row r="65" ht="108.75" customHeight="1">
+    <row r="65" ht="75.0" customHeight="1">
       <c r="A65" s="14">
         <v>64.0</v>
       </c>
-      <c r="B65" s="35" t="s">
-        <v>609</v>
+      <c r="B65" s="5" t="s">
+        <v>606</v>
       </c>
       <c r="C65" s="12" t="s">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="D65" s="12" t="s">
-        <v>610</v>
+        <v>607</v>
       </c>
       <c r="E65" s="12" t="s">
-        <v>30</v>
+        <v>534</v>
       </c>
       <c r="F65" s="12" t="s">
         <v>20</v>
@@ -8740,22 +8677,22 @@
         <v>81</v>
       </c>
       <c r="H65" s="12" t="s">
-        <v>611</v>
+        <v>608</v>
       </c>
       <c r="I65" s="12" t="s">
         <v>81</v>
       </c>
       <c r="J65" s="12" t="s">
-        <v>21</v>
+        <v>609</v>
       </c>
       <c r="K65" s="12" t="s">
-        <v>21</v>
+        <v>610</v>
       </c>
       <c r="L65" s="32" t="s">
+        <v>611</v>
+      </c>
+      <c r="M65" s="34" t="s">
         <v>612</v>
-      </c>
-      <c r="M65" s="34" t="s">
-        <v>613</v>
       </c>
       <c r="N65" s="33" t="s">
         <v>24</v>
@@ -8764,7 +8701,7 @@
         <v>185</v>
       </c>
       <c r="P65" s="9" t="s">
-        <v>614</v>
+        <v>613</v>
       </c>
       <c r="Q65" s="13"/>
       <c r="R65" s="13"/>
@@ -8784,24 +8721,24 @@
       <c r="AF65" s="13"/>
       <c r="AG65" s="13"/>
     </row>
-    <row r="66" ht="75.0" customHeight="1">
+    <row r="66" ht="218.25" customHeight="1">
       <c r="A66" s="5">
         <v>65.0</v>
       </c>
       <c r="B66" s="5" t="s">
+        <v>614</v>
+      </c>
+      <c r="C66" s="12" t="s">
+        <v>590</v>
+      </c>
+      <c r="D66" s="12" t="s">
         <v>615</v>
       </c>
-      <c r="C66" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D66" s="12" t="s">
+      <c r="E66" s="12" t="s">
         <v>616</v>
       </c>
-      <c r="E66" s="12" t="s">
-        <v>543</v>
-      </c>
       <c r="F66" s="12" t="s">
-        <v>20</v>
+        <v>551</v>
       </c>
       <c r="G66" s="12" t="s">
         <v>81</v>
@@ -8810,19 +8747,19 @@
         <v>617</v>
       </c>
       <c r="I66" s="12" t="s">
-        <v>81</v>
+        <v>618</v>
       </c>
       <c r="J66" s="12" t="s">
-        <v>618</v>
+        <v>619</v>
       </c>
       <c r="K66" s="12" t="s">
-        <v>619</v>
+        <v>620</v>
       </c>
       <c r="L66" s="32" t="s">
-        <v>620</v>
+        <v>621</v>
       </c>
       <c r="M66" s="34" t="s">
-        <v>621</v>
+        <v>622</v>
       </c>
       <c r="N66" s="33" t="s">
         <v>24</v>
@@ -8831,7 +8768,7 @@
         <v>185</v>
       </c>
       <c r="P66" s="9" t="s">
-        <v>622</v>
+        <v>623</v>
       </c>
       <c r="Q66" s="13"/>
       <c r="R66" s="13"/>
@@ -8851,54 +8788,54 @@
       <c r="AF66" s="13"/>
       <c r="AG66" s="13"/>
     </row>
-    <row r="67" ht="218.25" customHeight="1">
+    <row r="67" ht="90.75" customHeight="1">
       <c r="A67" s="14">
         <v>66.0</v>
       </c>
       <c r="B67" s="5" t="s">
-        <v>623</v>
+        <v>624</v>
       </c>
       <c r="C67" s="12" t="s">
-        <v>599</v>
+        <v>65</v>
       </c>
       <c r="D67" s="12" t="s">
-        <v>624</v>
+        <v>625</v>
       </c>
       <c r="E67" s="12" t="s">
-        <v>625</v>
+        <v>626</v>
       </c>
       <c r="F67" s="12" t="s">
-        <v>560</v>
+        <v>627</v>
       </c>
       <c r="G67" s="12" t="s">
         <v>81</v>
       </c>
       <c r="H67" s="12" t="s">
-        <v>626</v>
+        <v>628</v>
       </c>
       <c r="I67" s="12" t="s">
-        <v>627</v>
+        <v>574</v>
       </c>
       <c r="J67" s="12" t="s">
-        <v>628</v>
+        <v>21</v>
       </c>
       <c r="K67" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L67" s="32" t="s">
         <v>629</v>
       </c>
-      <c r="L67" s="32" t="s">
+      <c r="M67" s="34" t="s">
         <v>630</v>
       </c>
-      <c r="M67" s="34" t="s">
-        <v>631</v>
-      </c>
-      <c r="N67" s="33" t="s">
+      <c r="N67" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O67" s="12" t="s">
         <v>185</v>
       </c>
       <c r="P67" s="9" t="s">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="Q67" s="13"/>
       <c r="R67" s="13"/>
@@ -8918,33 +8855,33 @@
       <c r="AF67" s="13"/>
       <c r="AG67" s="13"/>
     </row>
-    <row r="68" ht="90.75" customHeight="1">
+    <row r="68" ht="84.75" customHeight="1">
       <c r="A68" s="5">
         <v>67.0</v>
       </c>
-      <c r="B68" s="5" t="s">
+      <c r="B68" s="35" t="s">
+        <v>632</v>
+      </c>
+      <c r="C68" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D68" s="12" t="s">
         <v>633</v>
       </c>
-      <c r="C68" s="12" t="s">
-        <v>65</v>
-      </c>
-      <c r="D68" s="12" t="s">
+      <c r="E68" s="12" t="s">
+        <v>30</v>
+      </c>
+      <c r="F68" s="12" t="s">
         <v>634</v>
-      </c>
-      <c r="E68" s="12" t="s">
-        <v>635</v>
-      </c>
-      <c r="F68" s="12" t="s">
-        <v>636</v>
       </c>
       <c r="G68" s="12" t="s">
         <v>81</v>
       </c>
       <c r="H68" s="12" t="s">
-        <v>637</v>
+        <v>635</v>
       </c>
       <c r="I68" s="12" t="s">
-        <v>583</v>
+        <v>81</v>
       </c>
       <c r="J68" s="12" t="s">
         <v>21</v>
@@ -8953,19 +8890,19 @@
         <v>21</v>
       </c>
       <c r="L68" s="32" t="s">
-        <v>638</v>
+        <v>636</v>
       </c>
       <c r="M68" s="34" t="s">
-        <v>639</v>
-      </c>
-      <c r="N68" s="18" t="s">
+        <v>637</v>
+      </c>
+      <c r="N68" s="33" t="s">
         <v>24</v>
       </c>
       <c r="O68" s="12" t="s">
         <v>185</v>
       </c>
       <c r="P68" s="9" t="s">
-        <v>640</v>
+        <v>638</v>
       </c>
       <c r="Q68" s="13"/>
       <c r="R68" s="13"/>
@@ -8985,51 +8922,51 @@
       <c r="AF68" s="13"/>
       <c r="AG68" s="13"/>
     </row>
-    <row r="69" ht="84.75" customHeight="1">
+    <row r="69" ht="79.5" customHeight="1">
       <c r="A69" s="14">
         <v>68.0</v>
       </c>
-      <c r="B69" s="35" t="s">
+      <c r="B69" s="5" t="s">
+        <v>639</v>
+      </c>
+      <c r="C69" s="12" t="s">
+        <v>395</v>
+      </c>
+      <c r="D69" s="12" t="s">
+        <v>640</v>
+      </c>
+      <c r="E69" s="12" t="s">
         <v>641</v>
       </c>
-      <c r="C69" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D69" s="12" t="s">
+      <c r="F69" s="12" t="s">
         <v>642</v>
-      </c>
-      <c r="E69" s="12" t="s">
-        <v>30</v>
-      </c>
-      <c r="F69" s="12" t="s">
-        <v>643</v>
       </c>
       <c r="G69" s="12" t="s">
         <v>81</v>
       </c>
       <c r="H69" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I69" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J69" s="12" t="s">
+        <v>643</v>
+      </c>
+      <c r="K69" s="12" t="s">
         <v>644</v>
-      </c>
-      <c r="I69" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="J69" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K69" s="12" t="s">
-        <v>21</v>
       </c>
       <c r="L69" s="32" t="s">
         <v>645</v>
       </c>
-      <c r="M69" s="34" t="s">
+      <c r="M69" s="10" t="s">
         <v>646</v>
       </c>
-      <c r="N69" s="33" t="s">
+      <c r="N69" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O69" s="12" t="s">
-        <v>185</v>
+        <v>414</v>
       </c>
       <c r="P69" s="9" t="s">
         <v>647</v>
@@ -9052,7 +8989,7 @@
       <c r="AF69" s="13"/>
       <c r="AG69" s="13"/>
     </row>
-    <row r="70" ht="79.5" customHeight="1">
+    <row r="70" ht="78.0" customHeight="1">
       <c r="A70" s="5">
         <v>69.0</v>
       </c>
@@ -9060,7 +8997,7 @@
         <v>648</v>
       </c>
       <c r="C70" s="12" t="s">
-        <v>224</v>
+        <v>28</v>
       </c>
       <c r="D70" s="12" t="s">
         <v>649</v>
@@ -9069,37 +9006,37 @@
         <v>650</v>
       </c>
       <c r="F70" s="12" t="s">
+        <v>44</v>
+      </c>
+      <c r="G70" s="12" t="s">
+        <v>68</v>
+      </c>
+      <c r="H70" s="12" t="s">
         <v>651</v>
       </c>
-      <c r="G70" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H70" s="12" t="s">
+      <c r="I70" s="12" t="s">
+        <v>450</v>
+      </c>
+      <c r="J70" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="I70" s="12" t="s">
+      <c r="K70" s="12" t="s">
         <v>21</v>
       </c>
-      <c r="J70" s="12" t="s">
+      <c r="L70" s="32" t="s">
         <v>652</v>
       </c>
-      <c r="K70" s="12" t="s">
+      <c r="M70" s="34" t="s">
         <v>653</v>
       </c>
-      <c r="L70" s="32" t="s">
+      <c r="N70" s="18" t="s">
+        <v>110</v>
+      </c>
+      <c r="O70" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="P70" s="9" t="s">
         <v>654</v>
-      </c>
-      <c r="M70" s="10" t="s">
-        <v>655</v>
-      </c>
-      <c r="N70" s="18" t="s">
-        <v>24</v>
-      </c>
-      <c r="O70" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="P70" s="9" t="s">
-        <v>656</v>
       </c>
       <c r="Q70" s="13"/>
       <c r="R70" s="13"/>
@@ -9119,54 +9056,54 @@
       <c r="AF70" s="13"/>
       <c r="AG70" s="13"/>
     </row>
-    <row r="71" ht="78.0" customHeight="1">
+    <row r="71" ht="190.5" customHeight="1">
       <c r="A71" s="14">
         <v>70.0</v>
       </c>
       <c r="B71" s="5" t="s">
+        <v>655</v>
+      </c>
+      <c r="C71" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="D71" s="12" t="s">
         <v>657</v>
       </c>
-      <c r="C71" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D71" s="12" t="s">
+      <c r="E71" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="F71" s="12" t="s">
         <v>658</v>
       </c>
-      <c r="E71" s="12" t="s">
+      <c r="G71" s="12" t="s">
+        <v>81</v>
+      </c>
+      <c r="H71" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I71" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J71" s="12" t="s">
+        <v>321</v>
+      </c>
+      <c r="K71" s="12" t="s">
+        <v>132</v>
+      </c>
+      <c r="L71" s="12" t="s">
         <v>659</v>
       </c>
-      <c r="F71" s="12" t="s">
-        <v>44</v>
-      </c>
-      <c r="G71" s="12" t="s">
-        <v>68</v>
-      </c>
-      <c r="H71" s="12" t="s">
+      <c r="M71" s="20" t="s">
         <v>660</v>
       </c>
-      <c r="I71" s="12" t="s">
-        <v>459</v>
-      </c>
-      <c r="J71" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K71" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="L71" s="32" t="s">
+      <c r="N71" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="O71" s="12" t="s">
         <v>661</v>
       </c>
-      <c r="M71" s="34" t="s">
+      <c r="P71" s="9" t="s">
         <v>662</v>
-      </c>
-      <c r="N71" s="18" t="s">
-        <v>110</v>
-      </c>
-      <c r="O71" s="12" t="s">
-        <v>423</v>
-      </c>
-      <c r="P71" s="9" t="s">
-        <v>663</v>
       </c>
       <c r="Q71" s="13"/>
       <c r="R71" s="13"/>
@@ -9186,51 +9123,51 @@
       <c r="AF71" s="13"/>
       <c r="AG71" s="13"/>
     </row>
-    <row r="72" ht="190.5" customHeight="1">
+    <row r="72" ht="201.75" customHeight="1">
       <c r="A72" s="5">
         <v>71.0</v>
       </c>
-      <c r="B72" s="5" t="s">
+      <c r="B72" s="12" t="s">
+        <v>663</v>
+      </c>
+      <c r="C72" s="12" t="s">
+        <v>656</v>
+      </c>
+      <c r="D72" s="12" t="s">
         <v>664</v>
       </c>
-      <c r="C72" s="12" t="s">
-        <v>665</v>
-      </c>
-      <c r="D72" s="12" t="s">
-        <v>666</v>
-      </c>
       <c r="E72" s="12" t="s">
-        <v>449</v>
+        <v>534</v>
       </c>
       <c r="F72" s="12" t="s">
-        <v>667</v>
+        <v>20</v>
       </c>
       <c r="G72" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H72" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I72" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="J72" s="12" t="s">
-        <v>331</v>
-      </c>
-      <c r="K72" s="12" t="s">
-        <v>132</v>
+      <c r="H72" s="9" t="s">
+        <v>665</v>
+      </c>
+      <c r="I72" s="9" t="s">
+        <v>666</v>
+      </c>
+      <c r="J72" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="K72" s="9" t="s">
+        <v>668</v>
       </c>
       <c r="L72" s="12" t="s">
-        <v>668</v>
+        <v>669</v>
       </c>
       <c r="M72" s="20" t="s">
-        <v>669</v>
+        <v>670</v>
       </c>
       <c r="N72" s="18" t="s">
         <v>24</v>
       </c>
       <c r="O72" s="12" t="s">
-        <v>670</v>
+        <v>661</v>
       </c>
       <c r="P72" s="9" t="s">
         <v>671</v>
@@ -9253,7 +9190,7 @@
       <c r="AF72" s="13"/>
       <c r="AG72" s="13"/>
     </row>
-    <row r="73" ht="201.75" customHeight="1">
+    <row r="73" ht="103.5" customHeight="1">
       <c r="A73" s="14">
         <v>72.0</v>
       </c>
@@ -9261,43 +9198,43 @@
         <v>672</v>
       </c>
       <c r="C73" s="12" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="D73" s="12" t="s">
         <v>673</v>
       </c>
       <c r="E73" s="12" t="s">
-        <v>543</v>
+        <v>440</v>
       </c>
       <c r="F73" s="12" t="s">
-        <v>20</v>
+        <v>658</v>
       </c>
       <c r="G73" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H73" s="9" t="s">
+      <c r="H73" s="12" t="s">
         <v>674</v>
       </c>
-      <c r="I73" s="9" t="s">
+      <c r="I73" s="12" t="s">
         <v>675</v>
       </c>
       <c r="J73" s="9" t="s">
+        <v>667</v>
+      </c>
+      <c r="K73" s="12" t="s">
         <v>676</v>
       </c>
-      <c r="K73" s="9" t="s">
+      <c r="L73" s="12" t="s">
         <v>677</v>
       </c>
-      <c r="L73" s="12" t="s">
+      <c r="M73" s="10" t="s">
         <v>678</v>
       </c>
-      <c r="M73" s="20" t="s">
+      <c r="N73" s="18" t="s">
         <v>679</v>
       </c>
-      <c r="N73" s="18" t="s">
-        <v>24</v>
-      </c>
       <c r="O73" s="12" t="s">
-        <v>670</v>
+        <v>185</v>
       </c>
       <c r="P73" s="9" t="s">
         <v>680</v>
@@ -9320,7 +9257,7 @@
       <c r="AF73" s="13"/>
       <c r="AG73" s="13"/>
     </row>
-    <row r="74" ht="103.5" customHeight="1">
+    <row r="74" ht="72.0" customHeight="1">
       <c r="A74" s="5">
         <v>73.0</v>
       </c>
@@ -9328,16 +9265,16 @@
         <v>681</v>
       </c>
       <c r="C74" s="12" t="s">
-        <v>665</v>
+        <v>656</v>
       </c>
       <c r="D74" s="12" t="s">
         <v>682</v>
       </c>
       <c r="E74" s="12" t="s">
-        <v>449</v>
+        <v>440</v>
       </c>
       <c r="F74" s="12" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="G74" s="12" t="s">
         <v>81</v>
@@ -9348,26 +9285,26 @@
       <c r="I74" s="12" t="s">
         <v>684</v>
       </c>
-      <c r="J74" s="9" t="s">
-        <v>676</v>
+      <c r="J74" s="12" t="s">
+        <v>21</v>
       </c>
       <c r="K74" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="L74" s="12" t="s">
         <v>685</v>
       </c>
-      <c r="L74" s="12" t="s">
+      <c r="M74" s="10" t="s">
         <v>686</v>
       </c>
-      <c r="M74" s="10" t="s">
+      <c r="N74" s="18" t="s">
+        <v>24</v>
+      </c>
+      <c r="O74" s="12" t="s">
+        <v>414</v>
+      </c>
+      <c r="P74" s="9" t="s">
         <v>687</v>
-      </c>
-      <c r="N74" s="18" t="s">
-        <v>688</v>
-      </c>
-      <c r="O74" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P74" s="9" t="s">
-        <v>689</v>
       </c>
       <c r="Q74" s="13"/>
       <c r="R74" s="13"/>
@@ -9387,51 +9324,51 @@
       <c r="AF74" s="13"/>
       <c r="AG74" s="13"/>
     </row>
-    <row r="75" ht="72.0" customHeight="1">
+    <row r="75" ht="59.25" customHeight="1">
       <c r="A75" s="14">
         <v>74.0</v>
       </c>
       <c r="B75" s="12" t="s">
+        <v>688</v>
+      </c>
+      <c r="C75" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D75" s="12" t="s">
+        <v>689</v>
+      </c>
+      <c r="E75" s="12" t="s">
+        <v>440</v>
+      </c>
+      <c r="F75" s="12" t="s">
+        <v>658</v>
+      </c>
+      <c r="G75" s="12" t="s">
         <v>690</v>
       </c>
-      <c r="C75" s="12" t="s">
-        <v>665</v>
-      </c>
-      <c r="D75" s="12" t="s">
+      <c r="H75" s="12" t="s">
         <v>691</v>
       </c>
-      <c r="E75" s="12" t="s">
-        <v>449</v>
-      </c>
-      <c r="F75" s="12" t="s">
-        <v>667</v>
-      </c>
-      <c r="G75" s="12" t="s">
+      <c r="I75" s="12" t="s">
         <v>81</v>
       </c>
-      <c r="H75" s="12" t="s">
+      <c r="J75" s="12" t="s">
         <v>692</v>
       </c>
-      <c r="I75" s="12" t="s">
+      <c r="K75" s="12" t="s">
         <v>693</v>
-      </c>
-      <c r="J75" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="K75" s="12" t="s">
-        <v>21</v>
       </c>
       <c r="L75" s="12" t="s">
         <v>694</v>
       </c>
-      <c r="M75" s="10" t="s">
+      <c r="M75" s="37" t="s">
         <v>695</v>
       </c>
       <c r="N75" s="18" t="s">
-        <v>24</v>
+        <v>166</v>
       </c>
       <c r="O75" s="12" t="s">
-        <v>423</v>
+        <v>185</v>
       </c>
       <c r="P75" s="9" t="s">
         <v>696</v>
@@ -9454,7 +9391,7 @@
       <c r="AF75" s="13"/>
       <c r="AG75" s="13"/>
     </row>
-    <row r="76" ht="59.25" customHeight="1">
+    <row r="76" ht="189.0" customHeight="1">
       <c r="A76" s="5">
         <v>75.0</v>
       </c>
@@ -9462,40 +9399,40 @@
         <v>697</v>
       </c>
       <c r="C76" s="12" t="s">
-        <v>41</v>
+        <v>17</v>
       </c>
       <c r="D76" s="12" t="s">
         <v>698</v>
       </c>
       <c r="E76" s="12" t="s">
-        <v>449</v>
+        <v>19</v>
       </c>
       <c r="F76" s="12" t="s">
-        <v>667</v>
+        <v>20</v>
       </c>
       <c r="G76" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H76" s="12" t="s">
         <v>699</v>
       </c>
-      <c r="H76" s="12" t="s">
+      <c r="I76" s="12" t="s">
         <v>700</v>
       </c>
-      <c r="I76" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="J76" s="12" t="s">
+      <c r="J76" s="9" t="s">
         <v>701</v>
       </c>
-      <c r="K76" s="12" t="s">
+      <c r="K76" s="9" t="s">
         <v>702</v>
       </c>
-      <c r="L76" s="12" t="s">
+      <c r="L76" s="9" t="s">
         <v>703</v>
       </c>
       <c r="M76" s="37" t="s">
         <v>704</v>
       </c>
-      <c r="N76" s="18" t="s">
-        <v>166</v>
+      <c r="N76" s="11" t="s">
+        <v>24</v>
       </c>
       <c r="O76" s="12" t="s">
         <v>185</v>
@@ -9521,7 +9458,7 @@
       <c r="AF76" s="13"/>
       <c r="AG76" s="13"/>
     </row>
-    <row r="77" ht="189.0" customHeight="1">
+    <row r="77" ht="100.5" customHeight="1">
       <c r="A77" s="14">
         <v>76.0</v>
       </c>
@@ -9529,37 +9466,37 @@
         <v>706</v>
       </c>
       <c r="C77" s="12" t="s">
-        <v>17</v>
+        <v>707</v>
       </c>
       <c r="D77" s="12" t="s">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="E77" s="12" t="s">
-        <v>19</v>
+        <v>80</v>
       </c>
       <c r="F77" s="12" t="s">
-        <v>20</v>
+        <v>658</v>
       </c>
       <c r="G77" s="12" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="H77" s="12" t="s">
-        <v>708</v>
-      </c>
-      <c r="I77" s="12" t="s">
         <v>709</v>
       </c>
+      <c r="I77" s="9" t="s">
+        <v>81</v>
+      </c>
       <c r="J77" s="9" t="s">
+        <v>701</v>
+      </c>
+      <c r="K77" s="9" t="s">
         <v>710</v>
       </c>
-      <c r="K77" s="9" t="s">
+      <c r="L77" s="9" t="s">
         <v>711</v>
       </c>
-      <c r="L77" s="9" t="s">
+      <c r="M77" s="37" t="s">
         <v>712</v>
-      </c>
-      <c r="M77" s="37" t="s">
-        <v>713</v>
       </c>
       <c r="N77" s="11" t="s">
         <v>24</v>
@@ -9568,7 +9505,7 @@
         <v>185</v>
       </c>
       <c r="P77" s="9" t="s">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="Q77" s="13"/>
       <c r="R77" s="13"/>
@@ -9588,54 +9525,54 @@
       <c r="AF77" s="13"/>
       <c r="AG77" s="13"/>
     </row>
-    <row r="78" ht="100.5" customHeight="1">
+    <row r="78" ht="65.25" customHeight="1">
       <c r="A78" s="5">
         <v>77.0</v>
       </c>
       <c r="B78" s="12" t="s">
+        <v>714</v>
+      </c>
+      <c r="C78" s="12" t="s">
+        <v>28</v>
+      </c>
+      <c r="D78" s="12" t="s">
         <v>715</v>
       </c>
-      <c r="C78" s="12" t="s">
+      <c r="E78" s="12" t="s">
+        <v>43</v>
+      </c>
+      <c r="F78" s="12" t="s">
+        <v>658</v>
+      </c>
+      <c r="G78" s="12" t="s">
         <v>716</v>
       </c>
-      <c r="D78" s="12" t="s">
+      <c r="H78" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="I78" s="12" t="s">
+        <v>21</v>
+      </c>
+      <c r="J78" s="9" t="s">
         <v>717</v>
       </c>
-      <c r="E78" s="12" t="s">
-        <v>80</v>
-      </c>
-      <c r="F78" s="12" t="s">
-        <v>667</v>
-      </c>
-      <c r="G78" s="12" t="s">
-        <v>81</v>
-      </c>
-      <c r="H78" s="12" t="s">
+      <c r="K78" s="9" t="s">
         <v>718</v>
       </c>
-      <c r="I78" s="9" t="s">
-        <v>81</v>
-      </c>
-      <c r="J78" s="9" t="s">
-        <v>710</v>
-      </c>
-      <c r="K78" s="9" t="s">
+      <c r="L78" s="9" t="s">
         <v>719</v>
       </c>
-      <c r="L78" s="9" t="s">
+      <c r="M78" s="38" t="s">
         <v>720</v>
       </c>
-      <c r="M78" s="37" t="s">
+      <c r="N78" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="O78" s="12" t="s">
+        <v>421</v>
+      </c>
+      <c r="P78" s="9" t="s">
         <v>721</v>
-      </c>
-      <c r="N78" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="O78" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P78" s="9" t="s">
-        <v>722</v>
       </c>
       <c r="Q78" s="13"/>
       <c r="R78" s="13"/>
@@ -9655,33 +9592,33 @@
       <c r="AF78" s="13"/>
       <c r="AG78" s="13"/>
     </row>
-    <row r="79" ht="65.25" customHeight="1">
+    <row r="79" ht="222.0" customHeight="1">
       <c r="A79" s="14">
         <v>78.0</v>
       </c>
       <c r="B79" s="12" t="s">
+        <v>722</v>
+      </c>
+      <c r="C79" s="12" t="s">
+        <v>41</v>
+      </c>
+      <c r="D79" s="12" t="s">
         <v>723</v>
-      </c>
-      <c r="C79" s="12" t="s">
-        <v>28</v>
-      </c>
-      <c r="D79" s="12" t="s">
-        <v>724</v>
       </c>
       <c r="E79" s="12" t="s">
         <v>43</v>
       </c>
       <c r="F79" s="12" t="s">
-        <v>667</v>
+        <v>658</v>
       </c>
       <c r="G79" s="12" t="s">
+        <v>124</v>
+      </c>
+      <c r="H79" s="12" t="s">
+        <v>724</v>
+      </c>
+      <c r="I79" s="9" t="s">
         <v>725</v>
-      </c>
-      <c r="H79" s="12" t="s">
-        <v>21</v>
-      </c>
-      <c r="I79" s="12" t="s">
-        <v>21</v>
       </c>
       <c r="J79" s="9" t="s">
         <v>726</v>
@@ -9692,17 +9629,17 @@
       <c r="L79" s="9" t="s">
         <v>728</v>
       </c>
-      <c r="M79" s="38" t="s">
+      <c r="M79" s="39" t="s">
         <v>729</v>
       </c>
       <c r="N79" s="11" t="s">
         <v>166</v>
       </c>
       <c r="O79" s="12" t="s">
-        <v>430</v>
+        <v>730</v>
       </c>
       <c r="P79" s="9" t="s">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="Q79" s="13"/>
       <c r="R79" s="13"/>
@@ -9722,27 +9659,27 @@
       <c r="AF79" s="13"/>
       <c r="AG79" s="13"/>
     </row>
-    <row r="80" ht="222.0" customHeight="1">
+    <row r="80" ht="193.5" customHeight="1">
       <c r="A80" s="5">
         <v>79.0</v>
       </c>
-      <c r="B80" s="12" t="s">
-        <v>731</v>
-      </c>
-      <c r="C80" s="12" t="s">
-        <v>41</v>
-      </c>
-      <c r="D80" s="12" t="s">
+      <c r="B80" s="18" t="s">
+        <v>244</v>
+      </c>
+      <c r="C80" s="18" t="s">
+        <v>17</v>
+      </c>
+      <c r="D80" s="18" t="s">
         <v>732</v>
       </c>
-      <c r="E80" s="12" t="s">
-        <v>43</v>
-      </c>
-      <c r="F80" s="12" t="s">
-        <v>667</v>
+      <c r="E80" s="18" t="s">
+        <v>550</v>
+      </c>
+      <c r="F80" s="18" t="s">
+        <v>20</v>
       </c>
       <c r="G80" s="12" t="s">
-        <v>124</v>
+        <v>81</v>
       </c>
       <c r="H80" s="12" t="s">
         <v>733</v>
@@ -9750,26 +9687,26 @@
       <c r="I80" s="9" t="s">
         <v>734</v>
       </c>
-      <c r="J80" s="9" t="s">
+      <c r="J80" s="11" t="s">
         <v>735</v>
       </c>
-      <c r="K80" s="9" t="s">
+      <c r="K80" s="11" t="s">
         <v>736</v>
       </c>
       <c r="L80" s="9" t="s">
         <v>737</v>
       </c>
-      <c r="M80" s="39" t="s">
+      <c r="M80" s="40" t="s">
         <v>738</v>
       </c>
       <c r="N80" s="11" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="O80" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="P80" s="9" t="s">
         <v>739</v>
-      </c>
-      <c r="P80" s="9" t="s">
-        <v>740</v>
       </c>
       <c r="Q80" s="13"/>
       <c r="R80" s="13"/>
@@ -9789,26 +9726,26 @@
       <c r="AF80" s="13"/>
       <c r="AG80" s="13"/>
     </row>
-    <row r="81" ht="193.5" customHeight="1">
+    <row r="81" ht="272.25" customHeight="1">
       <c r="A81" s="14">
         <v>80.0</v>
       </c>
-      <c r="B81" s="18" t="s">
-        <v>254</v>
+      <c r="B81" s="12" t="s">
+        <v>740</v>
       </c>
       <c r="C81" s="18" t="s">
-        <v>17</v>
+        <v>28</v>
       </c>
       <c r="D81" s="18" t="s">
         <v>741</v>
       </c>
       <c r="E81" s="18" t="s">
-        <v>559</v>
+        <v>534</v>
       </c>
       <c r="F81" s="18" t="s">
         <v>20</v>
       </c>
-      <c r="G81" s="12" t="s">
+      <c r="G81" s="18" t="s">
         <v>81</v>
       </c>
       <c r="H81" s="12" t="s">
@@ -9817,26 +9754,26 @@
       <c r="I81" s="9" t="s">
         <v>743</v>
       </c>
-      <c r="J81" s="11" t="s">
+      <c r="J81" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="K81" s="41" t="s">
+        <v>21</v>
+      </c>
+      <c r="L81" s="9" t="s">
         <v>744</v>
       </c>
-      <c r="K81" s="11" t="s">
+      <c r="M81" s="42" t="s">
         <v>745</v>
       </c>
-      <c r="L81" s="9" t="s">
+      <c r="N81" s="11" t="s">
+        <v>166</v>
+      </c>
+      <c r="O81" s="12" t="s">
         <v>746</v>
       </c>
-      <c r="M81" s="40" t="s">
+      <c r="P81" s="9" t="s">
         <v>747</v>
-      </c>
-      <c r="N81" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="O81" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P81" s="9" t="s">
-        <v>748</v>
       </c>
       <c r="Q81" s="13"/>
       <c r="R81" s="13"/>
@@ -9856,21 +9793,21 @@
       <c r="AF81" s="13"/>
       <c r="AG81" s="13"/>
     </row>
-    <row r="82" ht="272.25" customHeight="1">
+    <row r="82" ht="265.5" customHeight="1">
       <c r="A82" s="5">
         <v>81.0</v>
       </c>
-      <c r="B82" s="12" t="s">
-        <v>749</v>
+      <c r="B82" s="9" t="s">
+        <v>748</v>
       </c>
       <c r="C82" s="18" t="s">
         <v>28</v>
       </c>
-      <c r="D82" s="18" t="s">
-        <v>750</v>
+      <c r="D82" s="11" t="s">
+        <v>749</v>
       </c>
       <c r="E82" s="18" t="s">
-        <v>543</v>
+        <v>534</v>
       </c>
       <c r="F82" s="18" t="s">
         <v>20</v>
@@ -9878,32 +9815,32 @@
       <c r="G82" s="18" t="s">
         <v>81</v>
       </c>
-      <c r="H82" s="12" t="s">
+      <c r="H82" s="9" t="s">
+        <v>750</v>
+      </c>
+      <c r="I82" s="9" t="s">
         <v>751</v>
       </c>
-      <c r="I82" s="9" t="s">
+      <c r="J82" s="11" t="s">
+        <v>527</v>
+      </c>
+      <c r="K82" s="11" t="s">
         <v>752</v>
-      </c>
-      <c r="J82" s="41" t="s">
-        <v>21</v>
-      </c>
-      <c r="K82" s="41" t="s">
-        <v>21</v>
       </c>
       <c r="L82" s="9" t="s">
         <v>753</v>
       </c>
-      <c r="M82" s="42" t="s">
+      <c r="M82" s="43" t="s">
         <v>754</v>
       </c>
       <c r="N82" s="11" t="s">
         <v>166</v>
       </c>
       <c r="O82" s="12" t="s">
+        <v>185</v>
+      </c>
+      <c r="P82" s="9" t="s">
         <v>755</v>
-      </c>
-      <c r="P82" s="9" t="s">
-        <v>756</v>
       </c>
       <c r="Q82" s="13"/>
       <c r="R82" s="13"/>
@@ -9923,21 +9860,21 @@
       <c r="AF82" s="13"/>
       <c r="AG82" s="13"/>
     </row>
-    <row r="83" ht="265.5" customHeight="1">
+    <row r="83" ht="198.75" customHeight="1">
       <c r="A83" s="14">
         <v>82.0</v>
       </c>
       <c r="B83" s="9" t="s">
+        <v>756</v>
+      </c>
+      <c r="C83" s="11" t="s">
+        <v>17</v>
+      </c>
+      <c r="D83" s="11" t="s">
         <v>757</v>
       </c>
-      <c r="C83" s="18" t="s">
-        <v>28</v>
-      </c>
-      <c r="D83" s="11" t="s">
+      <c r="E83" s="11" t="s">
         <v>758</v>
-      </c>
-      <c r="E83" s="18" t="s">
-        <v>543</v>
       </c>
       <c r="F83" s="18" t="s">
         <v>20</v>
@@ -9948,11 +9885,11 @@
       <c r="H83" s="9" t="s">
         <v>759</v>
       </c>
-      <c r="I83" s="9" t="s">
+      <c r="I83" s="11" t="s">
         <v>760</v>
       </c>
       <c r="J83" s="11" t="s">
-        <v>536</v>
+        <v>321</v>
       </c>
       <c r="K83" s="11" t="s">
         <v>761</v>
@@ -9960,11 +9897,11 @@
       <c r="L83" s="9" t="s">
         <v>762</v>
       </c>
-      <c r="M83" s="43" t="s">
+      <c r="M83" s="44" t="s">
         <v>763</v>
       </c>
       <c r="N83" s="11" t="s">
-        <v>166</v>
+        <v>24</v>
       </c>
       <c r="O83" s="12" t="s">
         <v>185</v>
@@ -9990,55 +9927,23 @@
       <c r="AF83" s="13"/>
       <c r="AG83" s="13"/>
     </row>
-    <row r="84" ht="198.75" customHeight="1">
-      <c r="A84" s="5">
-        <v>83.0</v>
-      </c>
-      <c r="B84" s="9" t="s">
-        <v>765</v>
-      </c>
-      <c r="C84" s="11" t="s">
-        <v>17</v>
-      </c>
-      <c r="D84" s="11" t="s">
-        <v>766</v>
-      </c>
-      <c r="E84" s="11" t="s">
-        <v>767</v>
-      </c>
-      <c r="F84" s="18" t="s">
-        <v>20</v>
-      </c>
-      <c r="G84" s="18" t="s">
-        <v>81</v>
-      </c>
-      <c r="H84" s="9" t="s">
-        <v>768</v>
-      </c>
-      <c r="I84" s="11" t="s">
-        <v>769</v>
-      </c>
-      <c r="J84" s="11" t="s">
-        <v>331</v>
-      </c>
-      <c r="K84" s="11" t="s">
-        <v>770</v>
-      </c>
-      <c r="L84" s="9" t="s">
-        <v>771</v>
-      </c>
-      <c r="M84" s="44" t="s">
-        <v>772</v>
-      </c>
-      <c r="N84" s="11" t="s">
-        <v>24</v>
-      </c>
-      <c r="O84" s="12" t="s">
-        <v>185</v>
-      </c>
-      <c r="P84" s="9" t="s">
-        <v>773</v>
-      </c>
+    <row r="84" ht="18.75" customHeight="1">
+      <c r="A84" s="13"/>
+      <c r="B84" s="13"/>
+      <c r="C84" s="45"/>
+      <c r="D84" s="45"/>
+      <c r="E84" s="13"/>
+      <c r="F84" s="13"/>
+      <c r="G84" s="13"/>
+      <c r="H84" s="13"/>
+      <c r="I84" s="13"/>
+      <c r="J84" s="13"/>
+      <c r="K84" s="13"/>
+      <c r="L84" s="13"/>
+      <c r="M84" s="13"/>
+      <c r="N84" s="13"/>
+      <c r="O84" s="13"/>
+      <c r="P84" s="13"/>
       <c r="Q84" s="13"/>
       <c r="R84" s="13"/>
       <c r="S84" s="13"/>
@@ -10057,11 +9962,11 @@
       <c r="AF84" s="13"/>
       <c r="AG84" s="13"/>
     </row>
-    <row r="85" ht="18.75" customHeight="1">
+    <row r="85" ht="15.75" customHeight="1">
       <c r="A85" s="13"/>
       <c r="B85" s="13"/>
-      <c r="C85" s="45"/>
-      <c r="D85" s="45"/>
+      <c r="C85" s="13"/>
+      <c r="D85" s="13"/>
       <c r="E85" s="13"/>
       <c r="F85" s="13"/>
       <c r="G85" s="13"/>
@@ -15797,41 +15702,7 @@
       <c r="AF248" s="13"/>
       <c r="AG248" s="13"/>
     </row>
-    <row r="249" ht="15.75" customHeight="1">
-      <c r="A249" s="13"/>
-      <c r="B249" s="13"/>
-      <c r="C249" s="13"/>
-      <c r="D249" s="13"/>
-      <c r="E249" s="13"/>
-      <c r="F249" s="13"/>
-      <c r="G249" s="13"/>
-      <c r="H249" s="13"/>
-      <c r="I249" s="13"/>
-      <c r="J249" s="13"/>
-      <c r="K249" s="13"/>
-      <c r="L249" s="13"/>
-      <c r="M249" s="13"/>
-      <c r="N249" s="13"/>
-      <c r="O249" s="13"/>
-      <c r="P249" s="13"/>
-      <c r="Q249" s="13"/>
-      <c r="R249" s="13"/>
-      <c r="S249" s="13"/>
-      <c r="T249" s="13"/>
-      <c r="U249" s="13"/>
-      <c r="V249" s="13"/>
-      <c r="W249" s="13"/>
-      <c r="X249" s="13"/>
-      <c r="Y249" s="13"/>
-      <c r="Z249" s="13"/>
-      <c r="AA249" s="13"/>
-      <c r="AB249" s="13"/>
-      <c r="AC249" s="13"/>
-      <c r="AD249" s="13"/>
-      <c r="AE249" s="13"/>
-      <c r="AF249" s="13"/>
-      <c r="AG249" s="13"/>
-    </row>
+    <row r="249" ht="15.75" customHeight="1"/>
     <row r="250" ht="15.75" customHeight="1"/>
     <row r="251" ht="15.75" customHeight="1"/>
     <row r="252" ht="15.75" customHeight="1"/>
@@ -16562,9 +16433,8 @@
     <row r="977" ht="15.75" customHeight="1"/>
     <row r="978" ht="15.75" customHeight="1"/>
     <row r="979" ht="15.75" customHeight="1"/>
-    <row r="980" ht="15.75" customHeight="1"/>
   </sheetData>
-  <autoFilter ref="$B$1:$AG$38"/>
+  <autoFilter ref="$B$1:$AG$37"/>
   <hyperlinks>
     <hyperlink r:id="rId1" ref="M2"/>
     <hyperlink r:id="rId2" ref="M3"/>
@@ -16596,18 +16466,18 @@
     <hyperlink r:id="rId28" ref="M28"/>
     <hyperlink r:id="rId29" ref="M29"/>
     <hyperlink r:id="rId30" ref="M30"/>
-    <hyperlink r:id="rId31" ref="M31"/>
-    <hyperlink r:id="rId32" ref="L32"/>
-    <hyperlink r:id="rId33" ref="M32"/>
-    <hyperlink r:id="rId34" ref="L33"/>
-    <hyperlink r:id="rId35" ref="M33"/>
-    <hyperlink r:id="rId36" ref="L34"/>
-    <hyperlink r:id="rId37" ref="M34"/>
-    <hyperlink r:id="rId38" ref="L35"/>
-    <hyperlink r:id="rId39" ref="M35"/>
-    <hyperlink r:id="rId40" ref="L36"/>
-    <hyperlink r:id="rId41" ref="M36"/>
-    <hyperlink r:id="rId42" ref="L37"/>
+    <hyperlink r:id="rId31" ref="L31"/>
+    <hyperlink r:id="rId32" ref="M31"/>
+    <hyperlink r:id="rId33" ref="L32"/>
+    <hyperlink r:id="rId34" ref="M32"/>
+    <hyperlink r:id="rId35" ref="L33"/>
+    <hyperlink r:id="rId36" ref="M33"/>
+    <hyperlink r:id="rId37" ref="L34"/>
+    <hyperlink r:id="rId38" ref="M34"/>
+    <hyperlink r:id="rId39" ref="L35"/>
+    <hyperlink r:id="rId40" ref="M35"/>
+    <hyperlink r:id="rId41" ref="L36"/>
+    <hyperlink r:id="rId42" ref="M36"/>
     <hyperlink r:id="rId43" ref="M37"/>
     <hyperlink r:id="rId44" ref="M38"/>
     <hyperlink r:id="rId45" ref="M39"/>
@@ -16624,7 +16494,7 @@
     <hyperlink r:id="rId56" ref="M50"/>
     <hyperlink r:id="rId57" ref="M51"/>
     <hyperlink r:id="rId58" ref="M52"/>
-    <hyperlink r:id="rId59" ref="M53"/>
+    <hyperlink r:id="rId59" ref="M54"/>
     <hyperlink r:id="rId60" ref="M55"/>
     <hyperlink r:id="rId61" ref="M56"/>
     <hyperlink r:id="rId62" ref="M57"/>
@@ -16639,9 +16509,9 @@
     <hyperlink r:id="rId71" ref="M66"/>
     <hyperlink r:id="rId72" ref="M67"/>
     <hyperlink r:id="rId73" ref="M68"/>
-    <hyperlink r:id="rId74" ref="M69"/>
-    <hyperlink r:id="rId75" location=":~:text=Art.%201o%20-%20O%20Plano%20Diretor%2C%20institu%C3%ADdo%20por,os%20agentes%20p%C3%BAblicos%20e%20privados%20no%20territ%C3%B3rio%20municipal." ref="M70"/>
-    <hyperlink r:id="rId76" location=":~:text=DECRETO%20N%C2%BA%206.981%2C%20DE%2013%20DE%20OUTUBRO%20DE,aspectos%20relacionados%20ao%20uso%20sustent%C3%A1vel%20dos%20recursos%20pesqueiros." ref="M71"/>
+    <hyperlink r:id="rId74" location=":~:text=Art.%201o%20-%20O%20Plano%20Diretor%2C%20institu%C3%ADdo%20por,os%20agentes%20p%C3%BAblicos%20e%20privados%20no%20territ%C3%B3rio%20municipal." ref="M69"/>
+    <hyperlink r:id="rId75" location=":~:text=DECRETO%20N%C2%BA%206.981%2C%20DE%2013%20DE%20OUTUBRO%20DE,aspectos%20relacionados%20ao%20uso%20sustent%C3%A1vel%20dos%20recursos%20pesqueiros." ref="M70"/>
+    <hyperlink r:id="rId76" ref="M71"/>
     <hyperlink r:id="rId77" ref="M72"/>
     <hyperlink r:id="rId78" ref="M73"/>
     <hyperlink r:id="rId79" ref="M74"/>
@@ -16654,12 +16524,11 @@
     <hyperlink r:id="rId86" ref="M81"/>
     <hyperlink r:id="rId87" ref="M82"/>
     <hyperlink r:id="rId88" ref="M83"/>
-    <hyperlink r:id="rId89" ref="M84"/>
   </hyperlinks>
   <printOptions gridLines="1" horizontalCentered="1"/>
   <pageMargins bottom="0.75" footer="0.0" header="0.0" left="0.7" right="0.7" top="0.75"/>
   <pageSetup fitToHeight="0" paperSize="9" cellComments="atEnd" orientation="portrait" pageOrder="overThenDown"/>
-  <drawing r:id="rId90"/>
+  <drawing r:id="rId89"/>
 </worksheet>
 </file>
 
@@ -16689,7 +16558,7 @@
   <sheetData>
     <row r="1" ht="48.0" customHeight="1">
       <c r="A1" s="46" t="s">
-        <v>774</v>
+        <v>765</v>
       </c>
       <c r="B1" s="46" t="s">
         <v>1</v>
@@ -16722,10 +16591,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="49" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="M1" s="47" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="N1" s="50"/>
       <c r="O1" s="50"/>
@@ -16736,359 +16605,359 @@
     </row>
     <row r="2" ht="42.75" customHeight="1">
       <c r="A2" s="51" t="s">
-        <v>777</v>
+        <v>768</v>
       </c>
       <c r="B2" s="52"/>
       <c r="C2" s="52"/>
     </row>
     <row r="3" ht="36.75" customHeight="1">
       <c r="A3" s="51" t="s">
-        <v>778</v>
+        <v>769</v>
       </c>
     </row>
     <row r="4" ht="38.25" customHeight="1">
       <c r="A4" s="51" t="s">
-        <v>779</v>
+        <v>770</v>
       </c>
     </row>
     <row r="5" ht="25.5" customHeight="1">
       <c r="A5" s="51" t="s">
-        <v>780</v>
+        <v>771</v>
       </c>
     </row>
     <row r="6" ht="37.5" customHeight="1">
       <c r="A6" s="51" t="s">
-        <v>781</v>
+        <v>772</v>
       </c>
     </row>
     <row r="7" ht="34.5" customHeight="1">
       <c r="A7" s="51" t="s">
-        <v>782</v>
+        <v>773</v>
       </c>
     </row>
     <row r="8" ht="30.0" customHeight="1">
       <c r="A8" s="51" t="s">
-        <v>783</v>
+        <v>774</v>
       </c>
     </row>
     <row r="9" ht="34.5" customHeight="1">
       <c r="A9" s="51" t="s">
-        <v>784</v>
+        <v>775</v>
       </c>
     </row>
     <row r="10" ht="27.75" customHeight="1">
       <c r="A10" s="51" t="s">
-        <v>785</v>
+        <v>776</v>
       </c>
     </row>
     <row r="11" ht="30.0" customHeight="1">
       <c r="A11" s="51" t="s">
-        <v>786</v>
+        <v>777</v>
       </c>
     </row>
     <row r="12" ht="38.25" customHeight="1">
       <c r="A12" s="51" t="s">
-        <v>787</v>
+        <v>778</v>
       </c>
     </row>
     <row r="13" ht="24.75" customHeight="1">
       <c r="A13" s="51" t="s">
-        <v>788</v>
+        <v>779</v>
       </c>
     </row>
     <row r="14" ht="25.5" customHeight="1">
       <c r="A14" s="51" t="s">
-        <v>789</v>
+        <v>780</v>
       </c>
     </row>
     <row r="15" ht="36.0" customHeight="1">
       <c r="A15" s="51" t="s">
-        <v>790</v>
+        <v>781</v>
       </c>
     </row>
     <row r="16" ht="39.0" customHeight="1">
       <c r="A16" s="51" t="s">
-        <v>791</v>
+        <v>782</v>
       </c>
     </row>
     <row r="17" ht="27.75" customHeight="1">
       <c r="A17" s="51" t="s">
-        <v>792</v>
+        <v>783</v>
       </c>
     </row>
     <row r="18" ht="36.0" customHeight="1">
       <c r="A18" s="51" t="s">
-        <v>793</v>
+        <v>784</v>
       </c>
     </row>
     <row r="19" ht="21.0" customHeight="1">
       <c r="A19" s="51" t="s">
-        <v>794</v>
+        <v>785</v>
       </c>
     </row>
     <row r="20" ht="35.25" customHeight="1">
       <c r="A20" s="51" t="s">
-        <v>795</v>
+        <v>786</v>
       </c>
     </row>
     <row r="21" ht="24.75" customHeight="1">
       <c r="A21" s="51" t="s">
-        <v>796</v>
+        <v>787</v>
       </c>
     </row>
     <row r="22" ht="28.5" customHeight="1">
       <c r="A22" s="51" t="s">
-        <v>797</v>
+        <v>788</v>
       </c>
     </row>
     <row r="23" ht="38.25" customHeight="1">
       <c r="A23" s="51" t="s">
-        <v>798</v>
+        <v>789</v>
       </c>
     </row>
     <row r="24" ht="38.25" customHeight="1">
       <c r="A24" s="51" t="s">
-        <v>799</v>
+        <v>790</v>
       </c>
     </row>
     <row r="25" ht="25.5" customHeight="1">
       <c r="A25" s="51" t="s">
-        <v>800</v>
+        <v>791</v>
       </c>
     </row>
     <row r="26" ht="42.0" customHeight="1">
       <c r="A26" s="51" t="s">
-        <v>801</v>
+        <v>792</v>
       </c>
     </row>
     <row r="27" ht="29.25" customHeight="1">
       <c r="A27" s="51" t="s">
-        <v>802</v>
+        <v>793</v>
       </c>
     </row>
     <row r="28" ht="34.5" customHeight="1">
       <c r="A28" s="51" t="s">
-        <v>803</v>
+        <v>794</v>
       </c>
     </row>
     <row r="29" ht="30.0" customHeight="1">
       <c r="A29" s="51" t="s">
-        <v>804</v>
+        <v>795</v>
       </c>
     </row>
     <row r="30" ht="36.0" customHeight="1">
       <c r="A30" s="51" t="s">
-        <v>805</v>
+        <v>796</v>
       </c>
     </row>
     <row r="31" ht="44.25" customHeight="1">
       <c r="A31" s="51" t="s">
-        <v>806</v>
+        <v>797</v>
       </c>
     </row>
     <row r="32" ht="38.25" customHeight="1">
       <c r="A32" s="51" t="s">
-        <v>807</v>
+        <v>798</v>
       </c>
     </row>
     <row r="33" ht="41.25" customHeight="1">
       <c r="A33" s="51" t="s">
-        <v>808</v>
+        <v>799</v>
       </c>
     </row>
     <row r="34" ht="30.0" customHeight="1">
       <c r="A34" s="51" t="s">
-        <v>809</v>
+        <v>800</v>
       </c>
     </row>
     <row r="35" ht="43.5" customHeight="1">
       <c r="A35" s="51" t="s">
-        <v>810</v>
+        <v>801</v>
       </c>
     </row>
     <row r="36" ht="27.0" customHeight="1">
       <c r="A36" s="51" t="s">
-        <v>811</v>
+        <v>802</v>
       </c>
     </row>
     <row r="37" ht="26.25" customHeight="1">
       <c r="A37" s="51" t="s">
-        <v>812</v>
+        <v>803</v>
       </c>
     </row>
     <row r="38" ht="34.5" customHeight="1">
       <c r="A38" s="51" t="s">
-        <v>813</v>
+        <v>804</v>
       </c>
     </row>
     <row r="39" ht="40.5" customHeight="1">
       <c r="A39" s="51" t="s">
-        <v>814</v>
+        <v>805</v>
       </c>
     </row>
     <row r="40" ht="29.25" customHeight="1">
       <c r="A40" s="51" t="s">
-        <v>815</v>
+        <v>806</v>
       </c>
     </row>
     <row r="41" ht="33.75" customHeight="1">
       <c r="A41" s="51" t="s">
-        <v>816</v>
+        <v>807</v>
       </c>
     </row>
     <row r="42" ht="24.75" customHeight="1">
       <c r="A42" s="51" t="s">
-        <v>817</v>
+        <v>808</v>
       </c>
     </row>
     <row r="43" ht="30.0" customHeight="1">
       <c r="A43" s="51" t="s">
-        <v>818</v>
+        <v>809</v>
       </c>
     </row>
     <row r="44" ht="26.25" customHeight="1">
       <c r="A44" s="51" t="s">
-        <v>819</v>
+        <v>810</v>
       </c>
     </row>
     <row r="45" ht="36.0" customHeight="1">
       <c r="A45" s="51" t="s">
-        <v>820</v>
+        <v>811</v>
       </c>
     </row>
     <row r="46" ht="27.0" customHeight="1">
       <c r="A46" s="51" t="s">
-        <v>821</v>
+        <v>812</v>
       </c>
     </row>
     <row r="47" ht="23.25" customHeight="1">
       <c r="A47" s="51" t="s">
-        <v>822</v>
+        <v>813</v>
       </c>
     </row>
     <row r="48" ht="25.5" customHeight="1">
       <c r="A48" s="51" t="s">
-        <v>823</v>
+        <v>814</v>
       </c>
     </row>
     <row r="49" ht="23.25" customHeight="1">
       <c r="A49" s="51" t="s">
-        <v>824</v>
+        <v>815</v>
       </c>
     </row>
     <row r="50" ht="25.5" customHeight="1">
       <c r="A50" s="51" t="s">
-        <v>825</v>
+        <v>816</v>
       </c>
     </row>
     <row r="51" ht="31.5" customHeight="1">
       <c r="A51" s="51" t="s">
-        <v>826</v>
+        <v>817</v>
       </c>
     </row>
     <row r="52" ht="34.5" customHeight="1">
       <c r="A52" s="51" t="s">
-        <v>827</v>
+        <v>818</v>
       </c>
     </row>
     <row r="53" ht="25.5" customHeight="1">
       <c r="A53" s="51" t="s">
-        <v>828</v>
+        <v>819</v>
       </c>
     </row>
     <row r="54" ht="27.75" customHeight="1">
       <c r="A54" s="51" t="s">
-        <v>829</v>
+        <v>820</v>
       </c>
     </row>
     <row r="55" ht="29.25" customHeight="1">
       <c r="A55" s="51" t="s">
-        <v>830</v>
+        <v>821</v>
       </c>
     </row>
     <row r="56" ht="19.5" customHeight="1">
       <c r="A56" s="51" t="s">
-        <v>831</v>
+        <v>822</v>
       </c>
     </row>
     <row r="57" ht="23.25" customHeight="1">
       <c r="A57" s="51" t="s">
-        <v>832</v>
+        <v>823</v>
       </c>
     </row>
     <row r="58" ht="26.25" customHeight="1">
       <c r="A58" s="51" t="s">
-        <v>833</v>
+        <v>824</v>
       </c>
     </row>
     <row r="59" ht="25.5" customHeight="1">
       <c r="A59" s="51" t="s">
-        <v>834</v>
+        <v>825</v>
       </c>
     </row>
     <row r="60" ht="33.0" customHeight="1">
       <c r="A60" s="51" t="s">
-        <v>835</v>
+        <v>826</v>
       </c>
     </row>
     <row r="61" ht="38.25" customHeight="1">
       <c r="A61" s="51" t="s">
-        <v>836</v>
+        <v>827</v>
       </c>
     </row>
     <row r="62" ht="39.75" customHeight="1">
       <c r="A62" s="51" t="s">
-        <v>837</v>
+        <v>828</v>
       </c>
     </row>
     <row r="63" ht="41.25" customHeight="1">
       <c r="A63" s="51" t="s">
-        <v>838</v>
+        <v>829</v>
       </c>
     </row>
     <row r="64" ht="29.25" customHeight="1">
       <c r="A64" s="51" t="s">
-        <v>839</v>
+        <v>830</v>
       </c>
     </row>
     <row r="65" ht="40.5" customHeight="1">
       <c r="A65" s="51" t="s">
-        <v>840</v>
+        <v>831</v>
       </c>
     </row>
     <row r="66" ht="42.0" customHeight="1">
       <c r="A66" s="51" t="s">
-        <v>841</v>
+        <v>832</v>
       </c>
     </row>
     <row r="67" ht="25.5" customHeight="1">
       <c r="A67" s="51" t="s">
-        <v>842</v>
+        <v>833</v>
       </c>
     </row>
     <row r="68" ht="36.0" customHeight="1">
       <c r="A68" s="51" t="s">
-        <v>843</v>
+        <v>834</v>
       </c>
     </row>
     <row r="69" ht="32.25" customHeight="1">
       <c r="A69" s="51" t="s">
-        <v>844</v>
+        <v>835</v>
       </c>
     </row>
     <row r="70" ht="31.5" customHeight="1">
       <c r="A70" s="51" t="s">
-        <v>845</v>
+        <v>836</v>
       </c>
     </row>
     <row r="71" ht="30.0" customHeight="1">
       <c r="A71" s="51" t="s">
-        <v>846</v>
+        <v>837</v>
       </c>
     </row>
     <row r="72" ht="30.75" customHeight="1">
       <c r="A72" s="51" t="s">
-        <v>847</v>
+        <v>838</v>
       </c>
     </row>
   </sheetData>
@@ -17122,10 +16991,10 @@
   <sheetData>
     <row r="1" ht="32.25" customHeight="1">
       <c r="A1" s="53" t="s">
-        <v>848</v>
+        <v>839</v>
       </c>
       <c r="B1" s="53" t="s">
-        <v>849</v>
+        <v>840</v>
       </c>
       <c r="C1" s="54" t="s">
         <v>2</v>
@@ -17155,10 +17024,10 @@
         <v>10</v>
       </c>
       <c r="L1" s="54" t="s">
-        <v>775</v>
+        <v>766</v>
       </c>
       <c r="M1" s="54" t="s">
-        <v>776</v>
+        <v>767</v>
       </c>
       <c r="N1" s="56"/>
       <c r="O1" s="50"/>
@@ -17169,7 +17038,7 @@
     </row>
     <row r="2" ht="33.75" customHeight="1">
       <c r="A2" s="57" t="s">
-        <v>850</v>
+        <v>841</v>
       </c>
       <c r="B2" s="58"/>
       <c r="C2" s="58"/>
@@ -17187,7 +17056,7 @@
     </row>
     <row r="3" ht="31.5" customHeight="1">
       <c r="A3" s="57" t="s">
-        <v>851</v>
+        <v>842</v>
       </c>
       <c r="B3" s="58"/>
       <c r="C3" s="58"/>
@@ -17205,7 +17074,7 @@
     </row>
     <row r="4" ht="30.0" customHeight="1">
       <c r="A4" s="57" t="s">
-        <v>852</v>
+        <v>843</v>
       </c>
       <c r="B4" s="58"/>
       <c r="C4" s="58"/>
@@ -17223,7 +17092,7 @@
     </row>
     <row r="5" ht="36.0" customHeight="1">
       <c r="A5" s="57" t="s">
-        <v>853</v>
+        <v>844</v>
       </c>
       <c r="B5" s="58"/>
       <c r="C5" s="58"/>
@@ -17241,7 +17110,7 @@
     </row>
     <row r="6" ht="27.0" customHeight="1">
       <c r="A6" s="57" t="s">
-        <v>854</v>
+        <v>845</v>
       </c>
       <c r="B6" s="58"/>
       <c r="C6" s="58"/>
@@ -17259,7 +17128,7 @@
     </row>
     <row r="7" ht="36.0" customHeight="1">
       <c r="A7" s="57" t="s">
-        <v>855</v>
+        <v>846</v>
       </c>
       <c r="B7" s="58"/>
       <c r="C7" s="58"/>
@@ -17277,7 +17146,7 @@
     </row>
     <row r="8" ht="33.0" customHeight="1">
       <c r="A8" s="57" t="s">
-        <v>856</v>
+        <v>847</v>
       </c>
       <c r="B8" s="58"/>
       <c r="C8" s="58"/>
@@ -17295,7 +17164,7 @@
     </row>
     <row r="9" ht="34.5" customHeight="1">
       <c r="A9" s="57" t="s">
-        <v>857</v>
+        <v>848</v>
       </c>
       <c r="B9" s="58"/>
       <c r="C9" s="58"/>
@@ -17313,7 +17182,7 @@
     </row>
     <row r="10" ht="32.25" customHeight="1">
       <c r="A10" s="57" t="s">
-        <v>858</v>
+        <v>849</v>
       </c>
       <c r="B10" s="58"/>
       <c r="C10" s="58"/>
@@ -17331,7 +17200,7 @@
     </row>
     <row r="11" ht="26.25" customHeight="1">
       <c r="A11" s="57" t="s">
-        <v>859</v>
+        <v>850</v>
       </c>
       <c r="B11" s="58"/>
       <c r="C11" s="58"/>
@@ -17349,7 +17218,7 @@
     </row>
     <row r="12" ht="41.25" customHeight="1">
       <c r="A12" s="57" t="s">
-        <v>860</v>
+        <v>851</v>
       </c>
       <c r="B12" s="58"/>
       <c r="C12" s="58"/>
@@ -17367,7 +17236,7 @@
     </row>
     <row r="13" ht="29.25" customHeight="1">
       <c r="A13" s="57" t="s">
-        <v>861</v>
+        <v>852</v>
       </c>
       <c r="B13" s="58"/>
       <c r="C13" s="58"/>
@@ -17385,7 +17254,7 @@
     </row>
     <row r="14" ht="36.75" customHeight="1">
       <c r="A14" s="57" t="s">
-        <v>862</v>
+        <v>853</v>
       </c>
       <c r="B14" s="58"/>
       <c r="C14" s="58"/>
@@ -17403,7 +17272,7 @@
     </row>
     <row r="15" ht="37.5" customHeight="1">
       <c r="A15" s="57" t="s">
-        <v>863</v>
+        <v>854</v>
       </c>
       <c r="B15" s="58"/>
       <c r="C15" s="58"/>
@@ -17421,7 +17290,7 @@
     </row>
     <row r="16" ht="37.5" customHeight="1">
       <c r="A16" s="57" t="s">
-        <v>864</v>
+        <v>855</v>
       </c>
       <c r="B16" s="58"/>
       <c r="C16" s="58"/>
@@ -17439,7 +17308,7 @@
     </row>
     <row r="17" ht="33.0" customHeight="1">
       <c r="A17" s="57" t="s">
-        <v>865</v>
+        <v>856</v>
       </c>
       <c r="B17" s="58"/>
       <c r="C17" s="58"/>
@@ -17457,7 +17326,7 @@
     </row>
     <row r="18" ht="32.25" customHeight="1">
       <c r="A18" s="57" t="s">
-        <v>866</v>
+        <v>857</v>
       </c>
       <c r="B18" s="58"/>
       <c r="C18" s="58"/>
@@ -17475,7 +17344,7 @@
     </row>
     <row r="19" ht="27.75" customHeight="1">
       <c r="A19" s="57" t="s">
-        <v>867</v>
+        <v>858</v>
       </c>
       <c r="B19" s="58"/>
       <c r="C19" s="58"/>
@@ -17493,7 +17362,7 @@
     </row>
     <row r="20" ht="36.75" customHeight="1">
       <c r="A20" s="57" t="s">
-        <v>868</v>
+        <v>859</v>
       </c>
       <c r="B20" s="58"/>
       <c r="C20" s="58"/>
@@ -17511,7 +17380,7 @@
     </row>
     <row r="21" ht="44.25" customHeight="1">
       <c r="A21" s="57" t="s">
-        <v>869</v>
+        <v>860</v>
       </c>
       <c r="B21" s="58"/>
       <c r="C21" s="58"/>
@@ -17529,7 +17398,7 @@
     </row>
     <row r="22" ht="36.75" customHeight="1">
       <c r="A22" s="57" t="s">
-        <v>870</v>
+        <v>861</v>
       </c>
       <c r="B22" s="58"/>
       <c r="C22" s="58"/>
@@ -17547,7 +17416,7 @@
     </row>
     <row r="23" ht="31.5" customHeight="1">
       <c r="A23" s="57" t="s">
-        <v>871</v>
+        <v>862</v>
       </c>
       <c r="B23" s="58"/>
       <c r="C23" s="58"/>
@@ -17565,7 +17434,7 @@
     </row>
     <row r="24" ht="33.0" customHeight="1">
       <c r="A24" s="57" t="s">
-        <v>872</v>
+        <v>863</v>
       </c>
       <c r="B24" s="58"/>
       <c r="C24" s="58"/>
@@ -17583,7 +17452,7 @@
     </row>
     <row r="25" ht="30.0" customHeight="1">
       <c r="A25" s="57" t="s">
-        <v>873</v>
+        <v>864</v>
       </c>
       <c r="B25" s="58"/>
       <c r="C25" s="58"/>
@@ -17601,7 +17470,7 @@
     </row>
     <row r="26" ht="27.0" customHeight="1">
       <c r="A26" s="57" t="s">
-        <v>874</v>
+        <v>865</v>
       </c>
       <c r="B26" s="58"/>
       <c r="C26" s="58"/>
@@ -17619,7 +17488,7 @@
     </row>
     <row r="27" ht="34.5" customHeight="1">
       <c r="A27" s="57" t="s">
-        <v>875</v>
+        <v>866</v>
       </c>
       <c r="B27" s="58"/>
       <c r="C27" s="58"/>
@@ -17637,7 +17506,7 @@
     </row>
     <row r="28" ht="36.0" customHeight="1">
       <c r="A28" s="57" t="s">
-        <v>876</v>
+        <v>867</v>
       </c>
       <c r="B28" s="58"/>
       <c r="C28" s="58"/>
@@ -17655,7 +17524,7 @@
     </row>
     <row r="29" ht="33.0" customHeight="1">
       <c r="A29" s="57" t="s">
-        <v>877</v>
+        <v>868</v>
       </c>
       <c r="B29" s="58"/>
       <c r="C29" s="58"/>
@@ -17673,7 +17542,7 @@
     </row>
     <row r="30" ht="30.75" customHeight="1">
       <c r="A30" s="57" t="s">
-        <v>878</v>
+        <v>869</v>
       </c>
       <c r="B30" s="58"/>
       <c r="C30" s="58"/>
@@ -17691,7 +17560,7 @@
     </row>
     <row r="31" ht="32.25" customHeight="1">
       <c r="A31" s="57" t="s">
-        <v>879</v>
+        <v>870</v>
       </c>
       <c r="B31" s="58"/>
       <c r="C31" s="58"/>
@@ -17709,7 +17578,7 @@
     </row>
     <row r="32" ht="38.25" customHeight="1">
       <c r="A32" s="57" t="s">
-        <v>880</v>
+        <v>871</v>
       </c>
       <c r="B32" s="58"/>
       <c r="C32" s="58"/>
@@ -17727,7 +17596,7 @@
     </row>
     <row r="33" ht="33.75" customHeight="1">
       <c r="A33" s="57" t="s">
-        <v>881</v>
+        <v>872</v>
       </c>
       <c r="B33" s="58"/>
       <c r="C33" s="58"/>
@@ -17745,7 +17614,7 @@
     </row>
     <row r="34" ht="34.5" customHeight="1">
       <c r="A34" s="57" t="s">
-        <v>882</v>
+        <v>873</v>
       </c>
       <c r="B34" s="58"/>
       <c r="C34" s="58"/>
@@ -17763,7 +17632,7 @@
     </row>
     <row r="35" ht="36.75" customHeight="1">
       <c r="A35" s="57" t="s">
-        <v>883</v>
+        <v>874</v>
       </c>
       <c r="B35" s="58"/>
       <c r="C35" s="58"/>
@@ -17781,7 +17650,7 @@
     </row>
     <row r="36" ht="31.5" customHeight="1">
       <c r="A36" s="57" t="s">
-        <v>884</v>
+        <v>875</v>
       </c>
       <c r="B36" s="58"/>
       <c r="C36" s="58"/>
@@ -17799,7 +17668,7 @@
     </row>
     <row r="37" ht="30.0" customHeight="1">
       <c r="A37" s="57" t="s">
-        <v>885</v>
+        <v>876</v>
       </c>
       <c r="B37" s="58"/>
       <c r="C37" s="58"/>
@@ -17817,7 +17686,7 @@
     </row>
     <row r="38" ht="24.75" customHeight="1">
       <c r="A38" s="57" t="s">
-        <v>886</v>
+        <v>877</v>
       </c>
       <c r="B38" s="58"/>
       <c r="C38" s="58"/>
@@ -17835,7 +17704,7 @@
     </row>
     <row r="39" ht="25.5" customHeight="1">
       <c r="A39" s="57" t="s">
-        <v>887</v>
+        <v>878</v>
       </c>
       <c r="B39" s="58"/>
       <c r="C39" s="58"/>
@@ -17853,7 +17722,7 @@
     </row>
     <row r="40" ht="35.25" customHeight="1">
       <c r="A40" s="57" t="s">
-        <v>888</v>
+        <v>879</v>
       </c>
       <c r="B40" s="58"/>
       <c r="C40" s="58"/>
@@ -17871,7 +17740,7 @@
     </row>
     <row r="41" ht="27.75" customHeight="1">
       <c r="A41" s="57" t="s">
-        <v>889</v>
+        <v>880</v>
       </c>
       <c r="B41" s="58"/>
       <c r="C41" s="58"/>
@@ -17889,7 +17758,7 @@
     </row>
     <row r="42" ht="30.75" customHeight="1">
       <c r="A42" s="57" t="s">
-        <v>890</v>
+        <v>881</v>
       </c>
       <c r="B42" s="58"/>
       <c r="C42" s="58"/>
@@ -17907,7 +17776,7 @@
     </row>
     <row r="43" ht="27.75" customHeight="1">
       <c r="A43" s="57" t="s">
-        <v>891</v>
+        <v>882</v>
       </c>
       <c r="B43" s="58"/>
       <c r="C43" s="58"/>
@@ -17925,7 +17794,7 @@
     </row>
     <row r="44" ht="27.0" customHeight="1">
       <c r="A44" s="57" t="s">
-        <v>892</v>
+        <v>883</v>
       </c>
       <c r="B44" s="58"/>
       <c r="C44" s="58"/>
@@ -17943,7 +17812,7 @@
     </row>
     <row r="45" ht="25.5" customHeight="1">
       <c r="A45" s="57" t="s">
-        <v>893</v>
+        <v>884</v>
       </c>
       <c r="B45" s="58"/>
       <c r="C45" s="58"/>
@@ -17961,7 +17830,7 @@
     </row>
     <row r="46" ht="27.75" customHeight="1">
       <c r="A46" s="57" t="s">
-        <v>894</v>
+        <v>885</v>
       </c>
       <c r="B46" s="58"/>
       <c r="C46" s="58"/>
@@ -17979,7 +17848,7 @@
     </row>
     <row r="47" ht="33.0" customHeight="1">
       <c r="A47" s="57" t="s">
-        <v>895</v>
+        <v>886</v>
       </c>
       <c r="B47" s="58"/>
       <c r="C47" s="58"/>
@@ -17997,7 +17866,7 @@
     </row>
     <row r="48" ht="36.0" customHeight="1">
       <c r="A48" s="57" t="s">
-        <v>896</v>
+        <v>887</v>
       </c>
       <c r="B48" s="58"/>
       <c r="C48" s="58"/>
@@ -18015,7 +17884,7 @@
     </row>
     <row r="49" ht="24.75" customHeight="1">
       <c r="A49" s="57" t="s">
-        <v>897</v>
+        <v>888</v>
       </c>
       <c r="B49" s="58"/>
       <c r="C49" s="58"/>
@@ -18033,7 +17902,7 @@
     </row>
     <row r="50" ht="27.0" customHeight="1">
       <c r="A50" s="57" t="s">
-        <v>898</v>
+        <v>889</v>
       </c>
       <c r="B50" s="58"/>
       <c r="C50" s="58"/>
@@ -18051,7 +17920,7 @@
     </row>
     <row r="51" ht="30.75" customHeight="1">
       <c r="A51" s="57" t="s">
-        <v>899</v>
+        <v>890</v>
       </c>
       <c r="B51" s="58"/>
       <c r="C51" s="58"/>
@@ -18069,7 +17938,7 @@
     </row>
     <row r="52" ht="26.25" customHeight="1">
       <c r="A52" s="57" t="s">
-        <v>900</v>
+        <v>891</v>
       </c>
       <c r="B52" s="58"/>
       <c r="C52" s="58"/>
@@ -18087,7 +17956,7 @@
     </row>
     <row r="53" ht="25.5" customHeight="1">
       <c r="A53" s="57" t="s">
-        <v>901</v>
+        <v>892</v>
       </c>
       <c r="B53" s="58"/>
       <c r="C53" s="58"/>
@@ -18105,7 +17974,7 @@
     </row>
     <row r="54" ht="25.5" customHeight="1">
       <c r="A54" s="57" t="s">
-        <v>902</v>
+        <v>893</v>
       </c>
       <c r="B54" s="58"/>
       <c r="C54" s="58"/>
@@ -18123,7 +17992,7 @@
     </row>
     <row r="55" ht="23.25" customHeight="1">
       <c r="A55" s="57" t="s">
-        <v>903</v>
+        <v>894</v>
       </c>
       <c r="B55" s="58"/>
       <c r="C55" s="58"/>
@@ -18141,7 +18010,7 @@
     </row>
     <row r="56" ht="33.75" customHeight="1">
       <c r="A56" s="57" t="s">
-        <v>904</v>
+        <v>895</v>
       </c>
       <c r="B56" s="58"/>
       <c r="C56" s="58"/>
@@ -18159,7 +18028,7 @@
     </row>
     <row r="57" ht="27.75" customHeight="1">
       <c r="A57" s="57" t="s">
-        <v>905</v>
+        <v>896</v>
       </c>
       <c r="B57" s="58"/>
       <c r="C57" s="58"/>
@@ -18177,7 +18046,7 @@
     </row>
     <row r="58" ht="31.5" customHeight="1">
       <c r="A58" s="57" t="s">
-        <v>906</v>
+        <v>897</v>
       </c>
       <c r="B58" s="58"/>
       <c r="C58" s="58"/>
@@ -18195,7 +18064,7 @@
     </row>
     <row r="59" ht="29.25" customHeight="1">
       <c r="A59" s="57" t="s">
-        <v>907</v>
+        <v>898</v>
       </c>
       <c r="B59" s="58"/>
       <c r="C59" s="58"/>
@@ -18213,7 +18082,7 @@
     </row>
     <row r="60" ht="30.75" customHeight="1">
       <c r="A60" s="57" t="s">
-        <v>908</v>
+        <v>899</v>
       </c>
       <c r="B60" s="58"/>
       <c r="C60" s="58"/>
@@ -18231,7 +18100,7 @@
     </row>
     <row r="61" ht="31.5" customHeight="1">
       <c r="A61" s="57" t="s">
-        <v>909</v>
+        <v>900</v>
       </c>
       <c r="B61" s="58"/>
       <c r="C61" s="58"/>
@@ -18249,7 +18118,7 @@
     </row>
     <row r="62" ht="41.25" customHeight="1">
       <c r="A62" s="57" t="s">
-        <v>910</v>
+        <v>901</v>
       </c>
       <c r="B62" s="58"/>
       <c r="C62" s="58"/>
@@ -18267,7 +18136,7 @@
     </row>
     <row r="63" ht="41.25" customHeight="1">
       <c r="A63" s="57" t="s">
-        <v>911</v>
+        <v>902</v>
       </c>
       <c r="B63" s="58"/>
       <c r="C63" s="58"/>
@@ -18285,7 +18154,7 @@
     </row>
     <row r="64" ht="32.25" customHeight="1">
       <c r="A64" s="57" t="s">
-        <v>912</v>
+        <v>903</v>
       </c>
       <c r="B64" s="58"/>
       <c r="C64" s="58"/>
@@ -18303,7 +18172,7 @@
     </row>
     <row r="65" ht="33.0" customHeight="1">
       <c r="A65" s="57" t="s">
-        <v>913</v>
+        <v>904</v>
       </c>
       <c r="B65" s="58"/>
       <c r="C65" s="58"/>
@@ -18321,7 +18190,7 @@
     </row>
     <row r="66" ht="33.75" customHeight="1">
       <c r="A66" s="57" t="s">
-        <v>914</v>
+        <v>905</v>
       </c>
       <c r="B66" s="58"/>
       <c r="C66" s="58"/>
@@ -18339,7 +18208,7 @@
     </row>
     <row r="67" ht="27.0" customHeight="1">
       <c r="A67" s="57" t="s">
-        <v>915</v>
+        <v>906</v>
       </c>
       <c r="B67" s="58"/>
       <c r="C67" s="58"/>
@@ -18357,7 +18226,7 @@
     </row>
     <row r="68" ht="18.75" customHeight="1">
       <c r="A68" s="57" t="s">
-        <v>916</v>
+        <v>907</v>
       </c>
       <c r="B68" s="58"/>
       <c r="C68" s="58"/>
@@ -18375,7 +18244,7 @@
     </row>
     <row r="69" ht="21.75" customHeight="1">
       <c r="A69" s="57" t="s">
-        <v>917</v>
+        <v>908</v>
       </c>
       <c r="B69" s="58"/>
       <c r="C69" s="58"/>
@@ -18393,7 +18262,7 @@
     </row>
     <row r="70" ht="22.5" customHeight="1">
       <c r="A70" s="57" t="s">
-        <v>918</v>
+        <v>909</v>
       </c>
       <c r="B70" s="58"/>
       <c r="C70" s="58"/>
@@ -18411,7 +18280,7 @@
     </row>
     <row r="71" ht="18.75" customHeight="1">
       <c r="A71" s="57" t="s">
-        <v>919</v>
+        <v>910</v>
       </c>
       <c r="B71" s="58"/>
       <c r="C71" s="58"/>
@@ -18429,7 +18298,7 @@
     </row>
     <row r="72" ht="27.0" customHeight="1">
       <c r="A72" s="57" t="s">
-        <v>920</v>
+        <v>911</v>
       </c>
       <c r="B72" s="58"/>
       <c r="C72" s="58"/>
@@ -18447,7 +18316,7 @@
     </row>
     <row r="73" ht="27.75" customHeight="1">
       <c r="A73" s="57" t="s">
-        <v>921</v>
+        <v>912</v>
       </c>
       <c r="B73" s="58"/>
       <c r="C73" s="58"/>
@@ -18465,7 +18334,7 @@
     </row>
     <row r="74" ht="36.75" customHeight="1">
       <c r="A74" s="57" t="s">
-        <v>922</v>
+        <v>913</v>
       </c>
       <c r="B74" s="58"/>
       <c r="C74" s="58"/>
@@ -18483,7 +18352,7 @@
     </row>
     <row r="75" ht="36.75" customHeight="1">
       <c r="A75" s="57" t="s">
-        <v>923</v>
+        <v>914</v>
       </c>
       <c r="B75" s="58"/>
       <c r="C75" s="58"/>
@@ -18501,7 +18370,7 @@
     </row>
     <row r="76" ht="25.5" customHeight="1">
       <c r="A76" s="57" t="s">
-        <v>924</v>
+        <v>915</v>
       </c>
       <c r="B76" s="58"/>
       <c r="C76" s="58"/>
@@ -18519,7 +18388,7 @@
     </row>
     <row r="77" ht="27.0" customHeight="1">
       <c r="A77" s="57" t="s">
-        <v>925</v>
+        <v>916</v>
       </c>
       <c r="B77" s="58"/>
       <c r="C77" s="58"/>
@@ -18537,7 +18406,7 @@
     </row>
     <row r="78" ht="24.75" customHeight="1">
       <c r="A78" s="57" t="s">
-        <v>926</v>
+        <v>917</v>
       </c>
       <c r="B78" s="58"/>
       <c r="C78" s="58"/>
@@ -18555,7 +18424,7 @@
     </row>
     <row r="79" ht="30.0" customHeight="1">
       <c r="A79" s="57" t="s">
-        <v>927</v>
+        <v>918</v>
       </c>
       <c r="B79" s="58"/>
       <c r="C79" s="58"/>
@@ -18573,7 +18442,7 @@
     </row>
     <row r="80" ht="30.0" customHeight="1">
       <c r="A80" s="57" t="s">
-        <v>928</v>
+        <v>919</v>
       </c>
       <c r="B80" s="58"/>
       <c r="C80" s="58"/>
@@ -18591,7 +18460,7 @@
     </row>
     <row r="81" ht="27.75" customHeight="1">
       <c r="A81" s="57" t="s">
-        <v>929</v>
+        <v>920</v>
       </c>
       <c r="B81" s="58"/>
       <c r="C81" s="58"/>
@@ -18609,7 +18478,7 @@
     </row>
     <row r="82" ht="24.0" customHeight="1">
       <c r="A82" s="57" t="s">
-        <v>930</v>
+        <v>921</v>
       </c>
       <c r="B82" s="58"/>
       <c r="C82" s="58"/>
@@ -18627,7 +18496,7 @@
     </row>
     <row r="83" ht="34.5" customHeight="1">
       <c r="A83" s="57" t="s">
-        <v>931</v>
+        <v>922</v>
       </c>
       <c r="B83" s="58"/>
       <c r="C83" s="58"/>
@@ -18645,7 +18514,7 @@
     </row>
     <row r="84" ht="33.0" customHeight="1">
       <c r="A84" s="57" t="s">
-        <v>932</v>
+        <v>923</v>
       </c>
       <c r="B84" s="58"/>
       <c r="C84" s="58"/>
@@ -18663,7 +18532,7 @@
     </row>
     <row r="85" ht="25.5" customHeight="1">
       <c r="A85" s="57" t="s">
-        <v>933</v>
+        <v>924</v>
       </c>
       <c r="B85" s="58"/>
       <c r="C85" s="58"/>
@@ -18681,7 +18550,7 @@
     </row>
     <row r="86" ht="33.75" customHeight="1">
       <c r="A86" s="57" t="s">
-        <v>934</v>
+        <v>925</v>
       </c>
       <c r="B86" s="58"/>
       <c r="C86" s="58"/>
@@ -18699,7 +18568,7 @@
     </row>
     <row r="87" ht="31.5" customHeight="1">
       <c r="A87" s="57" t="s">
-        <v>935</v>
+        <v>926</v>
       </c>
       <c r="B87" s="58"/>
       <c r="C87" s="58"/>
@@ -18717,7 +18586,7 @@
     </row>
     <row r="88" ht="27.75" customHeight="1">
       <c r="A88" s="57" t="s">
-        <v>936</v>
+        <v>927</v>
       </c>
       <c r="B88" s="58"/>
       <c r="C88" s="58"/>
@@ -18735,7 +18604,7 @@
     </row>
     <row r="89" ht="25.5" customHeight="1">
       <c r="A89" s="57" t="s">
-        <v>937</v>
+        <v>928</v>
       </c>
       <c r="B89" s="58"/>
       <c r="C89" s="58"/>
@@ -18753,7 +18622,7 @@
     </row>
     <row r="90" ht="28.5" customHeight="1">
       <c r="A90" s="57" t="s">
-        <v>938</v>
+        <v>929</v>
       </c>
       <c r="B90" s="58"/>
       <c r="C90" s="58"/>
@@ -18771,7 +18640,7 @@
     </row>
     <row r="91" ht="32.25" customHeight="1">
       <c r="A91" s="57" t="s">
-        <v>939</v>
+        <v>930</v>
       </c>
       <c r="B91" s="58"/>
       <c r="C91" s="58"/>
@@ -18789,7 +18658,7 @@
     </row>
     <row r="92" ht="32.25" customHeight="1">
       <c r="A92" s="57" t="s">
-        <v>940</v>
+        <v>931</v>
       </c>
       <c r="B92" s="58"/>
       <c r="C92" s="58"/>
@@ -18807,7 +18676,7 @@
     </row>
     <row r="93" ht="25.5" customHeight="1">
       <c r="A93" s="57" t="s">
-        <v>941</v>
+        <v>932</v>
       </c>
       <c r="B93" s="58"/>
       <c r="C93" s="58"/>
@@ -18825,7 +18694,7 @@
     </row>
     <row r="94" ht="36.75" customHeight="1">
       <c r="A94" s="57" t="s">
-        <v>942</v>
+        <v>933</v>
       </c>
       <c r="B94" s="58"/>
       <c r="C94" s="58"/>
@@ -18843,7 +18712,7 @@
     </row>
     <row r="95" ht="30.75" customHeight="1">
       <c r="A95" s="57" t="s">
-        <v>943</v>
+        <v>934</v>
       </c>
       <c r="B95" s="58"/>
       <c r="C95" s="58"/>
@@ -18861,7 +18730,7 @@
     </row>
     <row r="96" ht="34.5" customHeight="1">
       <c r="A96" s="57" t="s">
-        <v>944</v>
+        <v>935</v>
       </c>
       <c r="B96" s="58"/>
       <c r="C96" s="58"/>
@@ -18879,7 +18748,7 @@
     </row>
     <row r="97" ht="32.25" customHeight="1">
       <c r="A97" s="57" t="s">
-        <v>945</v>
+        <v>936</v>
       </c>
       <c r="B97" s="58"/>
       <c r="C97" s="58"/>
@@ -18897,7 +18766,7 @@
     </row>
     <row r="98" ht="36.0" customHeight="1">
       <c r="A98" s="57" t="s">
-        <v>946</v>
+        <v>937</v>
       </c>
       <c r="B98" s="58"/>
       <c r="C98" s="58"/>
@@ -18915,7 +18784,7 @@
     </row>
     <row r="99" ht="23.25" customHeight="1">
       <c r="A99" s="57" t="s">
-        <v>947</v>
+        <v>938</v>
       </c>
       <c r="B99" s="58"/>
       <c r="C99" s="58"/>
@@ -18933,7 +18802,7 @@
     </row>
     <row r="100" ht="25.5" customHeight="1">
       <c r="A100" s="57" t="s">
-        <v>948</v>
+        <v>939</v>
       </c>
       <c r="B100" s="58"/>
       <c r="C100" s="58"/>
@@ -18951,7 +18820,7 @@
     </row>
     <row r="101" ht="30.75" customHeight="1">
       <c r="A101" s="57" t="s">
-        <v>949</v>
+        <v>940</v>
       </c>
       <c r="B101" s="58"/>
       <c r="C101" s="58"/>
@@ -18969,7 +18838,7 @@
     </row>
     <row r="102" ht="27.75" customHeight="1">
       <c r="A102" s="57" t="s">
-        <v>950</v>
+        <v>941</v>
       </c>
       <c r="B102" s="58"/>
       <c r="C102" s="58"/>
@@ -18987,7 +18856,7 @@
     </row>
     <row r="103" ht="25.5" customHeight="1">
       <c r="A103" s="57" t="s">
-        <v>951</v>
+        <v>942</v>
       </c>
       <c r="B103" s="58"/>
       <c r="C103" s="58"/>
@@ -19005,7 +18874,7 @@
     </row>
     <row r="104" ht="30.0" customHeight="1">
       <c r="A104" s="57" t="s">
-        <v>952</v>
+        <v>943</v>
       </c>
       <c r="B104" s="58"/>
       <c r="C104" s="58"/>
@@ -19023,7 +18892,7 @@
     </row>
     <row r="105" ht="21.0" customHeight="1">
       <c r="A105" s="57" t="s">
-        <v>953</v>
+        <v>944</v>
       </c>
       <c r="B105" s="58"/>
       <c r="C105" s="58"/>
@@ -19041,7 +18910,7 @@
     </row>
     <row r="106" ht="27.0" customHeight="1">
       <c r="A106" s="57" t="s">
-        <v>954</v>
+        <v>945</v>
       </c>
       <c r="B106" s="58"/>
       <c r="C106" s="58"/>
@@ -19059,7 +18928,7 @@
     </row>
     <row r="107" ht="39.0" customHeight="1">
       <c r="A107" s="57" t="s">
-        <v>955</v>
+        <v>946</v>
       </c>
       <c r="B107" s="58"/>
       <c r="C107" s="58"/>
@@ -19077,7 +18946,7 @@
     </row>
     <row r="108" ht="37.5" customHeight="1">
       <c r="A108" s="57" t="s">
-        <v>956</v>
+        <v>947</v>
       </c>
       <c r="B108" s="58"/>
       <c r="C108" s="58"/>
@@ -19095,7 +18964,7 @@
     </row>
     <row r="109" ht="32.25" customHeight="1">
       <c r="A109" s="57" t="s">
-        <v>957</v>
+        <v>948</v>
       </c>
       <c r="B109" s="58"/>
       <c r="C109" s="58"/>
@@ -19113,7 +18982,7 @@
     </row>
     <row r="110" ht="27.75" customHeight="1">
       <c r="A110" s="57" t="s">
-        <v>958</v>
+        <v>949</v>
       </c>
       <c r="B110" s="58"/>
       <c r="C110" s="58"/>
@@ -19131,7 +19000,7 @@
     </row>
     <row r="111" ht="27.0" customHeight="1">
       <c r="A111" s="57" t="s">
-        <v>959</v>
+        <v>950</v>
       </c>
       <c r="B111" s="58"/>
       <c r="C111" s="58"/>
@@ -19149,7 +19018,7 @@
     </row>
     <row r="112" ht="36.0" customHeight="1">
       <c r="A112" s="57" t="s">
-        <v>960</v>
+        <v>951</v>
       </c>
       <c r="B112" s="58"/>
       <c r="C112" s="58"/>
@@ -19167,7 +19036,7 @@
     </row>
     <row r="113" ht="48.0" customHeight="1">
       <c r="A113" s="57" t="s">
-        <v>961</v>
+        <v>952</v>
       </c>
       <c r="B113" s="58"/>
       <c r="C113" s="58"/>
@@ -19185,7 +19054,7 @@
     </row>
     <row r="114" ht="34.5" customHeight="1">
       <c r="A114" s="57" t="s">
-        <v>962</v>
+        <v>953</v>
       </c>
       <c r="B114" s="58"/>
       <c r="C114" s="58"/>
@@ -19203,7 +19072,7 @@
     </row>
     <row r="115" ht="35.25" customHeight="1">
       <c r="A115" s="57" t="s">
-        <v>963</v>
+        <v>954</v>
       </c>
       <c r="B115" s="58"/>
       <c r="C115" s="58"/>
@@ -19221,7 +19090,7 @@
     </row>
     <row r="116" ht="39.75" customHeight="1">
       <c r="A116" s="57" t="s">
-        <v>964</v>
+        <v>955</v>
       </c>
       <c r="B116" s="58"/>
       <c r="C116" s="58"/>
@@ -19239,7 +19108,7 @@
     </row>
     <row r="117" ht="30.0" customHeight="1">
       <c r="A117" s="57" t="s">
-        <v>965</v>
+        <v>956</v>
       </c>
       <c r="B117" s="58"/>
       <c r="C117" s="58"/>
@@ -19257,7 +19126,7 @@
     </row>
     <row r="118" ht="31.5" customHeight="1">
       <c r="A118" s="57" t="s">
-        <v>966</v>
+        <v>957</v>
       </c>
       <c r="B118" s="58"/>
       <c r="C118" s="58"/>
@@ -19275,7 +19144,7 @@
     </row>
     <row r="119" ht="34.5" customHeight="1">
       <c r="A119" s="57" t="s">
-        <v>967</v>
+        <v>958</v>
       </c>
       <c r="B119" s="58"/>
       <c r="C119" s="58"/>
@@ -19293,7 +19162,7 @@
     </row>
     <row r="120" ht="29.25" customHeight="1">
       <c r="A120" s="57" t="s">
-        <v>968</v>
+        <v>959</v>
       </c>
       <c r="B120" s="58"/>
       <c r="C120" s="58"/>
@@ -19311,7 +19180,7 @@
     </row>
     <row r="121">
       <c r="A121" s="57" t="s">
-        <v>969</v>
+        <v>960</v>
       </c>
       <c r="B121" s="58"/>
       <c r="C121" s="58"/>
@@ -19329,7 +19198,7 @@
     </row>
     <row r="122">
       <c r="A122" s="57" t="s">
-        <v>970</v>
+        <v>961</v>
       </c>
       <c r="B122" s="58"/>
       <c r="C122" s="58"/>
@@ -19347,7 +19216,7 @@
     </row>
     <row r="123" ht="34.5" customHeight="1">
       <c r="A123" s="57" t="s">
-        <v>971</v>
+        <v>962</v>
       </c>
       <c r="B123" s="58"/>
       <c r="C123" s="58"/>
@@ -19365,7 +19234,7 @@
     </row>
     <row r="124" ht="30.0" customHeight="1">
       <c r="A124" s="57" t="s">
-        <v>972</v>
+        <v>963</v>
       </c>
       <c r="B124" s="58"/>
       <c r="C124" s="58"/>
@@ -19383,7 +19252,7 @@
     </row>
     <row r="125">
       <c r="A125" s="59" t="s">
-        <v>973</v>
+        <v>964</v>
       </c>
       <c r="B125" s="58"/>
       <c r="C125" s="58"/>
